--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15690" windowHeight="14160"/>
+    <workbookView windowWidth="14610" windowHeight="9165"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="224">
   <si>
     <t>##var</t>
   </si>
@@ -79,13 +79,13 @@
     <t>描述</t>
   </si>
   <si>
-    <t>粗制长剑</t>
+    <t>冒险证明</t>
   </si>
   <si>
     <t>CardMagnification</t>
   </si>
   <si>
-    <t>结算时倍率+1</t>
+    <t>结算时提供+1倍率</t>
   </si>
   <si>
     <t>青铜项链</t>
@@ -94,7 +94,7 @@
     <t>SquarePlate</t>
   </si>
   <si>
-    <t>结算时方片花色牌可使倍率+1</t>
+    <t>亮出的每张方片牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>青铜手镯</t>
@@ -106,7 +106,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>结算时黑桃花色牌可使倍率+1</t>
+    <t>亮出的每张黑桃牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>青铜耳环</t>
@@ -115,7 +115,7 @@
     <t>RedHeart</t>
   </si>
   <si>
-    <t>结算时红心花色牌可使倍率+1</t>
+    <t>亮出的每张红心牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>青铜戒指</t>
@@ -124,7 +124,7 @@
     <t>PlumBlossom</t>
   </si>
   <si>
-    <t>结算时梅花花色牌可使倍率+1</t>
+    <t>亮出的每张梅花牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>木制长剑</t>
@@ -133,154 +133,286 @@
     <t>Couplet</t>
   </si>
   <si>
-    <t>对子在攻击时提供的倍率+1</t>
-  </si>
-  <si>
-    <t>青铜法杖</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>亮出的对子牌型在结算时提供+2倍率</t>
+  </si>
+  <si>
+    <t>木制法杖</t>
+  </si>
+  <si>
+    <t>Straight</t>
+  </si>
+  <si>
+    <t>亮出的顺子牌型在结算时提供+2倍率</t>
+  </si>
+  <si>
+    <t>木制长弓</t>
   </si>
   <si>
     <t>Flush</t>
   </si>
   <si>
-    <t>同花在攻击时提供的倍率+1</t>
-  </si>
-  <si>
-    <t>10008</t>
-  </si>
-  <si>
-    <t>铁质长剑</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>对子在攻击时提供的倍率+2</t>
-  </si>
-  <si>
-    <t>10009</t>
-  </si>
-  <si>
-    <t>白银法杖</t>
-  </si>
-  <si>
-    <t>同花在攻击时提供的倍率+2</t>
-  </si>
-  <si>
-    <t>10010</t>
-  </si>
-  <si>
-    <t>翡翠诗篇</t>
-  </si>
-  <si>
-    <t>Straight</t>
-  </si>
-  <si>
-    <t>顺子在攻击时提供的倍率+2</t>
-  </si>
-  <si>
-    <t>10011</t>
+    <t>亮出的同花牌型在结算时提供+2倍率</t>
+  </si>
+  <si>
+    <t>木制长矛</t>
+  </si>
+  <si>
+    <t>StraightFlush</t>
+  </si>
+  <si>
+    <t>亮出的同花顺牌型在结算时提供+2倍率</t>
+  </si>
+  <si>
+    <t>木制长斧</t>
+  </si>
+  <si>
+    <t>Leopard</t>
+  </si>
+  <si>
+    <t>亮出的豹子牌型在结算时提供+2倍率</t>
+  </si>
+  <si>
+    <t>木制圆盾</t>
+  </si>
+  <si>
+    <t>HeroTakeDamage</t>
+  </si>
+  <si>
+    <t>每次受到的伤害降低2点</t>
+  </si>
+  <si>
+    <t>20001</t>
   </si>
   <si>
     <t>白银项链</t>
   </si>
   <si>
-    <t>结算时方片花色牌可使倍率+2</t>
-  </si>
-  <si>
-    <t>10012</t>
+    <t>SquarePlateAttack</t>
+  </si>
+  <si>
+    <t>亮出的每张方片牌在结算时提供+2攻击力</t>
+  </si>
+  <si>
+    <t>20002</t>
   </si>
   <si>
     <t>白银手镯</t>
   </si>
   <si>
-    <t>结算时黑桃花色牌可使倍率+2</t>
-  </si>
-  <si>
-    <t>10013</t>
+    <t>SpadesAttack</t>
+  </si>
+  <si>
+    <t>亮出的每张黑桃牌在结算时提供+2攻击力</t>
+  </si>
+  <si>
+    <t>20003</t>
   </si>
   <si>
     <t>白银耳环</t>
   </si>
   <si>
-    <t>结算时红心花色牌可使倍率+2</t>
-  </si>
-  <si>
-    <t>10014</t>
+    <t>RedHeartAttack</t>
+  </si>
+  <si>
+    <t>亮出的每张红心牌在结算时提供+2攻击力</t>
+  </si>
+  <si>
+    <t>20004</t>
   </si>
   <si>
     <t>白银戒指</t>
   </si>
   <si>
-    <t>结算时梅花花色牌可使倍率+2</t>
-  </si>
-  <si>
-    <t>10015</t>
+    <t>PlumBlossomAttack</t>
+  </si>
+  <si>
+    <t>亮出的每张梅花牌在结算时提供+2攻击力</t>
+  </si>
+  <si>
+    <t>20005</t>
+  </si>
+  <si>
+    <t>铁制长剑</t>
+  </si>
+  <si>
+    <t>CoupletAttack</t>
+  </si>
+  <si>
+    <t>亮出的对子牌型在结算时提供+2攻击力</t>
+  </si>
+  <si>
+    <t>20006</t>
+  </si>
+  <si>
+    <t>铁制法杖</t>
+  </si>
+  <si>
+    <t>StraightAttack</t>
+  </si>
+  <si>
+    <t>亮出的顺子牌型在结算时提供+4攻击力</t>
+  </si>
+  <si>
+    <t>20007</t>
+  </si>
+  <si>
+    <t>铁制长弓</t>
+  </si>
+  <si>
+    <t>FlushAttack</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>亮出的同花牌型在结算时提供+6攻击力</t>
+  </si>
+  <si>
+    <t>20008</t>
+  </si>
+  <si>
+    <t>铁制长矛</t>
+  </si>
+  <si>
+    <t>StraightFlushAttack</t>
+  </si>
+  <si>
+    <t>亮出的同花顺牌型在结算时提供+8攻击力</t>
+  </si>
+  <si>
+    <t>20009</t>
+  </si>
+  <si>
+    <t>铁制长斧</t>
+  </si>
+  <si>
+    <t>LeopardAttack</t>
+  </si>
+  <si>
+    <t>亮出的豹子牌型在结算时提供+10攻击力</t>
+  </si>
+  <si>
+    <t>20010</t>
   </si>
   <si>
     <t>小精灵</t>
   </si>
   <si>
-    <t>MaxHp</t>
-  </si>
-  <si>
-    <t>立即获得300生命值</t>
-  </si>
-  <si>
-    <t>10016</t>
-  </si>
-  <si>
-    <t>EveryRoundHpUp</t>
-  </si>
-  <si>
-    <t>每次结算生命值+20</t>
-  </si>
-  <si>
-    <t>10017</t>
-  </si>
-  <si>
-    <t>翡翠长剑</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>对子在攻击时提供的倍率+3</t>
-  </si>
-  <si>
-    <t>10018</t>
-  </si>
-  <si>
-    <t>黄金法杖</t>
-  </si>
-  <si>
-    <t>同花在攻击时提供的倍率+3</t>
-  </si>
-  <si>
-    <t>10019</t>
-  </si>
-  <si>
-    <t>黄金头冠</t>
-  </si>
-  <si>
-    <t>StraightFlush</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>同花顺在攻击时提供的倍率+6</t>
-  </si>
-  <si>
-    <t>10020</t>
-  </si>
-  <si>
-    <t>黄金诗篇</t>
-  </si>
-  <si>
-    <t>顺子在攻击时提供的倍率+3</t>
-  </si>
-  <si>
-    <t>10021</t>
+    <t>HeroHpReplyEveryRoundEnding</t>
+  </si>
+  <si>
+    <t>每回合结束后恢复2点当前生命值</t>
+  </si>
+  <si>
+    <t>200101</t>
+  </si>
+  <si>
+    <t>HeroHpMax</t>
+  </si>
+  <si>
+    <t>获得30点生命值上限</t>
+  </si>
+  <si>
+    <t>20011</t>
+  </si>
+  <si>
+    <t>白条</t>
+  </si>
+  <si>
+    <t>Liability</t>
+  </si>
+  <si>
+    <t>可以负债,最多-20资金</t>
+  </si>
+  <si>
+    <t>20012</t>
+  </si>
+  <si>
+    <t>旗帜</t>
+  </si>
+  <si>
+    <t>EveryRubbingNum</t>
+  </si>
+  <si>
+    <t>在结算时,每剩余1个未使用的搓牌次数,都提供+1倍率</t>
+  </si>
+  <si>
+    <t>20013</t>
+  </si>
+  <si>
+    <t>恐怖面具</t>
+  </si>
+  <si>
+    <t>HeadCardAttack</t>
+  </si>
+  <si>
+    <t>亮出的每张人头牌在结算时提供+4攻击力</t>
+  </si>
+  <si>
+    <t>20014</t>
+  </si>
+  <si>
+    <t>黄金面具</t>
+  </si>
+  <si>
+    <t>ProOfHeadCardFunds</t>
+  </si>
+  <si>
+    <t>亮出的每张人头牌在结算时有30%概率+1资金</t>
+  </si>
+  <si>
+    <t>20015</t>
+  </si>
+  <si>
+    <t>黑白相机</t>
+  </si>
+  <si>
+    <t>Camera</t>
+  </si>
+  <si>
+    <t>结算时,未亮出的牌里每有1张黑桃或梅花,提供+4倍率</t>
+  </si>
+  <si>
+    <t>20016</t>
+  </si>
+  <si>
+    <t>丘比特</t>
+  </si>
+  <si>
+    <t>Cupid</t>
+  </si>
+  <si>
+    <t>结算时,未亮出的牌里每有1张方片或红心,提供+4倍率</t>
+  </si>
+  <si>
+    <t>20017</t>
+  </si>
+  <si>
+    <t>投资</t>
+  </si>
+  <si>
+    <t>ConsumeFundsGetAttack</t>
+  </si>
+  <si>
+    <t>每花费10资金,英雄+1基础攻击力</t>
+  </si>
+  <si>
+    <t>20018</t>
+  </si>
+  <si>
+    <t>补偿金</t>
+  </si>
+  <si>
+    <t>TakeDamageGetFunds</t>
+  </si>
+  <si>
+    <t>每次受到伤害时,+1资金</t>
+  </si>
+  <si>
+    <t>30001</t>
   </si>
   <si>
     <t>疯狂面具</t>
@@ -289,58 +421,289 @@
     <t>BloodSucking</t>
   </si>
   <si>
-    <t>0.01</t>
-  </si>
-  <si>
-    <t>每次攻击时,可获得1%的生命窃取</t>
-  </si>
-  <si>
-    <t>10022</t>
-  </si>
-  <si>
-    <t>钻石头冠</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>同花顺在攻击时提供的倍率+12</t>
-  </si>
-  <si>
-    <t>10023</t>
-  </si>
-  <si>
-    <t>国王权杖</t>
-  </si>
-  <si>
-    <t>Leopard</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>豹子在攻击时提供的倍率+50</t>
-  </si>
-  <si>
-    <t>10024</t>
-  </si>
-  <si>
-    <t>TwoThreeFive</t>
+    <t>造成伤害时,获得1%的生命窃取</t>
+  </si>
+  <si>
+    <t>30002</t>
+  </si>
+  <si>
+    <t>回旋刃</t>
+  </si>
+  <si>
+    <t>DoubleCardAttack</t>
+  </si>
+  <si>
+    <t>亮出的牌点数提供的攻击力加成翻倍</t>
+  </si>
+  <si>
+    <t>30003</t>
+  </si>
+  <si>
+    <t>致胜之剑</t>
+  </si>
+  <si>
+    <t>TheSwordOfVictory</t>
+  </si>
+  <si>
+    <t>结算伤害时,将留在手牌上最大牌点数转化为额外攻击力</t>
+  </si>
+  <si>
+    <t>30004</t>
+  </si>
+  <si>
+    <t>搓牌能手</t>
+  </si>
+  <si>
+    <t>EveryUseRubbingNum</t>
+  </si>
+  <si>
+    <t>每回合内,每搓1次牌,结算时提供的倍率+1</t>
+  </si>
+  <si>
+    <t>30005</t>
+  </si>
+  <si>
+    <t>会员卡</t>
+  </si>
+  <si>
+    <t>FreeShopRefresh</t>
+  </si>
+  <si>
+    <t>每次进入商店提供1次免费刷新的机会</t>
+  </si>
+  <si>
+    <t>30006</t>
+  </si>
+  <si>
+    <t>错峰出行</t>
+  </si>
+  <si>
+    <t>SpecialStraight</t>
+  </si>
+  <si>
+    <t>顺子牌型可以相隔1点组成</t>
+  </si>
+  <si>
+    <t>30007</t>
+  </si>
+  <si>
+    <t>致命黑八</t>
+  </si>
+  <si>
+    <t>SpecialEightCard</t>
+  </si>
+  <si>
+    <t>亮出的每张8在结算时提供+8攻击力</t>
+  </si>
+  <si>
+    <t>30008</t>
+  </si>
+  <si>
+    <t>偶数韵律</t>
+  </si>
+  <si>
+    <t>EvenNumberCard</t>
+  </si>
+  <si>
+    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+4倍率</t>
+  </si>
+  <si>
+    <t>30009</t>
+  </si>
+  <si>
+    <t>奇数韵律</t>
+  </si>
+  <si>
+    <t>OddNumberCard</t>
+  </si>
+  <si>
+    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+4倍率</t>
+  </si>
+  <si>
+    <t>30010</t>
+  </si>
+  <si>
+    <t>贵族</t>
+  </si>
+  <si>
+    <t>HeadCard</t>
+  </si>
+  <si>
+    <t>亮出的每张人头牌在结算时提供+6倍率</t>
+  </si>
+  <si>
+    <t>30011</t>
+  </si>
+  <si>
+    <t>工资卡</t>
+  </si>
+  <si>
+    <t>KillAfterSellingPrice</t>
+  </si>
+  <si>
+    <t>每击杀1名敌人,该收藏品的出售价格+1资金</t>
+  </si>
+  <si>
+    <t>30012</t>
+  </si>
+  <si>
+    <t>训练</t>
+  </si>
+  <si>
+    <t>EveryCardAttackForever</t>
+  </si>
+  <si>
+    <t>亮出的每张牌的点数在结算时会使其提供的攻击力永久+1</t>
+  </si>
+  <si>
+    <t>30013</t>
+  </si>
+  <si>
+    <t>九霄云外</t>
+  </si>
+  <si>
+    <t>SpecialNineCard</t>
+  </si>
+  <si>
+    <t>亮出的每张9在结算时提供2资金</t>
+  </si>
+  <si>
+    <t>SpecialTwoThreeFive</t>
   </si>
   <si>
     <t>散排235牌型等同于豹子牌型,并且可以战胜所有牌型</t>
   </si>
   <si>
-    <t>10025</t>
-  </si>
-  <si>
     <t>奢华沙发</t>
   </si>
   <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>立即获得5000生命值</t>
+    <t>获得500点生命值上限</t>
+  </si>
+  <si>
+    <t>老花眼</t>
+  </si>
+  <si>
+    <t>SpecialFlush</t>
+  </si>
+  <si>
+    <t>红桃和方片视为同一花色,黑桃和梅花视为同一花色</t>
+  </si>
+  <si>
+    <t>周星星</t>
+  </si>
+  <si>
+    <t>RubbingCardsNum</t>
+  </si>
+  <si>
+    <t>每回合搓牌次数+1</t>
+  </si>
+  <si>
+    <t>穷途末路</t>
+  </si>
+  <si>
+    <t>NoSkill</t>
+  </si>
+  <si>
+    <t>结算时,所有技能都无剩余使用次数,则提供+15倍率</t>
+  </si>
+  <si>
+    <t>收藏夹</t>
+  </si>
+  <si>
+    <t>EveryRelic</t>
+  </si>
+  <si>
+    <t>每有1个收藏品,结算时提供+5倍率</t>
+  </si>
+  <si>
+    <t>奢侈品</t>
+  </si>
+  <si>
+    <t>NoUseRubbingEveryRubbingNum</t>
+  </si>
+  <si>
+    <t>结算时,若未使用过搓牌,每个搓牌次数提供+6倍率</t>
+  </si>
+  <si>
+    <t>近视眼</t>
+  </si>
+  <si>
+    <t>AllCardIsHeadCard</t>
+  </si>
+  <si>
+    <t>所有牌均视为人头牌</t>
+  </si>
+  <si>
+    <t>顶尖学者</t>
+  </si>
+  <si>
+    <t>SpecialACard</t>
+  </si>
+  <si>
+    <t>亮出的每张A在结算时提供+6倍率</t>
+  </si>
+  <si>
+    <t>ACardAttack</t>
+  </si>
+  <si>
+    <t>亮出的每张A在结算时提供+6攻击力</t>
+  </si>
+  <si>
+    <t>老千</t>
+  </si>
+  <si>
+    <t>AccumulatedNumOfCardType</t>
+  </si>
+  <si>
+    <t>亮牌时,将该牌型在本局内亮出过的次数来提供倍率</t>
+  </si>
+  <si>
+    <t>天使</t>
+  </si>
+  <si>
+    <t>ProOfUpCardType</t>
+  </si>
+  <si>
+    <t>亮牌时,有25%概率将该牌型提供的倍率永久+1</t>
+  </si>
+  <si>
+    <t>双刃剑</t>
+  </si>
+  <si>
+    <t>每回合失去2次搓牌次数</t>
+  </si>
+  <si>
+    <t>结算时提供+20倍率</t>
+  </si>
+  <si>
+    <t>老搓家</t>
+  </si>
+  <si>
+    <t>RubbingCardRelic</t>
+  </si>
+  <si>
+    <t>每使用1次搓牌,结算时该收藏品永久提供+0.5倍率</t>
+  </si>
+  <si>
+    <t>幸运七</t>
+  </si>
+  <si>
+    <t>SpecialSevenCardPro</t>
+  </si>
+  <si>
+    <t>亮出的每张7结算时有7%概率提供攻击力和倍率</t>
+  </si>
+  <si>
+    <t>SpecialSevenCardAttack</t>
+  </si>
+  <si>
+    <t>幸运七触发时提供的攻击力</t>
+  </si>
+  <si>
+    <t>SpecialSevenCard</t>
+  </si>
+  <si>
+    <t>幸运七触发时提供的倍率</t>
   </si>
 </sst>
 </file>
@@ -506,12 +869,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -832,7 +1201,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -856,16 +1225,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -874,96 +1243,120 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1314,90 +1707,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="7.71666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.34166666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.825" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.325" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="5.75833333333333" style="3" customWidth="1"/>
+    <col min="2" max="2" width="7.49166666666667" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.475" style="4" customWidth="1"/>
+    <col min="4" max="4" width="21.8416666666667" style="4" customWidth="1"/>
+    <col min="5" max="5" width="5.86666666666667" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20.325" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4">
         <v>10001</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="4">
         <v>1</v>
       </c>
       <c r="F5" t="s">
@@ -1405,17 +1798,17 @@
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:6">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4">
         <v>10002</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="4">
         <v>1</v>
       </c>
       <c r="F6" t="s">
@@ -1423,16 +1816,16 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="B7" s="2">
+      <c r="B7" s="4">
         <v>10003</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F7" t="s">
@@ -1440,17 +1833,17 @@
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:6">
-      <c r="A8" s="1"/>
-      <c r="B8" s="2">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4">
         <v>10004</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="4">
         <v>1</v>
       </c>
       <c r="F8" t="s">
@@ -1458,17 +1851,17 @@
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:6">
-      <c r="A9" s="1"/>
-      <c r="B9" s="2">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4">
         <v>10005</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="4">
         <v>1</v>
       </c>
       <c r="F9" t="s">
@@ -1476,365 +1869,1044 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="B10" s="2">
+      <c r="B10" s="4">
         <v>10006</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>23</v>
+      <c r="E10" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="F10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:6">
+      <c r="A11" s="3"/>
+      <c r="B11" s="4">
+        <v>10007</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" customFormat="1" spans="1:6">
-      <c r="A11" s="1"/>
-      <c r="B11" s="2">
-        <v>10007</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1</v>
-      </c>
       <c r="F11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:6">
-      <c r="A12" s="1"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="B13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="A12" s="3"/>
+      <c r="B12" s="4">
+        <v>10008</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="D12" t="s">
         <v>39</v>
       </c>
+      <c r="E12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:6">
+      <c r="A13" s="3"/>
+      <c r="B13" s="4">
+        <v>10009</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:6">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="2">
+      <c r="A14" s="3"/>
+      <c r="B14" s="4">
+        <v>10010</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:6">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6">
+        <v>10011</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-2</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:6">
+      <c r="A16" s="3"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" customFormat="1" spans="1:6">
+      <c r="A17" s="3"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" customFormat="1" spans="1:6">
+      <c r="A18" s="3"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="B19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="1:6">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="4">
         <v>2</v>
       </c>
-      <c r="F14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" spans="1:6">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="2">
+      <c r="F20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="1:6">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="4">
         <v>2</v>
       </c>
-      <c r="F15" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="B16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" spans="1:6">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="2">
+      <c r="F21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" spans="1:6">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="4">
         <v>2</v>
       </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" spans="1:6">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="2">
-        <v>2</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="B19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" customFormat="1" spans="1:6">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="2">
-        <v>300</v>
-      </c>
-      <c r="F20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" spans="1:6">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E21" s="2">
-        <v>20</v>
-      </c>
-      <c r="F21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" spans="1:6">
-      <c r="A22" s="1"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="B23" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" t="s">
         <v>69</v>
       </c>
-      <c r="F23" t="s">
+    </row>
+    <row r="24" customFormat="1" spans="1:6">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" t="s">
         <v>72</v>
       </c>
-      <c r="D24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>69</v>
+      <c r="E24" s="4">
+        <v>4</v>
       </c>
       <c r="F24" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D25" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="3" t="s">
         <v>77</v>
       </c>
       <c r="F25" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="B26" s="1" t="s">
+    <row r="26" customFormat="1" spans="1:6">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="4" t="s">
         <v>80</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>69</v>
+        <v>81</v>
+      </c>
+      <c r="E26" s="4">
+        <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="B27" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="2" t="s">
+    </row>
+    <row r="27" customFormat="1" spans="1:6">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="C27" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="D27" s="4" t="s">
         <v>85</v>
+      </c>
+      <c r="E27" s="4">
+        <v>8</v>
       </c>
       <c r="F27" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
-      <c r="F28"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="1" t="s">
+    <row r="28" customFormat="1" spans="1:6">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C28" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D29" t="s">
-        <v>76</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="D28" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F29" t="s">
+      <c r="E28" s="4">
+        <v>2</v>
+      </c>
+      <c r="F28" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="1" t="s">
+    <row r="29" s="2" customFormat="1" spans="1:6">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C29" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E29" s="10">
+        <v>30</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E30" s="1" t="s">
+    </row>
+    <row r="30" customFormat="1" spans="1:6">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3" t="s">
         <v>94</v>
       </c>
+      <c r="C30" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="4">
+        <v>20</v>
+      </c>
       <c r="F30" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:6">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" s="4">
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="1:6">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E32" s="10">
+        <v>4</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="1:6">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="F33" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="1:6">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" s="4">
+        <v>4</v>
+      </c>
+      <c r="F34" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="1:6">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" s="4">
+        <v>4</v>
+      </c>
+      <c r="F35" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="1:6">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D36" t="s">
+        <v>120</v>
+      </c>
+      <c r="E36" s="4">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="1:6">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" t="s">
+        <v>124</v>
+      </c>
+      <c r="E37" s="4">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:6">
+      <c r="A38" s="3"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" customFormat="1" spans="1:6">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C39" t="s">
+        <v>127</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="F39" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" spans="1:6">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C40" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" t="s">
+        <v>132</v>
+      </c>
+      <c r="E40" s="4">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:6">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C41" t="s">
+        <v>135</v>
+      </c>
+      <c r="D41" t="s">
+        <v>136</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:6">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C42" t="s">
+        <v>139</v>
+      </c>
+      <c r="D42" t="s">
+        <v>140</v>
+      </c>
+      <c r="E42" s="4">
+        <v>1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:6">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C43" t="s">
+        <v>143</v>
+      </c>
+      <c r="D43" t="s">
+        <v>144</v>
+      </c>
+      <c r="E43" s="4">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" spans="1:6">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C44" t="s">
+        <v>147</v>
+      </c>
+      <c r="D44" t="s">
+        <v>148</v>
+      </c>
+      <c r="E44" s="4">
+        <v>1</v>
+      </c>
+      <c r="F44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:6">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" t="s">
+        <v>151</v>
+      </c>
+      <c r="D45" t="s">
+        <v>152</v>
+      </c>
+      <c r="E45" s="4">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:6">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C46" t="s">
+        <v>155</v>
+      </c>
+      <c r="D46" t="s">
+        <v>156</v>
+      </c>
+      <c r="E46" s="4">
+        <v>4</v>
+      </c>
+      <c r="F46" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" spans="1:6">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C47" t="s">
+        <v>159</v>
+      </c>
+      <c r="D47" t="s">
+        <v>160</v>
+      </c>
+      <c r="E47" s="4">
+        <v>4</v>
+      </c>
+      <c r="F47" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:6">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C48" t="s">
+        <v>163</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E48" s="4">
+        <v>6</v>
+      </c>
+      <c r="F48" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" spans="1:6">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C49" t="s">
+        <v>167</v>
+      </c>
+      <c r="D49" t="s">
+        <v>168</v>
+      </c>
+      <c r="E49" s="4">
+        <v>1</v>
+      </c>
+      <c r="F49" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="1:6">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C50" t="s">
+        <v>171</v>
+      </c>
+      <c r="D50" t="s">
+        <v>172</v>
+      </c>
+      <c r="E50" s="4">
+        <v>1</v>
+      </c>
+      <c r="F50" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:6">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C51" t="s">
+        <v>175</v>
+      </c>
+      <c r="D51" t="s">
+        <v>176</v>
+      </c>
+      <c r="E51" s="4">
+        <v>2</v>
+      </c>
+      <c r="F51" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" spans="1:6">
+      <c r="A52" s="3"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="E52" s="4"/>
+    </row>
+    <row r="53" customFormat="1" spans="1:6">
+      <c r="A53" s="3"/>
+      <c r="B53" s="4">
+        <v>40001</v>
+      </c>
+      <c r="C53" s="4">
         <v>235</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F31" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="B32" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" t="s">
-        <v>62</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F32" t="s">
-        <v>102</v>
-      </c>
+      <c r="D53" t="s">
+        <v>178</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="54" s="2" customFormat="1" spans="1:6">
+      <c r="A54" s="9"/>
+      <c r="B54" s="10">
+        <v>40002</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E54" s="10">
+        <v>500</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:6">
+      <c r="A55" s="3"/>
+      <c r="B55" s="4">
+        <v>40003</v>
+      </c>
+      <c r="C55" t="s">
+        <v>182</v>
+      </c>
+      <c r="D55" t="s">
+        <v>183</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" spans="1:6">
+      <c r="A56" s="3"/>
+      <c r="B56" s="4">
+        <v>40004</v>
+      </c>
+      <c r="C56" t="s">
+        <v>185</v>
+      </c>
+      <c r="D56" t="s">
+        <v>186</v>
+      </c>
+      <c r="E56" s="4">
+        <v>1</v>
+      </c>
+      <c r="F56" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" spans="1:6">
+      <c r="A57" s="3"/>
+      <c r="B57" s="4">
+        <v>40005</v>
+      </c>
+      <c r="C57" t="s">
+        <v>188</v>
+      </c>
+      <c r="D57" t="s">
+        <v>189</v>
+      </c>
+      <c r="E57" s="4">
+        <v>15</v>
+      </c>
+      <c r="F57" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" spans="1:6">
+      <c r="A58" s="3"/>
+      <c r="B58" s="4">
+        <v>40006</v>
+      </c>
+      <c r="C58" t="s">
+        <v>191</v>
+      </c>
+      <c r="D58" t="s">
+        <v>192</v>
+      </c>
+      <c r="E58" s="4">
+        <v>5</v>
+      </c>
+      <c r="F58" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" spans="1:6">
+      <c r="A59" s="3"/>
+      <c r="B59" s="4">
+        <v>40007</v>
+      </c>
+      <c r="C59" t="s">
+        <v>194</v>
+      </c>
+      <c r="D59" t="s">
+        <v>195</v>
+      </c>
+      <c r="E59" s="4">
+        <v>6</v>
+      </c>
+      <c r="F59" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" spans="1:6">
+      <c r="A60" s="3"/>
+      <c r="B60" s="4">
+        <v>40008</v>
+      </c>
+      <c r="C60" t="s">
+        <v>197</v>
+      </c>
+      <c r="D60" t="s">
+        <v>198</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" spans="1:6">
+      <c r="A61" s="3"/>
+      <c r="B61" s="4">
+        <v>40009</v>
+      </c>
+      <c r="C61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D61" t="s">
+        <v>201</v>
+      </c>
+      <c r="E61" s="4">
+        <v>6</v>
+      </c>
+      <c r="F61" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="62" s="2" customFormat="1" spans="1:6">
+      <c r="A62" s="9"/>
+      <c r="B62" s="10">
+        <v>400091</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="E62" s="10">
+        <v>6</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" spans="1:6">
+      <c r="A63" s="3"/>
+      <c r="B63" s="4">
+        <v>40010</v>
+      </c>
+      <c r="C63" t="s">
+        <v>205</v>
+      </c>
+      <c r="D63" t="s">
+        <v>206</v>
+      </c>
+      <c r="E63" s="4">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="64" customFormat="1" spans="1:6">
+      <c r="A64" s="3"/>
+      <c r="B64" s="4">
+        <v>40011</v>
+      </c>
+      <c r="C64" t="s">
+        <v>208</v>
+      </c>
+      <c r="D64" t="s">
+        <v>209</v>
+      </c>
+      <c r="E64" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="F64" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="65" customFormat="1" spans="1:6">
+      <c r="A65" s="3"/>
+      <c r="B65" s="4">
+        <v>40012</v>
+      </c>
+      <c r="C65" t="s">
+        <v>211</v>
+      </c>
+      <c r="D65" t="s">
+        <v>186</v>
+      </c>
+      <c r="E65" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F65" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="66" customFormat="1" spans="1:6">
+      <c r="A66" s="3"/>
+      <c r="B66" s="4">
+        <v>400121</v>
+      </c>
+      <c r="C66" t="s">
+        <v>211</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="4">
+        <v>20</v>
+      </c>
+      <c r="F66" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="67" customFormat="1" spans="1:6">
+      <c r="A67" s="3"/>
+      <c r="B67" s="4">
+        <v>40013</v>
+      </c>
+      <c r="C67" t="s">
+        <v>214</v>
+      </c>
+      <c r="D67" t="s">
+        <v>215</v>
+      </c>
+      <c r="E67" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F67" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" spans="1:6">
+      <c r="A68" s="3"/>
+      <c r="B68" s="4">
+        <v>40014</v>
+      </c>
+      <c r="C68" t="s">
+        <v>217</v>
+      </c>
+      <c r="D68" t="s">
+        <v>218</v>
+      </c>
+      <c r="E68" s="4">
+        <v>0.07</v>
+      </c>
+      <c r="F68" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="69" customFormat="1" spans="1:6">
+      <c r="A69" s="3"/>
+      <c r="B69" s="4">
+        <v>400141</v>
+      </c>
+      <c r="C69" t="s">
+        <v>217</v>
+      </c>
+      <c r="D69" t="s">
+        <v>220</v>
+      </c>
+      <c r="E69" s="4">
+        <v>77</v>
+      </c>
+      <c r="F69" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="70" customFormat="1" spans="1:6">
+      <c r="A70" s="3"/>
+      <c r="B70" s="4">
+        <v>400142</v>
+      </c>
+      <c r="C70" t="s">
+        <v>217</v>
+      </c>
+      <c r="D70" t="s">
+        <v>222</v>
+      </c>
+      <c r="E70" s="4">
+        <v>7</v>
+      </c>
+      <c r="F70" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="71" customFormat="1" spans="1:6">
+      <c r="A71" s="3"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="E71" s="4"/>
+    </row>
+    <row r="72" customFormat="1" spans="1:6">
+      <c r="A72" s="3"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72"/>
+      <c r="E72" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14610" windowHeight="9165"/>
+    <workbookView windowWidth="10875" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -181,7 +181,7 @@
     <t>HeroTakeDamage</t>
   </si>
   <si>
-    <t>每次受到的伤害降低2点</t>
+    <t>每次受到的伤害降低1点</t>
   </si>
   <si>
     <t>20001</t>
@@ -397,7 +397,7 @@
     <t>ConsumeFundsGetAttack</t>
   </si>
   <si>
-    <t>每花费10资金,英雄+1基础攻击力</t>
+    <t>每花费20资金,英雄+1基础攻击力</t>
   </si>
   <si>
     <t>20018</t>
@@ -565,7 +565,7 @@
     <t>SpecialNineCard</t>
   </si>
   <si>
-    <t>亮出的每张9在结算时提供2资金</t>
+    <t>亮出的每张9在结算时提供1资金</t>
   </si>
   <si>
     <t>SpecialTwoThreeFive</t>
@@ -869,18 +869,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1201,7 +1195,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1225,16 +1219,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1243,93 +1237,93 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
@@ -1341,17 +1335,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1962,16 +1950,16 @@
       <c r="B15" s="6">
         <v>10011</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>48</v>
       </c>
       <c r="E15" s="6">
-        <v>-2</v>
-      </c>
-      <c r="F15" s="8" t="s">
+        <v>-1</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2094,7 +2082,7 @@
         <v>72</v>
       </c>
       <c r="E24" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F24" t="s">
         <v>73</v>
@@ -2129,7 +2117,7 @@
         <v>81</v>
       </c>
       <c r="E26" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F26" t="s">
         <v>82</v>
@@ -2147,7 +2135,7 @@
         <v>85</v>
       </c>
       <c r="E27" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F27" t="s">
         <v>86</v>
@@ -2172,17 +2160,17 @@
       </c>
     </row>
     <row r="29" s="2" customFormat="1" spans="1:6">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9" t="s">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="8">
         <v>30</v>
       </c>
       <c r="F29" s="2" t="s">
@@ -2226,18 +2214,18 @@
       </c>
     </row>
     <row r="32" s="2" customFormat="1" spans="1:6">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9" t="s">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="10">
-        <v>4</v>
+      <c r="E32" s="8">
+        <v>2</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>105</v>
@@ -2255,7 +2243,7 @@
         <v>108</v>
       </c>
       <c r="E33" s="4">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F33" t="s">
         <v>109</v>
@@ -2273,7 +2261,7 @@
         <v>112</v>
       </c>
       <c r="E34" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F34" t="s">
         <v>113</v>
@@ -2291,7 +2279,7 @@
         <v>116</v>
       </c>
       <c r="E35" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F35" t="s">
         <v>117</v>
@@ -2309,7 +2297,7 @@
         <v>120</v>
       </c>
       <c r="E36" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F36" t="s">
         <v>121</v>
@@ -2351,7 +2339,7 @@
         <v>128</v>
       </c>
       <c r="E39" s="4">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F39" t="s">
         <v>129</v>
@@ -2457,7 +2445,7 @@
         <v>152</v>
       </c>
       <c r="E45" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F45" t="s">
         <v>153</v>
@@ -2475,7 +2463,7 @@
         <v>156</v>
       </c>
       <c r="E46" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F46" t="s">
         <v>157</v>
@@ -2493,7 +2481,7 @@
         <v>160</v>
       </c>
       <c r="E47" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F47" t="s">
         <v>161</v>
@@ -2511,7 +2499,7 @@
         <v>164</v>
       </c>
       <c r="E48" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F48" t="s">
         <v>165</v>
@@ -2565,7 +2553,7 @@
         <v>176</v>
       </c>
       <c r="E51" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" t="s">
         <v>177</v>
@@ -2594,17 +2582,17 @@
       </c>
     </row>
     <row r="54" s="2" customFormat="1" spans="1:6">
-      <c r="A54" s="9"/>
-      <c r="B54" s="10">
+      <c r="A54" s="7"/>
+      <c r="B54" s="8">
         <v>40002</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E54" s="10">
+      <c r="E54" s="8">
         <v>500</v>
       </c>
       <c r="F54" s="2" t="s">
@@ -2693,7 +2681,7 @@
         <v>195</v>
       </c>
       <c r="E59" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F59" t="s">
         <v>196</v>
@@ -2727,25 +2715,25 @@
         <v>201</v>
       </c>
       <c r="E61" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F61" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" spans="1:6">
-      <c r="A62" s="9"/>
-      <c r="B62" s="10">
+      <c r="A62" s="7"/>
+      <c r="B62" s="8">
         <v>400091</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="D62" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="E62" s="10">
-        <v>6</v>
+      <c r="E62" s="8">
+        <v>5</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>204</v>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="10875" windowHeight="9750"/>
+    <workbookView windowWidth="14190" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="223">
   <si>
     <t>##var</t>
   </si>
@@ -253,7 +253,7 @@
     <t>StraightAttack</t>
   </si>
   <si>
-    <t>亮出的顺子牌型在结算时提供+4攻击力</t>
+    <t>亮出的顺子牌型在结算时提供+2攻击力</t>
   </si>
   <si>
     <t>20007</t>
@@ -265,10 +265,7 @@
     <t>FlushAttack</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>亮出的同花牌型在结算时提供+6攻击力</t>
+    <t>亮出的同花牌型在结算时提供+2攻击力</t>
   </si>
   <si>
     <t>20008</t>
@@ -280,7 +277,7 @@
     <t>StraightFlushAttack</t>
   </si>
   <si>
-    <t>亮出的同花顺牌型在结算时提供+8攻击力</t>
+    <t>亮出的同花顺牌型在结算时提供+2攻击力</t>
   </si>
   <si>
     <t>20009</t>
@@ -292,7 +289,7 @@
     <t>LeopardAttack</t>
   </si>
   <si>
-    <t>亮出的豹子牌型在结算时提供+10攻击力</t>
+    <t>亮出的豹子牌型在结算时提供+2攻击力</t>
   </si>
   <si>
     <t>20010</t>
@@ -325,7 +322,7 @@
     <t>Liability</t>
   </si>
   <si>
-    <t>可以负债,最多-20资金</t>
+    <t>可以负债,最多-50金币</t>
   </si>
   <si>
     <t>20012</t>
@@ -337,7 +334,7 @@
     <t>EveryRubbingNum</t>
   </si>
   <si>
-    <t>在结算时,每剩余1个未使用的搓牌次数,都提供+1倍率</t>
+    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+1倍率</t>
   </si>
   <si>
     <t>20013</t>
@@ -349,7 +346,7 @@
     <t>HeadCardAttack</t>
   </si>
   <si>
-    <t>亮出的每张人头牌在结算时提供+4攻击力</t>
+    <t>亮出的每张人头牌在结算时提供+2攻击力</t>
   </si>
   <si>
     <t>20014</t>
@@ -361,7 +358,7 @@
     <t>ProOfHeadCardFunds</t>
   </si>
   <si>
-    <t>亮出的每张人头牌在结算时有30%概率+1资金</t>
+    <t>亮出的每张人头牌在结算时有20%概率+1金币</t>
   </si>
   <si>
     <t>20015</t>
@@ -373,7 +370,7 @@
     <t>Camera</t>
   </si>
   <si>
-    <t>结算时,未亮出的牌里每有1张黑桃或梅花,提供+4倍率</t>
+    <t>结算时,未亮出的牌里每有1张黑桃或梅花,提供+2倍率</t>
   </si>
   <si>
     <t>20016</t>
@@ -385,7 +382,7 @@
     <t>Cupid</t>
   </si>
   <si>
-    <t>结算时,未亮出的牌里每有1张方片或红心,提供+4倍率</t>
+    <t>结算时,未亮出的牌里每有1张方片或红心,提供+2倍率</t>
   </si>
   <si>
     <t>20017</t>
@@ -397,7 +394,7 @@
     <t>ConsumeFundsGetAttack</t>
   </si>
   <si>
-    <t>每花费20资金,英雄+1基础攻击力</t>
+    <t>每花费20资金,英雄+1攻击力</t>
   </si>
   <si>
     <t>20018</t>
@@ -409,7 +406,7 @@
     <t>TakeDamageGetFunds</t>
   </si>
   <si>
-    <t>每次受到伤害时,+1资金</t>
+    <t>每次受到伤害时,+10金币</t>
   </si>
   <si>
     <t>30001</t>
@@ -421,7 +418,7 @@
     <t>BloodSucking</t>
   </si>
   <si>
-    <t>造成伤害时,获得1%的生命窃取</t>
+    <t>造成伤害时,获得2%的生命窃取</t>
   </si>
   <si>
     <t>30002</t>
@@ -445,7 +442,7 @@
     <t>TheSwordOfVictory</t>
   </si>
   <si>
-    <t>结算伤害时,将留在手牌上最大牌点数转化为额外攻击力</t>
+    <t>结算伤害时,会将留在手牌上最大的牌点数转化为额外攻击力</t>
   </si>
   <si>
     <t>30004</t>
@@ -493,7 +490,7 @@
     <t>SpecialEightCard</t>
   </si>
   <si>
-    <t>亮出的每张8在结算时提供+8攻击力</t>
+    <t>亮出的每张8在结算时提供+6攻击力</t>
   </si>
   <si>
     <t>30008</t>
@@ -505,7 +502,7 @@
     <t>EvenNumberCard</t>
   </si>
   <si>
-    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+4倍率</t>
+    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+2倍率</t>
   </si>
   <si>
     <t>30009</t>
@@ -517,7 +514,7 @@
     <t>OddNumberCard</t>
   </si>
   <si>
-    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+4倍率</t>
+    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+2倍率</t>
   </si>
   <si>
     <t>30010</t>
@@ -529,7 +526,7 @@
     <t>HeadCard</t>
   </si>
   <si>
-    <t>亮出的每张人头牌在结算时提供+6倍率</t>
+    <t>亮出的每张人头牌在结算时提供+3倍率</t>
   </si>
   <si>
     <t>30011</t>
@@ -541,7 +538,7 @@
     <t>KillAfterSellingPrice</t>
   </si>
   <si>
-    <t>每击杀1名敌人,该收藏品的出售价格+1资金</t>
+    <t>每击杀1名敌人,该收藏品的出售价格+5金币</t>
   </si>
   <si>
     <t>30012</t>
@@ -565,7 +562,7 @@
     <t>SpecialNineCard</t>
   </si>
   <si>
-    <t>亮出的每张9在结算时提供1资金</t>
+    <t>亮出的每张9在结算时提供10金币</t>
   </si>
   <si>
     <t>SpecialTwoThreeFive</t>
@@ -622,7 +619,7 @@
     <t>NoUseRubbingEveryRubbingNum</t>
   </si>
   <si>
-    <t>结算时,若未使用过搓牌,每个搓牌次数提供+6倍率</t>
+    <t>结算时,若未使用过搓牌,每个搓牌次数提供+5倍率</t>
   </si>
   <si>
     <t>近视眼</t>
@@ -640,13 +637,13 @@
     <t>SpecialACard</t>
   </si>
   <si>
-    <t>亮出的每张A在结算时提供+6倍率</t>
+    <t>亮出的每张A在结算时提供+5倍率</t>
   </si>
   <si>
     <t>ACardAttack</t>
   </si>
   <si>
-    <t>亮出的每张A在结算时提供+6攻击力</t>
+    <t>亮出的每张A在结算时提供+5攻击力</t>
   </si>
   <si>
     <t>老千</t>
@@ -1695,7 +1692,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="5.75833333333333" style="3" customWidth="1"/>
@@ -1959,7 +1956,7 @@
       <c r="E15" s="6">
         <v>-1</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1967,934 +1964,922 @@
       <c r="A16" s="3"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
+      <c r="D16"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" customFormat="1" spans="1:6">
-      <c r="A17" s="3"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="E17" s="4"/>
+    <row r="17" spans="1:6">
+      <c r="B17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="18" customFormat="1" spans="1:6">
       <c r="A18" s="3"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="B18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="4">
+        <v>2</v>
+      </c>
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="1:6">
+      <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="4">
+        <v>2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" customFormat="1" spans="1:6">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="4">
-        <v>2</v>
-      </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="1:6">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" t="s">
-        <v>60</v>
+        <v>66</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="E21" s="4">
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:6">
+      <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="4">
+        <v>2</v>
+      </c>
+      <c r="F22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" spans="1:6">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" s="4">
-        <v>2</v>
-      </c>
       <c r="F23" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" customFormat="1" spans="1:6">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E24" s="4">
         <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" spans="1:6">
+      <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="4">
+        <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" customFormat="1" spans="1:6">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" t="s">
-        <v>81</v>
+        <v>87</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="E26" s="4">
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" spans="1:6">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E27" s="4">
-        <v>2</v>
-      </c>
-      <c r="F27" t="s">
-        <v>86</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:6">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="8">
+        <v>30</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="28" customFormat="1" spans="1:6">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
+      </c>
+      <c r="D28" t="s">
+        <v>95</v>
       </c>
       <c r="E28" s="4">
+        <v>50</v>
+      </c>
+      <c r="F28" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="1:6">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D29" t="s">
+        <v>99</v>
+      </c>
+      <c r="E29" s="4">
+        <v>1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="1:6">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="8">
         <v>2</v>
       </c>
-      <c r="F28" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:6">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" s="8">
-        <v>30</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" spans="1:6">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D30" t="s">
-        <v>96</v>
-      </c>
-      <c r="E30" s="4">
-        <v>20</v>
-      </c>
       <c r="F30" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="1:6">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" t="s">
-        <v>100</v>
+        <v>106</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="E31" s="4">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="F31" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:6">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E32" s="8">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="1:6">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" s="4">
         <v>2</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>105</v>
+      <c r="F32" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:6">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
+      </c>
+      <c r="D33" t="s">
+        <v>115</v>
       </c>
       <c r="E33" s="4">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:6">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D34" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E34" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F34" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:6">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E35" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:6">
       <c r="A36" s="3"/>
-      <c r="B36" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D36" t="s">
-        <v>120</v>
-      </c>
-      <c r="E36" s="4">
-        <v>20</v>
-      </c>
-      <c r="F36" t="s">
-        <v>121</v>
-      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="E36" s="4"/>
     </row>
     <row r="37" customFormat="1" spans="1:6">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D37" t="s">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="C37" t="s">
+        <v>126</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>127</v>
       </c>
       <c r="E37" s="4">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="F37" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:6">
       <c r="A38" s="3"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="E38" s="4"/>
+      <c r="B38" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38" t="s">
+        <v>130</v>
+      </c>
+      <c r="D38" t="s">
+        <v>131</v>
+      </c>
+      <c r="E38" s="4">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="39" customFormat="1" spans="1:6">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
-        <v>127</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E39" s="4">
-        <v>0.02</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="D39" t="s">
+        <v>135</v>
+      </c>
+      <c r="E39" s="4"/>
       <c r="F39" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:6">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C40" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D40" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E40" s="4">
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:6">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C41" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D41" t="s">
-        <v>136</v>
-      </c>
-      <c r="E41" s="4"/>
+        <v>143</v>
+      </c>
+      <c r="E41" s="4">
+        <v>1</v>
+      </c>
       <c r="F41" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:6">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D42" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E42" s="4">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="43" customFormat="1" spans="1:6">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C43" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D43" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E43" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F43" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:6">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C44" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D44" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="E44" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:6">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C45" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D45" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E45" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F45" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:6">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C46" t="s">
-        <v>155</v>
-      </c>
-      <c r="D46" t="s">
-        <v>156</v>
+        <v>162</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="E46" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" customFormat="1" spans="1:6">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C47" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D47" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="E47" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F47" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" customFormat="1" spans="1:6">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C48" t="s">
-        <v>163</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>164</v>
+        <v>170</v>
+      </c>
+      <c r="D48" t="s">
+        <v>171</v>
       </c>
       <c r="E48" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:6">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C49" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="D49" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E49" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50" customFormat="1" spans="1:6">
       <c r="A50" s="3"/>
-      <c r="B50" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C50" t="s">
-        <v>171</v>
-      </c>
-      <c r="D50" t="s">
-        <v>172</v>
-      </c>
-      <c r="E50" s="4">
-        <v>1</v>
-      </c>
-      <c r="F50" t="s">
-        <v>173</v>
-      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="E50" s="4"/>
     </row>
     <row r="51" customFormat="1" spans="1:6">
       <c r="A51" s="3"/>
-      <c r="B51" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C51" t="s">
-        <v>175</v>
+      <c r="B51" s="4">
+        <v>40001</v>
+      </c>
+      <c r="C51" s="4">
+        <v>235</v>
       </c>
       <c r="D51" t="s">
-        <v>176</v>
-      </c>
-      <c r="E51" s="4">
-        <v>1</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="E51" s="4"/>
       <c r="F51" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="52" customFormat="1" spans="1:6">
-      <c r="A52" s="3"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="E52" s="4"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" spans="1:6">
+      <c r="A52" s="7"/>
+      <c r="B52" s="8">
+        <v>40002</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E52" s="8">
+        <v>500</v>
+      </c>
+      <c r="F52" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="53" customFormat="1" spans="1:6">
       <c r="A53" s="3"/>
       <c r="B53" s="4">
-        <v>40001</v>
-      </c>
-      <c r="C53" s="4">
-        <v>235</v>
+        <v>40003</v>
+      </c>
+      <c r="C53" t="s">
+        <v>181</v>
       </c>
       <c r="D53" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="54" s="2" customFormat="1" spans="1:6">
-      <c r="A54" s="7"/>
-      <c r="B54" s="8">
-        <v>40002</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E54" s="8">
-        <v>500</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:6">
+      <c r="A54" s="3"/>
+      <c r="B54" s="4">
+        <v>40004</v>
+      </c>
+      <c r="C54" t="s">
+        <v>184</v>
+      </c>
+      <c r="D54" t="s">
+        <v>185</v>
+      </c>
+      <c r="E54" s="4">
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:6">
       <c r="A55" s="3"/>
       <c r="B55" s="4">
-        <v>40003</v>
+        <v>40005</v>
       </c>
       <c r="C55" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D55" t="s">
-        <v>183</v>
-      </c>
-      <c r="E55" s="4"/>
+        <v>188</v>
+      </c>
+      <c r="E55" s="4">
+        <v>15</v>
+      </c>
       <c r="F55" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:6">
       <c r="A56" s="3"/>
       <c r="B56" s="4">
-        <v>40004</v>
+        <v>40006</v>
       </c>
       <c r="C56" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D56" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E56" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F56" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:6">
       <c r="A57" s="3"/>
       <c r="B57" s="4">
-        <v>40005</v>
+        <v>40007</v>
       </c>
       <c r="C57" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D57" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E57" s="4">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F57" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:6">
       <c r="A58" s="3"/>
       <c r="B58" s="4">
-        <v>40006</v>
+        <v>40008</v>
       </c>
       <c r="C58" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D58" t="s">
-        <v>192</v>
-      </c>
-      <c r="E58" s="4">
-        <v>5</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="E58" s="4"/>
       <c r="F58" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:6">
       <c r="A59" s="3"/>
       <c r="B59" s="4">
-        <v>40007</v>
+        <v>40009</v>
       </c>
       <c r="C59" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D59" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E59" s="4">
         <v>5</v>
       </c>
       <c r="F59" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="60" customFormat="1" spans="1:6">
-      <c r="A60" s="3"/>
-      <c r="B60" s="4">
-        <v>40008</v>
-      </c>
-      <c r="C60" t="s">
-        <v>197</v>
-      </c>
-      <c r="D60" t="s">
-        <v>198</v>
-      </c>
-      <c r="E60" s="4"/>
-      <c r="F60" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="60" s="2" customFormat="1" spans="1:6">
+      <c r="A60" s="7"/>
+      <c r="B60" s="8">
+        <v>400091</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>199</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="E60" s="8">
+        <v>5</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:6">
       <c r="A61" s="3"/>
       <c r="B61" s="4">
-        <v>40009</v>
+        <v>40010</v>
       </c>
       <c r="C61" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D61" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E61" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="62" s="2" customFormat="1" spans="1:6">
-      <c r="A62" s="7"/>
-      <c r="B62" s="8">
-        <v>400091</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="E62" s="8">
-        <v>5</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" spans="1:6">
+      <c r="A62" s="3"/>
+      <c r="B62" s="4">
+        <v>40011</v>
+      </c>
+      <c r="C62" t="s">
+        <v>207</v>
+      </c>
+      <c r="D62" t="s">
+        <v>208</v>
+      </c>
+      <c r="E62" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="F62" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:6">
       <c r="A63" s="3"/>
       <c r="B63" s="4">
-        <v>40010</v>
+        <v>40012</v>
       </c>
       <c r="C63" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D63" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="E63" s="4">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="F63" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:6">
       <c r="A64" s="3"/>
       <c r="B64" s="4">
-        <v>40011</v>
+        <v>400121</v>
       </c>
       <c r="C64" t="s">
-        <v>208</v>
-      </c>
-      <c r="D64" t="s">
-        <v>209</v>
+        <v>210</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E64" s="4">
-        <v>0.25</v>
+        <v>20</v>
       </c>
       <c r="F64" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:6">
       <c r="A65" s="3"/>
       <c r="B65" s="4">
-        <v>40012</v>
+        <v>40013</v>
       </c>
       <c r="C65" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D65" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="E65" s="4">
-        <v>-2</v>
+        <v>0.5</v>
       </c>
       <c r="F65" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:6">
       <c r="A66" s="3"/>
       <c r="B66" s="4">
-        <v>400121</v>
+        <v>40014</v>
       </c>
       <c r="C66" t="s">
-        <v>211</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>16</v>
+        <v>216</v>
+      </c>
+      <c r="D66" t="s">
+        <v>217</v>
       </c>
       <c r="E66" s="4">
-        <v>20</v>
+        <v>0.07</v>
       </c>
       <c r="F66" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:6">
       <c r="A67" s="3"/>
       <c r="B67" s="4">
-        <v>40013</v>
+        <v>400141</v>
       </c>
       <c r="C67" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D67" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E67" s="4">
-        <v>0.5</v>
+        <v>77</v>
       </c>
       <c r="F67" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:6">
       <c r="A68" s="3"/>
       <c r="B68" s="4">
-        <v>40014</v>
+        <v>400142</v>
       </c>
       <c r="C68" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D68" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E68" s="4">
-        <v>0.07</v>
+        <v>7</v>
       </c>
       <c r="F68" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:6">
       <c r="A69" s="3"/>
-      <c r="B69" s="4">
-        <v>400141</v>
-      </c>
-      <c r="C69" t="s">
-        <v>217</v>
-      </c>
-      <c r="D69" t="s">
-        <v>220</v>
-      </c>
-      <c r="E69" s="4">
-        <v>77</v>
-      </c>
-      <c r="F69" t="s">
-        <v>221</v>
-      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="E69" s="4"/>
     </row>
     <row r="70" customFormat="1" spans="1:6">
       <c r="A70" s="3"/>
-      <c r="B70" s="4">
-        <v>400142</v>
-      </c>
-      <c r="C70" t="s">
-        <v>217</v>
-      </c>
-      <c r="D70" t="s">
-        <v>222</v>
-      </c>
-      <c r="E70" s="4">
-        <v>7</v>
-      </c>
-      <c r="F70" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="71" customFormat="1" spans="1:6">
-      <c r="A71" s="3"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="E71" s="4"/>
-    </row>
-    <row r="72" customFormat="1" spans="1:6">
-      <c r="A72" s="3"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72"/>
-      <c r="E72" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70"/>
+      <c r="E70" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14190" windowHeight="9750"/>
+    <workbookView windowWidth="16065" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="224">
   <si>
     <t>##var</t>
   </si>
@@ -241,7 +241,7 @@
     <t>CoupletAttack</t>
   </si>
   <si>
-    <t>亮出的对子牌型在结算时提供+2攻击力</t>
+    <t>亮出的对子牌型在结算时提供+4攻击力</t>
   </si>
   <si>
     <t>20006</t>
@@ -253,7 +253,7 @@
     <t>StraightAttack</t>
   </si>
   <si>
-    <t>亮出的顺子牌型在结算时提供+2攻击力</t>
+    <t>亮出的顺子牌型在结算时提供+6攻击力</t>
   </si>
   <si>
     <t>20007</t>
@@ -265,7 +265,10 @@
     <t>FlushAttack</t>
   </si>
   <si>
-    <t>亮出的同花牌型在结算时提供+2攻击力</t>
+    <t>6</t>
+  </si>
+  <si>
+    <t>亮出的同花牌型在结算时提供+6攻击力</t>
   </si>
   <si>
     <t>20008</t>
@@ -277,7 +280,7 @@
     <t>StraightFlushAttack</t>
   </si>
   <si>
-    <t>亮出的同花顺牌型在结算时提供+2攻击力</t>
+    <t>亮出的同花顺牌型在结算时提供+6攻击力</t>
   </si>
   <si>
     <t>20009</t>
@@ -289,7 +292,7 @@
     <t>LeopardAttack</t>
   </si>
   <si>
-    <t>亮出的豹子牌型在结算时提供+2攻击力</t>
+    <t>亮出的豹子牌型在结算时提供+6攻击力</t>
   </si>
   <si>
     <t>20010</t>
@@ -2049,7 +2052,7 @@
         <v>68</v>
       </c>
       <c r="E21" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21" t="s">
         <v>69</v>
@@ -2067,7 +2070,7 @@
         <v>72</v>
       </c>
       <c r="E22" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
         <v>73</v>
@@ -2084,226 +2087,226 @@
         <v>76</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="F23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" customFormat="1" spans="1:6">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E24" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:6">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E25" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" customFormat="1" spans="1:6">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E26" s="4">
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" spans="1:6">
       <c r="A27" s="7"/>
       <c r="B27" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E27" s="8">
         <v>30</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" customFormat="1" spans="1:6">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E28" s="4">
         <v>50</v>
       </c>
       <c r="F28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:6">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E29" s="4">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" spans="1:6">
       <c r="A30" s="7"/>
       <c r="B30" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E30" s="8">
         <v>2</v>
       </c>
       <c r="F30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="1:6">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E31" s="4">
         <v>0.2</v>
       </c>
       <c r="F31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" customFormat="1" spans="1:6">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E32" s="4">
         <v>2</v>
       </c>
       <c r="F32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:6">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E33" s="4">
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:6">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E34" s="4">
         <v>20</v>
       </c>
       <c r="F34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:6">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E35" s="4">
         <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:6">
@@ -2315,233 +2318,233 @@
     <row r="37" customFormat="1" spans="1:6">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E37" s="4">
         <v>0.02</v>
       </c>
       <c r="F37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:6">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E38" s="4">
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:6">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:6">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E40" s="4">
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:6">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D41" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E41" s="4">
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:6">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C42" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E42" s="4">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" customFormat="1" spans="1:6">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C43" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E43" s="4">
         <v>6</v>
       </c>
       <c r="F43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:6">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E44" s="4">
         <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:6">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E45" s="4">
         <v>2</v>
       </c>
       <c r="F45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:6">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E46" s="4">
         <v>3</v>
       </c>
       <c r="F46" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" customFormat="1" spans="1:6">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C47" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D47" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E47" s="4">
         <v>5</v>
       </c>
       <c r="F47" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" customFormat="1" spans="1:6">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D48" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E48" s="4">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:6">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C49" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D49" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E49" s="4">
         <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" customFormat="1" spans="1:6">
@@ -2559,11 +2562,11 @@
         <v>235</v>
       </c>
       <c r="D51" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" s="2" customFormat="1" spans="1:6">
@@ -2572,16 +2575,16 @@
         <v>40002</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E52" s="8">
         <v>500</v>
       </c>
       <c r="F52" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:6">
@@ -2590,14 +2593,14 @@
         <v>40003</v>
       </c>
       <c r="C53" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D53" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:6">
@@ -2606,16 +2609,16 @@
         <v>40004</v>
       </c>
       <c r="C54" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E54" s="4">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:6">
@@ -2624,16 +2627,16 @@
         <v>40005</v>
       </c>
       <c r="C55" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D55" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E55" s="4">
         <v>15</v>
       </c>
       <c r="F55" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:6">
@@ -2642,16 +2645,16 @@
         <v>40006</v>
       </c>
       <c r="C56" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D56" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E56" s="4">
         <v>5</v>
       </c>
       <c r="F56" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:6">
@@ -2660,16 +2663,16 @@
         <v>40007</v>
       </c>
       <c r="C57" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D57" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E57" s="4">
         <v>5</v>
       </c>
       <c r="F57" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:6">
@@ -2678,14 +2681,14 @@
         <v>40008</v>
       </c>
       <c r="C58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D58" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E58" s="4"/>
       <c r="F58" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:6">
@@ -2694,16 +2697,16 @@
         <v>40009</v>
       </c>
       <c r="C59" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D59" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E59" s="4">
         <v>5</v>
       </c>
       <c r="F59" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" spans="1:6">
@@ -2712,16 +2715,16 @@
         <v>400091</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E60" s="8">
         <v>5</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:6">
@@ -2730,16 +2733,16 @@
         <v>40010</v>
       </c>
       <c r="C61" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E61" s="4">
         <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:6">
@@ -2748,16 +2751,16 @@
         <v>40011</v>
       </c>
       <c r="C62" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D62" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E62" s="4">
         <v>0.25</v>
       </c>
       <c r="F62" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:6">
@@ -2766,16 +2769,16 @@
         <v>40012</v>
       </c>
       <c r="C63" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D63" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E63" s="4">
         <v>-2</v>
       </c>
       <c r="F63" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:6">
@@ -2784,7 +2787,7 @@
         <v>400121</v>
       </c>
       <c r="C64" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>16</v>
@@ -2793,7 +2796,7 @@
         <v>20</v>
       </c>
       <c r="F64" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:6">
@@ -2802,16 +2805,16 @@
         <v>40013</v>
       </c>
       <c r="C65" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D65" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E65" s="4">
         <v>0.5</v>
       </c>
       <c r="F65" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:6">
@@ -2820,16 +2823,16 @@
         <v>40014</v>
       </c>
       <c r="C66" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D66" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E66" s="4">
         <v>0.07</v>
       </c>
       <c r="F66" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:6">
@@ -2838,16 +2841,16 @@
         <v>400141</v>
       </c>
       <c r="C67" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D67" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E67" s="4">
         <v>77</v>
       </c>
       <c r="F67" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:6">
@@ -2856,16 +2859,16 @@
         <v>400142</v>
       </c>
       <c r="C68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D68" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E68" s="4">
         <v>7</v>
       </c>
       <c r="F68" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:6">

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16065" windowHeight="9750"/>
+    <workbookView windowWidth="15480" windowHeight="10815"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="387">
   <si>
     <t>##var</t>
   </si>
@@ -64,7 +64,7 @@
     <t>MechanismType</t>
   </si>
   <si>
-    <t>float</t>
+    <t>float[]</t>
   </si>
   <si>
     <t>效果名字</t>
@@ -184,6 +184,66 @@
     <t>每次受到的伤害降低1点</t>
   </si>
   <si>
+    <t>小钱包</t>
+  </si>
+  <si>
+    <t>EveryRoundGetGold</t>
+  </si>
+  <si>
+    <t>每回合开始时,获得1金币</t>
+  </si>
+  <si>
+    <t>绷带</t>
+  </si>
+  <si>
+    <t>HeroHpReplyEveryRoundEnding</t>
+  </si>
+  <si>
+    <t>每回合结束时,恢复2点生命</t>
+  </si>
+  <si>
+    <t>幸运草</t>
+  </si>
+  <si>
+    <t>EveryRoundEndingGetGoldPer</t>
+  </si>
+  <si>
+    <t>0.1|5</t>
+  </si>
+  <si>
+    <t>每回合结束后,有10%概率获得5金币</t>
+  </si>
+  <si>
+    <t>暴击拳套</t>
+  </si>
+  <si>
+    <t>EveryRoundEndingGetCritical</t>
+  </si>
+  <si>
+    <t>0.01|20</t>
+  </si>
+  <si>
+    <t>每回合结束后,提高1%暴击率,至多叠加20层</t>
+  </si>
+  <si>
+    <t>垫脚石</t>
+  </si>
+  <si>
+    <t>SteppingStone</t>
+  </si>
+  <si>
+    <t>每当你亮牌时大于场上所有敌人,就永久提供+1攻击力</t>
+  </si>
+  <si>
+    <t>反击拳套</t>
+  </si>
+  <si>
+    <t>BounceDamage</t>
+  </si>
+  <si>
+    <t>每当你受到伤害时,反弹2点伤害给攻击者</t>
+  </si>
+  <si>
     <t>20001</t>
   </si>
   <si>
@@ -301,9 +361,6 @@
     <t>小精灵</t>
   </si>
   <si>
-    <t>HeroHpReplyEveryRoundEnding</t>
-  </si>
-  <si>
     <t>每回合结束后恢复2点当前生命值</t>
   </si>
   <si>
@@ -412,6 +469,147 @@
     <t>每次受到伤害时,+10金币</t>
   </si>
   <si>
+    <t>20019</t>
+  </si>
+  <si>
+    <t>和平鸽</t>
+  </si>
+  <si>
+    <t>AllPeacePer</t>
+  </si>
+  <si>
+    <t>有25%概率将自身造成的伤害或受到的伤害降低为0</t>
+  </si>
+  <si>
+    <t>20020</t>
+  </si>
+  <si>
+    <t>勇气徽章</t>
+  </si>
+  <si>
+    <t>DefeatGetAttack</t>
+  </si>
+  <si>
+    <t>亮牌时,若牌型小于对方,则永久+1攻击力</t>
+  </si>
+  <si>
+    <t>20021</t>
+  </si>
+  <si>
+    <t>激励徽章</t>
+  </si>
+  <si>
+    <t>DefeatGetHpMax</t>
+  </si>
+  <si>
+    <t>亮牌时,若牌型小于对方,则永久+3血量上限</t>
+  </si>
+  <si>
+    <t>20022</t>
+  </si>
+  <si>
+    <t>记账本</t>
+  </si>
+  <si>
+    <t>DefeatAllGetGold</t>
+  </si>
+  <si>
+    <t>每回合结束时,若本回合未造成任何伤害,则获得5金币</t>
+  </si>
+  <si>
+    <t>20023</t>
+  </si>
+  <si>
+    <t>铁饭碗</t>
+  </si>
+  <si>
+    <t>IronRiceBowl</t>
+  </si>
+  <si>
+    <t>亮牌后无论胜负,均可获得1金币</t>
+  </si>
+  <si>
+    <t>20024</t>
+  </si>
+  <si>
+    <t>永恒之心</t>
+  </si>
+  <si>
+    <t>EveryRoundGetHpMax</t>
+  </si>
+  <si>
+    <t>每回合开始时,永久+2血量上限</t>
+  </si>
+  <si>
+    <t>20025</t>
+  </si>
+  <si>
+    <t>幸运同花</t>
+  </si>
+  <si>
+    <t>LuckyFlush</t>
+  </si>
+  <si>
+    <t>亮牌时,若敌人的牌型大于同花,则会被强行视作同花</t>
+  </si>
+  <si>
+    <t>20026</t>
+  </si>
+  <si>
+    <t>运动鞋</t>
+  </si>
+  <si>
+    <t>EveryRoundEndingGetEvade</t>
+  </si>
+  <si>
+    <t>每回合结束后,提高1%闪避率,至多叠加20层</t>
+  </si>
+  <si>
+    <t>20027</t>
+  </si>
+  <si>
+    <t>保温杯</t>
+  </si>
+  <si>
+    <t>ThermosCup</t>
+  </si>
+  <si>
+    <t>0.5|6</t>
+  </si>
+  <si>
+    <t>每回合结束后,若你的血量低于50%,则恢复6点生命</t>
+  </si>
+  <si>
+    <t>20028</t>
+  </si>
+  <si>
+    <t>利息</t>
+  </si>
+  <si>
+    <t>Interest</t>
+  </si>
+  <si>
+    <t>10|1</t>
+  </si>
+  <si>
+    <t>每拥有10金币,在回合结束后就会获得1金币</t>
+  </si>
+  <si>
+    <t>20029</t>
+  </si>
+  <si>
+    <t>小算盘</t>
+  </si>
+  <si>
+    <t>Abacus</t>
+  </si>
+  <si>
+    <t>1|3</t>
+  </si>
+  <si>
+    <t>每回合结束时,每剩余1次搓牌次数就获得3金币</t>
+  </si>
+  <si>
     <t>30001</t>
   </si>
   <si>
@@ -568,6 +766,162 @@
     <t>亮出的每张9在结算时提供10金币</t>
   </si>
   <si>
+    <t>30014</t>
+  </si>
+  <si>
+    <t>后备计划</t>
+  </si>
+  <si>
+    <t>DefeatAllGetGoldAndReplyHp</t>
+  </si>
+  <si>
+    <t>10|15</t>
+  </si>
+  <si>
+    <t>如果本回合牌型小于所有敌人,则立即获得10金币并回复15点生命值</t>
+  </si>
+  <si>
+    <t>30015</t>
+  </si>
+  <si>
+    <t>护身符</t>
+  </si>
+  <si>
+    <t>MissFirstDamage</t>
+  </si>
+  <si>
+    <t>每回合受到的第1次伤害完全免疫</t>
+  </si>
+  <si>
+    <t>30016</t>
+  </si>
+  <si>
+    <t>复盘笔记</t>
+  </si>
+  <si>
+    <t>DefeatGetMagnification</t>
+  </si>
+  <si>
+    <t>1|0.2</t>
+  </si>
+  <si>
+    <t>每输1次敌人,结算时就永久提供+0.2倍率</t>
+  </si>
+  <si>
+    <t>30017</t>
+  </si>
+  <si>
+    <t>幸运顺子</t>
+  </si>
+  <si>
+    <t>LuckyStraight</t>
+  </si>
+  <si>
+    <t>亮牌时,若敌人的牌型大于顺子,则会被强行视作顺子</t>
+  </si>
+  <si>
+    <t>30018</t>
+  </si>
+  <si>
+    <t>逆转沙漏</t>
+  </si>
+  <si>
+    <t>ReverseResult</t>
+  </si>
+  <si>
+    <t>当牌型小于敌人时,有30%概率反转对比结果,但伤害按自身牌型计算</t>
+  </si>
+  <si>
+    <t>30019</t>
+  </si>
+  <si>
+    <t>练习卷</t>
+  </si>
+  <si>
+    <t>NoKillMonsterGetMagnification</t>
+  </si>
+  <si>
+    <t>每回合结束后,若本回合你未击杀任何敌人,则永久提供+0.5倍率</t>
+  </si>
+  <si>
+    <t>30020</t>
+  </si>
+  <si>
+    <t>小本本</t>
+  </si>
+  <si>
+    <t>Revenge</t>
+  </si>
+  <si>
+    <t>本局内,对自己曾经输过的敌人造成伤害时,伤害+20%</t>
+  </si>
+  <si>
+    <t>30021</t>
+  </si>
+  <si>
+    <t>高贵徽章</t>
+  </si>
+  <si>
+    <t>NobleBadge</t>
+  </si>
+  <si>
+    <t>0.5|10</t>
+  </si>
+  <si>
+    <t>每回合开始时,若生命值高于50%,获得10金币</t>
+  </si>
+  <si>
+    <t>30022</t>
+  </si>
+  <si>
+    <t>陷阱</t>
+  </si>
+  <si>
+    <t>Trap</t>
+  </si>
+  <si>
+    <t>本局内,自己曾经输过的敌人在造成伤害时,伤害-20%</t>
+  </si>
+  <si>
+    <t>30023</t>
+  </si>
+  <si>
+    <t>好运来</t>
+  </si>
+  <si>
+    <t>DownGrade</t>
+  </si>
+  <si>
+    <t>0.15|1</t>
+  </si>
+  <si>
+    <t>每回合有15%概率使本回合所有敌人亮出的牌型自动降1级</t>
+  </si>
+  <si>
+    <t>30024</t>
+  </si>
+  <si>
+    <t>入场券</t>
+  </si>
+  <si>
+    <t>AdmissionTicket</t>
+  </si>
+  <si>
+    <t>每回合开始时,对所有敌人造成1次自身攻击力的伤害</t>
+  </si>
+  <si>
+    <t>30025</t>
+  </si>
+  <si>
+    <t>条约</t>
+  </si>
+  <si>
+    <t>MonsterDamage</t>
+  </si>
+  <si>
+    <t>所有敌人造成的伤害降低30%</t>
+  </si>
+  <si>
     <t>SpecialTwoThreeFive</t>
   </si>
   <si>
@@ -704,6 +1058,141 @@
   </si>
   <si>
     <t>幸运七触发时提供的倍率</t>
+  </si>
+  <si>
+    <t>武林秘籍</t>
+  </si>
+  <si>
+    <t>MissDamagePer</t>
+  </si>
+  <si>
+    <t>获得50%闪避率</t>
+  </si>
+  <si>
+    <t>MissGetDamage</t>
+  </si>
+  <si>
+    <t>1|2</t>
+  </si>
+  <si>
+    <t>闪避成功时会对敌人造成1次自身攻击力200%的伤害</t>
+  </si>
+  <si>
+    <t>幸运对子</t>
+  </si>
+  <si>
+    <t>LuckyCouplet</t>
+  </si>
+  <si>
+    <t>亮牌时,若敌人的牌型大于对子,则会被强行视作对子</t>
+  </si>
+  <si>
+    <t>小强</t>
+  </si>
+  <si>
+    <t>DefeatGetDamage</t>
+  </si>
+  <si>
+    <t>1|0.05</t>
+  </si>
+  <si>
+    <t>每输1次敌人,后续自身造成的所有伤害提高5%</t>
+  </si>
+  <si>
+    <t>救命稻草</t>
+  </si>
+  <si>
+    <t>AstrawToClutchAt</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>如果你受到了1次致命伤害,会将血量降低为1,且下次造成伤害的同时恢复本次伤害20%的血量,每关生效1次</t>
+  </si>
+  <si>
+    <t>专注</t>
+  </si>
+  <si>
+    <t>OneMonsterGetDamage</t>
+  </si>
+  <si>
+    <t>当场上只剩下一个敌人时,你对其造成的伤害+100%</t>
+  </si>
+  <si>
+    <t>变形魔方</t>
+  </si>
+  <si>
+    <t>CardUpGrade</t>
+  </si>
+  <si>
+    <t>每回合亮出的牌型强制提升一级</t>
+  </si>
+  <si>
+    <t>毒药</t>
+  </si>
+  <si>
+    <t>MonsterHpMax</t>
+  </si>
+  <si>
+    <t>-0.3</t>
+  </si>
+  <si>
+    <t>所有敌人血量降低30%[BOSS除外]</t>
+  </si>
+  <si>
+    <t>刺客秘籍</t>
+  </si>
+  <si>
+    <t>HeroCritical</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>获得50%暴击率</t>
+  </si>
+  <si>
+    <t>CriticalAoe</t>
+  </si>
+  <si>
+    <t>1|1</t>
+  </si>
+  <si>
+    <t>触发暴击时会对其他敌人造成1次自身攻击力100%的伤害</t>
+  </si>
+  <si>
+    <t>透视眼</t>
+  </si>
+  <si>
+    <t>PerspectiveNum</t>
+  </si>
+  <si>
+    <t>每回合透视次数+1</t>
+  </si>
+  <si>
+    <t>聚宝盆</t>
+  </si>
+  <si>
+    <t>DamageTurnToGold</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>每回合结束后,本回合自身总伤害输出的2%转化为金币</t>
+  </si>
+  <si>
+    <t>差距胶囊</t>
+  </si>
+  <si>
+    <t>GapDamage</t>
+  </si>
+  <si>
+    <t>1|0.15</t>
+  </si>
+  <si>
+    <t>比牌时,你的牌型与对方牌型每相隔1级,则造成/承受的伤害对应提高/降低15%</t>
   </si>
 </sst>
 </file>
@@ -869,12 +1358,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1195,7 +1696,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1219,16 +1720,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1237,97 +1738,103 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1339,6 +1846,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1695,90 +2211,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G110"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="5.75833333333333" style="3" customWidth="1"/>
-    <col min="2" max="2" width="7.49166666666667" style="3" customWidth="1"/>
-    <col min="3" max="3" width="8.475" style="4" customWidth="1"/>
-    <col min="4" max="4" width="21.8416666666667" style="4" customWidth="1"/>
-    <col min="5" max="5" width="5.86666666666667" style="3" customWidth="1"/>
-    <col min="6" max="6" width="20.325" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="5.75833333333333" style="5" customWidth="1"/>
+    <col min="2" max="2" width="7.49166666666667" style="5" customWidth="1"/>
+    <col min="3" max="3" width="8.475" style="6" customWidth="1"/>
+    <col min="4" max="4" width="21.8416666666667" style="6" customWidth="1"/>
+    <col min="5" max="5" width="8.36666666666667" style="5" customWidth="1"/>
+    <col min="6" max="6" width="20.325" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6">
         <v>10001</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="6">
         <v>1</v>
       </c>
       <c r="F5" t="s">
@@ -1786,17 +2302,17 @@
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:6">
-      <c r="A6" s="3"/>
-      <c r="B6" s="4">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6">
         <v>10002</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
@@ -1804,16 +2320,16 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="B7" s="4">
+      <c r="B7" s="6">
         <v>10003</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F7" t="s">
@@ -1821,17 +2337,17 @@
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:6">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6">
         <v>10004</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="6">
         <v>1</v>
       </c>
       <c r="F8" t="s">
@@ -1839,17 +2355,17 @@
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:6">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6">
         <v>10005</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="6">
         <v>1</v>
       </c>
       <c r="F9" t="s">
@@ -1857,16 +2373,16 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="B10" s="4">
+      <c r="B10" s="6">
         <v>10006</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="5" t="s">
         <v>33</v>
       </c>
       <c r="F10" t="s">
@@ -1874,17 +2390,17 @@
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:6">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6">
         <v>10007</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D11" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="5" t="s">
         <v>33</v>
       </c>
       <c r="F11" t="s">
@@ -1892,17 +2408,17 @@
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:6">
-      <c r="A12" s="3"/>
-      <c r="B12" s="4">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6">
         <v>10008</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
         <v>38</v>
       </c>
       <c r="D12" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="5" t="s">
         <v>33</v>
       </c>
       <c r="F12" t="s">
@@ -1910,17 +2426,17 @@
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:6">
-      <c r="A13" s="3"/>
-      <c r="B13" s="4">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6">
         <v>10009</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>41</v>
       </c>
       <c r="D13" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="5" t="s">
         <v>33</v>
       </c>
       <c r="F13" t="s">
@@ -1928,17 +2444,17 @@
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:6">
-      <c r="A14" s="3"/>
-      <c r="B14" s="4">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6">
         <v>10010</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="5" t="s">
         <v>33</v>
       </c>
       <c r="F14" t="s">
@@ -1946,943 +2462,1680 @@
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:6">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6">
+      <c r="A15" s="7"/>
+      <c r="B15" s="8">
         <v>10011</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="8">
         <v>-1</v>
       </c>
       <c r="F15" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="16" customFormat="1" spans="1:6">
-      <c r="A16" s="3"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="B17" s="3" t="s">
+    <row r="16" s="2" customFormat="1" spans="1:6">
+      <c r="A16" s="4"/>
+      <c r="B16" s="9">
+        <v>10012</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E16" s="9">
+        <v>1</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="3" t="s">
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:6">
+      <c r="A17" s="4"/>
+      <c r="B17" s="9">
+        <v>10013</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="9">
+        <v>2</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:6">
+      <c r="A18" s="4"/>
+      <c r="B18" s="9">
+        <v>10014</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="1:6">
+      <c r="A19" s="4"/>
+      <c r="B19" s="9">
+        <v>10015</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="1:6">
+      <c r="A20" s="4"/>
+      <c r="B20" s="9">
+        <v>10016</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="9">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="1:6">
+      <c r="A21" s="4"/>
+      <c r="B21" s="9">
+        <v>10017</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="9">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:6">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22"/>
+      <c r="E22" s="6"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" spans="1:6">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3" t="s">
+      <c r="F23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" spans="1:6">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="6">
+        <v>2</v>
+      </c>
+      <c r="F24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" spans="1:6">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="6">
+        <v>2</v>
+      </c>
+      <c r="F25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="B26" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="1:6">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="6">
+        <v>4</v>
+      </c>
+      <c r="F27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="1:6">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" s="6">
+        <v>6</v>
+      </c>
+      <c r="F28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="B29" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F29" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="1:6">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E30" s="6">
+        <v>6</v>
+      </c>
+      <c r="F30" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:6">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" s="6">
+        <v>6</v>
+      </c>
+      <c r="F31" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="1:6">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="E32" s="6">
         <v>2</v>
       </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" customFormat="1" spans="1:6">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="4">
+      <c r="F32" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" s="3" customFormat="1" spans="1:6">
+      <c r="A33" s="12"/>
+      <c r="B33" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E33" s="13">
+        <v>30</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="1:6">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" t="s">
+        <v>115</v>
+      </c>
+      <c r="E34" s="6">
+        <v>50</v>
+      </c>
+      <c r="F34" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="1:6">
+      <c r="A35" s="5"/>
+      <c r="B35" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" t="s">
+        <v>119</v>
+      </c>
+      <c r="E35" s="6">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36" s="3" customFormat="1" spans="1:6">
+      <c r="A36" s="12"/>
+      <c r="B36" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E36" s="13">
         <v>2</v>
       </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="B20" s="3" t="s">
+      <c r="F36" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="1:6">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="F37" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:6">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D38" t="s">
+        <v>131</v>
+      </c>
+      <c r="E38" s="6">
+        <v>2</v>
+      </c>
+      <c r="F38" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" spans="1:6">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D39" t="s">
+        <v>135</v>
+      </c>
+      <c r="E39" s="6">
+        <v>2</v>
+      </c>
+      <c r="F39" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" spans="1:6">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D40" t="s">
+        <v>139</v>
+      </c>
+      <c r="E40" s="6">
+        <v>20</v>
+      </c>
+      <c r="F40" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:6">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D41" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" s="6">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" spans="1:6">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" spans="1:6">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E43" s="9">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" spans="1:6">
+      <c r="A44" s="4"/>
+      <c r="B44" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E44" s="9">
+        <v>3</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" spans="1:6">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E45" s="9">
+        <v>5</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" spans="1:6">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E46" s="9">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" spans="1:6">
+      <c r="A47" s="4"/>
+      <c r="B47" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E47" s="9">
+        <v>2</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" spans="1:6">
+      <c r="A48" s="4"/>
+      <c r="B48" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E48" s="9"/>
+      <c r="F48" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" spans="1:6">
+      <c r="A49" s="4"/>
+      <c r="B49" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E49" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" spans="1:6">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="4">
-        <v>4</v>
-      </c>
-      <c r="F21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" spans="1:6">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" s="4">
+      <c r="F49" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" spans="1:6">
+      <c r="A50" s="4"/>
+      <c r="B50" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" spans="1:6">
+      <c r="A51" s="4"/>
+      <c r="B51" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" spans="1:6">
+      <c r="A52" s="4"/>
+      <c r="B52" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="1:6">
+      <c r="A53" s="5"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="E53" s="6"/>
+    </row>
+    <row r="54" customFormat="1" spans="1:6">
+      <c r="A54" s="5"/>
+      <c r="B54" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C54" t="s">
+        <v>193</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E54" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="F54" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:6">
+      <c r="A55" s="5"/>
+      <c r="B55" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C55" t="s">
+        <v>197</v>
+      </c>
+      <c r="D55" t="s">
+        <v>198</v>
+      </c>
+      <c r="E55" s="6">
+        <v>1</v>
+      </c>
+      <c r="F55" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" spans="1:6">
+      <c r="A56" s="5"/>
+      <c r="B56" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C56" t="s">
+        <v>201</v>
+      </c>
+      <c r="D56" t="s">
+        <v>202</v>
+      </c>
+      <c r="E56" s="6"/>
+      <c r="F56" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" spans="1:6">
+      <c r="A57" s="5"/>
+      <c r="B57" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C57" t="s">
+        <v>205</v>
+      </c>
+      <c r="D57" t="s">
+        <v>206</v>
+      </c>
+      <c r="E57" s="6">
+        <v>1</v>
+      </c>
+      <c r="F57" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" spans="1:6">
+      <c r="A58" s="5"/>
+      <c r="B58" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C58" t="s">
+        <v>209</v>
+      </c>
+      <c r="D58" t="s">
+        <v>210</v>
+      </c>
+      <c r="E58" s="6">
+        <v>1</v>
+      </c>
+      <c r="F58" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" spans="1:6">
+      <c r="A59" s="5"/>
+      <c r="B59" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C59" t="s">
+        <v>213</v>
+      </c>
+      <c r="D59" t="s">
+        <v>214</v>
+      </c>
+      <c r="E59" s="6">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" spans="1:6">
+      <c r="A60" s="5"/>
+      <c r="B60" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" t="s">
+        <v>217</v>
+      </c>
+      <c r="D60" t="s">
+        <v>218</v>
+      </c>
+      <c r="E60" s="6">
         <v>6</v>
       </c>
-      <c r="F22" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="B23" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D23" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="F60" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" spans="1:6">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C61" t="s">
+        <v>221</v>
+      </c>
+      <c r="D61" t="s">
+        <v>222</v>
+      </c>
+      <c r="E61" s="6">
+        <v>2</v>
+      </c>
+      <c r="F61" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" spans="1:6">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C62" t="s">
+        <v>225</v>
+      </c>
+      <c r="D62" t="s">
+        <v>226</v>
+      </c>
+      <c r="E62" s="6">
+        <v>2</v>
+      </c>
+      <c r="F62" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" spans="1:6">
+      <c r="A63" s="5"/>
+      <c r="B63" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C63" t="s">
+        <v>229</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E63" s="6">
+        <v>3</v>
+      </c>
+      <c r="F63" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="64" customFormat="1" spans="1:6">
+      <c r="A64" s="5"/>
+      <c r="B64" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C64" t="s">
+        <v>233</v>
+      </c>
+      <c r="D64" t="s">
+        <v>234</v>
+      </c>
+      <c r="E64" s="6">
+        <v>5</v>
+      </c>
+      <c r="F64" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="65" customFormat="1" spans="1:6">
+      <c r="A65" s="5"/>
+      <c r="B65" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C65" t="s">
+        <v>237</v>
+      </c>
+      <c r="D65" t="s">
+        <v>238</v>
+      </c>
+      <c r="E65" s="6">
+        <v>1</v>
+      </c>
+      <c r="F65" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="66" customFormat="1" spans="1:6">
+      <c r="A66" s="5"/>
+      <c r="B66" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C66" t="s">
+        <v>241</v>
+      </c>
+      <c r="D66" t="s">
+        <v>242</v>
+      </c>
+      <c r="E66" s="6">
+        <v>10</v>
+      </c>
+      <c r="F66" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" spans="1:6">
+      <c r="A67" s="4"/>
+      <c r="B67" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" spans="1:6">
+      <c r="A68" s="4"/>
+      <c r="B68" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E68" s="9">
+        <v>1</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" spans="1:6">
+      <c r="A69" s="4"/>
+      <c r="B69" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" spans="1:6">
+      <c r="A70" s="4"/>
+      <c r="B70" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E70" s="9"/>
+      <c r="F70" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" spans="1:6">
+      <c r="A71" s="4"/>
+      <c r="B71" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E71" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" spans="1:6">
+      <c r="A72" s="4"/>
+      <c r="B72" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E72" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="73" s="2" customFormat="1" spans="1:6">
+      <c r="A73" s="4"/>
+      <c r="B73" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E73" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="74" s="2" customFormat="1" spans="1:6">
+      <c r="A74" s="4"/>
+      <c r="B74" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="75" s="2" customFormat="1" spans="1:6">
+      <c r="A75" s="4"/>
+      <c r="B75" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E75" s="9">
+        <v>-0.2</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="76" s="2" customFormat="1" spans="1:6">
+      <c r="A76" s="4"/>
+      <c r="B76" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="77" s="2" customFormat="1" spans="1:6">
+      <c r="A77" s="4"/>
+      <c r="B77" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E77" s="9">
+        <v>1</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="78" s="2" customFormat="1" spans="1:6">
+      <c r="A78" s="4"/>
+      <c r="B78" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-0.3</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="79" customFormat="1" spans="1:6">
+      <c r="A79" s="5"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="E79" s="6"/>
+    </row>
+    <row r="80" customFormat="1" spans="1:6">
+      <c r="A80" s="5"/>
+      <c r="B80" s="6">
+        <v>40001</v>
+      </c>
+      <c r="C80" s="6">
+        <v>235</v>
+      </c>
+      <c r="D80" t="s">
+        <v>296</v>
+      </c>
+      <c r="E80" s="6"/>
+      <c r="F80" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="81" s="3" customFormat="1" spans="1:6">
+      <c r="A81" s="12"/>
+      <c r="B81" s="13">
+        <v>40002</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E81" s="13">
+        <v>500</v>
+      </c>
+      <c r="F81" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="82" customFormat="1" spans="1:6">
+      <c r="A82" s="5"/>
+      <c r="B82" s="6">
+        <v>40003</v>
+      </c>
+      <c r="C82" t="s">
+        <v>300</v>
+      </c>
+      <c r="D82" t="s">
+        <v>301</v>
+      </c>
+      <c r="E82" s="6"/>
+      <c r="F82" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="83" customFormat="1" spans="1:6">
+      <c r="A83" s="5"/>
+      <c r="B83" s="6">
+        <v>40004</v>
+      </c>
+      <c r="C83" t="s">
+        <v>303</v>
+      </c>
+      <c r="D83" t="s">
+        <v>304</v>
+      </c>
+      <c r="E83" s="6">
+        <v>1</v>
+      </c>
+      <c r="F83" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="84" customFormat="1" spans="1:6">
+      <c r="A84" s="5"/>
+      <c r="B84" s="6">
+        <v>40005</v>
+      </c>
+      <c r="C84" t="s">
+        <v>306</v>
+      </c>
+      <c r="D84" t="s">
+        <v>307</v>
+      </c>
+      <c r="E84" s="6">
+        <v>15</v>
+      </c>
+      <c r="F84" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="85" customFormat="1" spans="1:6">
+      <c r="A85" s="5"/>
+      <c r="B85" s="6">
+        <v>40006</v>
+      </c>
+      <c r="C85" t="s">
+        <v>309</v>
+      </c>
+      <c r="D85" t="s">
+        <v>310</v>
+      </c>
+      <c r="E85" s="6">
+        <v>5</v>
+      </c>
+      <c r="F85" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="86" customFormat="1" spans="1:6">
+      <c r="A86" s="5"/>
+      <c r="B86" s="6">
+        <v>40007</v>
+      </c>
+      <c r="C86" t="s">
+        <v>312</v>
+      </c>
+      <c r="D86" t="s">
+        <v>313</v>
+      </c>
+      <c r="E86" s="6">
+        <v>5</v>
+      </c>
+      <c r="F86" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="87" customFormat="1" spans="1:6">
+      <c r="A87" s="5"/>
+      <c r="B87" s="6">
+        <v>40008</v>
+      </c>
+      <c r="C87" t="s">
+        <v>315</v>
+      </c>
+      <c r="D87" t="s">
+        <v>316</v>
+      </c>
+      <c r="E87" s="6"/>
+      <c r="F87" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="88" customFormat="1" spans="1:6">
+      <c r="A88" s="5"/>
+      <c r="B88" s="6">
+        <v>40009</v>
+      </c>
+      <c r="C88" t="s">
+        <v>318</v>
+      </c>
+      <c r="D88" t="s">
+        <v>319</v>
+      </c>
+      <c r="E88" s="6">
+        <v>5</v>
+      </c>
+      <c r="F88" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="89" s="3" customFormat="1" spans="1:6">
+      <c r="A89" s="12"/>
+      <c r="B89" s="13">
+        <v>400091</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="E89" s="13">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="90" customFormat="1" spans="1:6">
+      <c r="A90" s="5"/>
+      <c r="B90" s="6">
+        <v>40010</v>
+      </c>
+      <c r="C90" t="s">
+        <v>323</v>
+      </c>
+      <c r="D90" t="s">
+        <v>324</v>
+      </c>
+      <c r="E90" s="6">
+        <v>1</v>
+      </c>
+      <c r="F90" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="91" customFormat="1" spans="1:6">
+      <c r="A91" s="5"/>
+      <c r="B91" s="6">
+        <v>40011</v>
+      </c>
+      <c r="C91" t="s">
+        <v>326</v>
+      </c>
+      <c r="D91" t="s">
+        <v>327</v>
+      </c>
+      <c r="E91" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F91" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="92" customFormat="1" spans="1:6">
+      <c r="A92" s="5"/>
+      <c r="B92" s="6">
+        <v>40012</v>
+      </c>
+      <c r="C92" t="s">
+        <v>329</v>
+      </c>
+      <c r="D92" t="s">
+        <v>304</v>
+      </c>
+      <c r="E92" s="6">
+        <v>-2</v>
+      </c>
+      <c r="F92" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="93" customFormat="1" spans="1:6">
+      <c r="A93" s="5"/>
+      <c r="B93" s="6">
+        <v>400121</v>
+      </c>
+      <c r="C93" t="s">
+        <v>329</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E93" s="6">
+        <v>20</v>
+      </c>
+      <c r="F93" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="94" customFormat="1" spans="1:6">
+      <c r="A94" s="5"/>
+      <c r="B94" s="6">
+        <v>40013</v>
+      </c>
+      <c r="C94" t="s">
+        <v>332</v>
+      </c>
+      <c r="D94" t="s">
+        <v>333</v>
+      </c>
+      <c r="E94" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="F94" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="95" customFormat="1" spans="1:6">
+      <c r="A95" s="5"/>
+      <c r="B95" s="6">
+        <v>40014</v>
+      </c>
+      <c r="C95" t="s">
+        <v>335</v>
+      </c>
+      <c r="D95" t="s">
+        <v>336</v>
+      </c>
+      <c r="E95" s="6">
+        <v>0.07</v>
+      </c>
+      <c r="F95" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="96" customFormat="1" spans="1:6">
+      <c r="A96" s="5"/>
+      <c r="B96" s="6">
+        <v>400141</v>
+      </c>
+      <c r="C96" t="s">
+        <v>335</v>
+      </c>
+      <c r="D96" t="s">
+        <v>338</v>
+      </c>
+      <c r="E96" s="6">
         <v>77</v>
       </c>
-      <c r="F23" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" spans="1:6">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" s="4">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" spans="1:6">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" s="4">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" spans="1:6">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E26" s="4">
-        <v>2</v>
-      </c>
-      <c r="F26" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:6">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E27" s="8">
-        <v>30</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" spans="1:6">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" t="s">
-        <v>96</v>
-      </c>
-      <c r="E28" s="4">
-        <v>50</v>
-      </c>
-      <c r="F28" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" spans="1:6">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D29" t="s">
-        <v>100</v>
-      </c>
-      <c r="E29" s="4">
-        <v>1</v>
-      </c>
-      <c r="F29" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:6">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E30" s="8">
-        <v>2</v>
-      </c>
-      <c r="F30" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" spans="1:6">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E31" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="F31" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" spans="1:6">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" t="s">
-        <v>112</v>
-      </c>
-      <c r="E32" s="4">
-        <v>2</v>
-      </c>
-      <c r="F32" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" spans="1:6">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D33" t="s">
-        <v>116</v>
-      </c>
-      <c r="E33" s="4">
-        <v>2</v>
-      </c>
-      <c r="F33" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="34" customFormat="1" spans="1:6">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D34" t="s">
-        <v>120</v>
-      </c>
-      <c r="E34" s="4">
-        <v>20</v>
-      </c>
-      <c r="F34" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="35" customFormat="1" spans="1:6">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D35" t="s">
-        <v>124</v>
-      </c>
-      <c r="E35" s="4">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="36" customFormat="1" spans="1:6">
-      <c r="A36" s="3"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="E36" s="4"/>
-    </row>
-    <row r="37" customFormat="1" spans="1:6">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C37" t="s">
-        <v>127</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E37" s="4">
-        <v>0.02</v>
-      </c>
-      <c r="F37" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="38" customFormat="1" spans="1:6">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C38" t="s">
-        <v>131</v>
-      </c>
-      <c r="D38" t="s">
-        <v>132</v>
-      </c>
-      <c r="E38" s="4">
-        <v>1</v>
-      </c>
-      <c r="F38" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="39" customFormat="1" spans="1:6">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C39" t="s">
-        <v>135</v>
-      </c>
-      <c r="D39" t="s">
-        <v>136</v>
-      </c>
-      <c r="E39" s="4"/>
-      <c r="F39" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" spans="1:6">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C40" t="s">
-        <v>139</v>
-      </c>
-      <c r="D40" t="s">
-        <v>140</v>
-      </c>
-      <c r="E40" s="4">
-        <v>1</v>
-      </c>
-      <c r="F40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" spans="1:6">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C41" t="s">
-        <v>143</v>
-      </c>
-      <c r="D41" t="s">
-        <v>144</v>
-      </c>
-      <c r="E41" s="4">
-        <v>1</v>
-      </c>
-      <c r="F41" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="42" customFormat="1" spans="1:6">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C42" t="s">
-        <v>147</v>
-      </c>
-      <c r="D42" t="s">
-        <v>148</v>
-      </c>
-      <c r="E42" s="4">
-        <v>1</v>
-      </c>
-      <c r="F42" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="43" customFormat="1" spans="1:6">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C43" t="s">
-        <v>151</v>
-      </c>
-      <c r="D43" t="s">
-        <v>152</v>
-      </c>
-      <c r="E43" s="4">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="44" customFormat="1" spans="1:6">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C44" t="s">
-        <v>155</v>
-      </c>
-      <c r="D44" t="s">
-        <v>156</v>
-      </c>
-      <c r="E44" s="4">
-        <v>2</v>
-      </c>
-      <c r="F44" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="45" customFormat="1" spans="1:6">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C45" t="s">
-        <v>159</v>
-      </c>
-      <c r="D45" t="s">
-        <v>160</v>
-      </c>
-      <c r="E45" s="4">
-        <v>2</v>
-      </c>
-      <c r="F45" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" spans="1:6">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C46" t="s">
-        <v>163</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="E46" s="4">
-        <v>3</v>
-      </c>
-      <c r="F46" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" spans="1:6">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C47" t="s">
-        <v>167</v>
-      </c>
-      <c r="D47" t="s">
-        <v>168</v>
-      </c>
-      <c r="E47" s="4">
-        <v>5</v>
-      </c>
-      <c r="F47" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" spans="1:6">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C48" t="s">
-        <v>171</v>
-      </c>
-      <c r="D48" t="s">
-        <v>172</v>
-      </c>
-      <c r="E48" s="4">
-        <v>1</v>
-      </c>
-      <c r="F48" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" spans="1:6">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C49" t="s">
-        <v>175</v>
-      </c>
-      <c r="D49" t="s">
-        <v>176</v>
-      </c>
-      <c r="E49" s="4">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="50" customFormat="1" spans="1:6">
-      <c r="A50" s="3"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="E50" s="4"/>
-    </row>
-    <row r="51" customFormat="1" spans="1:6">
-      <c r="A51" s="3"/>
-      <c r="B51" s="4">
-        <v>40001</v>
-      </c>
-      <c r="C51" s="4">
-        <v>235</v>
-      </c>
-      <c r="D51" t="s">
-        <v>178</v>
-      </c>
-      <c r="E51" s="4"/>
-      <c r="F51" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="52" s="2" customFormat="1" spans="1:6">
-      <c r="A52" s="7"/>
-      <c r="B52" s="8">
-        <v>40002</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E52" s="8">
-        <v>500</v>
-      </c>
-      <c r="F52" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" spans="1:6">
-      <c r="A53" s="3"/>
-      <c r="B53" s="4">
-        <v>40003</v>
-      </c>
-      <c r="C53" t="s">
-        <v>182</v>
-      </c>
-      <c r="D53" t="s">
-        <v>183</v>
-      </c>
-      <c r="E53" s="4"/>
-      <c r="F53" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="54" customFormat="1" spans="1:6">
-      <c r="A54" s="3"/>
-      <c r="B54" s="4">
-        <v>40004</v>
-      </c>
-      <c r="C54" t="s">
-        <v>185</v>
-      </c>
-      <c r="D54" t="s">
-        <v>186</v>
-      </c>
-      <c r="E54" s="4">
-        <v>1</v>
-      </c>
-      <c r="F54" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="55" customFormat="1" spans="1:6">
-      <c r="A55" s="3"/>
-      <c r="B55" s="4">
-        <v>40005</v>
-      </c>
-      <c r="C55" t="s">
-        <v>188</v>
-      </c>
-      <c r="D55" t="s">
-        <v>189</v>
-      </c>
-      <c r="E55" s="4">
-        <v>15</v>
-      </c>
-      <c r="F55" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="56" customFormat="1" spans="1:6">
-      <c r="A56" s="3"/>
-      <c r="B56" s="4">
-        <v>40006</v>
-      </c>
-      <c r="C56" t="s">
-        <v>191</v>
-      </c>
-      <c r="D56" t="s">
-        <v>192</v>
-      </c>
-      <c r="E56" s="4">
-        <v>5</v>
-      </c>
-      <c r="F56" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="57" customFormat="1" spans="1:6">
-      <c r="A57" s="3"/>
-      <c r="B57" s="4">
-        <v>40007</v>
-      </c>
-      <c r="C57" t="s">
-        <v>194</v>
-      </c>
-      <c r="D57" t="s">
-        <v>195</v>
-      </c>
-      <c r="E57" s="4">
-        <v>5</v>
-      </c>
-      <c r="F57" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="58" customFormat="1" spans="1:6">
-      <c r="A58" s="3"/>
-      <c r="B58" s="4">
-        <v>40008</v>
-      </c>
-      <c r="C58" t="s">
-        <v>197</v>
-      </c>
-      <c r="D58" t="s">
-        <v>198</v>
-      </c>
-      <c r="E58" s="4"/>
-      <c r="F58" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="59" customFormat="1" spans="1:6">
-      <c r="A59" s="3"/>
-      <c r="B59" s="4">
-        <v>40009</v>
-      </c>
-      <c r="C59" t="s">
-        <v>200</v>
-      </c>
-      <c r="D59" t="s">
-        <v>201</v>
-      </c>
-      <c r="E59" s="4">
-        <v>5</v>
-      </c>
-      <c r="F59" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="60" s="2" customFormat="1" spans="1:6">
-      <c r="A60" s="7"/>
-      <c r="B60" s="8">
-        <v>400091</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="E60" s="8">
-        <v>5</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="61" customFormat="1" spans="1:6">
-      <c r="A61" s="3"/>
-      <c r="B61" s="4">
-        <v>40010</v>
-      </c>
-      <c r="C61" t="s">
-        <v>205</v>
-      </c>
-      <c r="D61" t="s">
-        <v>206</v>
-      </c>
-      <c r="E61" s="4">
-        <v>1</v>
-      </c>
-      <c r="F61" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="62" customFormat="1" spans="1:6">
-      <c r="A62" s="3"/>
-      <c r="B62" s="4">
-        <v>40011</v>
-      </c>
-      <c r="C62" t="s">
-        <v>208</v>
-      </c>
-      <c r="D62" t="s">
-        <v>209</v>
-      </c>
-      <c r="E62" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="F62" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="63" customFormat="1" spans="1:6">
-      <c r="A63" s="3"/>
-      <c r="B63" s="4">
-        <v>40012</v>
-      </c>
-      <c r="C63" t="s">
-        <v>211</v>
-      </c>
-      <c r="D63" t="s">
-        <v>186</v>
-      </c>
-      <c r="E63" s="4">
-        <v>-2</v>
-      </c>
-      <c r="F63" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="64" customFormat="1" spans="1:6">
-      <c r="A64" s="3"/>
-      <c r="B64" s="4">
-        <v>400121</v>
-      </c>
-      <c r="C64" t="s">
-        <v>211</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E64" s="4">
-        <v>20</v>
-      </c>
-      <c r="F64" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="65" customFormat="1" spans="1:6">
-      <c r="A65" s="3"/>
-      <c r="B65" s="4">
-        <v>40013</v>
-      </c>
-      <c r="C65" t="s">
-        <v>214</v>
-      </c>
-      <c r="D65" t="s">
-        <v>215</v>
-      </c>
-      <c r="E65" s="4">
+      <c r="F96" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="97" customFormat="1" spans="1:7">
+      <c r="A97" s="5"/>
+      <c r="B97" s="6">
+        <v>400142</v>
+      </c>
+      <c r="C97" t="s">
+        <v>335</v>
+      </c>
+      <c r="D97" t="s">
+        <v>340</v>
+      </c>
+      <c r="E97" s="6">
+        <v>7</v>
+      </c>
+      <c r="F97" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="98" s="2" customFormat="1" spans="1:7">
+      <c r="A98" s="4"/>
+      <c r="B98" s="9">
+        <v>40015</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E98" s="9">
         <v>0.5</v>
       </c>
-      <c r="F65" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="66" customFormat="1" spans="1:6">
-      <c r="A66" s="3"/>
-      <c r="B66" s="4">
-        <v>40014</v>
-      </c>
-      <c r="C66" t="s">
-        <v>217</v>
-      </c>
-      <c r="D66" t="s">
-        <v>218</v>
-      </c>
-      <c r="E66" s="4">
-        <v>0.07</v>
-      </c>
-      <c r="F66" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="67" customFormat="1" spans="1:6">
-      <c r="A67" s="3"/>
-      <c r="B67" s="4">
-        <v>400141</v>
-      </c>
-      <c r="C67" t="s">
-        <v>217</v>
-      </c>
-      <c r="D67" t="s">
-        <v>220</v>
-      </c>
-      <c r="E67" s="4">
-        <v>77</v>
-      </c>
-      <c r="F67" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="68" customFormat="1" spans="1:6">
-      <c r="A68" s="3"/>
-      <c r="B68" s="4">
-        <v>400142</v>
-      </c>
-      <c r="C68" t="s">
-        <v>217</v>
-      </c>
-      <c r="D68" t="s">
-        <v>222</v>
-      </c>
-      <c r="E68" s="4">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="69" customFormat="1" spans="1:6">
-      <c r="A69" s="3"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="E69" s="4"/>
-    </row>
-    <row r="70" customFormat="1" spans="1:6">
-      <c r="A70" s="3"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70"/>
-      <c r="E70" s="4"/>
+      <c r="F98" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="99" s="2" customFormat="1" spans="1:7">
+      <c r="A99" s="4"/>
+      <c r="B99" s="9">
+        <v>400151</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="100" s="2" customFormat="1" spans="1:7">
+      <c r="A100" s="4"/>
+      <c r="B100" s="9">
+        <v>40016</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E100" s="9"/>
+      <c r="F100" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="101" s="4" customFormat="1" spans="1:7">
+      <c r="B101" s="9">
+        <v>40017</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="G101" s="2"/>
+    </row>
+    <row r="102" s="4" customFormat="1" spans="1:7">
+      <c r="B102" s="9">
+        <v>40018</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="G102" s="2"/>
+    </row>
+    <row r="103" s="4" customFormat="1" spans="1:7">
+      <c r="B103" s="9">
+        <v>40019</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="G103" s="2"/>
+    </row>
+    <row r="104" s="4" customFormat="1" spans="1:7">
+      <c r="B104" s="9">
+        <v>40020</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="G104" s="2"/>
+    </row>
+    <row r="105" s="4" customFormat="1" spans="1:7">
+      <c r="B105" s="9">
+        <v>40021</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="G105" s="2"/>
+    </row>
+    <row r="106" s="4" customFormat="1" spans="1:7">
+      <c r="B106" s="9">
+        <v>40022</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="G106" s="2"/>
+    </row>
+    <row r="107" s="4" customFormat="1" spans="1:7">
+      <c r="B107" s="9">
+        <v>400221</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G107" s="2"/>
+    </row>
+    <row r="108" s="4" customFormat="1" spans="1:7">
+      <c r="B108" s="9">
+        <v>40023</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="G108" s="2"/>
+    </row>
+    <row r="109" s="4" customFormat="1" spans="1:7">
+      <c r="B109" s="9">
+        <v>40024</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G109" s="2"/>
+    </row>
+    <row r="110" s="4" customFormat="1" spans="1:7">
+      <c r="B110" s="9">
+        <v>40025</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G110" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15480" windowHeight="10815"/>
+    <workbookView windowWidth="11310" windowHeight="10260"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="387">
   <si>
     <t>##var</t>
   </si>
@@ -133,10 +133,7 @@
     <t>Couplet</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>亮出的对子牌型在结算时提供+2倍率</t>
+    <t>亮出的对子牌型在结算时提供+3倍率</t>
   </si>
   <si>
     <t>木制法杖</t>
@@ -145,7 +142,7 @@
     <t>Straight</t>
   </si>
   <si>
-    <t>亮出的顺子牌型在结算时提供+2倍率</t>
+    <t>亮出的顺子牌型在结算时提供+3倍率</t>
   </si>
   <si>
     <t>木制长弓</t>
@@ -154,7 +151,7 @@
     <t>Flush</t>
   </si>
   <si>
-    <t>亮出的同花牌型在结算时提供+2倍率</t>
+    <t>亮出的同花牌型在结算时提供+3倍率</t>
   </si>
   <si>
     <t>木制长矛</t>
@@ -163,7 +160,7 @@
     <t>StraightFlush</t>
   </si>
   <si>
-    <t>亮出的同花顺牌型在结算时提供+2倍率</t>
+    <t>亮出的同花顺牌型在结算时提供+5倍率</t>
   </si>
   <si>
     <t>木制长斧</t>
@@ -172,7 +169,7 @@
     <t>Leopard</t>
   </si>
   <si>
-    <t>亮出的豹子牌型在结算时提供+2倍率</t>
+    <t>亮出的豹子牌型在结算时提供+6倍率</t>
   </si>
   <si>
     <t>木制圆盾</t>
@@ -208,10 +205,10 @@
     <t>EveryRoundEndingGetGoldPer</t>
   </si>
   <si>
-    <t>0.1|5</t>
-  </si>
-  <si>
-    <t>每回合结束后,有10%概率获得5金币</t>
+    <t>0.2|5</t>
+  </si>
+  <si>
+    <t>每回合结束后,有20%概率获得5金币</t>
   </si>
   <si>
     <t>暴击拳套</t>
@@ -232,7 +229,10 @@
     <t>SteppingStone</t>
   </si>
   <si>
-    <t>每当你亮牌时大于场上所有敌人,就永久提供+1攻击力</t>
+    <t>1|1</t>
+  </si>
+  <si>
+    <t>每关首次亮牌大于场上所有敌人时,永久+1攻击力</t>
   </si>
   <si>
     <t>反击拳套</t>
@@ -241,7 +241,7 @@
     <t>BounceDamage</t>
   </si>
   <si>
-    <t>每当你受到伤害时,反弹2点伤害给攻击者</t>
+    <t>每当你受到伤害时,反弹3点伤害给攻击者</t>
   </si>
   <si>
     <t>20001</t>
@@ -253,7 +253,7 @@
     <t>SquarePlateAttack</t>
   </si>
   <si>
-    <t>亮出的每张方片牌在结算时提供+2攻击力</t>
+    <t>亮出的每张方片牌在结算时提供+40攻击力</t>
   </si>
   <si>
     <t>20002</t>
@@ -265,7 +265,7 @@
     <t>SpadesAttack</t>
   </si>
   <si>
-    <t>亮出的每张黑桃牌在结算时提供+2攻击力</t>
+    <t>亮出的每张黑桃牌在结算时提供+40攻击力</t>
   </si>
   <si>
     <t>20003</t>
@@ -277,7 +277,7 @@
     <t>RedHeartAttack</t>
   </si>
   <si>
-    <t>亮出的每张红心牌在结算时提供+2攻击力</t>
+    <t>亮出的每张红心牌在结算时提供+40攻击力</t>
   </si>
   <si>
     <t>20004</t>
@@ -289,7 +289,7 @@
     <t>PlumBlossomAttack</t>
   </si>
   <si>
-    <t>亮出的每张梅花牌在结算时提供+2攻击力</t>
+    <t>亮出的每张梅花牌在结算时提供+40攻击力</t>
   </si>
   <si>
     <t>20005</t>
@@ -301,7 +301,7 @@
     <t>CoupletAttack</t>
   </si>
   <si>
-    <t>亮出的对子牌型在结算时提供+4攻击力</t>
+    <t>亮出的对子牌型在结算时提供+120攻击力</t>
   </si>
   <si>
     <t>20006</t>
@@ -313,7 +313,7 @@
     <t>StraightAttack</t>
   </si>
   <si>
-    <t>亮出的顺子牌型在结算时提供+6攻击力</t>
+    <t>亮出的顺子牌型在结算时提供+150攻击力</t>
   </si>
   <si>
     <t>20007</t>
@@ -325,10 +325,7 @@
     <t>FlushAttack</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>亮出的同花牌型在结算时提供+6攻击力</t>
+    <t>亮出的同花牌型在结算时提供+150攻击力</t>
   </si>
   <si>
     <t>20008</t>
@@ -340,7 +337,7 @@
     <t>StraightFlushAttack</t>
   </si>
   <si>
-    <t>亮出的同花顺牌型在结算时提供+6攻击力</t>
+    <t>亮出的同花顺牌型在结算时提供+300攻击力</t>
   </si>
   <si>
     <t>20009</t>
@@ -352,7 +349,7 @@
     <t>LeopardAttack</t>
   </si>
   <si>
-    <t>亮出的豹子牌型在结算时提供+6攻击力</t>
+    <t>亮出的豹子牌型在结算时提供+300攻击力</t>
   </si>
   <si>
     <t>20010</t>
@@ -406,7 +403,7 @@
     <t>HeadCardAttack</t>
   </si>
   <si>
-    <t>亮出的每张人头牌在结算时提供+2攻击力</t>
+    <t>亮出的每张人头牌在结算时提供+40攻击力</t>
   </si>
   <si>
     <t>20014</t>
@@ -418,7 +415,10 @@
     <t>ProOfHeadCardFunds</t>
   </si>
   <si>
-    <t>亮出的每张人头牌在结算时有20%概率+1金币</t>
+    <t>1|2</t>
+  </si>
+  <si>
+    <t>亮出的每张人头牌在结算时获得2金币</t>
   </si>
   <si>
     <t>20015</t>
@@ -454,7 +454,10 @@
     <t>ConsumeFundsGetAttack</t>
   </si>
   <si>
-    <t>每花费20资金,英雄+1攻击力</t>
+    <t>60|1</t>
+  </si>
+  <si>
+    <t>每花费60金币,英雄永久+1攻击力</t>
   </si>
   <si>
     <t>20018</t>
@@ -514,7 +517,7 @@
     <t>DefeatAllGetGold</t>
   </si>
   <si>
-    <t>每回合结束时,若本回合未造成任何伤害,则获得5金币</t>
+    <t>每回合结束时,若本回合未造成任何伤害,则获得10金币</t>
   </si>
   <si>
     <t>20023</t>
@@ -526,7 +529,7 @@
     <t>IronRiceBowl</t>
   </si>
   <si>
-    <t>亮牌后无论胜负,均可获得1金币</t>
+    <t>亮牌后无论胜负,均可获得2金币</t>
   </si>
   <si>
     <t>20024</t>
@@ -538,7 +541,7 @@
     <t>EveryRoundGetHpMax</t>
   </si>
   <si>
-    <t>每回合开始时,永久+2血量上限</t>
+    <t>每回合开始时,永久+1血量上限</t>
   </si>
   <si>
     <t>20025</t>
@@ -589,10 +592,10 @@
     <t>Interest</t>
   </si>
   <si>
-    <t>10|1</t>
-  </si>
-  <si>
-    <t>每拥有10金币,在回合结束后就会获得1金币</t>
+    <t>15|1|10</t>
+  </si>
+  <si>
+    <t>每通过1关时,每拥有15金币获得1金币,每关至多10金币</t>
   </si>
   <si>
     <t>20029</t>
@@ -619,7 +622,7 @@
     <t>BloodSucking</t>
   </si>
   <si>
-    <t>造成伤害时,获得2%的生命窃取</t>
+    <t>造成伤害时,获得5%的生命窃取</t>
   </si>
   <si>
     <t>30002</t>
@@ -631,7 +634,7 @@
     <t>DoubleCardAttack</t>
   </si>
   <si>
-    <t>亮出的牌点数提供的攻击力加成翻倍</t>
+    <t>亮出的牌点数提供的攻击力加成×3</t>
   </si>
   <si>
     <t>30003</t>
@@ -643,7 +646,7 @@
     <t>TheSwordOfVictory</t>
   </si>
   <si>
-    <t>结算伤害时,会将留在手牌上最大的牌点数转化为额外攻击力</t>
+    <t>结算伤害时,将留在手牌上最大的牌点数×4转化为额外攻击力</t>
   </si>
   <si>
     <t>30004</t>
@@ -691,7 +694,7 @@
     <t>SpecialEightCard</t>
   </si>
   <si>
-    <t>亮出的每张8在结算时提供+6攻击力</t>
+    <t>亮出的每张8在结算时提供+200攻击力</t>
   </si>
   <si>
     <t>30008</t>
@@ -703,7 +706,7 @@
     <t>EvenNumberCard</t>
   </si>
   <si>
-    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+2倍率</t>
+    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+6倍率</t>
   </si>
   <si>
     <t>30009</t>
@@ -715,7 +718,7 @@
     <t>OddNumberCard</t>
   </si>
   <si>
-    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+2倍率</t>
+    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+6倍率</t>
   </si>
   <si>
     <t>30010</t>
@@ -727,7 +730,7 @@
     <t>HeadCard</t>
   </si>
   <si>
-    <t>亮出的每张人头牌在结算时提供+3倍率</t>
+    <t>亮出的每张人头牌在结算时提供+5倍率</t>
   </si>
   <si>
     <t>30011</t>
@@ -751,7 +754,10 @@
     <t>EveryCardAttackForever</t>
   </si>
   <si>
-    <t>亮出的每张牌的点数在结算时会使其提供的攻击力永久+1</t>
+    <t>1|30</t>
+  </si>
+  <si>
+    <t>每回合首次亮牌时,随机1张亮出牌点数的攻击力永久+1,至多累计+30</t>
   </si>
   <si>
     <t>30013</t>
@@ -763,7 +769,7 @@
     <t>SpecialNineCard</t>
   </si>
   <si>
-    <t>亮出的每张9在结算时提供10金币</t>
+    <t>亮出的每张9在结算时提供15金币</t>
   </si>
   <si>
     <t>30014</t>
@@ -775,10 +781,10 @@
     <t>DefeatAllGetGoldAndReplyHp</t>
   </si>
   <si>
-    <t>10|15</t>
-  </si>
-  <si>
-    <t>如果本回合牌型小于所有敌人,则立即获得10金币并回复15点生命值</t>
+    <t>15|20</t>
+  </si>
+  <si>
+    <t>如果本回合牌型小于所有敌人,则立即获得15金币并回复20点生命值</t>
   </si>
   <si>
     <t>30015</t>
@@ -790,7 +796,7 @@
     <t>MissFirstDamage</t>
   </si>
   <si>
-    <t>每回合受到的第1次伤害完全免疫</t>
+    <t>每关受到的第1次伤害完全免疫</t>
   </si>
   <si>
     <t>30016</t>
@@ -841,7 +847,10 @@
     <t>NoKillMonsterGetMagnification</t>
   </si>
   <si>
-    <t>每回合结束后,若本回合你未击杀任何敌人,则永久提供+0.5倍率</t>
+    <t>0.2|6</t>
+  </si>
+  <si>
+    <t>每回合结束后,若本回合你未击杀任何敌人,则永久提供+0.2倍率,至多+6</t>
   </si>
   <si>
     <t>30020</t>
@@ -865,151 +874,154 @@
     <t>NobleBadge</t>
   </si>
   <si>
+    <t>0.5|15</t>
+  </si>
+  <si>
+    <t>每关开始时,若生命值高于50%,获得15金币</t>
+  </si>
+  <si>
+    <t>30022</t>
+  </si>
+  <si>
+    <t>陷阱</t>
+  </si>
+  <si>
+    <t>Trap</t>
+  </si>
+  <si>
+    <t>本局内,自己曾经输过的敌人在造成伤害时,伤害-20%</t>
+  </si>
+  <si>
+    <t>30023</t>
+  </si>
+  <si>
+    <t>好运来</t>
+  </si>
+  <si>
+    <t>DownGrade</t>
+  </si>
+  <si>
+    <t>0.15|1</t>
+  </si>
+  <si>
+    <t>每回合有15%概率使本回合所有敌人亮出的牌型自动降1级</t>
+  </si>
+  <si>
+    <t>30024</t>
+  </si>
+  <si>
+    <t>入场券</t>
+  </si>
+  <si>
+    <t>AdmissionTicket</t>
+  </si>
+  <si>
+    <t>每关开始时,对所有敌人造成2次自身攻击力的伤害</t>
+  </si>
+  <si>
+    <t>30025</t>
+  </si>
+  <si>
+    <t>条约</t>
+  </si>
+  <si>
+    <t>MonsterDamage</t>
+  </si>
+  <si>
+    <t>所有敌人造成的伤害降低30%</t>
+  </si>
+  <si>
+    <t>SpecialTwoThreeFive</t>
+  </si>
+  <si>
+    <t>散排235牌型等同于豹子牌型,并且可以战胜所有牌型</t>
+  </si>
+  <si>
+    <t>奢华沙发</t>
+  </si>
+  <si>
+    <t>获得500点生命值上限</t>
+  </si>
+  <si>
+    <t>老花眼</t>
+  </si>
+  <si>
+    <t>SpecialFlush</t>
+  </si>
+  <si>
+    <t>红桃和方片视为同一花色,黑桃和梅花视为同一花色</t>
+  </si>
+  <si>
+    <t>周星星</t>
+  </si>
+  <si>
+    <t>RubbingCardsNum</t>
+  </si>
+  <si>
+    <t>每回合搓牌次数+1</t>
+  </si>
+  <si>
+    <t>穷途末路</t>
+  </si>
+  <si>
+    <t>NoSkill</t>
+  </si>
+  <si>
+    <t>结算时,所有技能都无剩余使用次数,则提供+12倍率</t>
+  </si>
+  <si>
+    <t>收藏夹</t>
+  </si>
+  <si>
+    <t>EveryRelic</t>
+  </si>
+  <si>
+    <t>每有1个收藏品,结算时提供+1倍率</t>
+  </si>
+  <si>
+    <t>奢侈品</t>
+  </si>
+  <si>
+    <t>NoUseRubbingEveryRubbingNum</t>
+  </si>
+  <si>
+    <t>结算时,若未使用过搓牌,每个搓牌次数提供+3倍率</t>
+  </si>
+  <si>
+    <t>近视眼</t>
+  </si>
+  <si>
+    <t>AllCardIsHeadCard</t>
+  </si>
+  <si>
+    <t>所有牌均视为人头牌</t>
+  </si>
+  <si>
+    <t>顶尖学者</t>
+  </si>
+  <si>
+    <t>SpecialACard</t>
+  </si>
+  <si>
+    <t>亮出的每张A在结算时提供+8倍率</t>
+  </si>
+  <si>
+    <t>ACardAttack</t>
+  </si>
+  <si>
+    <t>亮出的每张A在结算时提供+400攻击力</t>
+  </si>
+  <si>
+    <t>老千</t>
+  </si>
+  <si>
+    <t>AccumulatedNumOfCardType</t>
+  </si>
+  <si>
     <t>0.5|10</t>
   </si>
   <si>
-    <t>每回合开始时,若生命值高于50%,获得10金币</t>
-  </si>
-  <si>
-    <t>30022</t>
-  </si>
-  <si>
-    <t>陷阱</t>
-  </si>
-  <si>
-    <t>Trap</t>
-  </si>
-  <si>
-    <t>本局内,自己曾经输过的敌人在造成伤害时,伤害-20%</t>
-  </si>
-  <si>
-    <t>30023</t>
-  </si>
-  <si>
-    <t>好运来</t>
-  </si>
-  <si>
-    <t>DownGrade</t>
-  </si>
-  <si>
-    <t>0.15|1</t>
-  </si>
-  <si>
-    <t>每回合有15%概率使本回合所有敌人亮出的牌型自动降1级</t>
-  </si>
-  <si>
-    <t>30024</t>
-  </si>
-  <si>
-    <t>入场券</t>
-  </si>
-  <si>
-    <t>AdmissionTicket</t>
-  </si>
-  <si>
-    <t>每回合开始时,对所有敌人造成1次自身攻击力的伤害</t>
-  </si>
-  <si>
-    <t>30025</t>
-  </si>
-  <si>
-    <t>条约</t>
-  </si>
-  <si>
-    <t>MonsterDamage</t>
-  </si>
-  <si>
-    <t>所有敌人造成的伤害降低30%</t>
-  </si>
-  <si>
-    <t>SpecialTwoThreeFive</t>
-  </si>
-  <si>
-    <t>散排235牌型等同于豹子牌型,并且可以战胜所有牌型</t>
-  </si>
-  <si>
-    <t>奢华沙发</t>
-  </si>
-  <si>
-    <t>获得500点生命值上限</t>
-  </si>
-  <si>
-    <t>老花眼</t>
-  </si>
-  <si>
-    <t>SpecialFlush</t>
-  </si>
-  <si>
-    <t>红桃和方片视为同一花色,黑桃和梅花视为同一花色</t>
-  </si>
-  <si>
-    <t>周星星</t>
-  </si>
-  <si>
-    <t>RubbingCardsNum</t>
-  </si>
-  <si>
-    <t>每回合搓牌次数+1</t>
-  </si>
-  <si>
-    <t>穷途末路</t>
-  </si>
-  <si>
-    <t>NoSkill</t>
-  </si>
-  <si>
-    <t>结算时,所有技能都无剩余使用次数,则提供+15倍率</t>
-  </si>
-  <si>
-    <t>收藏夹</t>
-  </si>
-  <si>
-    <t>EveryRelic</t>
-  </si>
-  <si>
-    <t>每有1个收藏品,结算时提供+5倍率</t>
-  </si>
-  <si>
-    <t>奢侈品</t>
-  </si>
-  <si>
-    <t>NoUseRubbingEveryRubbingNum</t>
-  </si>
-  <si>
-    <t>结算时,若未使用过搓牌,每个搓牌次数提供+5倍率</t>
-  </si>
-  <si>
-    <t>近视眼</t>
-  </si>
-  <si>
-    <t>AllCardIsHeadCard</t>
-  </si>
-  <si>
-    <t>所有牌均视为人头牌</t>
-  </si>
-  <si>
-    <t>顶尖学者</t>
-  </si>
-  <si>
-    <t>SpecialACard</t>
-  </si>
-  <si>
-    <t>亮出的每张A在结算时提供+5倍率</t>
-  </si>
-  <si>
-    <t>ACardAttack</t>
-  </si>
-  <si>
-    <t>亮出的每张A在结算时提供+5攻击力</t>
-  </si>
-  <si>
-    <t>老千</t>
-  </si>
-  <si>
-    <t>AccumulatedNumOfCardType</t>
-  </si>
-  <si>
-    <t>亮牌时,将该牌型在本局内亮出过的次数来提供倍率</t>
+    <t>亮牌时,该牌型本局内每重复亮出1次提供+0.5倍率,至多+10</t>
   </si>
   <si>
     <t>天使</t>
@@ -1027,7 +1039,7 @@
     <t>每回合失去2次搓牌次数</t>
   </si>
   <si>
-    <t>结算时提供+20倍率</t>
+    <t>结算时提供+10倍率</t>
   </si>
   <si>
     <t>老搓家</t>
@@ -1036,7 +1048,7 @@
     <t>RubbingCardRelic</t>
   </si>
   <si>
-    <t>每使用1次搓牌,结算时该收藏品永久提供+0.5倍率</t>
+    <t>每使用1次搓牌,结算时该收藏品永久提供+0.1倍率</t>
   </si>
   <si>
     <t>幸运七</t>
@@ -1045,7 +1057,7 @@
     <t>SpecialSevenCardPro</t>
   </si>
   <si>
-    <t>亮出的每张7结算时有7%概率提供攻击力和倍率</t>
+    <t>亮出的每张7结算时有25%概率提供攻击力和倍率</t>
   </si>
   <si>
     <t>SpecialSevenCardAttack</t>
@@ -1072,9 +1084,6 @@
     <t>MissGetDamage</t>
   </si>
   <si>
-    <t>1|2</t>
-  </si>
-  <si>
     <t>闪避成功时会对敌人造成1次自身攻击力200%的伤害</t>
   </si>
   <si>
@@ -1156,9 +1165,6 @@
     <t>CriticalAoe</t>
   </si>
   <si>
-    <t>1|1</t>
-  </si>
-  <si>
     <t>触发暴击时会对其他敌人造成1次自身攻击力100%的伤害</t>
   </si>
   <si>
@@ -1177,10 +1183,7 @@
     <t>DamageTurnToGold</t>
   </si>
   <si>
-    <t>0.02</t>
-  </si>
-  <si>
-    <t>每回合结束后,本回合自身总伤害输出的2%转化为金币</t>
+    <t>每回合结束后,本回合自身总伤害输出的15%转化为金币</t>
   </si>
   <si>
     <t>差距胶囊</t>
@@ -1189,10 +1192,7 @@
     <t>GapDamage</t>
   </si>
   <si>
-    <t>1|0.15</t>
-  </si>
-  <si>
-    <t>比牌时,你的牌型与对方牌型每相隔1级,则造成/承受的伤害对应提高/降低15%</t>
+    <t>比牌时,你的牌型与对方牌型每相隔1级,则造成/承受的伤害对应提高/降低20%</t>
   </si>
 </sst>
 </file>
@@ -1358,24 +1358,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1675,189 +1663,165 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2214,105 +2178,103 @@
   <dimension ref="A1:G110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="5.75833333333333" style="5" customWidth="1"/>
-    <col min="2" max="2" width="7.49166666666667" style="5" customWidth="1"/>
-    <col min="3" max="3" width="8.475" style="6" customWidth="1"/>
-    <col min="4" max="4" width="21.8416666666667" style="6" customWidth="1"/>
-    <col min="5" max="5" width="8.36666666666667" style="5" customWidth="1"/>
-    <col min="6" max="6" width="20.325" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="5.75833333333333" style="3" customWidth="1"/>
+    <col min="2" max="2" width="7.49166666666667" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.475" style="4" customWidth="1"/>
+    <col min="4" max="4" width="21.8416666666667" style="4" customWidth="1"/>
+    <col min="5" max="5" width="8.36666666666667" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20.325" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:6">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6">
+    <row r="5" spans="1:6">
+      <c r="B5" s="4">
         <v>10001</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>1</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:6">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6">
+    <row r="6" spans="1:6">
+      <c r="B6" s="4">
         <v>10002</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <v>1</v>
       </c>
       <c r="F6" t="s">
@@ -2320,52 +2282,50 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <v>10003</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="1:6">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6">
+    <row r="8" spans="1:6">
+      <c r="B8" s="4">
         <v>10004</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>1</v>
       </c>
       <c r="F8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="1:6">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6">
+    <row r="9" spans="1:6">
+      <c r="B9" s="4">
         <v>10005</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>1</v>
       </c>
       <c r="F9" t="s">
@@ -2373,229 +2333,223 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="B10" s="6">
+      <c r="B10" s="4">
         <v>10006</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="3">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
         <v>33</v>
       </c>
-      <c r="F10" t="s">
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" s="4">
+        <v>10007</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" customFormat="1" spans="1:6">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6">
-        <v>10007</v>
-      </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" t="s">
         <v>35</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" s="3">
+        <v>3</v>
+      </c>
+      <c r="F11" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" t="s">
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" s="4">
+        <v>10008</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="12" customFormat="1" spans="1:6">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6">
-        <v>10008</v>
-      </c>
-      <c r="C12" s="6" t="s">
+      <c r="D12" t="s">
         <v>38</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" s="3">
+        <v>3</v>
+      </c>
+      <c r="F12" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" t="s">
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" s="4">
+        <v>10009</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="13" customFormat="1" spans="1:6">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6">
-        <v>10009</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="D13" t="s">
         <v>41</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" s="3">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" t="s">
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" s="4">
+        <v>10010</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="14" customFormat="1" spans="1:6">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6">
-        <v>10010</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="D14" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="E14" s="3">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" t="s">
+    </row>
+    <row r="15" customFormat="1" spans="1:6">
+      <c r="A15" s="3"/>
+      <c r="B15" s="4">
+        <v>10011</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:6">
-      <c r="A15" s="7"/>
-      <c r="B15" s="8">
-        <v>10011</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F15" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="8">
-        <v>-1</v>
-      </c>
-      <c r="F15" t="s">
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:6">
+      <c r="A16" s="2"/>
+      <c r="B16" s="5">
+        <v>10012</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:6">
-      <c r="A16" s="4"/>
-      <c r="B16" s="9">
-        <v>10012</v>
-      </c>
-      <c r="C16" s="10" t="s">
+      <c r="D16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="9">
-        <v>1</v>
-      </c>
-      <c r="F16" s="10" t="s">
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:6">
+      <c r="A17" s="2"/>
+      <c r="B17" s="5">
+        <v>10013</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:6">
-      <c r="A17" s="4"/>
-      <c r="B17" s="9">
-        <v>10013</v>
-      </c>
-      <c r="C17" s="10" t="s">
+      <c r="D17" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="E17" s="5">
+        <v>2</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E17" s="9">
-        <v>2</v>
-      </c>
-      <c r="F17" s="10" t="s">
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:6">
+      <c r="A18" s="2"/>
+      <c r="B18" s="5">
+        <v>10014</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:6">
-      <c r="A18" s="4"/>
-      <c r="B18" s="9">
-        <v>10014</v>
-      </c>
-      <c r="C18" s="10" t="s">
+      <c r="D18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="F18" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="10" t="s">
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:6">
+      <c r="A19" s="2"/>
+      <c r="B19" s="5">
+        <v>10015</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:6">
-      <c r="A19" s="4"/>
-      <c r="B19" s="9">
-        <v>10015</v>
-      </c>
-      <c r="C19" s="10" t="s">
+      <c r="D19" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="F19" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="10" t="s">
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:6">
+      <c r="A20" s="2"/>
+      <c r="B20" s="5">
+        <v>10016</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:6">
-      <c r="A20" s="4"/>
-      <c r="B20" s="9">
-        <v>10016</v>
-      </c>
-      <c r="C20" s="10" t="s">
+      <c r="D20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="9">
-        <v>1</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:6">
-      <c r="A21" s="4"/>
-      <c r="B21" s="9">
+    <row r="21" s="1" customFormat="1" spans="1:6">
+      <c r="A21" s="2"/>
+      <c r="B21" s="5">
         <v>10017</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="9">
-        <v>2</v>
-      </c>
-      <c r="F21" s="2" t="s">
+      <c r="E21" s="5">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="22" customFormat="1" spans="1:6">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
+    <row r="22" spans="1:6">
+      <c r="B22" s="4"/>
       <c r="D22"/>
-      <c r="E22" s="6"/>
+      <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:6">
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C23" t="s">
@@ -2604,16 +2558,15 @@
       <c r="D23" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>33</v>
+      <c r="E23" s="3">
+        <v>40</v>
       </c>
       <c r="F23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="24" customFormat="1" spans="1:6">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5" t="s">
+    <row r="24" spans="1:6">
+      <c r="B24" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C24" t="s">
@@ -2622,16 +2575,15 @@
       <c r="D24" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="6">
-        <v>2</v>
+      <c r="E24" s="4">
+        <v>40</v>
       </c>
       <c r="F24" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="25" customFormat="1" spans="1:6">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5" t="s">
+    <row r="25" spans="1:6">
+      <c r="B25" s="3" t="s">
         <v>78</v>
       </c>
       <c r="C25" t="s">
@@ -2640,1502 +2592,1471 @@
       <c r="D25" t="s">
         <v>80</v>
       </c>
-      <c r="E25" s="6">
-        <v>2</v>
+      <c r="E25" s="4">
+        <v>40</v>
       </c>
       <c r="F25" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="4" t="s">
         <v>83</v>
       </c>
       <c r="D26" t="s">
         <v>84</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>33</v>
+      <c r="E26" s="3">
+        <v>40</v>
       </c>
       <c r="F26" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="27" customFormat="1" spans="1:6">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5" t="s">
+    <row r="27" spans="1:6">
+      <c r="B27" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="6">
-        <v>4</v>
+      <c r="E27" s="4">
+        <v>120</v>
       </c>
       <c r="F27" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="28" customFormat="1" spans="1:6">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5" t="s">
+    <row r="28" spans="1:6">
+      <c r="B28" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="4" t="s">
         <v>91</v>
       </c>
       <c r="D28" t="s">
         <v>92</v>
       </c>
-      <c r="E28" s="6">
-        <v>6</v>
+      <c r="E28" s="4">
+        <v>150</v>
       </c>
       <c r="F28" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="4" t="s">
         <v>95</v>
       </c>
       <c r="D29" t="s">
         <v>96</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="3">
+        <v>150</v>
+      </c>
+      <c r="F29" t="s">
         <v>97</v>
       </c>
-      <c r="F29" t="s">
+    </row>
+    <row r="30" spans="1:6">
+      <c r="B30" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="30" customFormat="1" spans="1:6">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="D30" t="s">
         <v>100</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" s="4">
+        <v>300</v>
+      </c>
+      <c r="F30" t="s">
         <v>101</v>
       </c>
-      <c r="E30" s="6">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
+    </row>
+    <row r="31" spans="1:6">
+      <c r="B31" s="3" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="31" customFormat="1" spans="1:6">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="D31" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="E31" s="4">
+        <v>300</v>
+      </c>
+      <c r="F31" t="s">
         <v>105</v>
       </c>
-      <c r="E31" s="6">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
+    </row>
+    <row r="32" spans="1:6">
+      <c r="B32" s="3" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="32" customFormat="1" spans="1:6">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="D32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E32" s="4">
+        <v>2</v>
+      </c>
+      <c r="F32" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E32" s="6">
-        <v>2</v>
-      </c>
-      <c r="F32" t="s">
+    </row>
+    <row r="33" customFormat="1" spans="1:6">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="33" s="3" customFormat="1" spans="1:6">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12" t="s">
+      <c r="C33" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="D33" s="13" t="s">
+      <c r="E33" s="4">
+        <v>30</v>
+      </c>
+      <c r="F33" t="s">
         <v>111</v>
       </c>
-      <c r="E33" s="13">
-        <v>30</v>
-      </c>
-      <c r="F33" s="3" t="s">
+    </row>
+    <row r="34" spans="1:6">
+      <c r="B34" s="3" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="34" customFormat="1" spans="1:6">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5" t="s">
+      <c r="C34" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="D34" t="s">
         <v>114</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" s="4">
+        <v>50</v>
+      </c>
+      <c r="F34" t="s">
         <v>115</v>
       </c>
-      <c r="E34" s="6">
-        <v>50</v>
-      </c>
-      <c r="F34" t="s">
+    </row>
+    <row r="35" spans="1:6">
+      <c r="B35" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="35" customFormat="1" spans="1:6">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="D35" t="s">
         <v>118</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" s="4">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="6">
-        <v>1</v>
-      </c>
-      <c r="F35" t="s">
+    </row>
+    <row r="36" customFormat="1" spans="1:6">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="36" s="3" customFormat="1" spans="1:6">
-      <c r="A36" s="12"/>
-      <c r="B36" s="12" t="s">
+      <c r="C36" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="D36" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="E36" s="4">
+        <v>40</v>
+      </c>
+      <c r="F36" t="s">
         <v>123</v>
       </c>
-      <c r="E36" s="13">
-        <v>2</v>
-      </c>
-      <c r="F36" t="s">
+    </row>
+    <row r="37" spans="1:6">
+      <c r="B37" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="37" customFormat="1" spans="1:6">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="D37" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="E37" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="E37" s="6">
-        <v>0.2</v>
       </c>
       <c r="F37" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="38" customFormat="1" spans="1:6">
-      <c r="A38" s="5"/>
-      <c r="B38" s="5" t="s">
+    <row r="38" spans="1:6">
+      <c r="B38" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="4" t="s">
         <v>130</v>
       </c>
       <c r="D38" t="s">
         <v>131</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="4">
         <v>2</v>
       </c>
       <c r="F38" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="39" customFormat="1" spans="1:6">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5" t="s">
+    <row r="39" spans="1:6">
+      <c r="B39" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="4" t="s">
         <v>134</v>
       </c>
       <c r="D39" t="s">
         <v>135</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="4">
         <v>2</v>
       </c>
       <c r="F39" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="40" customFormat="1" spans="1:6">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5" t="s">
+    <row r="40" spans="1:6">
+      <c r="B40" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="4" t="s">
         <v>138</v>
       </c>
       <c r="D40" t="s">
         <v>139</v>
       </c>
-      <c r="E40" s="6">
-        <v>20</v>
+      <c r="E40" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="F40" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" spans="1:6">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C41" s="6" t="s">
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="3" t="s">
         <v>142</v>
       </c>
+      <c r="C41" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="D41" t="s">
-        <v>143</v>
-      </c>
-      <c r="E41" s="6">
+        <v>144</v>
+      </c>
+      <c r="E41" s="4">
         <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="42" s="2" customFormat="1" spans="1:6">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C42" s="10" t="s">
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:6">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="C42" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E42" s="9">
+      <c r="D42" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E42" s="5">
         <v>0.25</v>
       </c>
-      <c r="F42" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" spans="1:6">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4" t="s">
+      <c r="F42" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C43" s="10" t="s">
+    </row>
+    <row r="43" s="1" customFormat="1" spans="1:6">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="C43" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E43" s="9">
+      <c r="D43" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E43" s="5">
         <v>1</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="44" s="2" customFormat="1" spans="1:6">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4" t="s">
+      <c r="F43" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C44" s="10" t="s">
+    </row>
+    <row r="44" s="1" customFormat="1" spans="1:6">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="C44" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="E44" s="9">
+      <c r="D44" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E44" s="5">
         <v>3</v>
       </c>
-      <c r="F44" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" spans="1:6">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4" t="s">
+      <c r="F44" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C45" s="10" t="s">
+    </row>
+    <row r="45" s="1" customFormat="1" spans="1:6">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="C45" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E45" s="9">
+      <c r="D45" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E45" s="5">
+        <v>10</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" spans="1:6">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E46" s="5">
+        <v>2</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" spans="1:6">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E47" s="5">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" spans="1:6">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E48" s="5">
+        <v>4</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" spans="1:6">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" spans="1:6">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" spans="1:6">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" spans="1:6">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="B53" s="4"/>
+      <c r="E53" s="4"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="B54" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C54" t="s">
+        <v>194</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E54" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="F54" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="B55" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C55" t="s">
+        <v>198</v>
+      </c>
+      <c r="D55" t="s">
+        <v>199</v>
+      </c>
+      <c r="E55" s="4">
+        <v>3</v>
+      </c>
+      <c r="F55" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="B56" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C56" t="s">
+        <v>202</v>
+      </c>
+      <c r="D56" t="s">
+        <v>203</v>
+      </c>
+      <c r="E56" s="4">
+        <v>4</v>
+      </c>
+      <c r="F56" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="B57" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C57" t="s">
+        <v>206</v>
+      </c>
+      <c r="D57" t="s">
+        <v>207</v>
+      </c>
+      <c r="E57" s="4">
+        <v>1</v>
+      </c>
+      <c r="F57" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="B58" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C58" t="s">
+        <v>210</v>
+      </c>
+      <c r="D58" t="s">
+        <v>211</v>
+      </c>
+      <c r="E58" s="4">
+        <v>1</v>
+      </c>
+      <c r="F58" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="B59" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C59" t="s">
+        <v>214</v>
+      </c>
+      <c r="D59" t="s">
+        <v>215</v>
+      </c>
+      <c r="E59" s="4">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="B60" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C60" t="s">
+        <v>218</v>
+      </c>
+      <c r="D60" t="s">
+        <v>219</v>
+      </c>
+      <c r="E60" s="4">
+        <v>200</v>
+      </c>
+      <c r="F60" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="B61" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C61" t="s">
+        <v>222</v>
+      </c>
+      <c r="D61" t="s">
+        <v>223</v>
+      </c>
+      <c r="E61" s="4">
+        <v>6</v>
+      </c>
+      <c r="F61" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="B62" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C62" t="s">
+        <v>226</v>
+      </c>
+      <c r="D62" t="s">
+        <v>227</v>
+      </c>
+      <c r="E62" s="4">
+        <v>6</v>
+      </c>
+      <c r="F62" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="B63" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C63" t="s">
+        <v>230</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E63" s="4">
         <v>5</v>
       </c>
-      <c r="F45" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" spans="1:6">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E46" s="9">
+      <c r="F63" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="B64" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C64" t="s">
+        <v>234</v>
+      </c>
+      <c r="D64" t="s">
+        <v>235</v>
+      </c>
+      <c r="E64" s="4">
+        <v>5</v>
+      </c>
+      <c r="F64" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="B65" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C65" t="s">
+        <v>238</v>
+      </c>
+      <c r="D65" t="s">
+        <v>239</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F65" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="B66" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C66" t="s">
+        <v>243</v>
+      </c>
+      <c r="D66" t="s">
+        <v>244</v>
+      </c>
+      <c r="E66" s="4">
+        <v>15</v>
+      </c>
+      <c r="F66" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="1" spans="1:6">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" spans="1:6">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E68" s="5">
         <v>1</v>
       </c>
-      <c r="F46" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" spans="1:6">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E47" s="9">
+      <c r="F68" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" spans="1:6">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="1" spans="1:6">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E70" s="5">
+        <v>3</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="71" s="1" customFormat="1" spans="1:6">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E71" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="72" s="1" customFormat="1" spans="1:6">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" spans="1:6">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E73" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="74" s="1" customFormat="1" spans="1:6">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" spans="1:6">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E75" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="76" s="1" customFormat="1" spans="1:6">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="77" s="1" customFormat="1" spans="1:6">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E77" s="5">
         <v>2</v>
       </c>
-      <c r="F47" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" spans="1:6">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E48" s="9"/>
-      <c r="F48" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="49" s="2" customFormat="1" spans="1:6">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="50" s="2" customFormat="1" spans="1:6">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="51" s="2" customFormat="1" spans="1:6">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="52" s="2" customFormat="1" spans="1:6">
-      <c r="A52" s="4"/>
-      <c r="B52" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" spans="1:6">
-      <c r="A53" s="5"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="E53" s="6"/>
-    </row>
-    <row r="54" customFormat="1" spans="1:6">
-      <c r="A54" s="5"/>
-      <c r="B54" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="C54" t="s">
-        <v>193</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="E54" s="6">
-        <v>0.02</v>
-      </c>
-      <c r="F54" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="55" customFormat="1" spans="1:6">
-      <c r="A55" s="5"/>
-      <c r="B55" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="C55" t="s">
-        <v>197</v>
-      </c>
-      <c r="D55" t="s">
-        <v>198</v>
-      </c>
-      <c r="E55" s="6">
+      <c r="F77" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="78" s="1" customFormat="1" spans="1:6">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E78" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="B79" s="4"/>
+      <c r="E79" s="4"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="B80" s="4">
+        <v>40001</v>
+      </c>
+      <c r="C80" s="4">
+        <v>235</v>
+      </c>
+      <c r="D80" t="s">
+        <v>299</v>
+      </c>
+      <c r="E80" s="4">
         <v>1</v>
       </c>
-      <c r="F55" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="56" customFormat="1" spans="1:6">
-      <c r="A56" s="5"/>
-      <c r="B56" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C56" t="s">
-        <v>201</v>
-      </c>
-      <c r="D56" t="s">
-        <v>202</v>
-      </c>
-      <c r="E56" s="6"/>
-      <c r="F56" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="57" customFormat="1" spans="1:6">
-      <c r="A57" s="5"/>
-      <c r="B57" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="C57" t="s">
-        <v>205</v>
-      </c>
-      <c r="D57" t="s">
-        <v>206</v>
-      </c>
-      <c r="E57" s="6">
+      <c r="F80" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="81" customFormat="1" spans="1:6">
+      <c r="A81" s="3"/>
+      <c r="B81" s="4">
+        <v>40002</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E81" s="4">
+        <v>500</v>
+      </c>
+      <c r="F81" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="4">
+        <v>40003</v>
+      </c>
+      <c r="C82" t="s">
+        <v>303</v>
+      </c>
+      <c r="D82" t="s">
+        <v>304</v>
+      </c>
+      <c r="E82" s="4">
         <v>1</v>
       </c>
-      <c r="F57" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="58" customFormat="1" spans="1:6">
-      <c r="A58" s="5"/>
-      <c r="B58" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C58" t="s">
-        <v>209</v>
-      </c>
-      <c r="D58" t="s">
-        <v>210</v>
-      </c>
-      <c r="E58" s="6">
+      <c r="F82" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="B83" s="4">
+        <v>40004</v>
+      </c>
+      <c r="C83" t="s">
+        <v>306</v>
+      </c>
+      <c r="D83" t="s">
+        <v>307</v>
+      </c>
+      <c r="E83" s="4">
         <v>1</v>
       </c>
-      <c r="F58" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="59" customFormat="1" spans="1:6">
-      <c r="A59" s="5"/>
-      <c r="B59" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C59" t="s">
-        <v>213</v>
-      </c>
-      <c r="D59" t="s">
-        <v>214</v>
-      </c>
-      <c r="E59" s="6">
+      <c r="F83" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="B84" s="4">
+        <v>40005</v>
+      </c>
+      <c r="C84" t="s">
+        <v>309</v>
+      </c>
+      <c r="D84" t="s">
+        <v>310</v>
+      </c>
+      <c r="E84" s="4">
+        <v>12</v>
+      </c>
+      <c r="F84" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="B85" s="4">
+        <v>40006</v>
+      </c>
+      <c r="C85" t="s">
+        <v>312</v>
+      </c>
+      <c r="D85" t="s">
+        <v>313</v>
+      </c>
+      <c r="E85" s="4">
         <v>1</v>
       </c>
-      <c r="F59" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="60" customFormat="1" spans="1:6">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="C60" t="s">
-        <v>217</v>
-      </c>
-      <c r="D60" t="s">
-        <v>218</v>
-      </c>
-      <c r="E60" s="6">
-        <v>6</v>
-      </c>
-      <c r="F60" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="61" customFormat="1" spans="1:6">
-      <c r="A61" s="5"/>
-      <c r="B61" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C61" t="s">
-        <v>221</v>
-      </c>
-      <c r="D61" t="s">
-        <v>222</v>
-      </c>
-      <c r="E61" s="6">
+      <c r="F85" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="4">
+        <v>40007</v>
+      </c>
+      <c r="C86" t="s">
+        <v>315</v>
+      </c>
+      <c r="D86" t="s">
+        <v>316</v>
+      </c>
+      <c r="E86" s="4">
+        <v>3</v>
+      </c>
+      <c r="F86" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="4">
+        <v>40008</v>
+      </c>
+      <c r="C87" t="s">
+        <v>318</v>
+      </c>
+      <c r="D87" t="s">
+        <v>319</v>
+      </c>
+      <c r="E87" s="4">
+        <v>1</v>
+      </c>
+      <c r="F87" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="B88" s="4">
+        <v>40009</v>
+      </c>
+      <c r="C88" t="s">
+        <v>321</v>
+      </c>
+      <c r="D88" t="s">
+        <v>322</v>
+      </c>
+      <c r="E88" s="4">
+        <v>8</v>
+      </c>
+      <c r="F88" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="89" customFormat="1" spans="1:6">
+      <c r="A89" s="3"/>
+      <c r="B89" s="4">
+        <v>400091</v>
+      </c>
+      <c r="C89" t="s">
+        <v>321</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="E89" s="4">
+        <v>400</v>
+      </c>
+      <c r="F89" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="B90" s="4">
+        <v>40010</v>
+      </c>
+      <c r="C90" t="s">
+        <v>326</v>
+      </c>
+      <c r="D90" t="s">
+        <v>327</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="F90" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="4">
+        <v>40011</v>
+      </c>
+      <c r="C91" t="s">
+        <v>330</v>
+      </c>
+      <c r="D91" t="s">
+        <v>331</v>
+      </c>
+      <c r="E91" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="F91" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="4">
+        <v>40012</v>
+      </c>
+      <c r="C92" t="s">
+        <v>333</v>
+      </c>
+      <c r="D92" t="s">
+        <v>307</v>
+      </c>
+      <c r="E92" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F92" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="B93" s="4">
+        <v>400121</v>
+      </c>
+      <c r="C93" t="s">
+        <v>333</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E93" s="4">
+        <v>10</v>
+      </c>
+      <c r="F93" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="B94" s="4">
+        <v>40013</v>
+      </c>
+      <c r="C94" t="s">
+        <v>336</v>
+      </c>
+      <c r="D94" t="s">
+        <v>337</v>
+      </c>
+      <c r="E94" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="F94" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="B95" s="4">
+        <v>40014</v>
+      </c>
+      <c r="C95" t="s">
+        <v>339</v>
+      </c>
+      <c r="D95" t="s">
+        <v>340</v>
+      </c>
+      <c r="E95" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="F95" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="B96" s="4">
+        <v>400141</v>
+      </c>
+      <c r="C96" t="s">
+        <v>339</v>
+      </c>
+      <c r="D96" t="s">
+        <v>342</v>
+      </c>
+      <c r="E96" s="4">
+        <v>77</v>
+      </c>
+      <c r="F96" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="B97" s="4">
+        <v>400142</v>
+      </c>
+      <c r="C97" t="s">
+        <v>339</v>
+      </c>
+      <c r="D97" t="s">
+        <v>344</v>
+      </c>
+      <c r="E97" s="4">
+        <v>7</v>
+      </c>
+      <c r="F97" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="98" s="1" customFormat="1" spans="1:7">
+      <c r="A98" s="2"/>
+      <c r="B98" s="5">
+        <v>40015</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E98" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="99" s="1" customFormat="1" spans="1:7">
+      <c r="A99" s="2"/>
+      <c r="B99" s="5">
+        <v>400151</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="100" s="1" customFormat="1" spans="1:7">
+      <c r="A100" s="2"/>
+      <c r="B100" s="5">
+        <v>40016</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E100" s="5">
         <v>2</v>
       </c>
-      <c r="F61" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="62" customFormat="1" spans="1:6">
-      <c r="A62" s="5"/>
-      <c r="B62" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C62" t="s">
-        <v>225</v>
-      </c>
-      <c r="D62" t="s">
-        <v>226</v>
-      </c>
-      <c r="E62" s="6">
-        <v>2</v>
-      </c>
-      <c r="F62" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="63" customFormat="1" spans="1:6">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="C63" t="s">
-        <v>229</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="E63" s="6">
-        <v>3</v>
-      </c>
-      <c r="F63" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="64" customFormat="1" spans="1:6">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C64" t="s">
-        <v>233</v>
-      </c>
-      <c r="D64" t="s">
-        <v>234</v>
-      </c>
-      <c r="E64" s="6">
-        <v>5</v>
-      </c>
-      <c r="F64" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="65" customFormat="1" spans="1:6">
-      <c r="A65" s="5"/>
-      <c r="B65" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="C65" t="s">
-        <v>237</v>
-      </c>
-      <c r="D65" t="s">
-        <v>238</v>
-      </c>
-      <c r="E65" s="6">
-        <v>1</v>
-      </c>
-      <c r="F65" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="66" customFormat="1" spans="1:6">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C66" t="s">
-        <v>241</v>
-      </c>
-      <c r="D66" t="s">
-        <v>242</v>
-      </c>
-      <c r="E66" s="6">
-        <v>10</v>
-      </c>
-      <c r="F66" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="67" s="2" customFormat="1" spans="1:6">
-      <c r="A67" s="4"/>
-      <c r="B67" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="C67" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E67" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="68" s="2" customFormat="1" spans="1:6">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="E68" s="9">
-        <v>1</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="69" s="2" customFormat="1" spans="1:6">
-      <c r="A69" s="4"/>
-      <c r="B69" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="70" s="2" customFormat="1" spans="1:6">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4" t="s">
+      <c r="F100" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="101" s="2" customFormat="1" spans="1:7">
+      <c r="B101" s="5">
+        <v>40017</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G101" s="1"/>
+    </row>
+    <row r="102" s="2" customFormat="1" spans="1:7">
+      <c r="B102" s="5">
+        <v>40018</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="G102" s="1"/>
+    </row>
+    <row r="103" s="2" customFormat="1" spans="1:7">
+      <c r="B103" s="5">
+        <v>40019</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="G103" s="1"/>
+    </row>
+    <row r="104" s="2" customFormat="1" spans="1:7">
+      <c r="B104" s="5">
+        <v>40020</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="G104" s="1"/>
+    </row>
+    <row r="105" s="2" customFormat="1" spans="1:7">
+      <c r="B105" s="5">
+        <v>40021</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="G105" s="1"/>
+    </row>
+    <row r="106" s="2" customFormat="1" spans="1:7">
+      <c r="B106" s="5">
+        <v>40022</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G106" s="1"/>
+    </row>
+    <row r="107" s="2" customFormat="1" spans="1:7">
+      <c r="B107" s="5">
+        <v>400221</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G107" s="1"/>
+    </row>
+    <row r="108" s="2" customFormat="1" spans="1:7">
+      <c r="B108" s="5">
+        <v>40023</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G108" s="1"/>
+    </row>
+    <row r="109" s="2" customFormat="1" spans="1:7">
+      <c r="B109" s="5">
+        <v>40024</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="E109" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="G109" s="1"/>
+    </row>
+    <row r="110" s="2" customFormat="1" spans="1:7">
+      <c r="B110" s="5">
+        <v>40025</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C70" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E70" s="9"/>
-      <c r="F70" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="71" s="2" customFormat="1" spans="1:6">
-      <c r="A71" s="4"/>
-      <c r="B71" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E71" s="9">
-        <v>0.3</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="72" s="2" customFormat="1" spans="1:6">
-      <c r="A72" s="4"/>
-      <c r="B72" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E72" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="73" s="2" customFormat="1" spans="1:6">
-      <c r="A73" s="4"/>
-      <c r="B73" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="E73" s="9">
-        <v>0.2</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="74" s="2" customFormat="1" spans="1:6">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="75" s="2" customFormat="1" spans="1:6">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E75" s="9">
-        <v>-0.2</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="76" s="2" customFormat="1" spans="1:6">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="E76" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="77" s="2" customFormat="1" spans="1:6">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E77" s="9">
-        <v>1</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="78" s="2" customFormat="1" spans="1:6">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-0.3</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="79" customFormat="1" spans="1:6">
-      <c r="A79" s="5"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="E79" s="6"/>
-    </row>
-    <row r="80" customFormat="1" spans="1:6">
-      <c r="A80" s="5"/>
-      <c r="B80" s="6">
-        <v>40001</v>
-      </c>
-      <c r="C80" s="6">
-        <v>235</v>
-      </c>
-      <c r="D80" t="s">
-        <v>296</v>
-      </c>
-      <c r="E80" s="6"/>
-      <c r="F80" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="81" s="3" customFormat="1" spans="1:6">
-      <c r="A81" s="12"/>
-      <c r="B81" s="13">
-        <v>40002</v>
-      </c>
-      <c r="C81" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="D81" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E81" s="13">
-        <v>500</v>
-      </c>
-      <c r="F81" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="82" customFormat="1" spans="1:6">
-      <c r="A82" s="5"/>
-      <c r="B82" s="6">
-        <v>40003</v>
-      </c>
-      <c r="C82" t="s">
-        <v>300</v>
-      </c>
-      <c r="D82" t="s">
-        <v>301</v>
-      </c>
-      <c r="E82" s="6"/>
-      <c r="F82" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="83" customFormat="1" spans="1:6">
-      <c r="A83" s="5"/>
-      <c r="B83" s="6">
-        <v>40004</v>
-      </c>
-      <c r="C83" t="s">
-        <v>303</v>
-      </c>
-      <c r="D83" t="s">
-        <v>304</v>
-      </c>
-      <c r="E83" s="6">
-        <v>1</v>
-      </c>
-      <c r="F83" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="84" customFormat="1" spans="1:6">
-      <c r="A84" s="5"/>
-      <c r="B84" s="6">
-        <v>40005</v>
-      </c>
-      <c r="C84" t="s">
-        <v>306</v>
-      </c>
-      <c r="D84" t="s">
-        <v>307</v>
-      </c>
-      <c r="E84" s="6">
-        <v>15</v>
-      </c>
-      <c r="F84" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="85" customFormat="1" spans="1:6">
-      <c r="A85" s="5"/>
-      <c r="B85" s="6">
-        <v>40006</v>
-      </c>
-      <c r="C85" t="s">
-        <v>309</v>
-      </c>
-      <c r="D85" t="s">
-        <v>310</v>
-      </c>
-      <c r="E85" s="6">
-        <v>5</v>
-      </c>
-      <c r="F85" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="86" customFormat="1" spans="1:6">
-      <c r="A86" s="5"/>
-      <c r="B86" s="6">
-        <v>40007</v>
-      </c>
-      <c r="C86" t="s">
-        <v>312</v>
-      </c>
-      <c r="D86" t="s">
-        <v>313</v>
-      </c>
-      <c r="E86" s="6">
-        <v>5</v>
-      </c>
-      <c r="F86" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="87" customFormat="1" spans="1:6">
-      <c r="A87" s="5"/>
-      <c r="B87" s="6">
-        <v>40008</v>
-      </c>
-      <c r="C87" t="s">
-        <v>315</v>
-      </c>
-      <c r="D87" t="s">
-        <v>316</v>
-      </c>
-      <c r="E87" s="6"/>
-      <c r="F87" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="88" customFormat="1" spans="1:6">
-      <c r="A88" s="5"/>
-      <c r="B88" s="6">
-        <v>40009</v>
-      </c>
-      <c r="C88" t="s">
-        <v>318</v>
-      </c>
-      <c r="D88" t="s">
-        <v>319</v>
-      </c>
-      <c r="E88" s="6">
-        <v>5</v>
-      </c>
-      <c r="F88" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="89" s="3" customFormat="1" spans="1:6">
-      <c r="A89" s="12"/>
-      <c r="B89" s="13">
-        <v>400091</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D89" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="E89" s="13">
-        <v>5</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="90" customFormat="1" spans="1:6">
-      <c r="A90" s="5"/>
-      <c r="B90" s="6">
-        <v>40010</v>
-      </c>
-      <c r="C90" t="s">
-        <v>323</v>
-      </c>
-      <c r="D90" t="s">
-        <v>324</v>
-      </c>
-      <c r="E90" s="6">
-        <v>1</v>
-      </c>
-      <c r="F90" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="91" customFormat="1" spans="1:6">
-      <c r="A91" s="5"/>
-      <c r="B91" s="6">
-        <v>40011</v>
-      </c>
-      <c r="C91" t="s">
-        <v>326</v>
-      </c>
-      <c r="D91" t="s">
-        <v>327</v>
-      </c>
-      <c r="E91" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="F91" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="92" customFormat="1" spans="1:6">
-      <c r="A92" s="5"/>
-      <c r="B92" s="6">
-        <v>40012</v>
-      </c>
-      <c r="C92" t="s">
-        <v>329</v>
-      </c>
-      <c r="D92" t="s">
-        <v>304</v>
-      </c>
-      <c r="E92" s="6">
-        <v>-2</v>
-      </c>
-      <c r="F92" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="93" customFormat="1" spans="1:6">
-      <c r="A93" s="5"/>
-      <c r="B93" s="6">
-        <v>400121</v>
-      </c>
-      <c r="C93" t="s">
-        <v>329</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E93" s="6">
-        <v>20</v>
-      </c>
-      <c r="F93" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="94" customFormat="1" spans="1:6">
-      <c r="A94" s="5"/>
-      <c r="B94" s="6">
-        <v>40013</v>
-      </c>
-      <c r="C94" t="s">
-        <v>332</v>
-      </c>
-      <c r="D94" t="s">
-        <v>333</v>
-      </c>
-      <c r="E94" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="F94" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="95" customFormat="1" spans="1:6">
-      <c r="A95" s="5"/>
-      <c r="B95" s="6">
-        <v>40014</v>
-      </c>
-      <c r="C95" t="s">
-        <v>335</v>
-      </c>
-      <c r="D95" t="s">
-        <v>336</v>
-      </c>
-      <c r="E95" s="6">
-        <v>0.07</v>
-      </c>
-      <c r="F95" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="96" customFormat="1" spans="1:6">
-      <c r="A96" s="5"/>
-      <c r="B96" s="6">
-        <v>400141</v>
-      </c>
-      <c r="C96" t="s">
-        <v>335</v>
-      </c>
-      <c r="D96" t="s">
-        <v>338</v>
-      </c>
-      <c r="E96" s="6">
-        <v>77</v>
-      </c>
-      <c r="F96" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="97" customFormat="1" spans="1:7">
-      <c r="A97" s="5"/>
-      <c r="B97" s="6">
-        <v>400142</v>
-      </c>
-      <c r="C97" t="s">
-        <v>335</v>
-      </c>
-      <c r="D97" t="s">
-        <v>340</v>
-      </c>
-      <c r="E97" s="6">
-        <v>7</v>
-      </c>
-      <c r="F97" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="98" s="2" customFormat="1" spans="1:7">
-      <c r="A98" s="4"/>
-      <c r="B98" s="9">
-        <v>40015</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="E98" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="99" s="2" customFormat="1" spans="1:7">
-      <c r="A99" s="4"/>
-      <c r="B99" s="9">
-        <v>400151</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E99" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="100" s="2" customFormat="1" spans="1:7">
-      <c r="A100" s="4"/>
-      <c r="B100" s="9">
-        <v>40016</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="E100" s="9"/>
-      <c r="F100" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="101" s="4" customFormat="1" spans="1:7">
-      <c r="B101" s="9">
-        <v>40017</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="G101" s="2"/>
-    </row>
-    <row r="102" s="4" customFormat="1" spans="1:7">
-      <c r="B102" s="9">
-        <v>40018</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="D102" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="E102" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="G102" s="2"/>
-    </row>
-    <row r="103" s="4" customFormat="1" spans="1:7">
-      <c r="B103" s="9">
-        <v>40019</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="E103" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="G103" s="2"/>
-    </row>
-    <row r="104" s="4" customFormat="1" spans="1:7">
-      <c r="B104" s="9">
-        <v>40020</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="G104" s="2"/>
-    </row>
-    <row r="105" s="4" customFormat="1" spans="1:7">
-      <c r="B105" s="9">
-        <v>40021</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D105" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="G105" s="2"/>
-    </row>
-    <row r="106" s="4" customFormat="1" spans="1:7">
-      <c r="B106" s="9">
-        <v>40022</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D106" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="G106" s="2"/>
-    </row>
-    <row r="107" s="4" customFormat="1" spans="1:7">
-      <c r="B107" s="9">
-        <v>400221</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="G107" s="2"/>
-    </row>
-    <row r="108" s="4" customFormat="1" spans="1:7">
-      <c r="B108" s="9">
-        <v>40023</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D108" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="E108" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="G108" s="2"/>
-    </row>
-    <row r="109" s="4" customFormat="1" spans="1:7">
-      <c r="B109" s="9">
-        <v>40024</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="E109" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="G109" s="2"/>
-    </row>
-    <row r="110" s="4" customFormat="1" spans="1:7">
-      <c r="B110" s="9">
-        <v>40025</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="F110" s="2" t="s">
+      <c r="F110" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="G110" s="2"/>
+      <c r="G110" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12105" windowHeight="11520"/>
+    <workbookView windowWidth="10350" windowHeight="11325"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="456">
   <si>
     <t>##var</t>
   </si>
@@ -1064,6 +1064,24 @@
   </si>
   <si>
     <t>每通过1关时,获得25金币</t>
+  </si>
+  <si>
+    <t>降低</t>
+  </si>
+  <si>
+    <t>ReduceLevel</t>
+  </si>
+  <si>
+    <t>比牌时,对方的牌型顺位降低1级</t>
+  </si>
+  <si>
+    <t>升职</t>
+  </si>
+  <si>
+    <t>UpLevel</t>
+  </si>
+  <si>
+    <t>比牌时,自己的牌型顺位提高1级</t>
   </si>
   <si>
     <t>SpecialTwoThreeFive</t>
@@ -1997,7 +2015,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2006,6 +2024,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2355,7 +2376,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="5.75833333333333" style="1" customWidth="1"/>
@@ -3916,72 +3937,72 @@
       </c>
     </row>
     <row r="94" spans="2:6">
-      <c r="B94" s="2"/>
-      <c r="E94" s="2"/>
+      <c r="B94" s="2">
+        <v>30031</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="E94" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="95" spans="2:6">
       <c r="B95" s="2">
-        <v>40001</v>
-      </c>
-      <c r="C95" s="2">
-        <v>235</v>
-      </c>
-      <c r="D95" t="s">
-        <v>344</v>
+        <v>30032</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>348</v>
       </c>
       <c r="E95" s="2">
         <v>1</v>
       </c>
-      <c r="F95" t="s">
-        <v>345</v>
+      <c r="F95" s="3" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="96" spans="2:6">
-      <c r="B96" s="2">
-        <v>40002</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E96" s="2">
-        <v>500</v>
-      </c>
-      <c r="F96" t="s">
-        <v>347</v>
-      </c>
+      <c r="B96" s="2"/>
+      <c r="E96" s="2"/>
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="2">
-        <v>40003</v>
-      </c>
-      <c r="C97" t="s">
-        <v>348</v>
+        <v>40001</v>
+      </c>
+      <c r="C97" s="2">
+        <v>235</v>
       </c>
       <c r="D97" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E97" s="2">
         <v>1</v>
       </c>
       <c r="F97" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="2">
-        <v>40004</v>
-      </c>
-      <c r="C98" t="s">
-        <v>351</v>
-      </c>
-      <c r="D98" t="s">
+        <v>40002</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>352</v>
       </c>
+      <c r="D98" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="E98" s="2">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="F98" t="s">
         <v>353</v>
@@ -3989,7 +4010,7 @@
     </row>
     <row r="99" spans="2:6">
       <c r="B99" s="2">
-        <v>40005</v>
+        <v>40003</v>
       </c>
       <c r="C99" t="s">
         <v>354</v>
@@ -3998,7 +4019,7 @@
         <v>355</v>
       </c>
       <c r="E99" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F99" t="s">
         <v>356</v>
@@ -4006,7 +4027,7 @@
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="2">
-        <v>40006</v>
+        <v>40004</v>
       </c>
       <c r="C100" t="s">
         <v>357</v>
@@ -4021,9 +4042,9 @@
         <v>359</v>
       </c>
     </row>
-    <row r="101" s="1" customFormat="1" spans="2:6">
+    <row r="101" spans="2:6">
       <c r="B101" s="2">
-        <v>40007</v>
+        <v>40005</v>
       </c>
       <c r="C101" t="s">
         <v>360</v>
@@ -4032,15 +4053,15 @@
         <v>361</v>
       </c>
       <c r="E101" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F101" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="102" s="1" customFormat="1" spans="2:6">
+    <row r="102" spans="2:6">
       <c r="B102" s="2">
-        <v>40008</v>
+        <v>40006</v>
       </c>
       <c r="C102" t="s">
         <v>363</v>
@@ -4057,7 +4078,7 @@
     </row>
     <row r="103" s="1" customFormat="1" spans="2:6">
       <c r="B103" s="2">
-        <v>40009</v>
+        <v>40007</v>
       </c>
       <c r="C103" t="s">
         <v>366</v>
@@ -4066,7 +4087,7 @@
         <v>367</v>
       </c>
       <c r="E103" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F103" t="s">
         <v>368</v>
@@ -4074,33 +4095,33 @@
     </row>
     <row r="104" s="1" customFormat="1" spans="2:6">
       <c r="B104" s="2">
-        <v>400091</v>
+        <v>40008</v>
       </c>
       <c r="C104" t="s">
-        <v>366</v>
-      </c>
-      <c r="D104" s="2" t="s">
         <v>369</v>
       </c>
+      <c r="D104" t="s">
+        <v>370</v>
+      </c>
       <c r="E104" s="2">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="F104" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" spans="2:6">
       <c r="B105" s="2">
-        <v>40010</v>
+        <v>40009</v>
       </c>
       <c r="C105" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D105" t="s">
-        <v>372</v>
-      </c>
-      <c r="E105" s="2" t="s">
         <v>373</v>
+      </c>
+      <c r="E105" s="2">
+        <v>8</v>
       </c>
       <c r="F105" t="s">
         <v>374</v>
@@ -4108,237 +4129,237 @@
     </row>
     <row r="106" s="1" customFormat="1" spans="2:6">
       <c r="B106" s="2">
-        <v>40011</v>
+        <v>400091</v>
       </c>
       <c r="C106" t="s">
+        <v>372</v>
+      </c>
+      <c r="D106" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" s="2">
+        <v>400</v>
+      </c>
+      <c r="F106" t="s">
         <v>376</v>
-      </c>
-      <c r="E106" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="F106" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" spans="2:6">
       <c r="B107" s="2">
-        <v>40012</v>
+        <v>40010</v>
       </c>
       <c r="C107" t="s">
+        <v>377</v>
+      </c>
+      <c r="D107" t="s">
         <v>378</v>
       </c>
-      <c r="D107" t="s">
-        <v>352</v>
-      </c>
-      <c r="E107" s="2">
-        <v>-2</v>
+      <c r="E107" s="2" t="s">
+        <v>379</v>
       </c>
       <c r="F107" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" spans="2:6">
       <c r="B108" s="2">
-        <v>400121</v>
+        <v>40011</v>
       </c>
       <c r="C108" t="s">
-        <v>378</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>16</v>
+        <v>381</v>
+      </c>
+      <c r="D108" t="s">
+        <v>382</v>
       </c>
       <c r="E108" s="2">
-        <v>10</v>
+        <v>0.25</v>
       </c>
       <c r="F108" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" spans="2:6">
       <c r="B109" s="2">
-        <v>40013</v>
+        <v>40012</v>
       </c>
       <c r="C109" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D109" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="E109" s="2">
-        <v>0.1</v>
+        <v>-2</v>
       </c>
       <c r="F109" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" spans="2:6">
       <c r="B110" s="2">
-        <v>40014</v>
+        <v>400121</v>
       </c>
       <c r="C110" t="s">
         <v>384</v>
       </c>
-      <c r="D110" t="s">
-        <v>385</v>
+      <c r="D110" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E110" s="2">
-        <v>0.25</v>
+        <v>10</v>
       </c>
       <c r="F110" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="111" spans="2:6">
+    <row r="111" s="1" customFormat="1" spans="2:6">
       <c r="B111" s="2">
-        <v>400141</v>
+        <v>40013</v>
       </c>
       <c r="C111" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D111" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E111" s="2">
-        <v>77</v>
+        <v>0.1</v>
       </c>
       <c r="F111" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="112" spans="2:6">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="112" s="1" customFormat="1" spans="2:6">
       <c r="B112" s="2">
-        <v>400142</v>
+        <v>40014</v>
       </c>
       <c r="C112" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D112" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E112" s="2">
-        <v>7</v>
+        <v>0.25</v>
       </c>
       <c r="F112" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="113" spans="2:6">
       <c r="B113" s="2">
-        <v>40015</v>
+        <v>400141</v>
       </c>
       <c r="C113" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D113" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E113" s="2">
-        <v>0.5</v>
+        <v>77</v>
       </c>
       <c r="F113" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="114" spans="2:6">
       <c r="B114" s="2">
-        <v>400151</v>
+        <v>400142</v>
       </c>
       <c r="C114" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D114" t="s">
-        <v>394</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>141</v>
+        <v>395</v>
+      </c>
+      <c r="E114" s="2">
+        <v>7</v>
       </c>
       <c r="F114" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="115" spans="2:6">
       <c r="B115" s="2">
-        <v>40016</v>
+        <v>40015</v>
       </c>
       <c r="C115" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D115" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E115" s="2">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="F115" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="2">
-        <v>40017</v>
+        <v>400151</v>
       </c>
       <c r="C116" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D116" t="s">
         <v>400</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="E116" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F116" t="s">
         <v>401</v>
-      </c>
-      <c r="F116" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="117" spans="2:6">
       <c r="B117" s="2">
-        <v>40018</v>
+        <v>40016</v>
       </c>
       <c r="C117" t="s">
+        <v>402</v>
+      </c>
+      <c r="D117" t="s">
         <v>403</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="E117" s="2">
+        <v>2</v>
+      </c>
+      <c r="F117" t="s">
         <v>404</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="F117" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="118" spans="2:6">
       <c r="B118" s="2">
-        <v>40019</v>
+        <v>40017</v>
       </c>
       <c r="C118" t="s">
+        <v>405</v>
+      </c>
+      <c r="D118" t="s">
+        <v>406</v>
+      </c>
+      <c r="E118" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="F118" t="s">
         <v>408</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F118" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="2">
-        <v>40020</v>
+        <v>40018</v>
       </c>
       <c r="C119" t="s">
+        <v>409</v>
+      </c>
+      <c r="D119" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="D119" s="2" t="s">
+      <c r="E119" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="F119" t="s">
         <v>412</v>
@@ -4346,7 +4367,7 @@
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="2">
-        <v>40021</v>
+        <v>40019</v>
       </c>
       <c r="C120" t="s">
         <v>413</v>
@@ -4355,41 +4376,41 @@
         <v>414</v>
       </c>
       <c r="E120" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F120" t="s">
         <v>415</v>
-      </c>
-      <c r="F120" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="2">
-        <v>40022</v>
+        <v>40020</v>
       </c>
       <c r="C121" t="s">
+        <v>416</v>
+      </c>
+      <c r="D121" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="E121" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F121" t="s">
         <v>418</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="F121" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="2">
-        <v>400221</v>
+        <v>40021</v>
       </c>
       <c r="C122" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D122" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="F122" t="s">
         <v>422</v>
@@ -4397,7 +4418,7 @@
     </row>
     <row r="123" spans="2:6">
       <c r="B123" s="2">
-        <v>40023</v>
+        <v>40022</v>
       </c>
       <c r="C123" t="s">
         <v>423</v>
@@ -4406,24 +4427,24 @@
         <v>424</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>23</v>
+        <v>425</v>
       </c>
       <c r="F123" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="124" spans="2:6">
       <c r="B124" s="2">
-        <v>40024</v>
+        <v>400221</v>
       </c>
       <c r="C124" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="E124" s="1">
-        <v>0.15</v>
+      <c r="E124" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F124" t="s">
         <v>428</v>
@@ -4431,7 +4452,7 @@
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="2">
-        <v>40025</v>
+        <v>40023</v>
       </c>
       <c r="C125" t="s">
         <v>429</v>
@@ -4440,7 +4461,7 @@
         <v>430</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>288</v>
+        <v>23</v>
       </c>
       <c r="F125" t="s">
         <v>431</v>
@@ -4448,16 +4469,16 @@
     </row>
     <row r="126" spans="2:6">
       <c r="B126" s="2">
-        <v>40026</v>
+        <v>40024</v>
       </c>
       <c r="C126" t="s">
         <v>432</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D126" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="E126" s="2">
-        <v>500</v>
+      <c r="E126" s="1">
+        <v>0.15</v>
       </c>
       <c r="F126" t="s">
         <v>434</v>
@@ -4465,70 +4486,104 @@
     </row>
     <row r="127" spans="2:6">
       <c r="B127" s="2">
-        <v>40027</v>
+        <v>40025</v>
       </c>
       <c r="C127" t="s">
         <v>435</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D127" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="E127" s="2" t="s">
+      <c r="E127" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F127" t="s">
         <v>437</v>
-      </c>
-      <c r="F127" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="128" spans="2:6">
       <c r="B128" s="2">
-        <v>40028</v>
+        <v>40026</v>
       </c>
       <c r="C128" t="s">
+        <v>438</v>
+      </c>
+      <c r="D128" t="s">
         <v>439</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" s="2">
+        <v>500</v>
+      </c>
+      <c r="F128" t="s">
         <v>440</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="F128" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="129" spans="2:6">
       <c r="B129" s="2">
-        <v>40029</v>
+        <v>40027</v>
       </c>
       <c r="C129" t="s">
+        <v>441</v>
+      </c>
+      <c r="D129" t="s">
+        <v>442</v>
+      </c>
+      <c r="E129" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="D129" t="s">
+      <c r="F129" t="s">
         <v>444</v>
-      </c>
-      <c r="E129" s="2">
-        <v>120</v>
-      </c>
-      <c r="F129" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="2">
+        <v>40028</v>
+      </c>
+      <c r="C130" t="s">
+        <v>445</v>
+      </c>
+      <c r="D130" t="s">
+        <v>446</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F130" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="131" spans="2:6">
+      <c r="B131" s="2">
+        <v>40029</v>
+      </c>
+      <c r="C131" t="s">
+        <v>449</v>
+      </c>
+      <c r="D131" t="s">
+        <v>450</v>
+      </c>
+      <c r="E131" s="2">
+        <v>120</v>
+      </c>
+      <c r="F131" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="132" spans="2:6">
+      <c r="B132" s="2">
         <v>40030</v>
       </c>
-      <c r="C130" t="s">
-        <v>446</v>
-      </c>
-      <c r="D130" t="s">
-        <v>447</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="F130" t="s">
-        <v>449</v>
+      <c r="C132" t="s">
+        <v>452</v>
+      </c>
+      <c r="D132" t="s">
+        <v>453</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F132" t="s">
+        <v>455</v>
       </c>
     </row>
   </sheetData>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0.2|5</t>
+          <t>0.25|8</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1|2</t>
+          <t>1|3</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>15|1|10</t>
+          <t>10|1|15</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1|3</t>
+          <t>1|5</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>15|20</t>
+          <t>25|20</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>0.5|15</t>
+          <t>0.5|25</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="E126" s="1" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>5|3</t>
+          <t>6|3</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="10350" windowHeight="11325" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
@@ -619,7 +619,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -628,9 +628,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1172,7 +1169,7 @@
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>结算时提供+1倍率</t>
         </is>
@@ -1187,7 +1184,7 @@
           <t>青铜项链</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>SquarePlate</t>
         </is>
@@ -1195,7 +1192,7 @@
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>亮出的每张方片牌在结算时提供+1倍率</t>
         </is>
@@ -1210,7 +1207,7 @@
           <t>青铜手镯</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>Spades</t>
         </is>
@@ -1220,7 +1217,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>亮出的每张黑桃牌在结算时提供+1倍率</t>
         </is>
@@ -1235,7 +1232,7 @@
           <t>青铜耳环</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>RedHeart</t>
         </is>
@@ -1243,7 +1240,7 @@
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>亮出的每张红心牌在结算时提供+1倍率</t>
         </is>
@@ -1258,7 +1255,7 @@
           <t>青铜戒指</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>PlumBlossom</t>
         </is>
@@ -1266,7 +1263,7 @@
       <c r="E9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr">
         <is>
           <t>亮出的每张梅花牌在结算时提供+1倍率</t>
         </is>
@@ -1289,7 +1286,7 @@
       <c r="E10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>亮出的对子牌型在结算时提供+3倍率</t>
         </is>
@@ -1304,7 +1301,7 @@
           <t>木制法杖</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>Straight</t>
         </is>
@@ -1312,7 +1309,7 @@
       <c r="E11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>亮出的顺子牌型在结算时提供+3倍率</t>
         </is>
@@ -1327,7 +1324,7 @@
           <t>木制长弓</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>Flush</t>
         </is>
@@ -1335,7 +1332,7 @@
       <c r="E12" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>亮出的同花牌型在结算时提供+3倍率</t>
         </is>
@@ -1350,7 +1347,7 @@
           <t>木制长矛</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>StraightFlush</t>
         </is>
@@ -1358,7 +1355,7 @@
       <c r="E13" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>亮出的同花顺牌型在结算时提供+5倍率</t>
         </is>
@@ -1381,7 +1378,7 @@
       <c r="E14" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>亮出的豹子牌型在结算时提供+6倍率</t>
         </is>
@@ -1404,7 +1401,7 @@
       <c r="E15" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="0" t="inlineStr">
         <is>
           <t>每次受到的伤害降低1点</t>
         </is>
@@ -1419,7 +1416,7 @@
           <t>小钱包</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>EveryRoundGetGold</t>
         </is>
@@ -1465,7 +1462,7 @@
           <t>幸运草</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>EveryRoundEndingGetGoldPer</t>
         </is>
@@ -1490,7 +1487,7 @@
           <t>暴击拳套</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>EveryRoundEndingGetCritical</t>
         </is>
@@ -1515,7 +1512,7 @@
           <t>垫脚石</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>SteppingStone</t>
         </is>
@@ -1525,7 +1522,7 @@
           <t>1|1</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="0" t="inlineStr">
         <is>
           <t>每关首次亮牌大于场上所有敌人时,永久+1攻击力</t>
         </is>
@@ -1540,7 +1537,7 @@
           <t>反击拳套</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>BounceDamage</t>
         </is>
@@ -1548,7 +1545,7 @@
       <c r="E21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="0" t="inlineStr">
         <is>
           <t>每当你受到伤害时,反弹3点伤害给攻击者</t>
         </is>
@@ -1558,12 +1555,12 @@
       <c r="B22" s="2" t="n">
         <v>10018</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>磨刀石</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>UseDamageMul</t>
         </is>
@@ -1571,7 +1568,7 @@
       <c r="E22" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="0" t="inlineStr">
         <is>
           <t>使用后,本次比牌你造成的伤害+50%</t>
         </is>
@@ -1581,12 +1578,12 @@
       <c r="B23" s="2" t="n">
         <v>10019</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>顺子心得</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>HandTypeMagUp</t>
         </is>
@@ -1596,7 +1593,7 @@
           <t>4|1</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="0" t="inlineStr">
         <is>
           <t>使用后,顺子牌型提供的倍率永久+1</t>
         </is>
@@ -1606,12 +1603,12 @@
       <c r="B24" s="2" t="n">
         <v>10020</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>急救粉</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>HealHpPercent</t>
         </is>
@@ -1619,7 +1616,7 @@
       <c r="E24" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="0" t="inlineStr">
         <is>
           <t>使用后,立即恢复30%最大生命</t>
         </is>
@@ -1629,12 +1626,12 @@
       <c r="B25" s="2" t="n">
         <v>10021</v>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>复仇之刺</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>LossRampDamage</t>
         </is>
@@ -1644,7 +1641,7 @@
           <t>0.2|1</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="0" t="inlineStr">
         <is>
           <t>每输1次比牌,你造成的伤害+20%,至多+100%,输后一直保留</t>
         </is>
@@ -1652,7 +1649,7 @@
     </row>
     <row r="26">
       <c r="B26" s="2" t="n"/>
-      <c r="D26" s="3" t="n"/>
+      <c r="D26" s="0" t="n"/>
       <c r="E26" s="2" t="n"/>
     </row>
     <row r="27">
@@ -1661,22 +1658,22 @@
           <t>20001</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>白银项链</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>SquarePlateAttack</t>
         </is>
       </c>
       <c r="E27" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>亮出的每张方片牌在结算时提供+40攻击力</t>
+        <v>25</v>
+      </c>
+      <c r="F27" s="0" t="inlineStr">
+        <is>
+          <t>亮出的每张方片牌在结算时提供+25攻击力</t>
         </is>
       </c>
     </row>
@@ -1686,22 +1683,22 @@
           <t>20002</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>白银手镯</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>SpadesAttack</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>亮出的每张黑桃牌在结算时提供+40攻击力</t>
+        <v>25</v>
+      </c>
+      <c r="F28" s="0" t="inlineStr">
+        <is>
+          <t>亮出的每张黑桃牌在结算时提供+25攻击力</t>
         </is>
       </c>
     </row>
@@ -1711,22 +1708,22 @@
           <t>20003</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>白银耳环</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>RedHeartAttack</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>亮出的每张红心牌在结算时提供+40攻击力</t>
+        <v>25</v>
+      </c>
+      <c r="F29" s="0" t="inlineStr">
+        <is>
+          <t>亮出的每张红心牌在结算时提供+25攻击力</t>
         </is>
       </c>
     </row>
@@ -1741,17 +1738,17 @@
           <t>白银戒指</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>PlumBlossomAttack</t>
         </is>
       </c>
       <c r="E30" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>亮出的每张梅花牌在结算时提供+40攻击力</t>
+        <v>25</v>
+      </c>
+      <c r="F30" s="0" t="inlineStr">
+        <is>
+          <t>亮出的每张梅花牌在结算时提供+25攻击力</t>
         </is>
       </c>
     </row>
@@ -1772,11 +1769,11 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>亮出的对子牌型在结算时提供+120攻击力</t>
+        <v>80</v>
+      </c>
+      <c r="F31" s="0" t="inlineStr">
+        <is>
+          <t>亮出的对子牌型在结算时提供+80攻击力</t>
         </is>
       </c>
     </row>
@@ -1791,17 +1788,17 @@
           <t>铁制法杖</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>StraightAttack</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>亮出的顺子牌型在结算时提供+150攻击力</t>
+        <v>130</v>
+      </c>
+      <c r="F32" s="0" t="inlineStr">
+        <is>
+          <t>亮出的顺子牌型在结算时提供+130攻击力</t>
         </is>
       </c>
     </row>
@@ -1816,17 +1813,17 @@
           <t>铁制长弓</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>FlushAttack</t>
         </is>
       </c>
       <c r="E33" s="1" t="n">
-        <v>150</v>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>亮出的同花牌型在结算时提供+150攻击力</t>
+        <v>100</v>
+      </c>
+      <c r="F33" s="0" t="inlineStr">
+        <is>
+          <t>亮出的同花牌型在结算时提供+100攻击力</t>
         </is>
       </c>
     </row>
@@ -1841,17 +1838,17 @@
           <t>铁制长矛</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>StraightFlushAttack</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>亮出的同花顺牌型在结算时提供+300攻击力</t>
+        <v>200</v>
+      </c>
+      <c r="F34" s="0" t="inlineStr">
+        <is>
+          <t>亮出的同花顺牌型在结算时提供+200攻击力</t>
         </is>
       </c>
     </row>
@@ -1872,11 +1869,11 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>亮出的豹子牌型在结算时提供+300攻击力</t>
+        <v>200</v>
+      </c>
+      <c r="F35" s="0" t="inlineStr">
+        <is>
+          <t>亮出的豹子牌型在结算时提供+200攻击力</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1896,7 @@
       <c r="E36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="0" t="inlineStr">
         <is>
           <t>每回合结束后恢复2点当前生命值</t>
         </is>
@@ -1924,7 +1921,7 @@
       <c r="E37" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" s="0" t="inlineStr">
         <is>
           <t>获得30点生命值上限</t>
         </is>
@@ -1941,7 +1938,7 @@
           <t>白条</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
         <is>
           <t>Liability</t>
         </is>
@@ -1949,7 +1946,7 @@
       <c r="E38" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" s="0" t="inlineStr">
         <is>
           <t>可以负债,最多-50金币</t>
         </is>
@@ -1966,7 +1963,7 @@
           <t>旗帜</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
         <is>
           <t>EveryRubbingNum</t>
         </is>
@@ -1974,7 +1971,7 @@
       <c r="E39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F39" s="0" t="inlineStr">
         <is>
           <t>在结算时,每剩余1个未使用的搓牌次数,就提供+1倍率</t>
         </is>
@@ -1999,7 +1996,7 @@
       <c r="E40" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F40" s="0" t="inlineStr">
         <is>
           <t>亮出的每张人头牌在结算时提供+40攻击力</t>
         </is>
@@ -2026,7 +2023,7 @@
           <t>1|3</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F41" s="0" t="inlineStr">
         <is>
           <t>亮出的每张人头牌在结算时获得2金币</t>
         </is>
@@ -2043,7 +2040,7 @@
           <t>黑白相机</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
         <is>
           <t>Camera</t>
         </is>
@@ -2051,7 +2048,7 @@
       <c r="E42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F42" s="0" t="inlineStr">
         <is>
           <t>结算时,未亮出的牌里每有1张黑桃或梅花,提供+2倍率</t>
         </is>
@@ -2068,7 +2065,7 @@
           <t>丘比特</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
         <is>
           <t>Cupid</t>
         </is>
@@ -2076,7 +2073,7 @@
       <c r="E43" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F43" s="0" t="inlineStr">
         <is>
           <t>结算时,未亮出的牌里每有1张方片或红心,提供+2倍率</t>
         </is>
@@ -2093,7 +2090,7 @@
           <t>投资</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="0" t="inlineStr">
         <is>
           <t>ConsumeFundsGetAttack</t>
         </is>
@@ -2103,7 +2100,7 @@
           <t>60|1</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F44" s="0" t="inlineStr">
         <is>
           <t>每花费60金币,英雄永久+1攻击力</t>
         </is>
@@ -2120,7 +2117,7 @@
           <t>补偿金</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
         <is>
           <t>TakeDamageGetFunds</t>
         </is>
@@ -2128,7 +2125,7 @@
       <c r="E45" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F45" s="0" t="inlineStr">
         <is>
           <t>每次受到伤害时,+10金币</t>
         </is>
@@ -2145,7 +2142,7 @@
           <t>和平鸽</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
         <is>
           <t>AllPeacePer</t>
         </is>
@@ -2153,7 +2150,7 @@
       <c r="E46" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F46" s="0" t="inlineStr">
         <is>
           <t>有25%概率将自身造成的伤害或受到的伤害降低为0</t>
         </is>
@@ -2170,7 +2167,7 @@
           <t>勇气徽章</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>DefeatGetAttack</t>
         </is>
@@ -2178,7 +2175,7 @@
       <c r="E47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F47" s="0" t="inlineStr">
         <is>
           <t>亮牌时,若牌型小于对方,则永久+1攻击力</t>
         </is>
@@ -2195,7 +2192,7 @@
           <t>激励徽章</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="0" t="inlineStr">
         <is>
           <t>DefeatGetHpMax</t>
         </is>
@@ -2203,7 +2200,7 @@
       <c r="E48" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F48" s="0" t="inlineStr">
         <is>
           <t>亮牌时,若牌型小于对方,则永久+3血量上限</t>
         </is>
@@ -2220,7 +2217,7 @@
           <t>记账本</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>DefeatAllGetGold</t>
         </is>
@@ -2228,7 +2225,7 @@
       <c r="E49" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F49" s="0" t="inlineStr">
         <is>
           <t>每回合结束时,若本回合未造成任何伤害,则获得10金币</t>
         </is>
@@ -2245,7 +2242,7 @@
           <t>铁饭碗</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>IronRiceBowl</t>
         </is>
@@ -2253,7 +2250,7 @@
       <c r="E50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F50" s="0" t="inlineStr">
         <is>
           <t>亮牌后无论胜负,均可获得2金币</t>
         </is>
@@ -2270,7 +2267,7 @@
           <t>永恒之心</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
         <is>
           <t>EveryRoundGetHpMax</t>
         </is>
@@ -2278,7 +2275,7 @@
       <c r="E51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F51" s="0" t="inlineStr">
         <is>
           <t>每回合开始时,永久+1血量上限</t>
         </is>
@@ -2295,7 +2292,7 @@
           <t>幸运顺子</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="0" t="inlineStr">
         <is>
           <t>LuckyStraight</t>
         </is>
@@ -2303,7 +2300,7 @@
       <c r="E52" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F52" s="0" t="inlineStr">
         <is>
           <t>亮牌时,若敌人的牌型大于顺子,则会被强行视作顺子</t>
         </is>
@@ -2320,7 +2317,7 @@
           <t>运动鞋</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="0" t="inlineStr">
         <is>
           <t>EveryRoundEndingGetEvade</t>
         </is>
@@ -2330,7 +2327,7 @@
           <t>0.01|20</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F53" s="0" t="inlineStr">
         <is>
           <t>每回合结束后,提高1%闪避率,至多叠加20层</t>
         </is>
@@ -2347,7 +2344,7 @@
           <t>保温杯</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="0" t="inlineStr">
         <is>
           <t>ThermosCup</t>
         </is>
@@ -2357,7 +2354,7 @@
           <t>0.5|6</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F54" s="0" t="inlineStr">
         <is>
           <t>每回合结束后,若你的血量低于50%,则恢复6点生命</t>
         </is>
@@ -2374,7 +2371,7 @@
           <t>利息</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="0" t="inlineStr">
         <is>
           <t>Interest</t>
         </is>
@@ -2384,7 +2381,7 @@
           <t>10|1|15</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F55" s="0" t="inlineStr">
         <is>
           <t>每通过1关时,每拥有15金币获得1金币,每关至多10金币</t>
         </is>
@@ -2401,7 +2398,7 @@
           <t>小算盘</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="0" t="inlineStr">
         <is>
           <t>Abacus</t>
         </is>
@@ -2411,7 +2408,7 @@
           <t>1|5</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F56" s="0" t="inlineStr">
         <is>
           <t>每回合结束时,每剩余1次搓牌次数就获得3金币</t>
         </is>
@@ -2421,12 +2418,12 @@
       <c r="B57" s="2" t="n">
         <v>20030</v>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="0" t="inlineStr">
         <is>
           <t>火药</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="0" t="inlineStr">
         <is>
           <t>UseDamageMul</t>
         </is>
@@ -2434,7 +2431,7 @@
       <c r="E57" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F57" s="0" t="inlineStr">
         <is>
           <t>使用后,本次比牌你造成的伤害翻倍</t>
         </is>
@@ -2444,12 +2441,12 @@
       <c r="B58" s="2" t="n">
         <v>20031</v>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="0" t="inlineStr">
         <is>
           <t>对子心得</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="0" t="inlineStr">
         <is>
           <t>HandTypeMagUp</t>
         </is>
@@ -2459,7 +2456,7 @@
           <t>2|3</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F58" s="0" t="inlineStr">
         <is>
           <t>使用后,对子牌型提供的倍率永久+3</t>
         </is>
@@ -2469,12 +2466,12 @@
       <c r="B59" s="2" t="n">
         <v>20032</v>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="0" t="inlineStr">
         <is>
           <t>黄金急救包</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="0" t="inlineStr">
         <is>
           <t>HealHpPercent</t>
         </is>
@@ -2482,7 +2479,7 @@
       <c r="E59" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F59" s="0" t="inlineStr">
         <is>
           <t>使用后,立即恢复60%最大生命</t>
         </is>
@@ -2492,12 +2489,12 @@
       <c r="B60" s="2" t="n">
         <v>20033</v>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="0" t="inlineStr">
         <is>
           <t>月光酒</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D60" s="0" t="inlineStr">
         <is>
           <t>WinHeal</t>
         </is>
@@ -2505,7 +2502,7 @@
       <c r="E60" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F60" s="0" t="inlineStr">
         <is>
           <t>每回合比牌获胜后,恢复3点生命</t>
         </is>
@@ -2515,12 +2512,12 @@
       <c r="B61" s="2" t="n">
         <v>20034</v>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="0" t="inlineStr">
         <is>
           <t>商人票据</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="0" t="inlineStr">
         <is>
           <t>NextShopDiscount</t>
         </is>
@@ -2528,7 +2525,7 @@
       <c r="E61" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F61" s="0" t="inlineStr">
         <is>
           <t>使用后,下一次进入商店时所有购买价格-50%</t>
         </is>
@@ -2538,12 +2535,12 @@
       <c r="B62" s="2" t="n">
         <v>20035</v>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="0" t="inlineStr">
         <is>
           <t>净化药水</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="0" t="inlineStr">
         <is>
           <t>RemoveBossEntry</t>
         </is>
@@ -2551,7 +2548,7 @@
       <c r="E62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="F62" s="0" t="inlineStr">
         <is>
           <t>使用后,移除本关内的1条BOSS词缀效果</t>
         </is>
@@ -2567,7 +2564,7 @@
           <t>30001</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="0" t="inlineStr">
         <is>
           <t>疯狂面具</t>
         </is>
@@ -2580,7 +2577,7 @@
       <c r="E64" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F64" s="0" t="inlineStr">
         <is>
           <t>造成伤害时,获得5%的生命窃取</t>
         </is>
@@ -2592,12 +2589,12 @@
           <t>30002</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="0" t="inlineStr">
         <is>
           <t>回旋刃</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D65" s="0" t="inlineStr">
         <is>
           <t>DoubleCardAttack</t>
         </is>
@@ -2605,7 +2602,7 @@
       <c r="E65" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F65" s="0" t="inlineStr">
         <is>
           <t>亮出的牌点数提供的攻击力加成×3</t>
         </is>
@@ -2617,12 +2614,12 @@
           <t>30003</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="0" t="inlineStr">
         <is>
           <t>致胜之剑</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" s="0" t="inlineStr">
         <is>
           <t>TheSwordOfVictory</t>
         </is>
@@ -2630,7 +2627,7 @@
       <c r="E66" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F66" s="3" t="inlineStr">
+      <c r="F66" s="0" t="inlineStr">
         <is>
           <t>结算伤害时,将留在手牌上最大的牌点数×4转化为额外攻击力</t>
         </is>
@@ -2642,12 +2639,12 @@
           <t>30004</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="0" t="inlineStr">
         <is>
           <t>搓牌能手</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" s="0" t="inlineStr">
         <is>
           <t>EveryUseRubbingNum</t>
         </is>
@@ -2655,7 +2652,7 @@
       <c r="E67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F67" s="0" t="inlineStr">
         <is>
           <t>每回合内,每搓1次牌,结算时提供的倍率+1</t>
         </is>
@@ -2667,12 +2664,12 @@
           <t>30005</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="0" t="inlineStr">
         <is>
           <t>会员卡</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D68" s="0" t="inlineStr">
         <is>
           <t>FreeShopRefresh</t>
         </is>
@@ -2680,7 +2677,7 @@
       <c r="E68" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F68" s="0" t="inlineStr">
         <is>
           <t>每次进入商店提供1次免费刷新的机会</t>
         </is>
@@ -2692,12 +2689,12 @@
           <t>30006</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="0" t="inlineStr">
         <is>
           <t>错峰出行</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D69" s="0" t="inlineStr">
         <is>
           <t>SpecialStraight</t>
         </is>
@@ -2705,7 +2702,7 @@
       <c r="E69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F69" s="0" t="inlineStr">
         <is>
           <t>顺子牌型可以相隔1点组成</t>
         </is>
@@ -2717,12 +2714,12 @@
           <t>30007</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="0" t="inlineStr">
         <is>
           <t>致命黑八</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D70" s="0" t="inlineStr">
         <is>
           <t>SpecialEightCard</t>
         </is>
@@ -2730,7 +2727,7 @@
       <c r="E70" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="F70" s="3" t="inlineStr">
+      <c r="F70" s="0" t="inlineStr">
         <is>
           <t>亮出的每张8在结算时提供+200攻击力</t>
         </is>
@@ -2742,12 +2739,12 @@
           <t>30008</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="0" t="inlineStr">
         <is>
           <t>偶数韵律</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D71" s="0" t="inlineStr">
         <is>
           <t>EvenNumberCard</t>
         </is>
@@ -2755,7 +2752,7 @@
       <c r="E71" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F71" s="0" t="inlineStr">
         <is>
           <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+6倍率</t>
         </is>
@@ -2767,12 +2764,12 @@
           <t>30009</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C72" s="0" t="inlineStr">
         <is>
           <t>奇数韵律</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" s="0" t="inlineStr">
         <is>
           <t>OddNumberCard</t>
         </is>
@@ -2780,7 +2777,7 @@
       <c r="E72" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="F72" s="0" t="inlineStr">
         <is>
           <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+6倍率</t>
         </is>
@@ -2792,7 +2789,7 @@
           <t>30010</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C73" s="0" t="inlineStr">
         <is>
           <t>贵族</t>
         </is>
@@ -2805,7 +2802,7 @@
       <c r="E73" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F73" s="0" t="inlineStr">
         <is>
           <t>亮出的每张人头牌在结算时提供+5倍率</t>
         </is>
@@ -2817,12 +2814,12 @@
           <t>30011</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" s="0" t="inlineStr">
         <is>
           <t>工资卡</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D74" s="0" t="inlineStr">
         <is>
           <t>KillAfterSellingPrice</t>
         </is>
@@ -2830,9 +2827,9 @@
       <c r="E74" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>每击杀1名敌人,该收藏品的出售价格+5金币</t>
+      <c r="F74" s="0" t="inlineStr">
+        <is>
+          <t>每击杀1名敌人,该圣物的出售价格+5金币</t>
         </is>
       </c>
     </row>
@@ -2842,12 +2839,12 @@
           <t>30012</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="0" t="inlineStr">
         <is>
           <t>训练</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D75" s="0" t="inlineStr">
         <is>
           <t>EveryCardAttackForever</t>
         </is>
@@ -2857,7 +2854,7 @@
           <t>1|30</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F75" s="0" t="inlineStr">
         <is>
           <t>每回合首次亮牌时,随机1张亮出牌点数的攻击力永久+1,至多累计+30</t>
         </is>
@@ -2869,12 +2866,12 @@
           <t>30013</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C76" s="0" t="inlineStr">
         <is>
           <t>九霄云外</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D76" s="0" t="inlineStr">
         <is>
           <t>SpecialNineCard</t>
         </is>
@@ -2882,7 +2879,7 @@
       <c r="E76" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="F76" s="0" t="inlineStr">
         <is>
           <t>亮出的每张9在结算时提供15金币</t>
         </is>
@@ -2899,7 +2896,7 @@
           <t>后备计划</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D77" s="0" t="inlineStr">
         <is>
           <t>DefeatAllGetGoldAndReplyHp</t>
         </is>
@@ -2909,7 +2906,7 @@
           <t>25|20</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="F77" s="0" t="inlineStr">
         <is>
           <t>如果本回合牌型小于所有敌人,则立即获得15金币并回复20点生命值</t>
         </is>
@@ -2926,7 +2923,7 @@
           <t>护身符</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D78" s="0" t="inlineStr">
         <is>
           <t>MissFirstDamage</t>
         </is>
@@ -2934,7 +2931,7 @@
       <c r="E78" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F78" s="0" t="inlineStr">
         <is>
           <t>每关受到的第1次伤害完全免疫</t>
         </is>
@@ -2951,7 +2948,7 @@
           <t>复盘笔记</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D79" s="0" t="inlineStr">
         <is>
           <t>DefeatGetMagnification</t>
         </is>
@@ -2961,7 +2958,7 @@
           <t>1|0.2</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F79" s="0" t="inlineStr">
         <is>
           <t>每输1次敌人,结算时就永久提供+0.2倍率</t>
         </is>
@@ -2978,7 +2975,7 @@
           <t>幸运同花</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D80" s="0" t="inlineStr">
         <is>
           <t>LuckyFlush</t>
         </is>
@@ -2986,7 +2983,7 @@
       <c r="E80" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F80" s="3" t="inlineStr">
+      <c r="F80" s="0" t="inlineStr">
         <is>
           <t>亮牌时,若敌人的牌型大于同花,则会被强行视作同花</t>
         </is>
@@ -3003,7 +3000,7 @@
           <t>逆转沙漏</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D81" s="0" t="inlineStr">
         <is>
           <t>ReverseResult</t>
         </is>
@@ -3011,7 +3008,7 @@
       <c r="E81" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="F81" s="3" t="inlineStr">
+      <c r="F81" s="0" t="inlineStr">
         <is>
           <t>当牌型小于敌人时,有30%概率反转对比结果,但伤害按自身牌型计算</t>
         </is>
@@ -3028,7 +3025,7 @@
           <t>练习卷</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="D82" s="0" t="inlineStr">
         <is>
           <t>NoKillMonsterGetMagnification</t>
         </is>
@@ -3038,7 +3035,7 @@
           <t>0.2|6</t>
         </is>
       </c>
-      <c r="F82" s="3" t="inlineStr">
+      <c r="F82" s="0" t="inlineStr">
         <is>
           <t>每回合结束后,若本回合你未击杀任何敌人,则永久提供+0.2倍率,至多+6</t>
         </is>
@@ -3055,7 +3052,7 @@
           <t>小本本</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D83" s="0" t="inlineStr">
         <is>
           <t>Revenge</t>
         </is>
@@ -3063,7 +3060,7 @@
       <c r="E83" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="F83" s="3" t="inlineStr">
+      <c r="F83" s="0" t="inlineStr">
         <is>
           <t>本局内,对自己曾经输过的敌人造成伤害时,伤害+20%</t>
         </is>
@@ -3080,7 +3077,7 @@
           <t>高贵徽章</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D84" s="0" t="inlineStr">
         <is>
           <t>NobleBadge</t>
         </is>
@@ -3090,7 +3087,7 @@
           <t>0.5|25</t>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr">
+      <c r="F84" s="0" t="inlineStr">
         <is>
           <t>每关开始时,若生命值高于50%,获得15金币</t>
         </is>
@@ -3107,7 +3104,7 @@
           <t>陷阱</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D85" s="0" t="inlineStr">
         <is>
           <t>Trap</t>
         </is>
@@ -3115,7 +3112,7 @@
       <c r="E85" s="2" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F85" s="3" t="inlineStr">
+      <c r="F85" s="0" t="inlineStr">
         <is>
           <t>本局内,自己曾经输过的敌人在造成伤害时,伤害-20%</t>
         </is>
@@ -3132,7 +3129,7 @@
           <t>好运来</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="D86" s="0" t="inlineStr">
         <is>
           <t>DownGrade</t>
         </is>
@@ -3142,7 +3139,7 @@
           <t>0.15|1</t>
         </is>
       </c>
-      <c r="F86" s="3" t="inlineStr">
+      <c r="F86" s="0" t="inlineStr">
         <is>
           <t>每回合有15%概率使本回合所有敌人亮出的牌型自动降1级</t>
         </is>
@@ -3159,7 +3156,7 @@
           <t>入场券</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="D87" s="0" t="inlineStr">
         <is>
           <t>AdmissionTicket</t>
         </is>
@@ -3167,7 +3164,7 @@
       <c r="E87" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F87" s="3" t="inlineStr">
+      <c r="F87" s="0" t="inlineStr">
         <is>
           <t>每关开始时,对所有敌人造成2次自身攻击力的伤害</t>
         </is>
@@ -3184,7 +3181,7 @@
           <t>条约</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="D88" s="0" t="inlineStr">
         <is>
           <t>MonsterDamage</t>
         </is>
@@ -3192,7 +3189,7 @@
       <c r="E88" s="2" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F88" s="3" t="inlineStr">
+      <c r="F88" s="0" t="inlineStr">
         <is>
           <t>所有敌人造成的伤害降低30%</t>
         </is>
@@ -3202,12 +3199,12 @@
       <c r="B89" s="2" t="n">
         <v>30026</v>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C89" s="0" t="inlineStr">
         <is>
           <t>同花心得</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D89" s="0" t="inlineStr">
         <is>
           <t>HandTypeMagUp</t>
         </is>
@@ -3217,7 +3214,7 @@
           <t>3|8</t>
         </is>
       </c>
-      <c r="F89" s="3" t="inlineStr">
+      <c r="F89" s="0" t="inlineStr">
         <is>
           <t>使用后,同花牌型提供的倍率永久+8</t>
         </is>
@@ -3227,12 +3224,12 @@
       <c r="B90" s="2" t="n">
         <v>30027</v>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C90" s="0" t="inlineStr">
         <is>
           <t>豹子精髓</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D90" s="0" t="inlineStr">
         <is>
           <t>FirstLeopardGold</t>
         </is>
@@ -3240,7 +3237,7 @@
       <c r="E90" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="F90" s="3" t="inlineStr">
+      <c r="F90" s="0" t="inlineStr">
         <is>
           <t>使用后,本局内你首次亮出豹子时,额外获得300金币</t>
         </is>
@@ -3250,12 +3247,12 @@
       <c r="B91" s="2" t="n">
         <v>30028</v>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C91" s="0" t="inlineStr">
         <is>
           <t>时之沙</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="D91" s="0" t="inlineStr">
         <is>
           <t>LevelWinDamageUp</t>
         </is>
@@ -3263,7 +3260,7 @@
       <c r="E91" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="F91" s="3" t="inlineStr">
+      <c r="F91" s="0" t="inlineStr">
         <is>
           <t>使用后,本关内你比牌获胜时的伤害+30%</t>
         </is>
@@ -3273,12 +3270,12 @@
       <c r="B92" s="2" t="n">
         <v>30029</v>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C92" s="0" t="inlineStr">
         <is>
           <t>巨人药剂</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D92" s="0" t="inlineStr">
         <is>
           <t>LevelHpMaxUp</t>
         </is>
@@ -3286,7 +3283,7 @@
       <c r="E92" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="F92" s="3" t="inlineStr">
+      <c r="F92" s="0" t="inlineStr">
         <is>
           <t>使用后,本关内生命上限+80,并立即恢复80点生命</t>
         </is>
@@ -3296,12 +3293,12 @@
       <c r="B93" s="2" t="n">
         <v>30030</v>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C93" s="0" t="inlineStr">
         <is>
           <t>丰收图腾</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D93" s="0" t="inlineStr">
         <is>
           <t>GoldPerLevelClear</t>
         </is>
@@ -3309,7 +3306,7 @@
       <c r="E93" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="F93" s="3" t="inlineStr">
+      <c r="F93" s="0" t="inlineStr">
         <is>
           <t>每通过1关时,获得25金币</t>
         </is>
@@ -3319,7 +3316,7 @@
       <c r="B94" s="2" t="n">
         <v>30031</v>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C94" s="0" t="inlineStr">
         <is>
           <t>降低</t>
         </is>
@@ -3332,7 +3329,7 @@
       <c r="E94" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="F94" s="3" t="inlineStr">
+      <c r="F94" s="0" t="inlineStr">
         <is>
           <t>比牌时,对方的牌型顺位降低1级</t>
         </is>
@@ -3342,7 +3339,7 @@
       <c r="B95" s="2" t="n">
         <v>30032</v>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C95" s="0" t="inlineStr">
         <is>
           <t>升职</t>
         </is>
@@ -3355,7 +3352,7 @@
       <c r="E95" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F95" s="3" t="inlineStr">
+      <c r="F95" s="0" t="inlineStr">
         <is>
           <t>比牌时,自己的牌型顺位提高1级</t>
         </is>
@@ -3372,7 +3369,7 @@
       <c r="C97" s="2" t="n">
         <v>235</v>
       </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="D97" s="0" t="inlineStr">
         <is>
           <t>SpecialTwoThreeFive</t>
         </is>
@@ -3380,7 +3377,7 @@
       <c r="E97" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F97" s="3" t="inlineStr">
+      <c r="F97" s="0" t="inlineStr">
         <is>
           <t>散排235牌型等同于豹子牌型,并且可以战胜所有牌型</t>
         </is>
@@ -3403,7 +3400,7 @@
       <c r="E98" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F98" s="3" t="inlineStr">
+      <c r="F98" s="0" t="inlineStr">
         <is>
           <t>获得500点生命值上限</t>
         </is>
@@ -3413,12 +3410,12 @@
       <c r="B99" s="2" t="n">
         <v>40003</v>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C99" s="0" t="inlineStr">
         <is>
           <t>老花眼</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="D99" s="0" t="inlineStr">
         <is>
           <t>SpecialFlush</t>
         </is>
@@ -3426,7 +3423,7 @@
       <c r="E99" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F99" s="3" t="inlineStr">
+      <c r="F99" s="0" t="inlineStr">
         <is>
           <t>红桃和方片视为同一花色,黑桃和梅花视为同一花色</t>
         </is>
@@ -3436,12 +3433,12 @@
       <c r="B100" s="2" t="n">
         <v>40004</v>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="C100" s="0" t="inlineStr">
         <is>
           <t>周星星</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D100" s="0" t="inlineStr">
         <is>
           <t>RubbingCardsNum</t>
         </is>
@@ -3449,7 +3446,7 @@
       <c r="E100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F100" s="3" t="inlineStr">
+      <c r="F100" s="0" t="inlineStr">
         <is>
           <t>每回合搓牌次数+1</t>
         </is>
@@ -3459,12 +3456,12 @@
       <c r="B101" s="2" t="n">
         <v>40005</v>
       </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="C101" s="0" t="inlineStr">
         <is>
           <t>穷途末路</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="D101" s="0" t="inlineStr">
         <is>
           <t>NoSkill</t>
         </is>
@@ -3472,7 +3469,7 @@
       <c r="E101" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F101" s="3" t="inlineStr">
+      <c r="F101" s="0" t="inlineStr">
         <is>
           <t>结算时,所有技能都无剩余使用次数,则提供+12倍率</t>
         </is>
@@ -3482,12 +3479,12 @@
       <c r="B102" s="2" t="n">
         <v>40006</v>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C102" s="0" t="inlineStr">
         <is>
           <t>收藏夹</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D102" s="0" t="inlineStr">
         <is>
           <t>EveryRelic</t>
         </is>
@@ -3495,9 +3492,9 @@
       <c r="E102" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>每有1个收藏品,结算时提供+1倍率</t>
+      <c r="F102" s="0" t="inlineStr">
+        <is>
+          <t>每有1个圣物,结算时提供+1倍率</t>
         </is>
       </c>
     </row>
@@ -3505,12 +3502,12 @@
       <c r="B103" s="2" t="n">
         <v>40007</v>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C103" s="0" t="inlineStr">
         <is>
           <t>奢侈品</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="D103" s="0" t="inlineStr">
         <is>
           <t>NoUseRubbingEveryRubbingNum</t>
         </is>
@@ -3518,7 +3515,7 @@
       <c r="E103" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F103" s="3" t="inlineStr">
+      <c r="F103" s="0" t="inlineStr">
         <is>
           <t>结算时,若未使用过搓牌,每个搓牌次数提供+3倍率</t>
         </is>
@@ -3528,12 +3525,12 @@
       <c r="B104" s="2" t="n">
         <v>40008</v>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="C104" s="0" t="inlineStr">
         <is>
           <t>近视眼</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr">
+      <c r="D104" s="0" t="inlineStr">
         <is>
           <t>AllCardIsHeadCard</t>
         </is>
@@ -3541,7 +3538,7 @@
       <c r="E104" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F104" s="3" t="inlineStr">
+      <c r="F104" s="0" t="inlineStr">
         <is>
           <t>所有牌均视为人头牌</t>
         </is>
@@ -3551,12 +3548,12 @@
       <c r="B105" s="2" t="n">
         <v>40009</v>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C105" s="0" t="inlineStr">
         <is>
           <t>顶尖学者</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="D105" s="0" t="inlineStr">
         <is>
           <t>SpecialACard</t>
         </is>
@@ -3564,7 +3561,7 @@
       <c r="E105" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F105" s="3" t="inlineStr">
+      <c r="F105" s="0" t="inlineStr">
         <is>
           <t>亮出的每张A在结算时提供+8倍率</t>
         </is>
@@ -3574,7 +3571,7 @@
       <c r="B106" s="2" t="n">
         <v>400091</v>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="C106" s="0" t="inlineStr">
         <is>
           <t>顶尖学者</t>
         </is>
@@ -3587,7 +3584,7 @@
       <c r="E106" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="F106" s="3" t="inlineStr">
+      <c r="F106" s="0" t="inlineStr">
         <is>
           <t>亮出的每张A在结算时提供+400攻击力</t>
         </is>
@@ -3597,12 +3594,12 @@
       <c r="B107" s="2" t="n">
         <v>40010</v>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="C107" s="0" t="inlineStr">
         <is>
           <t>老千</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
+      <c r="D107" s="0" t="inlineStr">
         <is>
           <t>AccumulatedNumOfCardType</t>
         </is>
@@ -3612,7 +3609,7 @@
           <t>0.5|10</t>
         </is>
       </c>
-      <c r="F107" s="3" t="inlineStr">
+      <c r="F107" s="0" t="inlineStr">
         <is>
           <t>亮牌时,该牌型本局内每重复亮出1次提供+0.5倍率,至多+10</t>
         </is>
@@ -3622,12 +3619,12 @@
       <c r="B108" s="2" t="n">
         <v>40011</v>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="C108" s="0" t="inlineStr">
         <is>
           <t>天使</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
+      <c r="D108" s="0" t="inlineStr">
         <is>
           <t>ProOfUpCardType</t>
         </is>
@@ -3635,7 +3632,7 @@
       <c r="E108" s="2" t="n">
         <v>0.35</v>
       </c>
-      <c r="F108" s="3" t="inlineStr">
+      <c r="F108" s="0" t="inlineStr">
         <is>
           <t>亮牌时,有25%概率将该牌型提供的倍率永久+1</t>
         </is>
@@ -3645,12 +3642,12 @@
       <c r="B109" s="2" t="n">
         <v>40012</v>
       </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="C109" s="0" t="inlineStr">
         <is>
           <t>双刃剑</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr">
+      <c r="D109" s="0" t="inlineStr">
         <is>
           <t>RubbingCardsNum</t>
         </is>
@@ -3658,7 +3655,7 @@
       <c r="E109" s="2" t="n">
         <v>-2</v>
       </c>
-      <c r="F109" s="3" t="inlineStr">
+      <c r="F109" s="0" t="inlineStr">
         <is>
           <t>每回合失去2次搓牌次数</t>
         </is>
@@ -3668,7 +3665,7 @@
       <c r="B110" s="2" t="n">
         <v>400121</v>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C110" s="0" t="inlineStr">
         <is>
           <t>双刃剑</t>
         </is>
@@ -3681,7 +3678,7 @@
       <c r="E110" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F110" s="3" t="inlineStr">
+      <c r="F110" s="0" t="inlineStr">
         <is>
           <t>结算时提供+10倍率</t>
         </is>
@@ -3691,12 +3688,12 @@
       <c r="B111" s="2" t="n">
         <v>40013</v>
       </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="C111" s="0" t="inlineStr">
         <is>
           <t>老搓家</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr">
+      <c r="D111" s="0" t="inlineStr">
         <is>
           <t>RubbingCardRelic</t>
         </is>
@@ -3704,9 +3701,9 @@
       <c r="E111" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t>每使用1次搓牌,结算时该收藏品永久提供+0.1倍率</t>
+      <c r="F111" s="0" t="inlineStr">
+        <is>
+          <t>每使用1次搓牌,结算时该圣物永久提供+0.1倍率</t>
         </is>
       </c>
     </row>
@@ -3714,12 +3711,12 @@
       <c r="B112" s="2" t="n">
         <v>40014</v>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="C112" s="0" t="inlineStr">
         <is>
           <t>幸运七</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
+      <c r="D112" s="0" t="inlineStr">
         <is>
           <t>SpecialSevenCardPro</t>
         </is>
@@ -3727,7 +3724,7 @@
       <c r="E112" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="F112" s="3" t="inlineStr">
+      <c r="F112" s="0" t="inlineStr">
         <is>
           <t>亮出的每张7结算时有25%概率提供攻击力和倍率</t>
         </is>
@@ -3737,12 +3734,12 @@
       <c r="B113" s="2" t="n">
         <v>400141</v>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C113" s="0" t="inlineStr">
         <is>
           <t>幸运七</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="D113" s="0" t="inlineStr">
         <is>
           <t>SpecialSevenCardAttack</t>
         </is>
@@ -3750,7 +3747,7 @@
       <c r="E113" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="F113" s="3" t="inlineStr">
+      <c r="F113" s="0" t="inlineStr">
         <is>
           <t>幸运七触发时提供的攻击力</t>
         </is>
@@ -3760,12 +3757,12 @@
       <c r="B114" s="2" t="n">
         <v>400142</v>
       </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="C114" s="0" t="inlineStr">
         <is>
           <t>幸运七</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
+      <c r="D114" s="0" t="inlineStr">
         <is>
           <t>SpecialSevenCard</t>
         </is>
@@ -3773,7 +3770,7 @@
       <c r="E114" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F114" s="3" t="inlineStr">
+      <c r="F114" s="0" t="inlineStr">
         <is>
           <t>幸运七触发时提供的倍率</t>
         </is>
@@ -3783,12 +3780,12 @@
       <c r="B115" s="2" t="n">
         <v>40015</v>
       </c>
-      <c r="C115" s="3" t="inlineStr">
+      <c r="C115" s="0" t="inlineStr">
         <is>
           <t>武林秘籍</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr">
+      <c r="D115" s="0" t="inlineStr">
         <is>
           <t>MissDamagePer</t>
         </is>
@@ -3796,7 +3793,7 @@
       <c r="E115" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F115" s="3" t="inlineStr">
+      <c r="F115" s="0" t="inlineStr">
         <is>
           <t>获得50%闪避率</t>
         </is>
@@ -3806,12 +3803,12 @@
       <c r="B116" s="2" t="n">
         <v>400151</v>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="C116" s="0" t="inlineStr">
         <is>
           <t>武林秘籍</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="D116" s="0" t="inlineStr">
         <is>
           <t>MissGetDamage</t>
         </is>
@@ -3821,7 +3818,7 @@
           <t>1|2</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr">
+      <c r="F116" s="0" t="inlineStr">
         <is>
           <t>闪避成功时会对敌人造成1次自身攻击力200%的伤害</t>
         </is>
@@ -3831,12 +3828,12 @@
       <c r="B117" s="2" t="n">
         <v>40016</v>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C117" s="0" t="inlineStr">
         <is>
           <t>幸运对子</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D117" s="0" t="inlineStr">
         <is>
           <t>LuckyCouplet</t>
         </is>
@@ -3844,7 +3841,7 @@
       <c r="E117" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F117" s="3" t="inlineStr">
+      <c r="F117" s="0" t="inlineStr">
         <is>
           <t>亮牌时,若敌人的牌型大于对子,则会被强行视作对子</t>
         </is>
@@ -3854,12 +3851,12 @@
       <c r="B118" s="2" t="n">
         <v>40017</v>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C118" s="0" t="inlineStr">
         <is>
           <t>小强</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D118" s="0" t="inlineStr">
         <is>
           <t>DefeatGetDamage</t>
         </is>
@@ -3869,7 +3866,7 @@
           <t>1|0.05</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr">
+      <c r="F118" s="0" t="inlineStr">
         <is>
           <t>每输1次敌人,后续自身造成的所有伤害提高5%</t>
         </is>
@@ -3879,7 +3876,7 @@
       <c r="B119" s="2" t="n">
         <v>40018</v>
       </c>
-      <c r="C119" s="3" t="inlineStr">
+      <c r="C119" s="0" t="inlineStr">
         <is>
           <t>救命稻草</t>
         </is>
@@ -3894,7 +3891,7 @@
           <t>0.2</t>
         </is>
       </c>
-      <c r="F119" s="3" t="inlineStr">
+      <c r="F119" s="0" t="inlineStr">
         <is>
           <t>如果你受到了1次致命伤害,会将血量降低为1,且下次造成伤害的同时恢复本次伤害20%的血量,每关生效1次</t>
         </is>
@@ -3904,7 +3901,7 @@
       <c r="B120" s="2" t="n">
         <v>40019</v>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C120" s="0" t="inlineStr">
         <is>
           <t>专注</t>
         </is>
@@ -3919,7 +3916,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr">
+      <c r="F120" s="0" t="inlineStr">
         <is>
           <t>当场上只剩下一个敌人时,你对其造成的伤害+100%</t>
         </is>
@@ -3929,7 +3926,7 @@
       <c r="B121" s="2" t="n">
         <v>40020</v>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C121" s="0" t="inlineStr">
         <is>
           <t>变形魔方</t>
         </is>
@@ -3944,7 +3941,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F121" s="3" t="inlineStr">
+      <c r="F121" s="0" t="inlineStr">
         <is>
           <t>每回合亮出的牌型强制提升一级</t>
         </is>
@@ -3954,7 +3951,7 @@
       <c r="B122" s="2" t="n">
         <v>40021</v>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C122" s="0" t="inlineStr">
         <is>
           <t>毒药</t>
         </is>
@@ -3969,7 +3966,7 @@
           <t>-0.3</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr">
+      <c r="F122" s="0" t="inlineStr">
         <is>
           <t>所有敌人血量降低30%[BOSS除外]</t>
         </is>
@@ -3979,7 +3976,7 @@
       <c r="B123" s="2" t="n">
         <v>40022</v>
       </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="C123" s="0" t="inlineStr">
         <is>
           <t>刺客秘籍</t>
         </is>
@@ -3994,7 +3991,7 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="F123" s="3" t="inlineStr">
+      <c r="F123" s="0" t="inlineStr">
         <is>
           <t>获得50%暴击率</t>
         </is>
@@ -4004,7 +4001,7 @@
       <c r="B124" s="2" t="n">
         <v>400221</v>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="C124" s="0" t="inlineStr">
         <is>
           <t>刺客秘籍</t>
         </is>
@@ -4019,7 +4016,7 @@
           <t>1|1</t>
         </is>
       </c>
-      <c r="F124" s="3" t="inlineStr">
+      <c r="F124" s="0" t="inlineStr">
         <is>
           <t>触发暴击时会对其他敌人造成1次自身攻击力100%的伤害</t>
         </is>
@@ -4029,7 +4026,7 @@
       <c r="B125" s="2" t="n">
         <v>40023</v>
       </c>
-      <c r="C125" s="3" t="inlineStr">
+      <c r="C125" s="0" t="inlineStr">
         <is>
           <t>透视眼</t>
         </is>
@@ -4044,7 +4041,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F125" s="3" t="inlineStr">
+      <c r="F125" s="0" t="inlineStr">
         <is>
           <t>每回合透视次数+1</t>
         </is>
@@ -4054,7 +4051,7 @@
       <c r="B126" s="2" t="n">
         <v>40024</v>
       </c>
-      <c r="C126" s="3" t="inlineStr">
+      <c r="C126" s="0" t="inlineStr">
         <is>
           <t>聚宝盆</t>
         </is>
@@ -4067,7 +4064,7 @@
       <c r="E126" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="F126" s="3" t="inlineStr">
+      <c r="F126" s="0" t="inlineStr">
         <is>
           <t>每回合结束后,本回合自身总伤害输出的15%转化为金币</t>
         </is>
@@ -4077,7 +4074,7 @@
       <c r="B127" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="C127" s="3" t="inlineStr">
+      <c r="C127" s="0" t="inlineStr">
         <is>
           <t>差距胶囊</t>
         </is>
@@ -4092,7 +4089,7 @@
           <t>1|0.2</t>
         </is>
       </c>
-      <c r="F127" s="3" t="inlineStr">
+      <c r="F127" s="0" t="inlineStr">
         <is>
           <t>比牌时,你的牌型与对方牌型每相隔1级,则造成/承受的伤害对应提高/降低20%</t>
         </is>
@@ -4102,12 +4099,12 @@
       <c r="B128" s="2" t="n">
         <v>40026</v>
       </c>
-      <c r="C128" s="3" t="inlineStr">
+      <c r="C128" s="0" t="inlineStr">
         <is>
           <t>神之左手</t>
         </is>
       </c>
-      <c r="D128" s="3" t="inlineStr">
+      <c r="D128" s="0" t="inlineStr">
         <is>
           <t>UseDamageFixed</t>
         </is>
@@ -4115,7 +4112,7 @@
       <c r="E128" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F128" s="3" t="inlineStr">
+      <c r="F128" s="0" t="inlineStr">
         <is>
           <t>使用后,本次比牌你造成的伤害固定为500点</t>
         </is>
@@ -4125,12 +4122,12 @@
       <c r="B129" s="2" t="n">
         <v>40027</v>
       </c>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="C129" s="0" t="inlineStr">
         <is>
           <t>凤凰羽毛</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="D129" s="0" t="inlineStr">
         <is>
           <t>UseRoundNullify</t>
         </is>
@@ -4140,7 +4137,7 @@
           <t>1|0.3</t>
         </is>
       </c>
-      <c r="F129" s="3" t="inlineStr">
+      <c r="F129" s="0" t="inlineStr">
         <is>
           <t>使用后,本次比牌你受到的所有伤害变为0,并立即恢复30%最大生命</t>
         </is>
@@ -4150,12 +4147,12 @@
       <c r="B130" s="2" t="n">
         <v>40028</v>
       </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="C130" s="0" t="inlineStr">
         <is>
           <t>时光宝盒</t>
         </is>
       </c>
-      <c r="D130" s="3" t="inlineStr">
+      <c r="D130" s="0" t="inlineStr">
         <is>
           <t>RandomHandTypeMagUp</t>
         </is>
@@ -4165,7 +4162,7 @@
           <t>6|3</t>
         </is>
       </c>
-      <c r="F130" s="3" t="inlineStr">
+      <c r="F130" s="0" t="inlineStr">
         <is>
           <t>使用后,随机3种牌型的倍率永久+5</t>
         </is>
@@ -4175,12 +4172,12 @@
       <c r="B131" s="2" t="n">
         <v>40029</v>
       </c>
-      <c r="C131" s="3" t="inlineStr">
+      <c r="C131" s="0" t="inlineStr">
         <is>
           <t>龙心</t>
         </is>
       </c>
-      <c r="D131" s="3" t="inlineStr">
+      <c r="D131" s="0" t="inlineStr">
         <is>
           <t>MaxHpUpAndHeal</t>
         </is>
@@ -4188,7 +4185,7 @@
       <c r="E131" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="F131" s="3" t="inlineStr">
+      <c r="F131" s="0" t="inlineStr">
         <is>
           <t>使用后,永久获得120点生命上限,并立即恢复120点生命</t>
         </is>
@@ -4198,12 +4195,12 @@
       <c r="B132" s="2" t="n">
         <v>40030</v>
       </c>
-      <c r="C132" s="3" t="inlineStr">
+      <c r="C132" s="0" t="inlineStr">
         <is>
           <t>贪欲之冠</t>
         </is>
       </c>
-      <c r="D132" s="3" t="inlineStr">
+      <c r="D132" s="0" t="inlineStr">
         <is>
           <t>GoldDamageScale</t>
         </is>
@@ -4213,7 +4210,7 @@
           <t>40|8|1</t>
         </is>
       </c>
-      <c r="F132" s="3" t="inlineStr">
+      <c r="F132" s="0" t="inlineStr">
         <is>
           <t>每拥有40金币,你造成的伤害+8%,至多+100%</t>
         </is>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -4106,15 +4106,15 @@
       </c>
       <c r="D128" s="0" t="inlineStr">
         <is>
-          <t>UseDamageFixed</t>
+          <t>UseDamageMul</t>
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>500</v>
+        <v>3</v>
       </c>
       <c r="F128" s="0" t="inlineStr">
         <is>
-          <t>使用后,本次比牌你造成的伤害固定为500点</t>
+          <t>使用后,本次比牌你造成的伤害提高300%</t>
         </is>
       </c>
     </row>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="13170" windowHeight="10470"/>
+    <workbookView windowWidth="13170" windowHeight="11550"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="470">
   <si>
     <t>##var</t>
   </si>
@@ -682,6 +682,36 @@
     <t>使用后,顺子牌型提供的倍率永久+1</t>
   </si>
   <si>
+    <t>20033</t>
+  </si>
+  <si>
+    <t>第一位</t>
+  </si>
+  <si>
+    <t>CardProvideAttack</t>
+  </si>
+  <si>
+    <t>亮牌时的第一张牌提供其点数对应的攻击力加成</t>
+  </si>
+  <si>
+    <t>20034</t>
+  </si>
+  <si>
+    <t>第二位</t>
+  </si>
+  <si>
+    <t>亮牌时的第二张牌提供其点数对应的攻击力加成</t>
+  </si>
+  <si>
+    <t>20035</t>
+  </si>
+  <si>
+    <t>第三位</t>
+  </si>
+  <si>
+    <t>亮牌时的第三张牌提供其点数对应的攻击力加成</t>
+  </si>
+  <si>
     <t>30001</t>
   </si>
   <si>
@@ -1073,6 +1103,18 @@
   </si>
   <si>
     <t>使用后,移除本关内的1条BOSS词缀效果</t>
+  </si>
+  <si>
+    <t>30032</t>
+  </si>
+  <si>
+    <t>三花聚顶</t>
+  </si>
+  <si>
+    <t>1|2|3</t>
+  </si>
+  <si>
+    <t>亮出的每张牌都提供其点数对应的攻击力加成</t>
   </si>
   <si>
     <t>SpecialTwoThreeFive</t>
@@ -1571,18 +1613,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1909,7 +1945,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -1933,16 +1969,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
@@ -1951,89 +1987,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2061,7 +2097,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2070,13 +2106,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2427,7 +2457,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="5.75833333333333" style="3" customWidth="1"/>
@@ -3079,7 +3109,7 @@
       </c>
     </row>
     <row r="39" s="2" customFormat="1" spans="2:7">
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C39" s="8" t="s">
@@ -3091,7 +3121,7 @@
       <c r="E39" s="8">
         <v>3</v>
       </c>
-      <c r="F39" s="13" t="s">
+      <c r="F39" s="12" t="s">
         <v>133</v>
       </c>
       <c r="G39" s="10"/>
@@ -3199,7 +3229,7 @@
       </c>
     </row>
     <row r="46" s="2" customFormat="1" spans="2:7">
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C46" s="8" t="s">
@@ -3211,13 +3241,13 @@
       <c r="E46" s="8">
         <v>1</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" s="9" t="s">
         <v>163</v>
       </c>
       <c r="G46" s="10"/>
     </row>
     <row r="47" s="2" customFormat="1" spans="2:7">
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C47" s="8" t="s">
@@ -3229,7 +3259,7 @@
       <c r="E47" s="8">
         <v>3</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F47" s="9" t="s">
         <v>167</v>
       </c>
       <c r="G47" s="10"/>
@@ -3320,7 +3350,7 @@
       </c>
     </row>
     <row r="53" s="2" customFormat="1" spans="2:7">
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="2" t="s">
         <v>189</v>
       </c>
       <c r="C53" s="8" t="s">
@@ -3332,7 +3362,7 @@
       <c r="E53" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="9" t="s">
         <v>193</v>
       </c>
       <c r="G53" s="10"/>
@@ -3440,986 +3470,990 @@
         <v>215</v>
       </c>
     </row>
-    <row r="60" spans="2:7">
-      <c r="C60"/>
-      <c r="E60" s="4"/>
-      <c r="F60"/>
-    </row>
-    <row r="61" spans="2:7">
-      <c r="B61" s="3" t="s">
+    <row r="60" s="2" customFormat="1" spans="2:7">
+      <c r="B60" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C60" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D60" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E60" s="8">
+        <v>1</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G60" s="10"/>
+    </row>
+    <row r="61" s="2" customFormat="1" spans="2:7">
+      <c r="B61" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E61" s="8">
+        <v>2</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G61" s="10"/>
+    </row>
+    <row r="62" s="2" customFormat="1" spans="2:7">
+      <c r="B62" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E62" s="8">
+        <v>3</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="G62" s="10"/>
+    </row>
+    <row r="63" spans="2:7">
+      <c r="C63"/>
+      <c r="E63" s="4"/>
+      <c r="F63"/>
+    </row>
+    <row r="64" spans="2:7">
+      <c r="B64" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C64" t="s">
+        <v>227</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E64" s="4">
         <v>0.05</v>
       </c>
-      <c r="F61" s="11" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="62" spans="2:7">
-      <c r="B62" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C62" t="s">
-        <v>221</v>
-      </c>
-      <c r="D62" t="s">
-        <v>222</v>
-      </c>
-      <c r="E62" s="4">
-        <v>2</v>
-      </c>
-      <c r="F62" s="11" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7">
-      <c r="B63" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C63" t="s">
-        <v>225</v>
-      </c>
-      <c r="D63" t="s">
-        <v>226</v>
-      </c>
-      <c r="E63" s="4">
-        <v>4</v>
-      </c>
-      <c r="F63" s="11" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="64" s="2" customFormat="1" spans="2:7">
-      <c r="B64" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="C64" s="10" t="s">
+      <c r="F64" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="D64" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="E64" s="8">
-        <v>1</v>
-      </c>
-      <c r="F64" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="G64" s="10"/>
     </row>
     <row r="65" spans="2:7">
       <c r="B65" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C65" t="s">
+        <v>231</v>
+      </c>
+      <c r="D65" t="s">
         <v>232</v>
       </c>
-      <c r="C65" t="s">
+      <c r="E65" s="4">
+        <v>2</v>
+      </c>
+      <c r="F65" s="11" t="s">
         <v>233</v>
-      </c>
-      <c r="D65" t="s">
-        <v>234</v>
-      </c>
-      <c r="E65" s="4">
-        <v>1</v>
-      </c>
-      <c r="F65" s="11" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="66" spans="2:7">
       <c r="B66" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C66" t="s">
+        <v>235</v>
+      </c>
+      <c r="D66" t="s">
         <v>236</v>
       </c>
-      <c r="C66" t="s">
+      <c r="E66" s="4">
+        <v>4</v>
+      </c>
+      <c r="F66" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="D66" t="s">
+    </row>
+    <row r="67" s="2" customFormat="1" spans="2:7">
+      <c r="B67" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E66" s="4">
+      <c r="C67" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="E67" s="8">
         <v>1</v>
       </c>
-      <c r="F66" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7">
-      <c r="B67" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C67" t="s">
+      <c r="F67" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="D67" t="s">
-        <v>242</v>
-      </c>
-      <c r="E67" s="4">
-        <v>50</v>
-      </c>
-      <c r="F67" s="11" t="s">
-        <v>243</v>
-      </c>
+      <c r="G67" s="10"/>
     </row>
     <row r="68" spans="2:7">
       <c r="B68" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C68" t="s">
+        <v>243</v>
+      </c>
+      <c r="D68" t="s">
         <v>244</v>
       </c>
-      <c r="C68" t="s">
+      <c r="E68" s="4">
+        <v>1</v>
+      </c>
+      <c r="F68" s="11" t="s">
         <v>245</v>
-      </c>
-      <c r="D68" t="s">
-        <v>246</v>
-      </c>
-      <c r="E68" s="4">
-        <v>4</v>
-      </c>
-      <c r="F68" s="11" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="69" spans="2:7">
       <c r="B69" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C69" t="s">
+        <v>247</v>
+      </c>
+      <c r="D69" t="s">
         <v>248</v>
       </c>
-      <c r="C69" t="s">
+      <c r="E69" s="4">
+        <v>1</v>
+      </c>
+      <c r="F69" s="11" t="s">
         <v>249</v>
-      </c>
-      <c r="D69" t="s">
-        <v>250</v>
-      </c>
-      <c r="E69" s="4">
-        <v>4</v>
-      </c>
-      <c r="F69" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="70" spans="2:7">
       <c r="B70" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C70" t="s">
+        <v>251</v>
+      </c>
+      <c r="D70" t="s">
         <v>252</v>
       </c>
-      <c r="C70" t="s">
+      <c r="E70" s="4">
+        <v>50</v>
+      </c>
+      <c r="F70" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="D70" s="4" t="s">
+    </row>
+    <row r="71" spans="2:7">
+      <c r="B71" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="E70" s="4">
-        <v>5</v>
-      </c>
-      <c r="F70" t="s">
+      <c r="C71" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="71" s="2" customFormat="1" spans="2:7">
-      <c r="B71" s="12" t="s">
+      <c r="D71" t="s">
         <v>256</v>
       </c>
-      <c r="C71" s="10" t="s">
+      <c r="E71" s="4">
+        <v>4</v>
+      </c>
+      <c r="F71" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="D71" s="10" t="s">
+    </row>
+    <row r="72" spans="2:7">
+      <c r="B72" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E71" s="8">
-        <v>50</v>
-      </c>
-      <c r="F71" s="14" t="s">
+      <c r="C72" t="s">
         <v>259</v>
       </c>
-      <c r="G71" s="10"/>
-    </row>
-    <row r="72" s="2" customFormat="1" spans="2:7">
-      <c r="B72" s="12" t="s">
+      <c r="D72" t="s">
         <v>260</v>
       </c>
-      <c r="C72" s="10" t="s">
+      <c r="E72" s="4">
+        <v>4</v>
+      </c>
+      <c r="F72" t="s">
         <v>261</v>
       </c>
-      <c r="D72" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="F72" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="G72" s="10"/>
     </row>
     <row r="73" spans="2:7">
       <c r="B73" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C73" t="s">
+        <v>263</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E73" s="4">
+        <v>5</v>
+      </c>
+      <c r="F73" t="s">
         <v>265</v>
       </c>
-      <c r="C73" t="s">
+    </row>
+    <row r="74" s="2" customFormat="1" spans="2:7">
+      <c r="B74" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="D73" t="s">
+      <c r="C74" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="E73" s="4">
-        <v>30</v>
-      </c>
-      <c r="F73" s="11" t="s">
+      <c r="D74" s="10" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="74" spans="2:7">
-      <c r="B74" s="3" t="s">
+      <c r="E74" s="8">
+        <v>50</v>
+      </c>
+      <c r="F74" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="G74" s="10"/>
+    </row>
+    <row r="75" s="2" customFormat="1" spans="2:7">
+      <c r="B75" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D74" t="s">
+      <c r="C75" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="D75" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="F74" s="11" t="s">
+      <c r="E75" s="8" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="75" spans="2:7">
-      <c r="B75" s="3" t="s">
+      <c r="F75" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="C75" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="D75" t="s">
-        <v>276</v>
-      </c>
-      <c r="E75" s="4">
-        <v>1</v>
-      </c>
-      <c r="F75" s="11" t="s">
-        <v>277</v>
-      </c>
+      <c r="G75" s="10"/>
     </row>
     <row r="76" spans="2:7">
       <c r="B76" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C76" t="s">
+        <v>276</v>
+      </c>
+      <c r="D76" t="s">
+        <v>277</v>
+      </c>
+      <c r="E76" s="4">
+        <v>30</v>
+      </c>
+      <c r="F76" s="11" t="s">
         <v>278</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="D76" t="s">
-        <v>280</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="F76" s="11" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="77" spans="2:7">
       <c r="B77" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D77" t="s">
+        <v>281</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="F77" s="11" t="s">
         <v>283</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="D77" t="s">
-        <v>285</v>
-      </c>
-      <c r="E77" s="4">
-        <v>3</v>
-      </c>
-      <c r="F77" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="78" spans="2:7">
       <c r="B78" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D78" t="s">
+        <v>286</v>
+      </c>
+      <c r="E78" s="4">
+        <v>1</v>
+      </c>
+      <c r="F78" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="C78" s="4" t="s">
+    </row>
+    <row r="79" spans="2:7">
+      <c r="B79" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="D78" t="s">
+      <c r="C79" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="E78" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F78" s="11" t="s">
+      <c r="D79" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="79" s="2" customFormat="1" spans="2:7">
-      <c r="B79" s="12" t="s">
+      <c r="E79" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="F79" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="D79" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="F79" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="G79" s="10"/>
     </row>
     <row r="80" spans="2:7">
       <c r="B80" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D80" t="s">
+        <v>295</v>
+      </c>
+      <c r="E80" s="4">
+        <v>3</v>
+      </c>
+      <c r="F80" t="s">
         <v>296</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="D80" t="s">
-        <v>298</v>
-      </c>
-      <c r="E80" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F80" s="11" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="81" spans="2:7">
       <c r="B81" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D81" t="s">
+        <v>299</v>
+      </c>
+      <c r="E81" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F81" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="C81" s="4" t="s">
+    </row>
+    <row r="82" s="2" customFormat="1" spans="2:7">
+      <c r="B82" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D81" t="s">
+      <c r="C82" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="D82" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="F81" s="11" t="s">
+      <c r="E82" s="8" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="82" spans="2:7">
-      <c r="B82" s="3" t="s">
+      <c r="F82" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="C82" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="D82" t="s">
-        <v>307</v>
-      </c>
-      <c r="E82" s="4">
-        <v>-0.3</v>
-      </c>
-      <c r="F82" s="11" t="s">
-        <v>308</v>
-      </c>
+      <c r="G82" s="10"/>
     </row>
     <row r="83" spans="2:7">
       <c r="B83" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="D83" t="s">
+        <v>308</v>
+      </c>
+      <c r="E83" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F83" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="C83" s="4" t="s">
+    </row>
+    <row r="84" spans="2:7">
+      <c r="B84" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="D83" t="s">
+      <c r="C84" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="E83" s="4" t="s">
+      <c r="D84" t="s">
         <v>312</v>
       </c>
-      <c r="F83" s="11" t="s">
+      <c r="E84" s="4" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="84" s="2" customFormat="1" spans="2:7">
-      <c r="B84" s="12" t="s">
+      <c r="F84" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="C84" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="E84" s="8">
-        <v>1</v>
-      </c>
-      <c r="F84" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="G84" s="10"/>
     </row>
     <row r="85" spans="2:7">
       <c r="B85" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D85" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E85" s="4">
         <v>-0.3</v>
       </c>
       <c r="F85" s="11" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7">
+      <c r="B86" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D86" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="86" s="2" customFormat="1" spans="2:7">
-      <c r="B86" s="12" t="s">
+      <c r="E86" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="C86" s="10" t="s">
+      <c r="F86" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="D86" s="10" t="s">
+    </row>
+    <row r="87" s="2" customFormat="1" spans="2:7">
+      <c r="B87" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E86" s="8">
+      <c r="C87" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="E87" s="8">
+        <v>1</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="G87" s="10"/>
+    </row>
+    <row r="88" spans="2:7">
+      <c r="B88" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D88" t="s">
+        <v>330</v>
+      </c>
+      <c r="E88" s="4">
+        <v>-0.3</v>
+      </c>
+      <c r="F88" s="11" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="89" s="2" customFormat="1" spans="2:7">
+      <c r="B89" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="E89" s="8">
         <v>300</v>
       </c>
-      <c r="F86" s="14" t="s">
-        <v>325</v>
-      </c>
-      <c r="G86" s="10"/>
-    </row>
-    <row r="87" s="2" customFormat="1" spans="2:7">
-      <c r="B87" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="D87" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="E87" s="8">
+      <c r="F89" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="G89" s="10"/>
+    </row>
+    <row r="90" s="2" customFormat="1" spans="2:7">
+      <c r="B90" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="E90" s="8">
         <v>0.2</v>
       </c>
-      <c r="F87" s="14" t="s">
-        <v>329</v>
-      </c>
-      <c r="G87" s="10"/>
-    </row>
-    <row r="88" s="2" customFormat="1" spans="2:7">
-      <c r="B88" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="C88" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="D88" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="F88" s="14" t="s">
-        <v>334</v>
-      </c>
-      <c r="G88" s="10"/>
-    </row>
-    <row r="89" spans="2:7">
-      <c r="B89" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C89" t="s">
-        <v>336</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="E89" s="4">
+      <c r="F90" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="G90" s="10"/>
+    </row>
+    <row r="91" s="2" customFormat="1" spans="2:7">
+      <c r="B91" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="G91" s="10"/>
+    </row>
+    <row r="92" spans="2:7">
+      <c r="B92" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C92" t="s">
+        <v>346</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E92" s="4">
         <v>-1</v>
       </c>
-      <c r="F89" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="90" spans="2:7">
-      <c r="B90" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="C90" t="s">
-        <v>340</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="E90" s="4">
-        <v>1</v>
-      </c>
-      <c r="F90" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="91" spans="2:7">
-      <c r="B91" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C91" t="s">
-        <v>344</v>
-      </c>
-      <c r="D91" t="s">
-        <v>345</v>
-      </c>
-      <c r="E91" s="4">
-        <v>1</v>
-      </c>
-      <c r="F91" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="92" spans="2:7">
-      <c r="B92" s="4"/>
-      <c r="D92"/>
-      <c r="E92" s="4"/>
-      <c r="F92"/>
+      <c r="F92" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="93" spans="2:7">
-      <c r="B93" s="4">
-        <v>40001</v>
-      </c>
-      <c r="C93" s="4">
-        <v>235</v>
-      </c>
-      <c r="D93" t="s">
-        <v>347</v>
+      <c r="B93" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C93" t="s">
+        <v>350</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>351</v>
       </c>
       <c r="E93" s="4">
         <v>1</v>
       </c>
-      <c r="F93" s="11" t="s">
-        <v>348</v>
+      <c r="F93" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="94" spans="2:7">
-      <c r="B94" s="4">
+      <c r="B94" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C94" t="s">
+        <v>354</v>
+      </c>
+      <c r="D94" t="s">
+        <v>355</v>
+      </c>
+      <c r="E94" s="4">
+        <v>1</v>
+      </c>
+      <c r="F94" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="95" s="2" customFormat="1" spans="2:7">
+      <c r="B95" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="G95" s="10"/>
+    </row>
+    <row r="96" spans="2:7">
+      <c r="B96" s="4"/>
+      <c r="D96"/>
+      <c r="E96" s="4"/>
+      <c r="F96"/>
+    </row>
+    <row r="97" spans="2:7">
+      <c r="B97" s="4">
+        <v>40001</v>
+      </c>
+      <c r="C97" s="4">
+        <v>235</v>
+      </c>
+      <c r="D97" t="s">
+        <v>361</v>
+      </c>
+      <c r="E97" s="4">
+        <v>1</v>
+      </c>
+      <c r="F97" s="11" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7">
+      <c r="B98" s="4">
         <v>40002</v>
       </c>
-      <c r="C94" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="D94" s="4" t="s">
+      <c r="C98" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E94" s="4">
+      <c r="E98" s="4">
         <v>500</v>
       </c>
-      <c r="F94" s="11" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="95" spans="2:7">
-      <c r="B95" s="4">
+      <c r="F98" s="11" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7">
+      <c r="B99" s="4">
         <v>40003</v>
       </c>
-      <c r="C95" t="s">
-        <v>351</v>
-      </c>
-      <c r="D95" t="s">
-        <v>352</v>
-      </c>
-      <c r="E95" s="4">
+      <c r="C99" t="s">
+        <v>365</v>
+      </c>
+      <c r="D99" t="s">
+        <v>366</v>
+      </c>
+      <c r="E99" s="4">
         <v>1</v>
       </c>
-      <c r="F95" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="96" s="2" customFormat="1" spans="2:7">
-      <c r="B96" s="8">
+      <c r="F99" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="100" s="2" customFormat="1" spans="2:7">
+      <c r="B100" s="8">
         <v>40004</v>
       </c>
-      <c r="C96" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="D96" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="E96" s="8">
+      <c r="C100" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="D100" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="E100" s="8">
         <v>1</v>
       </c>
-      <c r="F96" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="G96" s="10"/>
-    </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="4">
+      <c r="F100" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="G100" s="10"/>
+    </row>
+    <row r="101" spans="2:7">
+      <c r="B101" s="4">
         <v>40005</v>
       </c>
-      <c r="C97" t="s">
-        <v>357</v>
-      </c>
-      <c r="D97" t="s">
-        <v>358</v>
-      </c>
-      <c r="E97" s="4">
+      <c r="C101" t="s">
+        <v>371</v>
+      </c>
+      <c r="D101" t="s">
+        <v>372</v>
+      </c>
+      <c r="E101" s="4">
         <v>12</v>
       </c>
-      <c r="F97" s="11" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="98" spans="2:6">
-      <c r="B98" s="4">
+      <c r="F101" s="11" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7">
+      <c r="B102" s="4">
         <v>40006</v>
       </c>
-      <c r="C98" t="s">
-        <v>360</v>
-      </c>
-      <c r="D98" t="s">
-        <v>361</v>
-      </c>
-      <c r="E98" s="4">
+      <c r="C102" t="s">
+        <v>374</v>
+      </c>
+      <c r="D102" t="s">
+        <v>375</v>
+      </c>
+      <c r="E102" s="4">
         <v>3</v>
       </c>
-      <c r="F98" s="11" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="99" s="2" customFormat="1" spans="2:6">
-      <c r="B99" s="8">
+      <c r="F102" s="11" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="103" s="2" customFormat="1" spans="2:7">
+      <c r="B103" s="8">
         <v>40007</v>
       </c>
-      <c r="C99" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="D99" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="E99" s="8">
+      <c r="C103" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="D103" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="E103" s="8">
         <v>2</v>
       </c>
-      <c r="F99" s="14" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="100" s="3" customFormat="1" spans="2:6">
-      <c r="B100" s="4">
+      <c r="F103" s="9" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="104" s="3" customFormat="1" spans="2:7">
+      <c r="B104" s="4">
         <v>40008</v>
       </c>
-      <c r="C100" t="s">
-        <v>366</v>
-      </c>
-      <c r="D100" t="s">
-        <v>367</v>
-      </c>
-      <c r="E100" s="4">
+      <c r="C104" t="s">
+        <v>380</v>
+      </c>
+      <c r="D104" t="s">
+        <v>381</v>
+      </c>
+      <c r="E104" s="4">
         <v>1</v>
       </c>
-      <c r="F100" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="101" s="3" customFormat="1" spans="2:6">
-      <c r="B101" s="4">
+      <c r="F104" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="105" s="3" customFormat="1" spans="2:7">
+      <c r="B105" s="4">
         <v>40009</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C105" t="s">
+        <v>383</v>
+      </c>
+      <c r="D105" t="s">
+        <v>384</v>
+      </c>
+      <c r="E105" s="4">
+        <v>8</v>
+      </c>
+      <c r="F105" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="106" s="3" customFormat="1" spans="2:7">
+      <c r="B106" s="4">
+        <v>400091</v>
+      </c>
+      <c r="C106" t="s">
+        <v>383</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="E106" s="4">
+        <v>50</v>
+      </c>
+      <c r="F106" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="107" s="2" customFormat="1" spans="2:7">
+      <c r="B107" s="8">
+        <v>40010</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="108" s="3" customFormat="1" spans="2:7">
+      <c r="B108" s="4">
+        <v>40011</v>
+      </c>
+      <c r="C108" t="s">
+        <v>391</v>
+      </c>
+      <c r="D108" t="s">
+        <v>392</v>
+      </c>
+      <c r="E108" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F108" s="11" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="109" s="2" customFormat="1" spans="2:7">
+      <c r="B109" s="8">
+        <v>40012</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D109" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="D101" t="s">
-        <v>370</v>
-      </c>
-      <c r="E101" s="4">
-        <v>8</v>
-      </c>
-      <c r="F101" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="102" s="3" customFormat="1" spans="2:6">
-      <c r="B102" s="4">
-        <v>400091</v>
-      </c>
-      <c r="C102" t="s">
-        <v>369</v>
-      </c>
-      <c r="D102" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="E102" s="4">
-        <v>50</v>
-      </c>
-      <c r="F102" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="103" s="2" customFormat="1" spans="2:6">
-      <c r="B103" s="8">
-        <v>40010</v>
-      </c>
-      <c r="C103" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="D103" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="E103" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="F103" s="14" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="104" s="3" customFormat="1" spans="2:6">
-      <c r="B104" s="4">
-        <v>40011</v>
-      </c>
-      <c r="C104" t="s">
-        <v>377</v>
-      </c>
-      <c r="D104" t="s">
-        <v>378</v>
-      </c>
-      <c r="E104" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F104" s="11" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="105" s="2" customFormat="1" spans="2:6">
-      <c r="B105" s="8">
-        <v>40012</v>
-      </c>
-      <c r="C105" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="D105" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="E105" s="8">
+      <c r="E109" s="8">
         <v>-2</v>
       </c>
-      <c r="F105" s="10" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="106" s="2" customFormat="1" spans="2:6">
-      <c r="B106" s="8">
+      <c r="F109" s="10" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="110" s="2" customFormat="1" spans="2:7">
+      <c r="B110" s="8">
         <v>400121</v>
       </c>
-      <c r="C106" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="D106" s="2" t="s">
+      <c r="C110" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D110" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E106" s="8">
+      <c r="E110" s="8">
         <v>15</v>
       </c>
-      <c r="F106" s="10" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="107" s="3" customFormat="1" spans="2:6">
-      <c r="B107" s="4">
+      <c r="F110" s="10" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="111" s="3" customFormat="1" spans="2:7">
+      <c r="B111" s="4">
         <v>40013</v>
       </c>
-      <c r="C107" t="s">
-        <v>383</v>
-      </c>
-      <c r="D107" t="s">
-        <v>384</v>
-      </c>
-      <c r="E107" s="4">
+      <c r="C111" t="s">
+        <v>397</v>
+      </c>
+      <c r="D111" t="s">
+        <v>398</v>
+      </c>
+      <c r="E111" s="4">
         <v>0.1</v>
       </c>
-      <c r="F107" s="11" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="108" s="3" customFormat="1" spans="2:6">
-      <c r="B108" s="4">
+      <c r="F111" s="11" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="112" s="3" customFormat="1" spans="2:7">
+      <c r="B112" s="4">
         <v>40014</v>
       </c>
-      <c r="C108" t="s">
-        <v>386</v>
-      </c>
-      <c r="D108" t="s">
-        <v>387</v>
-      </c>
-      <c r="E108" s="4">
+      <c r="C112" t="s">
+        <v>400</v>
+      </c>
+      <c r="D112" t="s">
+        <v>401</v>
+      </c>
+      <c r="E112" s="4">
         <v>1</v>
       </c>
-      <c r="F108" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="109" spans="2:6">
-      <c r="B109" s="4">
-        <v>400141</v>
-      </c>
-      <c r="C109" t="s">
-        <v>386</v>
-      </c>
-      <c r="D109" t="s">
-        <v>389</v>
-      </c>
-      <c r="E109" s="4">
-        <v>77</v>
-      </c>
-      <c r="F109" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="110" spans="2:6">
-      <c r="B110" s="4">
-        <v>400142</v>
-      </c>
-      <c r="C110" t="s">
-        <v>386</v>
-      </c>
-      <c r="D110" t="s">
-        <v>391</v>
-      </c>
-      <c r="E110" s="4">
-        <v>7</v>
-      </c>
-      <c r="F110" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="111" spans="2:6">
-      <c r="B111" s="4">
-        <v>40015</v>
-      </c>
-      <c r="C111" t="s">
-        <v>393</v>
-      </c>
-      <c r="D111" t="s">
-        <v>394</v>
-      </c>
-      <c r="E111" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F111" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="112" spans="2:6">
-      <c r="B112" s="4">
-        <v>400151</v>
-      </c>
-      <c r="C112" t="s">
-        <v>393</v>
-      </c>
-      <c r="D112" t="s">
-        <v>396</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>397</v>
-      </c>
       <c r="F112" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="113" spans="2:7">
       <c r="B113" s="4">
-        <v>40016</v>
+        <v>400141</v>
       </c>
       <c r="C113" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D113" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E113" s="4">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="F113" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="114" spans="2:7">
       <c r="B114" s="4">
-        <v>40017</v>
+        <v>400142</v>
       </c>
       <c r="C114" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D114" t="s">
-        <v>403</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="F114" s="11" t="s">
         <v>405</v>
+      </c>
+      <c r="E114" s="4">
+        <v>7</v>
+      </c>
+      <c r="F114" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="115" spans="2:7">
       <c r="B115" s="4">
-        <v>40018</v>
+        <v>40015</v>
       </c>
       <c r="C115" t="s">
-        <v>406</v>
-      </c>
-      <c r="D115" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="E115" s="3" t="s">
+      <c r="D115" t="s">
         <v>408</v>
       </c>
-      <c r="F115" s="11" t="s">
+      <c r="E115" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F115" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="116" spans="2:7">
       <c r="B116" s="4">
-        <v>40019</v>
+        <v>400151</v>
       </c>
       <c r="C116" t="s">
+        <v>407</v>
+      </c>
+      <c r="D116" t="s">
         <v>410</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="E116" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="E116" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F116" s="11" t="s">
+      <c r="F116" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="117" spans="2:7">
       <c r="B117" s="4">
-        <v>40020</v>
+        <v>40016</v>
       </c>
       <c r="C117" t="s">
         <v>413</v>
       </c>
-      <c r="D117" s="4" t="s">
+      <c r="D117" t="s">
         <v>414</v>
       </c>
-      <c r="E117" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F117" s="11" t="s">
+      <c r="E117" s="4">
+        <v>2</v>
+      </c>
+      <c r="F117" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="118" spans="2:7">
       <c r="B118" s="4">
-        <v>40021</v>
+        <v>40017</v>
       </c>
       <c r="C118" t="s">
         <v>416</v>
       </c>
-      <c r="D118" s="4" t="s">
+      <c r="D118" t="s">
         <v>417</v>
       </c>
       <c r="E118" s="3" t="s">
@@ -4431,7 +4465,7 @@
     </row>
     <row r="119" spans="2:7">
       <c r="B119" s="4">
-        <v>40022</v>
+        <v>40018</v>
       </c>
       <c r="C119" t="s">
         <v>420</v>
@@ -4442,185 +4476,253 @@
       <c r="E119" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="F119" t="s">
+      <c r="F119" s="11" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="120" spans="2:7">
       <c r="B120" s="4">
-        <v>400221</v>
+        <v>40019</v>
       </c>
       <c r="C120" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>263</v>
+        <v>23</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="121" s="2" customFormat="1" spans="2:7">
-      <c r="B121" s="8">
-        <v>40023</v>
-      </c>
-      <c r="C121" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="D121" s="8" t="s">
+    </row>
+    <row r="121" spans="2:7">
+      <c r="B121" s="4">
+        <v>40020</v>
+      </c>
+      <c r="C121" t="s">
         <v>427</v>
       </c>
-      <c r="E121" s="2" t="s">
+      <c r="D121" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="E121" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F121" s="14" t="s">
-        <v>428</v>
-      </c>
-      <c r="G121" s="10"/>
+      <c r="F121" s="11" t="s">
+        <v>429</v>
+      </c>
     </row>
     <row r="122" spans="2:7">
       <c r="B122" s="4">
-        <v>40024</v>
+        <v>40021</v>
       </c>
       <c r="C122" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="E122" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="F122" t="s">
         <v>431</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="F122" s="11" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="123" spans="2:7">
       <c r="B123" s="4">
+        <v>40022</v>
+      </c>
+      <c r="C123" t="s">
+        <v>434</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F123" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="124" spans="2:7">
+      <c r="B124" s="4">
+        <v>400221</v>
+      </c>
+      <c r="C124" t="s">
+        <v>434</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F124" s="11" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="125" s="2" customFormat="1" spans="2:7">
+      <c r="B125" s="8">
+        <v>40023</v>
+      </c>
+      <c r="C125" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="D125" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="G125" s="10"/>
+    </row>
+    <row r="126" spans="2:7">
+      <c r="B126" s="4">
+        <v>40024</v>
+      </c>
+      <c r="C126" t="s">
+        <v>443</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="E126" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F126" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="127" spans="2:7">
+      <c r="B127" s="4">
         <v>40025</v>
       </c>
-      <c r="C123" t="s">
-        <v>432</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="F123" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="124" s="2" customFormat="1" spans="2:7">
-      <c r="B124" s="8">
-        <v>40026</v>
-      </c>
-      <c r="C124" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="D124" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E124" s="8">
-        <v>2</v>
-      </c>
-      <c r="F124" s="14" t="s">
-        <v>436</v>
-      </c>
-      <c r="G124" s="10"/>
-    </row>
-    <row r="125" spans="2:7">
-      <c r="B125" s="4">
-        <v>40027</v>
-      </c>
-      <c r="C125" t="s">
-        <v>437</v>
-      </c>
-      <c r="D125" t="s">
-        <v>438</v>
-      </c>
-      <c r="E125" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="F125" s="11" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="126" s="2" customFormat="1" spans="2:7">
-      <c r="B126" s="8">
-        <v>40028</v>
-      </c>
-      <c r="C126" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D126" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="F126" s="14" t="s">
-        <v>444</v>
-      </c>
-      <c r="G126" s="10"/>
-    </row>
-    <row r="127" s="2" customFormat="1" spans="2:7">
-      <c r="B127" s="8">
-        <v>40029</v>
-      </c>
-      <c r="C127" s="10" t="s">
-        <v>445</v>
-      </c>
-      <c r="D127" s="10" t="s">
+      <c r="C127" t="s">
         <v>446</v>
       </c>
-      <c r="E127" s="8" t="s">
+      <c r="D127" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="F127" s="14" t="s">
+      <c r="E127" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F127" t="s">
         <v>448</v>
       </c>
-      <c r="G127" s="10"/>
     </row>
     <row r="128" s="2" customFormat="1" spans="2:7">
       <c r="B128" s="8">
-        <v>40030</v>
+        <v>40026</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>449</v>
       </c>
       <c r="D128" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E128" s="8">
+        <v>2</v>
+      </c>
+      <c r="F128" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="E128" s="8" t="s">
+      <c r="G128" s="10"/>
+    </row>
+    <row r="129" spans="2:7">
+      <c r="B129" s="4">
+        <v>40027</v>
+      </c>
+      <c r="C129" t="s">
         <v>451</v>
       </c>
-      <c r="F128" s="14" t="s">
+      <c r="D129" t="s">
         <v>452</v>
       </c>
-      <c r="G128" s="10"/>
-    </row>
-    <row r="129" s="2" customFormat="1" spans="2:7">
-      <c r="B129" s="8">
+      <c r="E129" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="F129" s="11" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="130" s="2" customFormat="1" spans="2:7">
+      <c r="B130" s="8">
+        <v>40028</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="D130" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="F130" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="G130" s="10"/>
+    </row>
+    <row r="131" s="2" customFormat="1" spans="2:7">
+      <c r="B131" s="8">
+        <v>40029</v>
+      </c>
+      <c r="C131" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="D131" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="F131" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="G131" s="10"/>
+    </row>
+    <row r="132" s="2" customFormat="1" spans="2:7">
+      <c r="B132" s="8">
+        <v>40030</v>
+      </c>
+      <c r="C132" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="D132" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="F132" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="G132" s="10"/>
+    </row>
+    <row r="133" s="2" customFormat="1" spans="2:7">
+      <c r="B133" s="8">
         <v>40031</v>
       </c>
-      <c r="C129" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="D129" s="10" t="s">
-        <v>454</v>
-      </c>
-      <c r="E129" s="8">
+      <c r="C133" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="D133" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="E133" s="8">
         <v>5</v>
       </c>
-      <c r="F129" s="14" t="s">
-        <v>455</v>
-      </c>
-      <c r="G129" s="10"/>
+      <c r="F133" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="G133" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="13170" windowHeight="11550"/>
+    <workbookView windowWidth="17910" windowHeight="10440"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="468">
   <si>
     <t>##var</t>
   </si>
@@ -295,7 +295,7 @@
     <t>SquarePlate</t>
   </si>
   <si>
-    <t>亮出的每张方片牌在结算时提供+1倍率</t>
+    <t>亮出的每张方片牌在结算时提供+2倍率</t>
   </si>
   <si>
     <t>20002</t>
@@ -307,7 +307,7 @@
     <t>Spades</t>
   </si>
   <si>
-    <t>亮出的每张黑桃牌在结算时提供+1倍率</t>
+    <t>亮出的每张黑桃牌在结算时提供+2倍率</t>
   </si>
   <si>
     <t>20003</t>
@@ -319,7 +319,7 @@
     <t>RedHeart</t>
   </si>
   <si>
-    <t>亮出的每张红心牌在结算时提供+1倍率</t>
+    <t>亮出的每张红心牌在结算时提供+2倍率</t>
   </si>
   <si>
     <t>20004</t>
@@ -331,7 +331,7 @@
     <t>PlumBlossom</t>
   </si>
   <si>
-    <t>亮出的每张梅花牌在结算时提供+1倍率</t>
+    <t>亮出的每张梅花牌在结算时提供+2倍率</t>
   </si>
   <si>
     <t>20005</t>
@@ -430,10 +430,10 @@
     <t>恐怖面具</t>
   </si>
   <si>
-    <t>HeadCardAttack</t>
-  </si>
-  <si>
-    <t>亮出的每张人头牌在结算时提供+3倍率</t>
+    <t>HeadCard</t>
+  </si>
+  <si>
+    <t>亮出的每张人头牌在结算时提供+2倍率</t>
   </si>
   <si>
     <t>20013</t>
@@ -664,10 +664,10 @@
     <t>同花心得</t>
   </si>
   <si>
-    <t>3|1</t>
-  </si>
-  <si>
-    <t>使用后,同花牌型提供的倍率永久+1</t>
+    <t>3|2</t>
+  </si>
+  <si>
+    <t>使用后,同花牌型提供的倍率永久+2</t>
   </si>
   <si>
     <t>20032</t>
@@ -676,10 +676,10 @@
     <t>顺子心得</t>
   </si>
   <si>
-    <t>4|1</t>
-  </si>
-  <si>
-    <t>使用后,顺子牌型提供的倍率永久+1</t>
+    <t>4|2</t>
+  </si>
+  <si>
+    <t>使用后,顺子牌型提供的倍率永久+2</t>
   </si>
   <si>
     <t>20033</t>
@@ -745,7 +745,7 @@
     <t>TheSwordOfVictory</t>
   </si>
   <si>
-    <t>结算伤害时,将留在手牌上最大的牌点数×4转化为额外攻击力</t>
+    <t>结算伤害时,将留在手牌上最大的牌点数×2转化为额外攻击力</t>
   </si>
   <si>
     <t>30004</t>
@@ -793,7 +793,7 @@
     <t>SpecialEightCard</t>
   </si>
   <si>
-    <t>亮出的每张8在结算时提供+50攻击力</t>
+    <t>亮出的每张8在结算时提供+100攻击力</t>
   </si>
   <si>
     <t>30008</t>
@@ -805,7 +805,7 @@
     <t>EvenNumberCard</t>
   </si>
   <si>
-    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+4倍率</t>
+    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+2倍率</t>
   </si>
   <si>
     <t>30009</t>
@@ -817,7 +817,7 @@
     <t>OddNumberCard</t>
   </si>
   <si>
-    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+4倍率</t>
+    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+2倍率</t>
   </si>
   <si>
     <t>30010</t>
@@ -826,10 +826,7 @@
     <t>贵族</t>
   </si>
   <si>
-    <t>HeadCard</t>
-  </si>
-  <si>
-    <t>亮出的每张人头牌在结算时提供+5倍率</t>
+    <t>亮出的每张人头牌在结算时提供+4倍率</t>
   </si>
   <si>
     <t>30011</t>
@@ -841,7 +838,7 @@
     <t>KillAfterSellingPrice</t>
   </si>
   <si>
-    <t>每击杀1名敌人,就会获得50金币</t>
+    <t>每击杀1名敌人,这件圣物的出售价格+10金币</t>
   </si>
   <si>
     <t>30012</t>
@@ -1060,7 +1057,7 @@
     <t>巨人药剂</t>
   </si>
   <si>
-    <t>GiantPotion</t>
+    <t>MaxHpUpAndHeal</t>
   </si>
   <si>
     <t>80|80</t>
@@ -1162,7 +1159,7 @@
     <t>EveryRelic</t>
   </si>
   <si>
-    <t>每拥有1个圣物,结算时提供+3倍率</t>
+    <t>每拥有1个圣物,结算时提供+0.5倍率</t>
   </si>
   <si>
     <t>奢侈品</t>
@@ -1189,13 +1186,13 @@
     <t>SpecialACard</t>
   </si>
   <si>
-    <t>亮出的每张A在结算时提供+8倍率</t>
+    <t>亮出的每张A在结算时提供+6倍率</t>
   </si>
   <si>
     <t>ACardAttack</t>
   </si>
   <si>
-    <t>亮出的每张A在结算时提供+50攻击力</t>
+    <t>亮出的每张A在结算时提供+66攻击力</t>
   </si>
   <si>
     <t>老千</t>
@@ -1369,7 +1366,7 @@
     <t>DamageTurnToGold</t>
   </si>
   <si>
-    <t>每回合结束后,本回合自身总伤害输出的15%转化为金币</t>
+    <t>每回合结束后,本回合自身总伤害输出的20%转化为金币</t>
   </si>
   <si>
     <t>差距胶囊</t>
@@ -1405,7 +1402,7 @@
     <t>RandomHandTypeMagUp</t>
   </si>
   <si>
-    <t>3|5</t>
+    <t>5|3</t>
   </si>
   <si>
     <t>使用后,随机3种牌型的提供的倍率永久+5</t>
@@ -1414,9 +1411,6 @@
     <t>龙心</t>
   </si>
   <si>
-    <t>MaxHpUpAndHeal</t>
-  </si>
-  <si>
     <t>120|120</t>
   </si>
   <si>
@@ -1441,7 +1435,7 @@
     <t>EveryRubbingNum</t>
   </si>
   <si>
-    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+5攻击力</t>
+    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+12攻击力</t>
   </si>
 </sst>
 </file>
@@ -2069,44 +2063,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2460,86 +2436,86 @@
   <dimension ref="A1:G133"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="5.75833333333333" style="3" customWidth="1"/>
-    <col min="2" max="2" width="7.49166666666667" style="3" customWidth="1"/>
-    <col min="3" max="3" width="8.475" style="4" customWidth="1"/>
-    <col min="4" max="4" width="21.8416666666667" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.36666666666667" style="3" customWidth="1"/>
-    <col min="6" max="6" width="20.325" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="3" customWidth="1"/>
+    <col min="1" max="1" width="5.75833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.49166666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.475" style="3" customWidth="1"/>
+    <col min="4" max="4" width="21.8416666666667" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.36666666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.325" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>10001</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>1</v>
       </c>
       <c r="F5" t="s">
@@ -2547,78 +2523,78 @@
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:7">
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <v>10002</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="3">
         <v>1</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:7">
-      <c r="B7" s="5">
+      <c r="B7" s="3">
         <v>10003</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:7">
-      <c r="B8" s="5">
+      <c r="B8" s="3">
         <v>10004</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="3">
         <v>1</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:7">
-      <c r="B9" s="5">
+      <c r="B9" s="3">
         <v>10005</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="3">
         <v>1</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:7">
-      <c r="B10" s="5">
+      <c r="B10" s="3">
         <v>10006</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2627,202 +2603,202 @@
       <c r="E10" s="1">
         <v>3</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:7">
-      <c r="B11" s="5">
+      <c r="B11" s="3">
         <v>10007</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:7">
-      <c r="B12" s="5">
+      <c r="B12" s="3">
         <v>10008</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" t="s">
         <v>38</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:7">
-      <c r="B13" s="5">
+      <c r="B13" s="3">
         <v>10009</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" t="s">
         <v>41</v>
       </c>
       <c r="E13" s="1">
         <v>5</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:7">
-      <c r="B14" s="5">
+      <c r="B14" s="3">
         <v>10010</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:7">
-      <c r="B15" s="8">
+      <c r="B15" s="4">
         <v>10011</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="4">
         <v>-0.02</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G15" s="10"/>
+      <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="B16" s="4">
+      <c r="B16" s="3">
         <v>10012</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D16" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="3">
         <v>2</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="4">
+      <c r="B17" s="3">
         <v>10013</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="3">
         <v>2</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="4">
+      <c r="B18" s="3">
         <v>10014</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D18" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="4">
+      <c r="B19" s="3">
         <v>10015</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D19" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="2:7">
-      <c r="B20" s="8">
+      <c r="B20" s="4">
         <v>10016</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G20" s="10"/>
+      <c r="G20" s="5"/>
     </row>
     <row r="21" s="2" customFormat="1" spans="2:7">
-      <c r="B21" s="8">
+      <c r="B21" s="4">
         <v>10017</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="4">
         <v>0.01</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="10"/>
+      <c r="G21" s="5"/>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="4">
+      <c r="B22" s="3">
         <v>10018</v>
       </c>
       <c r="C22" t="s">
@@ -2831,15 +2807,15 @@
       <c r="D22" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="3">
         <v>0.25</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="4">
+      <c r="B23" s="3">
         <v>10019</v>
       </c>
       <c r="C23" t="s">
@@ -2848,33 +2824,33 @@
       <c r="D23" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="3">
         <v>0.2</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" spans="2:7">
-      <c r="B24" s="8">
+      <c r="B24" s="4">
         <v>10020</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G24" s="10"/>
+      <c r="G24" s="5"/>
     </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="4">
+      <c r="B25" s="3">
         <v>10021</v>
       </c>
       <c r="C25" t="s">
@@ -2883,95 +2859,95 @@
       <c r="D25" t="s">
         <v>81</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="4"/>
+      <c r="B26" s="3"/>
       <c r="D26"/>
-      <c r="E26" s="4"/>
+      <c r="E26" s="3"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="2:7">
       <c r="B27" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" t="s">
         <v>85</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" t="s">
         <v>86</v>
       </c>
-      <c r="E27" s="5">
-        <v>1</v>
-      </c>
-      <c r="F27" s="7" t="s">
+      <c r="E27" s="3">
+        <v>2</v>
+      </c>
+      <c r="F27" t="s">
         <v>87</v>
       </c>
-      <c r="G27" s="6"/>
+      <c r="G27"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="2:7">
       <c r="B28" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" t="s">
         <v>90</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28" s="7" t="s">
+      <c r="E28" s="1">
+        <v>2</v>
+      </c>
+      <c r="F28" t="s">
         <v>91</v>
       </c>
-      <c r="G28" s="6"/>
+      <c r="G28"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="2:7">
       <c r="B29" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" t="s">
         <v>93</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" t="s">
         <v>94</v>
       </c>
-      <c r="E29" s="5">
-        <v>1</v>
-      </c>
-      <c r="F29" s="7" t="s">
+      <c r="E29" s="3">
+        <v>2</v>
+      </c>
+      <c r="F29" t="s">
         <v>95</v>
       </c>
-      <c r="G29" s="6"/>
+      <c r="G29"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="2:7">
       <c r="B30" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" t="s">
         <v>98</v>
       </c>
-      <c r="E30" s="5">
-        <v>1</v>
-      </c>
-      <c r="F30" s="7" t="s">
+      <c r="E30" s="3">
+        <v>2</v>
+      </c>
+      <c r="F30" t="s">
         <v>99</v>
       </c>
-      <c r="G30" s="6"/>
+      <c r="G30"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="2:7">
       <c r="B31" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="3" t="s">
         <v>101</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -2980,94 +2956,94 @@
       <c r="E31" s="1">
         <v>3</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" t="s">
         <v>103</v>
       </c>
-      <c r="G31" s="6"/>
+      <c r="G31"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="2:7">
       <c r="B32" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" t="s">
         <v>106</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" t="s">
         <v>107</v>
       </c>
-      <c r="G32" s="6"/>
+      <c r="G32"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="2:7">
       <c r="B33" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" t="s">
         <v>110</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" t="s">
         <v>111</v>
       </c>
-      <c r="G33" s="6"/>
+      <c r="G33"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="2:7">
       <c r="B34" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" t="s">
         <v>114</v>
       </c>
       <c r="E34" s="1">
         <v>5</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" t="s">
         <v>115</v>
       </c>
-      <c r="G34" s="6"/>
+      <c r="G34"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="2:7">
       <c r="B35" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="3" t="s">
         <v>118</v>
       </c>
       <c r="E35" s="1">
         <v>6</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" t="s">
         <v>119</v>
       </c>
-      <c r="G35" s="6"/>
+      <c r="G35"/>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="3">
         <v>2</v>
       </c>
       <c r="F36" t="s">
@@ -3075,16 +3051,16 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="3">
         <v>30</v>
       </c>
       <c r="F37" t="s">
@@ -3092,19 +3068,19 @@
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="3" t="s">
         <v>127</v>
       </c>
       <c r="D38" t="s">
         <v>128</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38" s="3">
         <v>150</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="3" t="s">
         <v>129</v>
       </c>
     </row>
@@ -3112,82 +3088,82 @@
       <c r="B39" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E39" s="8">
-        <v>3</v>
-      </c>
-      <c r="F39" s="12" t="s">
+      <c r="E39" s="4">
+        <v>2</v>
+      </c>
+      <c r="F39" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="G39" s="10"/>
+      <c r="G39" s="5"/>
     </row>
     <row r="40" spans="2:7">
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="41" spans="2:7">
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="3" t="s">
         <v>140</v>
       </c>
       <c r="D41" t="s">
         <v>141</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="3">
         <v>2</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="42" spans="2:7">
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="3" t="s">
         <v>144</v>
       </c>
       <c r="D42" t="s">
         <v>145</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="3">
         <v>2</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="43" spans="2:7">
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="3" t="s">
         <v>148</v>
       </c>
       <c r="D43" t="s">
         <v>149</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="3" t="s">
         <v>150</v>
       </c>
       <c r="F43" t="s">
@@ -3195,16 +3171,16 @@
       </c>
     </row>
     <row r="44" spans="2:7">
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="3" t="s">
         <v>153</v>
       </c>
       <c r="D44" t="s">
         <v>154</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E44" s="3">
         <v>10</v>
       </c>
       <c r="F44" t="s">
@@ -3212,19 +3188,19 @@
       </c>
     </row>
     <row r="45" spans="2:7">
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="3" t="s">
         <v>157</v>
       </c>
       <c r="D45" t="s">
         <v>158</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E45" s="3">
         <v>0.2</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="3" t="s">
         <v>159</v>
       </c>
     </row>
@@ -3232,83 +3208,83 @@
       <c r="B46" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E46" s="8">
+      <c r="E46" s="4">
         <v>1</v>
       </c>
-      <c r="F46" s="9" t="s">
+      <c r="F46" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="G46" s="10"/>
+      <c r="G46" s="5"/>
     </row>
     <row r="47" s="2" customFormat="1" spans="2:7">
       <c r="B47" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="E47" s="8">
+      <c r="E47" s="4">
         <v>3</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G47" s="10"/>
+      <c r="G47" s="5"/>
     </row>
     <row r="48" spans="2:7">
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="3" t="s">
         <v>169</v>
       </c>
       <c r="D48" t="s">
         <v>170</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E48" s="3">
         <v>3</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="49" spans="2:7">
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="3" t="s">
         <v>173</v>
       </c>
       <c r="D49" t="s">
         <v>174</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E49" s="3">
         <v>1</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="50" spans="2:7">
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="3" t="s">
         <v>177</v>
       </c>
       <c r="D50" t="s">
         <v>178</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E50" s="3">
         <v>4</v>
       </c>
       <c r="F50" t="s">
@@ -3316,16 +3292,16 @@
       </c>
     </row>
     <row r="51" spans="2:7">
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="3" t="s">
         <v>181</v>
       </c>
       <c r="D51" t="s">
         <v>182</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="3" t="s">
         <v>61</v>
       </c>
       <c r="F51" t="s">
@@ -3333,19 +3309,19 @@
       </c>
     </row>
     <row r="52" spans="2:7">
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D52" t="s">
         <v>186</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" t="s">
         <v>188</v>
       </c>
     </row>
@@ -3353,22 +3329,22 @@
       <c r="B53" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E53" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="F53" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="G53" s="10"/>
+      <c r="G53" s="5"/>
     </row>
     <row r="54" spans="2:7">
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="1" t="s">
         <v>194</v>
       </c>
       <c r="C54" t="s">
@@ -3377,15 +3353,15 @@
       <c r="D54" t="s">
         <v>71</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E54" s="3">
         <v>0.5</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="55" spans="2:7">
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="1" t="s">
         <v>197</v>
       </c>
       <c r="C55" t="s">
@@ -3394,15 +3370,15 @@
       <c r="D55" t="s">
         <v>74</v>
       </c>
-      <c r="E55" s="4">
+      <c r="E55" s="3">
         <v>0.4</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="56" spans="2:7">
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="1" t="s">
         <v>200</v>
       </c>
       <c r="C56" t="s">
@@ -3411,15 +3387,15 @@
       <c r="D56" t="s">
         <v>202</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E56" s="3">
         <v>3</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="57" spans="2:7">
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="1" t="s">
         <v>204</v>
       </c>
       <c r="C57" t="s">
@@ -3428,33 +3404,33 @@
       <c r="D57" t="s">
         <v>206</v>
       </c>
-      <c r="E57" s="4">
+      <c r="E57" s="3">
         <v>0.5</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="2:7">
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" t="s">
         <v>209</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D58" t="s">
         <v>81</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F58" s="7" t="s">
+      <c r="F58" t="s">
         <v>211</v>
       </c>
-      <c r="G58" s="6"/>
+      <c r="G58"/>
     </row>
     <row r="59" spans="2:7">
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="1" t="s">
         <v>212</v>
       </c>
       <c r="C59" t="s">
@@ -3463,7 +3439,7 @@
       <c r="D59" t="s">
         <v>81</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E59" s="3" t="s">
         <v>214</v>
       </c>
       <c r="F59" t="s">
@@ -3474,80 +3450,80 @@
       <c r="B60" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="E60" s="8">
+      <c r="E60" s="4">
         <v>1</v>
       </c>
-      <c r="F60" s="9" t="s">
+      <c r="F60" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="G60" s="10"/>
+      <c r="G60" s="5"/>
     </row>
     <row r="61" s="2" customFormat="1" spans="2:7">
       <c r="B61" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D61" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="E61" s="8">
+      <c r="E61" s="4">
         <v>2</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="F61" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="G61" s="10"/>
+      <c r="G61" s="5"/>
     </row>
     <row r="62" s="2" customFormat="1" spans="2:7">
       <c r="B62" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="D62" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="E62" s="8">
+      <c r="E62" s="4">
         <v>3</v>
       </c>
-      <c r="F62" s="9" t="s">
+      <c r="F62" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="G62" s="10"/>
+      <c r="G62" s="5"/>
     </row>
     <row r="63" spans="2:7">
       <c r="C63"/>
-      <c r="E63" s="4"/>
+      <c r="E63" s="3"/>
       <c r="F63"/>
     </row>
     <row r="64" spans="2:7">
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="1" t="s">
         <v>226</v>
       </c>
       <c r="C64" t="s">
         <v>227</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="E64" s="4">
+      <c r="E64" s="3">
         <v>0.05</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="F64" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="65" spans="2:7">
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="1" t="s">
         <v>230</v>
       </c>
       <c r="C65" t="s">
@@ -3556,15 +3532,15 @@
       <c r="D65" t="s">
         <v>232</v>
       </c>
-      <c r="E65" s="4">
+      <c r="E65" s="3">
         <v>2</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F65" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="66" spans="2:7">
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="1" t="s">
         <v>234</v>
       </c>
       <c r="C66" t="s">
@@ -3573,10 +3549,10 @@
       <c r="D66" t="s">
         <v>236</v>
       </c>
-      <c r="E66" s="4">
-        <v>4</v>
-      </c>
-      <c r="F66" s="11" t="s">
+      <c r="E66" s="3">
+        <v>2</v>
+      </c>
+      <c r="F66" t="s">
         <v>237</v>
       </c>
     </row>
@@ -3584,22 +3560,22 @@
       <c r="B67" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C67" s="10" t="s">
+      <c r="C67" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="D67" s="10" t="s">
+      <c r="D67" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="E67" s="8">
+      <c r="E67" s="4">
         <v>1</v>
       </c>
-      <c r="F67" s="9" t="s">
+      <c r="F67" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="G67" s="10"/>
+      <c r="G67" s="5"/>
     </row>
     <row r="68" spans="2:7">
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="1" t="s">
         <v>242</v>
       </c>
       <c r="C68" t="s">
@@ -3608,15 +3584,15 @@
       <c r="D68" t="s">
         <v>244</v>
       </c>
-      <c r="E68" s="4">
+      <c r="E68" s="3">
         <v>1</v>
       </c>
-      <c r="F68" s="11" t="s">
+      <c r="F68" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="69" spans="2:7">
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="1" t="s">
         <v>246</v>
       </c>
       <c r="C69" t="s">
@@ -3625,15 +3601,15 @@
       <c r="D69" t="s">
         <v>248</v>
       </c>
-      <c r="E69" s="4">
+      <c r="E69" s="3">
         <v>1</v>
       </c>
-      <c r="F69" s="11" t="s">
+      <c r="F69" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="70" spans="2:7">
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="1" t="s">
         <v>250</v>
       </c>
       <c r="C70" t="s">
@@ -3642,15 +3618,15 @@
       <c r="D70" t="s">
         <v>252</v>
       </c>
-      <c r="E70" s="4">
-        <v>50</v>
-      </c>
-      <c r="F70" s="11" t="s">
+      <c r="E70" s="3">
+        <v>100</v>
+      </c>
+      <c r="F70" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="71" spans="2:7">
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="1" t="s">
         <v>254</v>
       </c>
       <c r="C71" t="s">
@@ -3659,15 +3635,15 @@
       <c r="D71" t="s">
         <v>256</v>
       </c>
-      <c r="E71" s="4">
-        <v>4</v>
-      </c>
-      <c r="F71" s="11" t="s">
+      <c r="E71" s="3">
+        <v>2</v>
+      </c>
+      <c r="F71" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="72" spans="2:7">
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="1" t="s">
         <v>258</v>
       </c>
       <c r="C72" t="s">
@@ -3676,1053 +3652,1053 @@
       <c r="D72" t="s">
         <v>260</v>
       </c>
-      <c r="E72" s="4">
-        <v>4</v>
+      <c r="E72" s="3">
+        <v>2</v>
       </c>
       <c r="F72" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="73" spans="2:7">
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="1" t="s">
         <v>262</v>
       </c>
       <c r="C73" t="s">
         <v>263</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E73" s="3">
+        <v>4</v>
+      </c>
+      <c r="F73" t="s">
         <v>264</v>
-      </c>
-      <c r="E73" s="4">
-        <v>5</v>
-      </c>
-      <c r="F73" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="74" s="2" customFormat="1" spans="2:7">
       <c r="B74" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C74" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="C74" s="10" t="s">
+      <c r="D74" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="E74" s="4">
+        <v>10</v>
+      </c>
+      <c r="F74" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="E74" s="8">
-        <v>50</v>
-      </c>
-      <c r="F74" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="G74" s="10"/>
+      <c r="G74" s="5"/>
     </row>
     <row r="75" s="2" customFormat="1" spans="2:7">
       <c r="B75" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C75" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C75" s="10" t="s">
+      <c r="D75" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="E75" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="E75" s="8" t="s">
+      <c r="F75" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="F75" s="9" t="s">
+      <c r="G75" s="5"/>
+    </row>
+    <row r="76" spans="2:7">
+      <c r="B76" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="G75" s="10"/>
-    </row>
-    <row r="76" spans="2:7">
-      <c r="B76" s="3" t="s">
+      <c r="C76" t="s">
         <v>275</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>276</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" s="3">
+        <v>30</v>
+      </c>
+      <c r="F76" t="s">
         <v>277</v>
       </c>
-      <c r="E76" s="4">
-        <v>30</v>
-      </c>
-      <c r="F76" s="11" t="s">
+    </row>
+    <row r="77" spans="2:7">
+      <c r="B77" s="1" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="77" spans="2:7">
-      <c r="B77" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="D77" t="s">
         <v>280</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E77" s="4" t="s">
+      <c r="F77" t="s">
         <v>282</v>
       </c>
-      <c r="F77" s="11" t="s">
+    </row>
+    <row r="78" spans="2:7">
+      <c r="B78" s="1" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="78" spans="2:7">
-      <c r="B78" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="D78" t="s">
         <v>285</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" s="3">
+        <v>1</v>
+      </c>
+      <c r="F78" t="s">
         <v>286</v>
       </c>
-      <c r="E78" s="4">
-        <v>1</v>
-      </c>
-      <c r="F78" s="11" t="s">
+    </row>
+    <row r="79" spans="2:7">
+      <c r="B79" s="1" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="79" spans="2:7">
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="D79" t="s">
         <v>289</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="E79" s="4" t="s">
+      <c r="F79" t="s">
         <v>291</v>
       </c>
-      <c r="F79" s="11" t="s">
+    </row>
+    <row r="80" spans="2:7">
+      <c r="B80" s="1" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="80" spans="2:7">
-      <c r="B80" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="D80" t="s">
         <v>294</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" s="3">
+        <v>3</v>
+      </c>
+      <c r="F80" t="s">
         <v>295</v>
       </c>
-      <c r="E80" s="4">
-        <v>3</v>
-      </c>
-      <c r="F80" t="s">
+    </row>
+    <row r="81" spans="2:7">
+      <c r="B81" s="1" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="81" spans="2:7">
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="D81" t="s">
         <v>298</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F81" t="s">
         <v>299</v>
-      </c>
-      <c r="E81" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F81" s="11" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="82" s="2" customFormat="1" spans="2:7">
       <c r="B82" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="D82" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="D82" s="10" t="s">
+      <c r="E82" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="E82" s="8" t="s">
+      <c r="F82" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="F82" s="9" t="s">
+      <c r="G82" s="5"/>
+    </row>
+    <row r="83" spans="2:7">
+      <c r="B83" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="G82" s="10"/>
-    </row>
-    <row r="83" spans="2:7">
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="D83" t="s">
         <v>307</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F83" t="s">
         <v>308</v>
       </c>
-      <c r="E83" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F83" s="11" t="s">
+    </row>
+    <row r="84" spans="2:7">
+      <c r="B84" s="1" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="84" spans="2:7">
-      <c r="B84" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="D84" t="s">
         <v>311</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="E84" s="4" t="s">
+      <c r="F84" t="s">
         <v>313</v>
       </c>
-      <c r="F84" s="11" t="s">
+    </row>
+    <row r="85" spans="2:7">
+      <c r="B85" s="1" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="85" spans="2:7">
-      <c r="B85" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="D85" t="s">
         <v>316</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" s="3">
+        <v>-0.3</v>
+      </c>
+      <c r="F85" t="s">
         <v>317</v>
       </c>
-      <c r="E85" s="4">
-        <v>-0.3</v>
-      </c>
-      <c r="F85" s="11" t="s">
+    </row>
+    <row r="86" spans="2:7">
+      <c r="B86" s="1" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="86" spans="2:7">
-      <c r="B86" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="D86" t="s">
         <v>320</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="E86" s="4" t="s">
+      <c r="F86" t="s">
         <v>322</v>
-      </c>
-      <c r="F86" s="11" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="87" s="2" customFormat="1" spans="2:7">
       <c r="B87" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="D87" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="D87" s="10" t="s">
+      <c r="E87" s="4">
+        <v>1</v>
+      </c>
+      <c r="F87" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="E87" s="8">
-        <v>1</v>
-      </c>
-      <c r="F87" s="9" t="s">
+      <c r="G87" s="5"/>
+    </row>
+    <row r="88" spans="2:7">
+      <c r="B88" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="G87" s="10"/>
-    </row>
-    <row r="88" spans="2:7">
-      <c r="B88" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="D88" t="s">
         <v>329</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" s="3">
+        <v>-0.3</v>
+      </c>
+      <c r="F88" t="s">
         <v>330</v>
-      </c>
-      <c r="E88" s="4">
-        <v>-0.3</v>
-      </c>
-      <c r="F88" s="11" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="89" s="2" customFormat="1" spans="2:7">
       <c r="B89" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C89" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="C89" s="10" t="s">
+      <c r="D89" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="D89" s="10" t="s">
+      <c r="E89" s="4">
+        <v>300</v>
+      </c>
+      <c r="F89" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="E89" s="8">
-        <v>300</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="G89" s="10"/>
+      <c r="G89" s="5"/>
     </row>
     <row r="90" s="2" customFormat="1" spans="2:7">
       <c r="B90" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C90" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="C90" s="10" t="s">
+      <c r="D90" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="D90" s="10" t="s">
+      <c r="E90" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="F90" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="E90" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="G90" s="10"/>
+      <c r="G90" s="5"/>
     </row>
     <row r="91" s="2" customFormat="1" spans="2:7">
       <c r="B91" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C91" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="C91" s="10" t="s">
+      <c r="D91" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="D91" s="10" t="s">
+      <c r="E91" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="E91" s="8" t="s">
+      <c r="F91" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="F91" s="9" t="s">
+      <c r="G91" s="5"/>
+    </row>
+    <row r="92" spans="2:7">
+      <c r="B92" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="G91" s="10"/>
-    </row>
-    <row r="92" spans="2:7">
-      <c r="B92" s="3" t="s">
+      <c r="C92" t="s">
         <v>345</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="E92" s="3">
+        <v>-1</v>
+      </c>
+      <c r="F92" t="s">
         <v>347</v>
       </c>
-      <c r="E92" s="4">
-        <v>-1</v>
-      </c>
-      <c r="F92" t="s">
+    </row>
+    <row r="93" spans="2:7">
+      <c r="B93" s="1" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="93" spans="2:7">
-      <c r="B93" s="3" t="s">
+      <c r="C93" t="s">
         <v>349</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="E93" s="3">
+        <v>1</v>
+      </c>
+      <c r="F93" t="s">
         <v>351</v>
       </c>
-      <c r="E93" s="4">
+    </row>
+    <row r="94" spans="2:7">
+      <c r="B94" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C94" t="s">
+        <v>353</v>
+      </c>
+      <c r="D94" t="s">
+        <v>354</v>
+      </c>
+      <c r="E94" s="3">
         <v>1</v>
       </c>
-      <c r="F93" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="94" spans="2:7">
-      <c r="B94" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C94" t="s">
-        <v>354</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="F94" t="s">
         <v>355</v>
-      </c>
-      <c r="E94" s="4">
-        <v>1</v>
-      </c>
-      <c r="F94" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="95" s="2" customFormat="1" spans="2:7">
       <c r="B95" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="C95" s="8" t="s">
+      <c r="D95" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E95" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="D95" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="E95" s="8" t="s">
+      <c r="F95" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="F95" s="9" t="s">
+      <c r="G95" s="5"/>
+    </row>
+    <row r="96" spans="2:7">
+      <c r="B96" s="3"/>
+      <c r="D96"/>
+      <c r="E96" s="3"/>
+      <c r="F96"/>
+    </row>
+    <row r="97" spans="2:7">
+      <c r="B97" s="3">
+        <v>40001</v>
+      </c>
+      <c r="C97" s="3">
+        <v>235</v>
+      </c>
+      <c r="D97" t="s">
         <v>360</v>
       </c>
-      <c r="G95" s="10"/>
-    </row>
-    <row r="96" spans="2:7">
-      <c r="B96" s="4"/>
-      <c r="D96"/>
-      <c r="E96" s="4"/>
-      <c r="F96"/>
-    </row>
-    <row r="97" spans="2:7">
-      <c r="B97" s="4">
-        <v>40001</v>
-      </c>
-      <c r="C97" s="4">
-        <v>235</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="E97" s="3">
+        <v>1</v>
+      </c>
+      <c r="F97" t="s">
         <v>361</v>
       </c>
-      <c r="E97" s="4">
+    </row>
+    <row r="98" spans="2:7">
+      <c r="B98" s="3">
+        <v>40002</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E98" s="3">
+        <v>500</v>
+      </c>
+      <c r="F98" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7">
+      <c r="B99" s="3">
+        <v>40003</v>
+      </c>
+      <c r="C99" t="s">
+        <v>364</v>
+      </c>
+      <c r="D99" t="s">
+        <v>365</v>
+      </c>
+      <c r="E99" s="3">
         <v>1</v>
       </c>
-      <c r="F97" s="11" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7">
-      <c r="B98" s="4">
-        <v>40002</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E98" s="4">
-        <v>500</v>
-      </c>
-      <c r="F98" s="11" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7">
-      <c r="B99" s="4">
-        <v>40003</v>
-      </c>
-      <c r="C99" t="s">
-        <v>365</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="F99" t="s">
         <v>366</v>
       </c>
-      <c r="E99" s="4">
+    </row>
+    <row r="100" s="2" customFormat="1" spans="2:7">
+      <c r="B100" s="4">
+        <v>40004</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="E100" s="4">
         <v>1</v>
       </c>
-      <c r="F99" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="100" s="2" customFormat="1" spans="2:7">
-      <c r="B100" s="8">
-        <v>40004</v>
-      </c>
-      <c r="C100" s="10" t="s">
+      <c r="F100" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="G100" s="5"/>
+    </row>
+    <row r="101" spans="2:7">
+      <c r="B101" s="3">
+        <v>40005</v>
+      </c>
+      <c r="C101" t="s">
+        <v>370</v>
+      </c>
+      <c r="D101" t="s">
+        <v>371</v>
+      </c>
+      <c r="E101" s="3">
+        <v>12</v>
+      </c>
+      <c r="F101" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7">
+      <c r="B102" s="3">
+        <v>40006</v>
+      </c>
+      <c r="C102" t="s">
+        <v>373</v>
+      </c>
+      <c r="D102" t="s">
+        <v>374</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F102" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="103" s="2" customFormat="1" spans="2:7">
+      <c r="B103" s="4">
+        <v>40007</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="E103" s="4">
+        <v>3</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="104" s="1" customFormat="1" spans="2:7">
+      <c r="B104" s="3">
+        <v>40008</v>
+      </c>
+      <c r="C104" t="s">
+        <v>379</v>
+      </c>
+      <c r="D104" t="s">
+        <v>380</v>
+      </c>
+      <c r="E104" s="3">
+        <v>1</v>
+      </c>
+      <c r="F104" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="105" s="1" customFormat="1" spans="2:7">
+      <c r="B105" s="3">
+        <v>40009</v>
+      </c>
+      <c r="C105" t="s">
+        <v>382</v>
+      </c>
+      <c r="D105" t="s">
+        <v>383</v>
+      </c>
+      <c r="E105" s="3">
+        <v>6</v>
+      </c>
+      <c r="F105" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="106" s="1" customFormat="1" spans="2:7">
+      <c r="B106" s="3">
+        <v>400091</v>
+      </c>
+      <c r="C106" t="s">
+        <v>382</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="E106" s="3">
+        <v>66</v>
+      </c>
+      <c r="F106" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="107" s="2" customFormat="1" spans="2:7">
+      <c r="B107" s="4">
+        <v>40010</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="108" s="1" customFormat="1" spans="2:7">
+      <c r="B108" s="3">
+        <v>40011</v>
+      </c>
+      <c r="C108" t="s">
+        <v>390</v>
+      </c>
+      <c r="D108" t="s">
+        <v>391</v>
+      </c>
+      <c r="E108" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F108" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="109" s="2" customFormat="1" spans="2:7">
+      <c r="B109" s="4">
+        <v>40012</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D109" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="D100" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="E100" s="8">
-        <v>1</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="G100" s="10"/>
-    </row>
-    <row r="101" spans="2:7">
-      <c r="B101" s="4">
-        <v>40005</v>
-      </c>
-      <c r="C101" t="s">
-        <v>371</v>
-      </c>
-      <c r="D101" t="s">
-        <v>372</v>
-      </c>
-      <c r="E101" s="4">
-        <v>12</v>
-      </c>
-      <c r="F101" s="11" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="102" spans="2:7">
-      <c r="B102" s="4">
-        <v>40006</v>
-      </c>
-      <c r="C102" t="s">
-        <v>374</v>
-      </c>
-      <c r="D102" t="s">
-        <v>375</v>
-      </c>
-      <c r="E102" s="4">
-        <v>3</v>
-      </c>
-      <c r="F102" s="11" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="103" s="2" customFormat="1" spans="2:7">
-      <c r="B103" s="8">
-        <v>40007</v>
-      </c>
-      <c r="C103" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="D103" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="E103" s="8">
-        <v>2</v>
-      </c>
-      <c r="F103" s="9" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="104" s="3" customFormat="1" spans="2:7">
-      <c r="B104" s="4">
-        <v>40008</v>
-      </c>
-      <c r="C104" t="s">
-        <v>380</v>
-      </c>
-      <c r="D104" t="s">
-        <v>381</v>
-      </c>
-      <c r="E104" s="4">
-        <v>1</v>
-      </c>
-      <c r="F104" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="105" s="3" customFormat="1" spans="2:7">
-      <c r="B105" s="4">
-        <v>40009</v>
-      </c>
-      <c r="C105" t="s">
-        <v>383</v>
-      </c>
-      <c r="D105" t="s">
-        <v>384</v>
-      </c>
-      <c r="E105" s="4">
-        <v>8</v>
-      </c>
-      <c r="F105" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="106" s="3" customFormat="1" spans="2:7">
-      <c r="B106" s="4">
-        <v>400091</v>
-      </c>
-      <c r="C106" t="s">
-        <v>383</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="E106" s="4">
-        <v>50</v>
-      </c>
-      <c r="F106" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="107" s="2" customFormat="1" spans="2:7">
-      <c r="B107" s="8">
-        <v>40010</v>
-      </c>
-      <c r="C107" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="D107" s="10" t="s">
-        <v>389</v>
-      </c>
-      <c r="E107" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="F107" s="9" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="108" s="3" customFormat="1" spans="2:7">
-      <c r="B108" s="4">
-        <v>40011</v>
-      </c>
-      <c r="C108" t="s">
-        <v>391</v>
-      </c>
-      <c r="D108" t="s">
-        <v>392</v>
-      </c>
-      <c r="E108" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F108" s="11" t="s">
+      <c r="E109" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="110" s="2" customFormat="1" spans="2:7">
+      <c r="B110" s="4">
+        <v>400121</v>
+      </c>
+      <c r="C110" s="5" t="s">
         <v>393</v>
-      </c>
-    </row>
-    <row r="109" s="2" customFormat="1" spans="2:7">
-      <c r="B109" s="8">
-        <v>40012</v>
-      </c>
-      <c r="C109" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="D109" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="E109" s="8">
-        <v>-2</v>
-      </c>
-      <c r="F109" s="10" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="110" s="2" customFormat="1" spans="2:7">
-      <c r="B110" s="8">
-        <v>400121</v>
-      </c>
-      <c r="C110" s="10" t="s">
-        <v>394</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E110" s="8">
+      <c r="E110" s="4">
         <v>15</v>
       </c>
-      <c r="F110" s="10" t="s">
+      <c r="F110" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="111" s="1" customFormat="1" spans="2:7">
+      <c r="B111" s="3">
+        <v>40013</v>
+      </c>
+      <c r="C111" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="111" s="3" customFormat="1" spans="2:7">
-      <c r="B111" s="4">
-        <v>40013</v>
-      </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>397</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F111" t="s">
         <v>398</v>
       </c>
-      <c r="E111" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="F111" s="11" t="s">
+    </row>
+    <row r="112" s="1" customFormat="1" spans="2:7">
+      <c r="B112" s="3">
+        <v>40014</v>
+      </c>
+      <c r="C112" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="112" s="3" customFormat="1" spans="2:7">
-      <c r="B112" s="4">
-        <v>40014</v>
-      </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>400</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" s="3">
+        <v>1</v>
+      </c>
+      <c r="F112" t="s">
         <v>401</v>
       </c>
-      <c r="E112" s="4">
-        <v>1</v>
-      </c>
-      <c r="F112" t="s">
+    </row>
+    <row r="113" spans="2:7">
+      <c r="B113" s="3">
+        <v>400141</v>
+      </c>
+      <c r="C113" t="s">
+        <v>399</v>
+      </c>
+      <c r="D113" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="113" spans="2:7">
-      <c r="B113" s="4">
-        <v>400141</v>
-      </c>
-      <c r="C113" t="s">
-        <v>400</v>
-      </c>
-      <c r="D113" t="s">
+      <c r="E113" s="3">
+        <v>77</v>
+      </c>
+      <c r="F113" t="s">
         <v>403</v>
       </c>
-      <c r="E113" s="4">
-        <v>77</v>
-      </c>
-      <c r="F113" t="s">
+    </row>
+    <row r="114" spans="2:7">
+      <c r="B114" s="3">
+        <v>400142</v>
+      </c>
+      <c r="C114" t="s">
+        <v>399</v>
+      </c>
+      <c r="D114" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="114" spans="2:7">
-      <c r="B114" s="4">
-        <v>400142</v>
-      </c>
-      <c r="C114" t="s">
-        <v>400</v>
-      </c>
-      <c r="D114" t="s">
+      <c r="E114" s="3">
+        <v>7</v>
+      </c>
+      <c r="F114" t="s">
         <v>405</v>
       </c>
-      <c r="E114" s="4">
-        <v>7</v>
-      </c>
-      <c r="F114" t="s">
+    </row>
+    <row r="115" spans="2:7">
+      <c r="B115" s="3">
+        <v>40015</v>
+      </c>
+      <c r="C115" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="115" spans="2:7">
-      <c r="B115" s="4">
-        <v>40015</v>
-      </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
         <v>407</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F115" t="s">
         <v>408</v>
       </c>
-      <c r="E115" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F115" t="s">
+    </row>
+    <row r="116" spans="2:7">
+      <c r="B116" s="3">
+        <v>400151</v>
+      </c>
+      <c r="C116" t="s">
+        <v>406</v>
+      </c>
+      <c r="D116" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="116" spans="2:7">
-      <c r="B116" s="4">
-        <v>400151</v>
-      </c>
-      <c r="C116" t="s">
-        <v>407</v>
-      </c>
-      <c r="D116" t="s">
+      <c r="E116" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="E116" s="4" t="s">
+      <c r="F116" t="s">
         <v>411</v>
       </c>
-      <c r="F116" t="s">
+    </row>
+    <row r="117" spans="2:7">
+      <c r="B117" s="3">
+        <v>40016</v>
+      </c>
+      <c r="C117" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="117" spans="2:7">
-      <c r="B117" s="4">
-        <v>40016</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>413</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" s="3">
+        <v>2</v>
+      </c>
+      <c r="F117" t="s">
         <v>414</v>
       </c>
-      <c r="E117" s="4">
-        <v>2</v>
-      </c>
-      <c r="F117" t="s">
+    </row>
+    <row r="118" spans="2:7">
+      <c r="B118" s="3">
+        <v>40017</v>
+      </c>
+      <c r="C118" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="118" spans="2:7">
-      <c r="B118" s="4">
-        <v>40017</v>
-      </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
         <v>416</v>
       </c>
-      <c r="D118" t="s">
+      <c r="E118" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E118" s="3" t="s">
+      <c r="F118" t="s">
         <v>418</v>
       </c>
-      <c r="F118" s="11" t="s">
+    </row>
+    <row r="119" spans="2:7">
+      <c r="B119" s="3">
+        <v>40018</v>
+      </c>
+      <c r="C119" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="119" spans="2:7">
-      <c r="B119" s="4">
-        <v>40018</v>
-      </c>
-      <c r="C119" t="s">
+      <c r="D119" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="D119" s="4" t="s">
+      <c r="E119" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="E119" s="3" t="s">
+      <c r="F119" t="s">
         <v>422</v>
       </c>
-      <c r="F119" s="11" t="s">
+    </row>
+    <row r="120" spans="2:7">
+      <c r="B120" s="3">
+        <v>40019</v>
+      </c>
+      <c r="C120" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="120" spans="2:7">
-      <c r="B120" s="4">
-        <v>40019</v>
-      </c>
-      <c r="C120" t="s">
+      <c r="D120" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="D120" s="4" t="s">
+      <c r="E120" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F120" t="s">
         <v>425</v>
       </c>
-      <c r="E120" s="3" t="s">
+    </row>
+    <row r="121" spans="2:7">
+      <c r="B121" s="3">
+        <v>40020</v>
+      </c>
+      <c r="C121" t="s">
+        <v>426</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F120" s="11" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="121" spans="2:7">
-      <c r="B121" s="4">
-        <v>40020</v>
-      </c>
-      <c r="C121" t="s">
-        <v>427</v>
-      </c>
-      <c r="D121" s="4" t="s">
+      <c r="F121" t="s">
         <v>428</v>
       </c>
-      <c r="E121" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F121" s="11" t="s">
+    </row>
+    <row r="122" spans="2:7">
+      <c r="B122" s="3">
+        <v>40021</v>
+      </c>
+      <c r="C122" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="122" spans="2:7">
-      <c r="B122" s="4">
-        <v>40021</v>
-      </c>
-      <c r="C122" t="s">
+      <c r="D122" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="D122" s="4" t="s">
+      <c r="E122" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="E122" s="3" t="s">
+      <c r="F122" t="s">
         <v>432</v>
       </c>
-      <c r="F122" s="11" t="s">
+    </row>
+    <row r="123" spans="2:7">
+      <c r="B123" s="3">
+        <v>40022</v>
+      </c>
+      <c r="C123" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="123" spans="2:7">
-      <c r="B123" s="4">
-        <v>40022</v>
-      </c>
-      <c r="C123" t="s">
+      <c r="D123" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="D123" s="4" t="s">
+      <c r="E123" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="E123" s="3" t="s">
+      <c r="F123" t="s">
         <v>436</v>
       </c>
-      <c r="F123" t="s">
+    </row>
+    <row r="124" spans="2:7">
+      <c r="B124" s="3">
+        <v>400221</v>
+      </c>
+      <c r="C124" t="s">
+        <v>433</v>
+      </c>
+      <c r="D124" s="3" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="124" spans="2:7">
-      <c r="B124" s="4">
-        <v>400221</v>
-      </c>
-      <c r="C124" t="s">
-        <v>434</v>
-      </c>
-      <c r="D124" s="4" t="s">
+      <c r="E124" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F124" t="s">
         <v>438</v>
       </c>
-      <c r="E124" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="F124" s="11" t="s">
+    </row>
+    <row r="125" s="2" customFormat="1" spans="2:7">
+      <c r="B125" s="4">
+        <v>40023</v>
+      </c>
+      <c r="C125" s="5" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="125" s="2" customFormat="1" spans="2:7">
-      <c r="B125" s="8">
-        <v>40023</v>
-      </c>
-      <c r="C125" s="10" t="s">
+      <c r="D125" s="4" t="s">
         <v>440</v>
-      </c>
-      <c r="D125" s="8" t="s">
-        <v>441</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F125" s="9" t="s">
+      <c r="F125" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="G125" s="5"/>
+    </row>
+    <row r="126" spans="2:7">
+      <c r="B126" s="3">
+        <v>40024</v>
+      </c>
+      <c r="C126" t="s">
         <v>442</v>
       </c>
-      <c r="G125" s="10"/>
-    </row>
-    <row r="126" spans="2:7">
-      <c r="B126" s="4">
-        <v>40024</v>
-      </c>
-      <c r="C126" t="s">
+      <c r="D126" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="D126" s="4" t="s">
+      <c r="E126" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="F126" t="s">
         <v>444</v>
       </c>
-      <c r="E126" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="F126" t="s">
+    </row>
+    <row r="127" spans="2:7">
+      <c r="B127" s="3">
+        <v>40025</v>
+      </c>
+      <c r="C127" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="127" spans="2:7">
-      <c r="B127" s="4">
-        <v>40025</v>
-      </c>
-      <c r="C127" t="s">
+      <c r="D127" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="D127" s="4" t="s">
+      <c r="E127" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F127" t="s">
         <v>447</v>
       </c>
-      <c r="E127" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="F127" t="s">
+    </row>
+    <row r="128" s="2" customFormat="1" spans="2:7">
+      <c r="B128" s="4">
+        <v>40026</v>
+      </c>
+      <c r="C128" s="5" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="128" s="2" customFormat="1" spans="2:7">
-      <c r="B128" s="8">
-        <v>40026</v>
-      </c>
-      <c r="C128" s="10" t="s">
+      <c r="D128" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E128" s="4">
+        <v>2</v>
+      </c>
+      <c r="F128" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="D128" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E128" s="8">
-        <v>2</v>
-      </c>
-      <c r="F128" s="9" t="s">
+      <c r="G128" s="5"/>
+    </row>
+    <row r="129" spans="2:7">
+      <c r="B129" s="3">
+        <v>40027</v>
+      </c>
+      <c r="C129" t="s">
         <v>450</v>
       </c>
-      <c r="G128" s="10"/>
-    </row>
-    <row r="129" spans="2:7">
-      <c r="B129" s="4">
-        <v>40027</v>
-      </c>
-      <c r="C129" t="s">
+      <c r="D129" t="s">
         <v>451</v>
       </c>
-      <c r="D129" t="s">
+      <c r="E129" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="E129" s="4" t="s">
+      <c r="F129" t="s">
         <v>453</v>
       </c>
-      <c r="F129" s="11" t="s">
+    </row>
+    <row r="130" s="2" customFormat="1" spans="2:7">
+      <c r="B130" s="4">
+        <v>40028</v>
+      </c>
+      <c r="C130" s="5" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="130" s="2" customFormat="1" spans="2:7">
-      <c r="B130" s="8">
-        <v>40028</v>
-      </c>
-      <c r="C130" s="10" t="s">
+      <c r="D130" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="D130" s="10" t="s">
+      <c r="E130" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="E130" s="8" t="s">
+      <c r="F130" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="F130" s="9" t="s">
+      <c r="G130" s="5"/>
+    </row>
+    <row r="131" s="2" customFormat="1" spans="2:7">
+      <c r="B131" s="4">
+        <v>40029</v>
+      </c>
+      <c r="C131" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="G130" s="10"/>
-    </row>
-    <row r="131" s="2" customFormat="1" spans="2:7">
-      <c r="B131" s="8">
-        <v>40029</v>
-      </c>
-      <c r="C131" s="10" t="s">
+      <c r="D131" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="E131" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="D131" s="10" t="s">
+      <c r="F131" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="E131" s="8" t="s">
+      <c r="G131" s="5"/>
+    </row>
+    <row r="132" s="2" customFormat="1" spans="2:7">
+      <c r="B132" s="4">
+        <v>40030</v>
+      </c>
+      <c r="C132" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="F131" s="9" t="s">
+      <c r="D132" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="G131" s="10"/>
-    </row>
-    <row r="132" s="2" customFormat="1" spans="2:7">
-      <c r="B132" s="8">
-        <v>40030</v>
-      </c>
-      <c r="C132" s="10" t="s">
+      <c r="E132" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="D132" s="10" t="s">
+      <c r="F132" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="E132" s="8" t="s">
+      <c r="G132" s="5"/>
+    </row>
+    <row r="133" s="2" customFormat="1" spans="2:7">
+      <c r="B133" s="4">
+        <v>40031</v>
+      </c>
+      <c r="C133" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="F132" s="9" t="s">
+      <c r="D133" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="G132" s="10"/>
-    </row>
-    <row r="133" s="2" customFormat="1" spans="2:7">
-      <c r="B133" s="8">
-        <v>40031</v>
-      </c>
-      <c r="C133" s="8" t="s">
+      <c r="E133" s="4">
+        <v>12</v>
+      </c>
+      <c r="F133" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="D133" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="E133" s="8">
-        <v>5</v>
-      </c>
-      <c r="F133" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="G133" s="10"/>
+      <c r="G133" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17910" windowHeight="10440"/>
+    <workbookView windowWidth="16590" windowHeight="10440"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="472">
   <si>
     <t>##var</t>
   </si>
@@ -142,7 +142,10 @@
     <t>StraightAttack</t>
   </si>
   <si>
-    <t>亮出的顺子牌型在结算时提供+3攻击力</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>亮出的顺子牌型在结算时提供+5攻击力</t>
   </si>
   <si>
     <t>木制长弓</t>
@@ -151,7 +154,10 @@
     <t>FlushAttack</t>
   </si>
   <si>
-    <t>亮出的同花牌型在结算时提供+3攻击力</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>亮出的同花牌型在结算时提供+4攻击力</t>
   </si>
   <si>
     <t>木制长矛</t>
@@ -160,7 +166,10 @@
     <t>StraightFlushAttack</t>
   </si>
   <si>
-    <t>亮出的同花顺牌型在结算时提供+5攻击力</t>
+    <t>6</t>
+  </si>
+  <si>
+    <t>亮出的同花顺牌型在结算时提供+6攻击力</t>
   </si>
   <si>
     <t>木制长斧</t>
@@ -169,7 +178,10 @@
     <t>LeopardAttack</t>
   </si>
   <si>
-    <t>亮出的豹子牌型在结算时提供+6攻击力</t>
+    <t>7</t>
+  </si>
+  <si>
+    <t>亮出的豹子牌型在结算时提供+7攻击力</t>
   </si>
   <si>
     <t>木制圆盾</t>
@@ -178,7 +190,7 @@
     <t>HeroTakeDamage</t>
   </si>
   <si>
-    <t>每次受到的伤害降低2%</t>
+    <t>每次受到的伤害降低5%</t>
   </si>
   <si>
     <t>小钱包</t>
@@ -295,7 +307,7 @@
     <t>SquarePlate</t>
   </si>
   <si>
-    <t>亮出的每张方片牌在结算时提供+2倍率</t>
+    <t>亮出的每张方片牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>20002</t>
@@ -307,7 +319,7 @@
     <t>Spades</t>
   </si>
   <si>
-    <t>亮出的每张黑桃牌在结算时提供+2倍率</t>
+    <t>亮出的每张黑桃牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>20003</t>
@@ -319,7 +331,7 @@
     <t>RedHeart</t>
   </si>
   <si>
-    <t>亮出的每张红心牌在结算时提供+2倍率</t>
+    <t>亮出的每张红心牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>20004</t>
@@ -331,7 +343,7 @@
     <t>PlumBlossom</t>
   </si>
   <si>
-    <t>亮出的每张梅花牌在结算时提供+2倍率</t>
+    <t>亮出的每张梅花牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>20005</t>
@@ -355,7 +367,7 @@
     <t>Straight</t>
   </si>
   <si>
-    <t>亮出的顺子牌型在结算时提供+3倍率</t>
+    <t>亮出的顺子牌型在结算时提供+5倍率</t>
   </si>
   <si>
     <t>20007</t>
@@ -367,7 +379,7 @@
     <t>Flush</t>
   </si>
   <si>
-    <t>亮出的同花牌型在结算时提供+3倍率</t>
+    <t>亮出的同花牌型在结算时提供+4倍率</t>
   </si>
   <si>
     <t>20008</t>
@@ -379,7 +391,7 @@
     <t>StraightFlush</t>
   </si>
   <si>
-    <t>亮出的同花顺牌型在结算时提供+5倍率</t>
+    <t>亮出的同花顺牌型在结算时提供+6倍率</t>
   </si>
   <si>
     <t>20009</t>
@@ -391,7 +403,7 @@
     <t>Leopard</t>
   </si>
   <si>
-    <t>亮出的豹子牌型在结算时提供+6倍率</t>
+    <t>亮出的豹子牌型在结算时提供+7倍率</t>
   </si>
   <si>
     <t>20010</t>
@@ -433,7 +445,7 @@
     <t>HeadCard</t>
   </si>
   <si>
-    <t>亮出的每张人头牌在结算时提供+2倍率</t>
+    <t>亮出的每张人头牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>20013</t>
@@ -2617,11 +2629,11 @@
       <c r="D11" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="1">
-        <v>3</v>
+      <c r="E11" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:7">
@@ -2629,16 +2641,16 @@
         <v>10008</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="1">
-        <v>3</v>
+        <v>39</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:7">
@@ -2646,16 +2658,16 @@
         <v>10009</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="1">
-        <v>5</v>
+        <v>43</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:7">
@@ -2663,16 +2675,16 @@
         <v>10010</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="1">
-        <v>6</v>
+        <v>47</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:7">
@@ -2680,16 +2692,16 @@
         <v>10011</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E15" s="4">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G15" s="5"/>
     </row>
@@ -2698,16 +2710,16 @@
         <v>10012</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E16" s="3">
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -2715,16 +2727,16 @@
         <v>10013</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E17" s="3">
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="2:7">
@@ -2732,16 +2744,16 @@
         <v>10014</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="2:7">
@@ -2749,16 +2761,16 @@
         <v>10015</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F19" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="2:7">
@@ -2766,16 +2778,16 @@
         <v>10016</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G20" s="5"/>
     </row>
@@ -2784,16 +2796,16 @@
         <v>10017</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E21" s="4">
         <v>0.01</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G21" s="5"/>
     </row>
@@ -2802,16 +2814,16 @@
         <v>10018</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E22" s="3">
         <v>0.25</v>
       </c>
       <c r="F22" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="2:7">
@@ -2819,16 +2831,16 @@
         <v>10019</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E23" s="3">
         <v>0.2</v>
       </c>
       <c r="F23" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" spans="2:7">
@@ -2836,16 +2848,16 @@
         <v>10020</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G24" s="5"/>
     </row>
@@ -2854,16 +2866,16 @@
         <v>10021</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F25" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="2:7">
@@ -2873,630 +2885,630 @@
     </row>
     <row r="27" s="1" customFormat="1" spans="2:7">
       <c r="B27" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E27" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G27"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="2:7">
       <c r="B28" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" s="1">
-        <v>2</v>
+        <v>94</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F28" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G28"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="2:7">
       <c r="B29" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E29" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G29"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="2:7">
       <c r="B30" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D30" t="s">
-        <v>98</v>
-      </c>
-      <c r="E30" s="3">
-        <v>2</v>
+        <v>102</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G30"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="2:7">
       <c r="B31" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E31" s="1">
         <v>3</v>
       </c>
       <c r="F31" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G31"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="2:7">
       <c r="B32" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="1">
-        <v>3</v>
+        <v>110</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="F32" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G32"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="2:7">
       <c r="B33" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
-        <v>110</v>
-      </c>
-      <c r="E33" s="1">
-        <v>3</v>
+        <v>114</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="F33" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G33"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="2:7">
       <c r="B34" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E34" s="1">
-        <v>5</v>
+        <v>118</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="F34" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G34"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="2:7">
       <c r="B35" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E35" s="1">
-        <v>6</v>
+        <v>122</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="F35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G35"/>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E36" s="3">
         <v>2</v>
       </c>
       <c r="F36" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="2:7">
       <c r="B37" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E37" s="3">
         <v>30</v>
       </c>
       <c r="F37" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="2:7">
       <c r="B38" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D38" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E38" s="3">
         <v>150</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" spans="2:7">
       <c r="B39" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E39" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G39" s="5"/>
     </row>
     <row r="40" spans="2:7">
       <c r="B40" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F40" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="2:7">
       <c r="B41" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D41" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E41" s="3">
         <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="2:7">
       <c r="B42" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D42" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E42" s="3">
         <v>2</v>
       </c>
       <c r="F42" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="2:7">
       <c r="B43" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D43" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F43" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="2:7">
       <c r="B44" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D44" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E44" s="3">
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="2:7">
       <c r="B45" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D45" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E45" s="3">
         <v>0.2</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" spans="2:7">
       <c r="B46" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E46" s="4">
         <v>1</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G46" s="5"/>
     </row>
     <row r="47" s="2" customFormat="1" spans="2:7">
       <c r="B47" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E47" s="4">
         <v>3</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G47" s="5"/>
     </row>
     <row r="48" spans="2:7">
       <c r="B48" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D48" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E48" s="3">
         <v>3</v>
       </c>
       <c r="F48" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="49" spans="2:7">
       <c r="B49" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D49" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E49" s="3">
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="2:7">
       <c r="B50" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D50" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E50" s="3">
         <v>4</v>
       </c>
       <c r="F50" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="51" spans="2:7">
       <c r="B51" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D51" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F51" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="52" spans="2:7">
       <c r="B52" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D52" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F52" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53" s="2" customFormat="1" spans="2:7">
       <c r="B53" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G53" s="5"/>
     </row>
     <row r="54" spans="2:7">
       <c r="B54" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C54" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D54" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E54" s="3">
         <v>0.5</v>
       </c>
       <c r="F54" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="55" spans="2:7">
       <c r="B55" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C55" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D55" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E55" s="3">
         <v>0.4</v>
       </c>
       <c r="F55" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="56" spans="2:7">
       <c r="B56" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C56" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D56" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E56" s="3">
         <v>3</v>
       </c>
       <c r="F56" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="57" spans="2:7">
       <c r="B57" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C57" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D57" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E57" s="3">
         <v>0.5</v>
       </c>
       <c r="F57" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="2:7">
       <c r="B58" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C58" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D58" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F58" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G58"/>
     </row>
     <row r="59" spans="2:7">
       <c r="B59" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C59" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D59" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F59" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" spans="2:7">
       <c r="B60" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E60" s="4">
         <v>1</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G60" s="5"/>
     </row>
     <row r="61" s="2" customFormat="1" spans="2:7">
       <c r="B61" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E61" s="4">
         <v>2</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G61" s="5"/>
     </row>
     <row r="62" s="2" customFormat="1" spans="2:7">
       <c r="B62" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E62" s="4">
         <v>3</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="G62" s="5"/>
     </row>
@@ -3507,554 +3519,554 @@
     </row>
     <row r="64" spans="2:7">
       <c r="B64" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C64" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E64" s="3">
         <v>0.05</v>
       </c>
       <c r="F64" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="65" spans="2:7">
       <c r="B65" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C65" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D65" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E65" s="3">
         <v>2</v>
       </c>
       <c r="F65" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="66" spans="2:7">
       <c r="B66" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C66" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D66" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E66" s="3">
         <v>2</v>
       </c>
       <c r="F66" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" spans="2:7">
       <c r="B67" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E67" s="4">
         <v>1</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G67" s="5"/>
     </row>
     <row r="68" spans="2:7">
       <c r="B68" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C68" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D68" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E68" s="3">
         <v>1</v>
       </c>
       <c r="F68" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="69" spans="2:7">
       <c r="B69" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C69" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D69" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E69" s="3">
         <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="70" spans="2:7">
       <c r="B70" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C70" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D70" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E70" s="3">
         <v>100</v>
       </c>
       <c r="F70" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="71" spans="2:7">
       <c r="B71" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C71" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E71" s="3">
         <v>2</v>
       </c>
       <c r="F71" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="72" spans="2:7">
       <c r="B72" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D72" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E72" s="3">
         <v>2</v>
       </c>
       <c r="F72" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="73" spans="2:7">
       <c r="B73" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E73" s="3">
         <v>4</v>
       </c>
       <c r="F73" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="74" s="2" customFormat="1" spans="2:7">
       <c r="B74" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E74" s="4">
         <v>10</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="G74" s="5"/>
     </row>
     <row r="75" s="2" customFormat="1" spans="2:7">
       <c r="B75" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G75" s="5"/>
     </row>
     <row r="76" spans="2:7">
       <c r="B76" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C76" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D76" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E76" s="3">
         <v>30</v>
       </c>
       <c r="F76" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="77" spans="2:7">
       <c r="B77" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D77" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F77" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="78" spans="2:7">
       <c r="B78" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D78" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E78" s="3">
         <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="79" spans="2:7">
       <c r="B79" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D79" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F79" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="80" spans="2:7">
       <c r="B80" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D80" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E80" s="3">
         <v>3</v>
       </c>
       <c r="F80" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="81" spans="2:7">
       <c r="B81" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D81" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E81" s="3">
         <v>0.5</v>
       </c>
       <c r="F81" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="82" s="2" customFormat="1" spans="2:7">
       <c r="B82" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G82" s="5"/>
     </row>
     <row r="83" spans="2:7">
       <c r="B83" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D83" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E83" s="3">
         <v>0.5</v>
       </c>
       <c r="F83" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="84" spans="2:7">
       <c r="B84" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D84" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F84" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="85" spans="2:7">
       <c r="B85" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D85" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E85" s="3">
         <v>-0.3</v>
       </c>
       <c r="F85" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="86" spans="2:7">
       <c r="B86" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D86" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F86" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="87" s="2" customFormat="1" spans="2:7">
       <c r="B87" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E87" s="4">
         <v>1</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G87" s="5"/>
     </row>
     <row r="88" spans="2:7">
       <c r="B88" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D88" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E88" s="3">
         <v>-0.3</v>
       </c>
       <c r="F88" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="89" s="2" customFormat="1" spans="2:7">
       <c r="B89" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E89" s="4">
         <v>300</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G89" s="5"/>
     </row>
     <row r="90" s="2" customFormat="1" spans="2:7">
       <c r="B90" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E90" s="4">
         <v>0.2</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="G90" s="5"/>
     </row>
     <row r="91" s="2" customFormat="1" spans="2:7">
       <c r="B91" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="G91" s="5"/>
     </row>
     <row r="92" spans="2:7">
       <c r="B92" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C92" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E92" s="3">
         <v>-1</v>
       </c>
       <c r="F92" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="93" spans="2:7">
       <c r="B93" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C93" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E93" s="3">
         <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="2:7">
       <c r="B94" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C94" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D94" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E94" s="3">
         <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" s="2" customFormat="1" spans="2:7">
       <c r="B95" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="G95" s="5"/>
     </row>
@@ -4072,13 +4084,13 @@
         <v>235</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E97" s="3">
         <v>1</v>
       </c>
       <c r="F97" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="98" spans="2:7">
@@ -4086,16 +4098,16 @@
         <v>40002</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E98" s="3">
         <v>500</v>
       </c>
       <c r="F98" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="99" spans="2:7">
@@ -4103,16 +4115,16 @@
         <v>40003</v>
       </c>
       <c r="C99" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D99" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E99" s="3">
         <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="100" s="2" customFormat="1" spans="2:7">
@@ -4120,16 +4132,16 @@
         <v>40004</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E100" s="4">
         <v>1</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="G100" s="5"/>
     </row>
@@ -4138,16 +4150,16 @@
         <v>40005</v>
       </c>
       <c r="C101" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D101" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E101" s="3">
         <v>12</v>
       </c>
       <c r="F101" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="102" spans="2:7">
@@ -4155,16 +4167,16 @@
         <v>40006</v>
       </c>
       <c r="C102" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D102" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E102" s="3">
         <v>0.5</v>
       </c>
       <c r="F102" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="103" s="2" customFormat="1" spans="2:7">
@@ -4172,16 +4184,16 @@
         <v>40007</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E103" s="4">
         <v>3</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" spans="2:7">
@@ -4189,16 +4201,16 @@
         <v>40008</v>
       </c>
       <c r="C104" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D104" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E104" s="3">
         <v>1</v>
       </c>
       <c r="F104" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" spans="2:7">
@@ -4206,16 +4218,16 @@
         <v>40009</v>
       </c>
       <c r="C105" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D105" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E105" s="3">
         <v>6</v>
       </c>
       <c r="F105" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" spans="2:7">
@@ -4223,16 +4235,16 @@
         <v>400091</v>
       </c>
       <c r="C106" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E106" s="3">
         <v>66</v>
       </c>
       <c r="F106" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="107" s="2" customFormat="1" spans="2:7">
@@ -4240,16 +4252,16 @@
         <v>40010</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" spans="2:7">
@@ -4257,16 +4269,16 @@
         <v>40011</v>
       </c>
       <c r="C108" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D108" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E108" s="3">
         <v>0.5</v>
       </c>
       <c r="F108" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="109" s="2" customFormat="1" spans="2:7">
@@ -4274,16 +4286,16 @@
         <v>40012</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E109" s="4">
         <v>-2</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="110" s="2" customFormat="1" spans="2:7">
@@ -4291,7 +4303,7 @@
         <v>400121</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>16</v>
@@ -4300,7 +4312,7 @@
         <v>15</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="111" s="1" customFormat="1" spans="2:7">
@@ -4308,16 +4320,16 @@
         <v>40013</v>
       </c>
       <c r="C111" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D111" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E111" s="3">
         <v>0.1</v>
       </c>
       <c r="F111" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" spans="2:7">
@@ -4325,16 +4337,16 @@
         <v>40014</v>
       </c>
       <c r="C112" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D112" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E112" s="3">
         <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="113" spans="2:7">
@@ -4342,16 +4354,16 @@
         <v>400141</v>
       </c>
       <c r="C113" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D113" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E113" s="3">
         <v>77</v>
       </c>
       <c r="F113" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="114" spans="2:7">
@@ -4359,16 +4371,16 @@
         <v>400142</v>
       </c>
       <c r="C114" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D114" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E114" s="3">
         <v>7</v>
       </c>
       <c r="F114" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="115" spans="2:7">
@@ -4376,16 +4388,16 @@
         <v>40015</v>
       </c>
       <c r="C115" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D115" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E115" s="3">
         <v>0.5</v>
       </c>
       <c r="F115" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="116" spans="2:7">
@@ -4393,16 +4405,16 @@
         <v>400151</v>
       </c>
       <c r="C116" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D116" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F116" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="117" spans="2:7">
@@ -4410,16 +4422,16 @@
         <v>40016</v>
       </c>
       <c r="C117" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D117" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E117" s="3">
         <v>2</v>
       </c>
       <c r="F117" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="118" spans="2:7">
@@ -4427,16 +4439,16 @@
         <v>40017</v>
       </c>
       <c r="C118" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D118" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F118" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="119" spans="2:7">
@@ -4444,16 +4456,16 @@
         <v>40018</v>
       </c>
       <c r="C119" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F119" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="120" spans="2:7">
@@ -4461,16 +4473,16 @@
         <v>40019</v>
       </c>
       <c r="C120" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F120" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="121" spans="2:7">
@@ -4478,16 +4490,16 @@
         <v>40020</v>
       </c>
       <c r="C121" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F121" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="122" spans="2:7">
@@ -4495,16 +4507,16 @@
         <v>40021</v>
       </c>
       <c r="C122" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F122" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="123" spans="2:7">
@@ -4512,16 +4524,16 @@
         <v>40022</v>
       </c>
       <c r="C123" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F123" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="124" spans="2:7">
@@ -4529,16 +4541,16 @@
         <v>400221</v>
       </c>
       <c r="C124" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F124" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="125" s="2" customFormat="1" spans="2:7">
@@ -4546,16 +4558,16 @@
         <v>40023</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G125" s="5"/>
     </row>
@@ -4564,16 +4576,16 @@
         <v>40024</v>
       </c>
       <c r="C126" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E126" s="1">
         <v>0.2</v>
       </c>
       <c r="F126" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="127" spans="2:7">
@@ -4581,16 +4593,16 @@
         <v>40025</v>
       </c>
       <c r="C127" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F127" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="128" s="2" customFormat="1" spans="2:7">
@@ -4598,16 +4610,16 @@
         <v>40026</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E128" s="4">
         <v>2</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G128" s="5"/>
     </row>
@@ -4616,16 +4628,16 @@
         <v>40027</v>
       </c>
       <c r="C129" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D129" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F129" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="130" s="2" customFormat="1" spans="2:7">
@@ -4633,16 +4645,16 @@
         <v>40028</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="G130" s="5"/>
     </row>
@@ -4651,16 +4663,16 @@
         <v>40029</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="G131" s="5"/>
     </row>
@@ -4669,16 +4681,16 @@
         <v>40030</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="G132" s="5"/>
     </row>
@@ -4687,16 +4699,16 @@
         <v>40031</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E133" s="4">
         <v>12</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="G133" s="5"/>
     </row>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16590" windowHeight="10440"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1009,10 +1009,10 @@
     <t>DownGrade</t>
   </si>
   <si>
-    <t>0.5|1</t>
-  </si>
-  <si>
-    <t>每回合有50%概率使本回合所有敌人亮出的牌型顺位降1级</t>
+    <t>0.25|1</t>
+  </si>
+  <si>
+    <t>每回合有25%概率使本回合所有敌人亮出的牌型顺位降1级</t>
   </si>
   <si>
     <t>30024</t>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -916,475 +916,475 @@
     <t>DefeatGetMagnification</t>
   </si>
   <si>
+    <t>每输1次敌人,结算时就永久提供+1倍率</t>
+  </si>
+  <si>
+    <t>30017</t>
+  </si>
+  <si>
+    <t>幸运同花</t>
+  </si>
+  <si>
+    <t>LuckyFlush</t>
+  </si>
+  <si>
+    <t>亮牌时,若敌人的牌型大于同花,则会被强行视作同花</t>
+  </si>
+  <si>
+    <t>30018</t>
+  </si>
+  <si>
+    <t>逆转沙漏</t>
+  </si>
+  <si>
+    <t>ReverseResult</t>
+  </si>
+  <si>
+    <t>当牌型小于敌人时,有50%概率反转对比结果,但伤害按自身牌型计算</t>
+  </si>
+  <si>
+    <t>30019</t>
+  </si>
+  <si>
+    <t>练习卷</t>
+  </si>
+  <si>
+    <t>NoKillMonsterGetMagnification</t>
+  </si>
+  <si>
+    <t>1|0.5</t>
+  </si>
+  <si>
+    <t>每击杀1名敌人,结算时就永久提供+0.5倍率</t>
+  </si>
+  <si>
+    <t>30020</t>
+  </si>
+  <si>
+    <t>小本本</t>
+  </si>
+  <si>
+    <t>Revenge</t>
+  </si>
+  <si>
+    <t>本局内,对自己曾经输过的敌人造成伤害时,伤害+50%</t>
+  </si>
+  <si>
+    <t>30021</t>
+  </si>
+  <si>
+    <t>高贵徽章</t>
+  </si>
+  <si>
+    <t>NobleBadge</t>
+  </si>
+  <si>
+    <t>0.5|50</t>
+  </si>
+  <si>
+    <t>每关开始时,若血量高于50%,则获得50金币</t>
+  </si>
+  <si>
+    <t>30022</t>
+  </si>
+  <si>
+    <t>陷阱</t>
+  </si>
+  <si>
+    <t>Trap</t>
+  </si>
+  <si>
+    <t>本局内,曾经赢过自己的敌人在造成伤害时,伤害-30%</t>
+  </si>
+  <si>
+    <t>30023</t>
+  </si>
+  <si>
+    <t>好运来</t>
+  </si>
+  <si>
+    <t>DownGrade</t>
+  </si>
+  <si>
+    <t>0.25|1</t>
+  </si>
+  <si>
+    <t>每回合有25%概率使本回合所有敌人亮出的牌型顺位降1级</t>
+  </si>
+  <si>
+    <t>30024</t>
+  </si>
+  <si>
+    <t>入场券</t>
+  </si>
+  <si>
+    <t>AdmissionTicket</t>
+  </si>
+  <si>
+    <t>每回合开始时,对所有敌人造成1次自身攻击力的伤害</t>
+  </si>
+  <si>
+    <t>30025</t>
+  </si>
+  <si>
+    <t>条约</t>
+  </si>
+  <si>
+    <t>MonsterDamage</t>
+  </si>
+  <si>
+    <t>所有敌人造成的伤害降低30%</t>
+  </si>
+  <si>
+    <t>30026</t>
+  </si>
+  <si>
+    <t>豹子精髓</t>
+  </si>
+  <si>
+    <t>FirstLeopardGold</t>
+  </si>
+  <si>
+    <t>使用后,本局内你亮出豹子时,就会获得300金币</t>
+  </si>
+  <si>
+    <t>30027</t>
+  </si>
+  <si>
+    <t>时之沙</t>
+  </si>
+  <si>
+    <t>LevelWinDamageUp</t>
+  </si>
+  <si>
+    <t>使用后,本关内你比牌获胜时的伤害+20%</t>
+  </si>
+  <si>
+    <t>30028</t>
+  </si>
+  <si>
+    <t>巨人药剂</t>
+  </si>
+  <si>
+    <t>MaxHpUpAndHeal</t>
+  </si>
+  <si>
+    <t>80|80</t>
+  </si>
+  <si>
+    <t>使用后,玩家生命上限+80,并立即恢复80点血量</t>
+  </si>
+  <si>
+    <t>30029</t>
+  </si>
+  <si>
+    <t>降低</t>
+  </si>
+  <si>
+    <t>ReduceLevel</t>
+  </si>
+  <si>
+    <t>比牌时,对方的牌型顺位降低1级</t>
+  </si>
+  <si>
+    <t>30030</t>
+  </si>
+  <si>
+    <t>升职</t>
+  </si>
+  <si>
+    <t>UpLevel</t>
+  </si>
+  <si>
+    <t>比牌时,自己的牌型顺位提高1级</t>
+  </si>
+  <si>
+    <t>30031</t>
+  </si>
+  <si>
+    <t>净化药水</t>
+  </si>
+  <si>
+    <t>RemoveBossEntry</t>
+  </si>
+  <si>
+    <t>使用后,移除本关内的1条BOSS词缀效果</t>
+  </si>
+  <si>
+    <t>30032</t>
+  </si>
+  <si>
+    <t>三花聚顶</t>
+  </si>
+  <si>
+    <t>1|2|3</t>
+  </si>
+  <si>
+    <t>亮出的每张牌都提供其点数对应的攻击力加成</t>
+  </si>
+  <si>
+    <t>SpecialTwoThreeFive</t>
+  </si>
+  <si>
+    <t>高牌235等同于豹子牌型,并且可以战胜所有牌型</t>
+  </si>
+  <si>
+    <t>奢华沙发</t>
+  </si>
+  <si>
+    <t>获得500点生命上限</t>
+  </si>
+  <si>
+    <t>老花眼</t>
+  </si>
+  <si>
+    <t>SpecialFlush</t>
+  </si>
+  <si>
+    <t>红桃和方片视为同一花色,黑桃和梅花视为同一花色</t>
+  </si>
+  <si>
+    <t>周星星</t>
+  </si>
+  <si>
+    <t>RubbingCardsNum</t>
+  </si>
+  <si>
+    <t>每关[搓牌]使用次数+1</t>
+  </si>
+  <si>
+    <t>穷途末路</t>
+  </si>
+  <si>
+    <t>NoSkill</t>
+  </si>
+  <si>
+    <t>结算时,若所有技能都无剩余使用次数,则提供+12倍率</t>
+  </si>
+  <si>
+    <t>收藏夹</t>
+  </si>
+  <si>
+    <t>EveryRelic</t>
+  </si>
+  <si>
+    <t>每拥有1个圣物,结算时提供+0.5倍率</t>
+  </si>
+  <si>
+    <t>奢侈品</t>
+  </si>
+  <si>
+    <t>NoUseRubbingEveryRubbingNum</t>
+  </si>
+  <si>
+    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+3倍率</t>
+  </si>
+  <si>
+    <t>近视眼</t>
+  </si>
+  <si>
+    <t>AllCardIsHeadCard</t>
+  </si>
+  <si>
+    <t>所有牌均视为人头牌</t>
+  </si>
+  <si>
+    <t>顶尖学者</t>
+  </si>
+  <si>
+    <t>SpecialACard</t>
+  </si>
+  <si>
+    <t>亮出的每张A在结算时提供+6倍率</t>
+  </si>
+  <si>
+    <t>ACardAttack</t>
+  </si>
+  <si>
+    <t>亮出的每张A在结算时提供+66攻击力</t>
+  </si>
+  <si>
+    <t>老千</t>
+  </si>
+  <si>
+    <t>AccumulatedNumOfCardType</t>
+  </si>
+  <si>
+    <t>亮牌时,该牌型本局内每重复亮出1次就提供+1倍率</t>
+  </si>
+  <si>
+    <t>天使</t>
+  </si>
+  <si>
+    <t>ProOfUpCardType</t>
+  </si>
+  <si>
+    <t>亮牌时,有50%概率将该牌型提供的倍率永久+1</t>
+  </si>
+  <si>
+    <t>双刃剑</t>
+  </si>
+  <si>
+    <t>失去2次搓牌次数</t>
+  </si>
+  <si>
+    <t>结算时提供+15倍率</t>
+  </si>
+  <si>
+    <t>老搓家</t>
+  </si>
+  <si>
+    <t>RubbingCardRelic</t>
+  </si>
+  <si>
+    <t>每使用1次搓牌,该圣物永久提供+0.1倍率</t>
+  </si>
+  <si>
+    <t>幸运七</t>
+  </si>
+  <si>
+    <t>SpecialSevenCardPro</t>
+  </si>
+  <si>
+    <t>亮出的每张7结算时有100%概率提供攻击力和倍率</t>
+  </si>
+  <si>
+    <t>SpecialSevenCardAttack</t>
+  </si>
+  <si>
+    <t>幸运七触发时提供的攻击力</t>
+  </si>
+  <si>
+    <t>SpecialSevenCard</t>
+  </si>
+  <si>
+    <t>幸运七触发时提供的倍率</t>
+  </si>
+  <si>
+    <t>武林秘籍</t>
+  </si>
+  <si>
+    <t>MissDamagePer</t>
+  </si>
+  <si>
+    <t>获得50%闪避率</t>
+  </si>
+  <si>
+    <t>MissGetDamage</t>
+  </si>
+  <si>
+    <t>1|2</t>
+  </si>
+  <si>
+    <t>闪避成功时会对敌人造成1次自身攻击力200%的伤害</t>
+  </si>
+  <si>
+    <t>幸运对子</t>
+  </si>
+  <si>
+    <t>LuckyCouplet</t>
+  </si>
+  <si>
+    <t>亮牌时,若敌人的牌型大于对子,则会被强行视作对子</t>
+  </si>
+  <si>
+    <t>小强</t>
+  </si>
+  <si>
+    <t>DefeatGetDamage</t>
+  </si>
+  <si>
+    <t>1|0.1</t>
+  </si>
+  <si>
+    <t>每输1次敌人,后续自身造成的伤害提高10%</t>
+  </si>
+  <si>
+    <t>救命稻草</t>
+  </si>
+  <si>
+    <t>AstrawToClutchAt</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>受到致命伤害时血量降为1,且下次造成伤害时回复该伤害20%的血量,每关生效1次</t>
+  </si>
+  <si>
+    <t>专注</t>
+  </si>
+  <si>
+    <t>OneMonsterGetDamage</t>
+  </si>
+  <si>
+    <t>当场上只剩一个敌人时,对其造成的伤害+100%</t>
+  </si>
+  <si>
+    <t>变形魔方</t>
+  </si>
+  <si>
+    <t>CardUpGrade</t>
+  </si>
+  <si>
+    <t>每回合亮出的牌型顺位提升一级</t>
+  </si>
+  <si>
+    <t>毒药</t>
+  </si>
+  <si>
+    <t>MonsterHpMax</t>
+  </si>
+  <si>
+    <t>-0.3</t>
+  </si>
+  <si>
+    <t>所有敌人血量降低30%[BOSS除外]</t>
+  </si>
+  <si>
+    <t>刺客秘籍</t>
+  </si>
+  <si>
+    <t>HeroCritical</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>获得50%暴击率</t>
+  </si>
+  <si>
+    <t>CriticalAoe</t>
+  </si>
+  <si>
+    <t>触发暴击时会对其他敌人造成1次自身攻击力的伤害</t>
+  </si>
+  <si>
+    <t>透视眼</t>
+  </si>
+  <si>
+    <t>PerspectiveNum</t>
+  </si>
+  <si>
+    <t>每关[透视]使用次数+1</t>
+  </si>
+  <si>
+    <t>聚宝盆</t>
+  </si>
+  <si>
+    <t>DamageTurnToGold</t>
+  </si>
+  <si>
+    <t>每回合结束后,本回合自身总伤害输出的20%转化为金币</t>
+  </si>
+  <si>
+    <t>差距胶囊</t>
+  </si>
+  <si>
+    <t>GapDamage</t>
+  </si>
+  <si>
     <t>1|0.2</t>
-  </si>
-  <si>
-    <t>每输1次敌人,结算时就永久提供+0.2倍率</t>
-  </si>
-  <si>
-    <t>30017</t>
-  </si>
-  <si>
-    <t>幸运同花</t>
-  </si>
-  <si>
-    <t>LuckyFlush</t>
-  </si>
-  <si>
-    <t>亮牌时,若敌人的牌型大于同花,则会被强行视作同花</t>
-  </si>
-  <si>
-    <t>30018</t>
-  </si>
-  <si>
-    <t>逆转沙漏</t>
-  </si>
-  <si>
-    <t>ReverseResult</t>
-  </si>
-  <si>
-    <t>当牌型小于敌人时,有50%概率反转对比结果,但伤害按自身牌型计算</t>
-  </si>
-  <si>
-    <t>30019</t>
-  </si>
-  <si>
-    <t>练习卷</t>
-  </si>
-  <si>
-    <t>NoKillMonsterGetMagnification</t>
-  </si>
-  <si>
-    <t>1|0.5</t>
-  </si>
-  <si>
-    <t>每击杀1名敌人,结算时就永久提供+0.5倍率</t>
-  </si>
-  <si>
-    <t>30020</t>
-  </si>
-  <si>
-    <t>小本本</t>
-  </si>
-  <si>
-    <t>Revenge</t>
-  </si>
-  <si>
-    <t>本局内,对自己曾经输过的敌人造成伤害时,伤害+50%</t>
-  </si>
-  <si>
-    <t>30021</t>
-  </si>
-  <si>
-    <t>高贵徽章</t>
-  </si>
-  <si>
-    <t>NobleBadge</t>
-  </si>
-  <si>
-    <t>0.5|50</t>
-  </si>
-  <si>
-    <t>每关开始时,若血量高于50%,则获得50金币</t>
-  </si>
-  <si>
-    <t>30022</t>
-  </si>
-  <si>
-    <t>陷阱</t>
-  </si>
-  <si>
-    <t>Trap</t>
-  </si>
-  <si>
-    <t>本局内,曾经赢过自己的敌人在造成伤害时,伤害-30%</t>
-  </si>
-  <si>
-    <t>30023</t>
-  </si>
-  <si>
-    <t>好运来</t>
-  </si>
-  <si>
-    <t>DownGrade</t>
-  </si>
-  <si>
-    <t>0.25|1</t>
-  </si>
-  <si>
-    <t>每回合有25%概率使本回合所有敌人亮出的牌型顺位降1级</t>
-  </si>
-  <si>
-    <t>30024</t>
-  </si>
-  <si>
-    <t>入场券</t>
-  </si>
-  <si>
-    <t>AdmissionTicket</t>
-  </si>
-  <si>
-    <t>每回合开始时,对所有敌人造成1次自身攻击力的伤害</t>
-  </si>
-  <si>
-    <t>30025</t>
-  </si>
-  <si>
-    <t>条约</t>
-  </si>
-  <si>
-    <t>MonsterDamage</t>
-  </si>
-  <si>
-    <t>所有敌人造成的伤害降低30%</t>
-  </si>
-  <si>
-    <t>30026</t>
-  </si>
-  <si>
-    <t>豹子精髓</t>
-  </si>
-  <si>
-    <t>FirstLeopardGold</t>
-  </si>
-  <si>
-    <t>使用后,本局内你亮出豹子时,就会获得300金币</t>
-  </si>
-  <si>
-    <t>30027</t>
-  </si>
-  <si>
-    <t>时之沙</t>
-  </si>
-  <si>
-    <t>LevelWinDamageUp</t>
-  </si>
-  <si>
-    <t>使用后,本关内你比牌获胜时的伤害+20%</t>
-  </si>
-  <si>
-    <t>30028</t>
-  </si>
-  <si>
-    <t>巨人药剂</t>
-  </si>
-  <si>
-    <t>MaxHpUpAndHeal</t>
-  </si>
-  <si>
-    <t>80|80</t>
-  </si>
-  <si>
-    <t>使用后,玩家生命上限+80,并立即恢复80点血量</t>
-  </si>
-  <si>
-    <t>30029</t>
-  </si>
-  <si>
-    <t>降低</t>
-  </si>
-  <si>
-    <t>ReduceLevel</t>
-  </si>
-  <si>
-    <t>比牌时,对方的牌型顺位降低1级</t>
-  </si>
-  <si>
-    <t>30030</t>
-  </si>
-  <si>
-    <t>升职</t>
-  </si>
-  <si>
-    <t>UpLevel</t>
-  </si>
-  <si>
-    <t>比牌时,自己的牌型顺位提高1级</t>
-  </si>
-  <si>
-    <t>30031</t>
-  </si>
-  <si>
-    <t>净化药水</t>
-  </si>
-  <si>
-    <t>RemoveBossEntry</t>
-  </si>
-  <si>
-    <t>使用后,移除本关内的1条BOSS词缀效果</t>
-  </si>
-  <si>
-    <t>30032</t>
-  </si>
-  <si>
-    <t>三花聚顶</t>
-  </si>
-  <si>
-    <t>1|2|3</t>
-  </si>
-  <si>
-    <t>亮出的每张牌都提供其点数对应的攻击力加成</t>
-  </si>
-  <si>
-    <t>SpecialTwoThreeFive</t>
-  </si>
-  <si>
-    <t>高牌235等同于豹子牌型,并且可以战胜所有牌型</t>
-  </si>
-  <si>
-    <t>奢华沙发</t>
-  </si>
-  <si>
-    <t>获得500点生命上限</t>
-  </si>
-  <si>
-    <t>老花眼</t>
-  </si>
-  <si>
-    <t>SpecialFlush</t>
-  </si>
-  <si>
-    <t>红桃和方片视为同一花色,黑桃和梅花视为同一花色</t>
-  </si>
-  <si>
-    <t>周星星</t>
-  </si>
-  <si>
-    <t>RubbingCardsNum</t>
-  </si>
-  <si>
-    <t>每关[搓牌]使用次数+1</t>
-  </si>
-  <si>
-    <t>穷途末路</t>
-  </si>
-  <si>
-    <t>NoSkill</t>
-  </si>
-  <si>
-    <t>结算时,若所有技能都无剩余使用次数,则提供+12倍率</t>
-  </si>
-  <si>
-    <t>收藏夹</t>
-  </si>
-  <si>
-    <t>EveryRelic</t>
-  </si>
-  <si>
-    <t>每拥有1个圣物,结算时提供+0.5倍率</t>
-  </si>
-  <si>
-    <t>奢侈品</t>
-  </si>
-  <si>
-    <t>NoUseRubbingEveryRubbingNum</t>
-  </si>
-  <si>
-    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+3倍率</t>
-  </si>
-  <si>
-    <t>近视眼</t>
-  </si>
-  <si>
-    <t>AllCardIsHeadCard</t>
-  </si>
-  <si>
-    <t>所有牌均视为人头牌</t>
-  </si>
-  <si>
-    <t>顶尖学者</t>
-  </si>
-  <si>
-    <t>SpecialACard</t>
-  </si>
-  <si>
-    <t>亮出的每张A在结算时提供+6倍率</t>
-  </si>
-  <si>
-    <t>ACardAttack</t>
-  </si>
-  <si>
-    <t>亮出的每张A在结算时提供+66攻击力</t>
-  </si>
-  <si>
-    <t>老千</t>
-  </si>
-  <si>
-    <t>AccumulatedNumOfCardType</t>
-  </si>
-  <si>
-    <t>亮牌时,该牌型本局内每重复亮出1次就提供+1倍率</t>
-  </si>
-  <si>
-    <t>天使</t>
-  </si>
-  <si>
-    <t>ProOfUpCardType</t>
-  </si>
-  <si>
-    <t>亮牌时,有50%概率将该牌型提供的倍率永久+1</t>
-  </si>
-  <si>
-    <t>双刃剑</t>
-  </si>
-  <si>
-    <t>失去2次搓牌次数</t>
-  </si>
-  <si>
-    <t>结算时提供+15倍率</t>
-  </si>
-  <si>
-    <t>老搓家</t>
-  </si>
-  <si>
-    <t>RubbingCardRelic</t>
-  </si>
-  <si>
-    <t>每使用1次搓牌,该圣物永久提供+0.1倍率</t>
-  </si>
-  <si>
-    <t>幸运七</t>
-  </si>
-  <si>
-    <t>SpecialSevenCardPro</t>
-  </si>
-  <si>
-    <t>亮出的每张7结算时有100%概率提供攻击力和倍率</t>
-  </si>
-  <si>
-    <t>SpecialSevenCardAttack</t>
-  </si>
-  <si>
-    <t>幸运七触发时提供的攻击力</t>
-  </si>
-  <si>
-    <t>SpecialSevenCard</t>
-  </si>
-  <si>
-    <t>幸运七触发时提供的倍率</t>
-  </si>
-  <si>
-    <t>武林秘籍</t>
-  </si>
-  <si>
-    <t>MissDamagePer</t>
-  </si>
-  <si>
-    <t>获得50%闪避率</t>
-  </si>
-  <si>
-    <t>MissGetDamage</t>
-  </si>
-  <si>
-    <t>1|2</t>
-  </si>
-  <si>
-    <t>闪避成功时会对敌人造成1次自身攻击力200%的伤害</t>
-  </si>
-  <si>
-    <t>幸运对子</t>
-  </si>
-  <si>
-    <t>LuckyCouplet</t>
-  </si>
-  <si>
-    <t>亮牌时,若敌人的牌型大于对子,则会被强行视作对子</t>
-  </si>
-  <si>
-    <t>小强</t>
-  </si>
-  <si>
-    <t>DefeatGetDamage</t>
-  </si>
-  <si>
-    <t>1|0.1</t>
-  </si>
-  <si>
-    <t>每输1次敌人,后续自身造成的伤害提高10%</t>
-  </si>
-  <si>
-    <t>救命稻草</t>
-  </si>
-  <si>
-    <t>AstrawToClutchAt</t>
-  </si>
-  <si>
-    <t>0.2</t>
-  </si>
-  <si>
-    <t>受到致命伤害时血量降为1,且下次造成伤害时回复该伤害20%的血量,每关生效1次</t>
-  </si>
-  <si>
-    <t>专注</t>
-  </si>
-  <si>
-    <t>OneMonsterGetDamage</t>
-  </si>
-  <si>
-    <t>当场上只剩一个敌人时,对其造成的伤害+100%</t>
-  </si>
-  <si>
-    <t>变形魔方</t>
-  </si>
-  <si>
-    <t>CardUpGrade</t>
-  </si>
-  <si>
-    <t>每回合亮出的牌型顺位提升一级</t>
-  </si>
-  <si>
-    <t>毒药</t>
-  </si>
-  <si>
-    <t>MonsterHpMax</t>
-  </si>
-  <si>
-    <t>-0.3</t>
-  </si>
-  <si>
-    <t>所有敌人血量降低30%[BOSS除外]</t>
-  </si>
-  <si>
-    <t>刺客秘籍</t>
-  </si>
-  <si>
-    <t>HeroCritical</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>获得50%暴击率</t>
-  </si>
-  <si>
-    <t>CriticalAoe</t>
-  </si>
-  <si>
-    <t>触发暴击时会对其他敌人造成1次自身攻击力的伤害</t>
-  </si>
-  <si>
-    <t>透视眼</t>
-  </si>
-  <si>
-    <t>PerspectiveNum</t>
-  </si>
-  <si>
-    <t>每关[透视]使用次数+1</t>
-  </si>
-  <si>
-    <t>聚宝盆</t>
-  </si>
-  <si>
-    <t>DamageTurnToGold</t>
-  </si>
-  <si>
-    <t>每回合结束后,本回合自身总伤害输出的20%转化为金币</t>
-  </si>
-  <si>
-    <t>差距胶囊</t>
-  </si>
-  <si>
-    <t>GapDamage</t>
   </si>
   <si>
     <t>比牌时,你的牌型与对方牌型每相隔1级,则造成/承受的伤害对应提高/降低20%</t>
@@ -3786,287 +3786,287 @@
         <v>293</v>
       </c>
       <c r="E79" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F79" t="s">
         <v>294</v>
-      </c>
-      <c r="F79" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="80" spans="2:7">
       <c r="B80" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="D80" t="s">
         <v>297</v>
-      </c>
-      <c r="D80" t="s">
-        <v>298</v>
       </c>
       <c r="E80" s="3">
         <v>3</v>
       </c>
       <c r="F80" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="81" spans="2:7">
       <c r="B81" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="D81" t="s">
         <v>301</v>
-      </c>
-      <c r="D81" t="s">
-        <v>302</v>
       </c>
       <c r="E81" s="3">
         <v>0.5</v>
       </c>
       <c r="F81" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="82" s="2" customFormat="1" spans="2:7">
       <c r="B82" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="D82" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="E82" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="E82" s="4" t="s">
+      <c r="F82" s="5" t="s">
         <v>307</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>308</v>
       </c>
       <c r="G82" s="5"/>
     </row>
     <row r="83" spans="2:7">
       <c r="B83" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="D83" t="s">
         <v>310</v>
-      </c>
-      <c r="D83" t="s">
-        <v>311</v>
       </c>
       <c r="E83" s="3">
         <v>0.5</v>
       </c>
       <c r="F83" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="84" spans="2:7">
       <c r="B84" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="D84" t="s">
         <v>314</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="F84" t="s">
         <v>316</v>
-      </c>
-      <c r="F84" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="85" spans="2:7">
       <c r="B85" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="D85" t="s">
         <v>319</v>
-      </c>
-      <c r="D85" t="s">
-        <v>320</v>
       </c>
       <c r="E85" s="3">
         <v>-0.3</v>
       </c>
       <c r="F85" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="86" spans="2:7">
       <c r="B86" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="D86" t="s">
         <v>323</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="F86" t="s">
         <v>325</v>
-      </c>
-      <c r="F86" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="87" s="2" customFormat="1" spans="2:7">
       <c r="B87" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="D87" s="5" t="s">
         <v>328</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>329</v>
       </c>
       <c r="E87" s="4">
         <v>1</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G87" s="5"/>
     </row>
     <row r="88" spans="2:7">
       <c r="B88" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="D88" t="s">
         <v>332</v>
-      </c>
-      <c r="D88" t="s">
-        <v>333</v>
       </c>
       <c r="E88" s="3">
         <v>-0.3</v>
       </c>
       <c r="F88" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="89" s="2" customFormat="1" spans="2:7">
       <c r="B89" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C89" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="D89" s="5" t="s">
         <v>336</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>337</v>
       </c>
       <c r="E89" s="4">
         <v>300</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G89" s="5"/>
     </row>
     <row r="90" s="2" customFormat="1" spans="2:7">
       <c r="B90" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C90" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="D90" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="E90" s="4">
         <v>0.2</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G90" s="5"/>
     </row>
     <row r="91" s="2" customFormat="1" spans="2:7">
       <c r="B91" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C91" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="D91" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="D91" s="5" t="s">
+      <c r="E91" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="E91" s="4" t="s">
+      <c r="F91" s="5" t="s">
         <v>346</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>347</v>
       </c>
       <c r="G91" s="5"/>
     </row>
     <row r="92" spans="2:7">
       <c r="B92" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C92" t="s">
         <v>348</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>350</v>
       </c>
       <c r="E92" s="3">
         <v>-1</v>
       </c>
       <c r="F92" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="2:7">
       <c r="B93" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C93" t="s">
         <v>352</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="E93" s="3">
         <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="2:7">
       <c r="B94" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C94" t="s">
         <v>356</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
         <v>357</v>
-      </c>
-      <c r="D94" t="s">
-        <v>358</v>
       </c>
       <c r="E94" s="3">
         <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" s="2" customFormat="1" spans="2:7">
       <c r="B95" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>361</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>222</v>
       </c>
       <c r="E95" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="F95" s="5" t="s">
         <v>362</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>363</v>
       </c>
       <c r="G95" s="5"/>
     </row>
@@ -4084,13 +4084,13 @@
         <v>235</v>
       </c>
       <c r="D97" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E97" s="3">
         <v>1</v>
       </c>
       <c r="F97" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="2:7">
@@ -4098,7 +4098,7 @@
         <v>40002</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>128</v>
@@ -4107,7 +4107,7 @@
         <v>500</v>
       </c>
       <c r="F98" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="99" spans="2:7">
@@ -4115,16 +4115,16 @@
         <v>40003</v>
       </c>
       <c r="C99" t="s">
+        <v>367</v>
+      </c>
+      <c r="D99" t="s">
         <v>368</v>
-      </c>
-      <c r="D99" t="s">
-        <v>369</v>
       </c>
       <c r="E99" s="3">
         <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="100" s="2" customFormat="1" spans="2:7">
@@ -4132,16 +4132,16 @@
         <v>40004</v>
       </c>
       <c r="C100" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="D100" s="5" t="s">
         <v>371</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>372</v>
       </c>
       <c r="E100" s="4">
         <v>1</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G100" s="5"/>
     </row>
@@ -4150,16 +4150,16 @@
         <v>40005</v>
       </c>
       <c r="C101" t="s">
+        <v>373</v>
+      </c>
+      <c r="D101" t="s">
         <v>374</v>
-      </c>
-      <c r="D101" t="s">
-        <v>375</v>
       </c>
       <c r="E101" s="3">
         <v>12</v>
       </c>
       <c r="F101" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="102" spans="2:7">
@@ -4167,16 +4167,16 @@
         <v>40006</v>
       </c>
       <c r="C102" t="s">
+        <v>376</v>
+      </c>
+      <c r="D102" t="s">
         <v>377</v>
-      </c>
-      <c r="D102" t="s">
-        <v>378</v>
       </c>
       <c r="E102" s="3">
         <v>0.5</v>
       </c>
       <c r="F102" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="103" s="2" customFormat="1" spans="2:7">
@@ -4184,16 +4184,16 @@
         <v>40007</v>
       </c>
       <c r="C103" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="D103" s="5" t="s">
         <v>380</v>
-      </c>
-      <c r="D103" s="5" t="s">
-        <v>381</v>
       </c>
       <c r="E103" s="4">
         <v>3</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" spans="2:7">
@@ -4201,16 +4201,16 @@
         <v>40008</v>
       </c>
       <c r="C104" t="s">
+        <v>382</v>
+      </c>
+      <c r="D104" t="s">
         <v>383</v>
-      </c>
-      <c r="D104" t="s">
-        <v>384</v>
       </c>
       <c r="E104" s="3">
         <v>1</v>
       </c>
       <c r="F104" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" spans="2:7">
@@ -4218,16 +4218,16 @@
         <v>40009</v>
       </c>
       <c r="C105" t="s">
+        <v>385</v>
+      </c>
+      <c r="D105" t="s">
         <v>386</v>
-      </c>
-      <c r="D105" t="s">
-        <v>387</v>
       </c>
       <c r="E105" s="3">
         <v>6</v>
       </c>
       <c r="F105" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" spans="2:7">
@@ -4235,16 +4235,16 @@
         <v>400091</v>
       </c>
       <c r="C106" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E106" s="3">
         <v>66</v>
       </c>
       <c r="F106" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="107" s="2" customFormat="1" spans="2:7">
@@ -4252,16 +4252,16 @@
         <v>40010</v>
       </c>
       <c r="C107" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="D107" s="5" t="s">
         <v>391</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>392</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>276</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" spans="2:7">
@@ -4269,16 +4269,16 @@
         <v>40011</v>
       </c>
       <c r="C108" t="s">
+        <v>393</v>
+      </c>
+      <c r="D108" t="s">
         <v>394</v>
-      </c>
-      <c r="D108" t="s">
-        <v>395</v>
       </c>
       <c r="E108" s="3">
         <v>0.5</v>
       </c>
       <c r="F108" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="109" s="2" customFormat="1" spans="2:7">
@@ -4286,16 +4286,16 @@
         <v>40012</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E109" s="4">
         <v>-2</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="110" s="2" customFormat="1" spans="2:7">
@@ -4303,7 +4303,7 @@
         <v>400121</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>16</v>
@@ -4312,7 +4312,7 @@
         <v>15</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="111" s="1" customFormat="1" spans="2:7">
@@ -4320,16 +4320,16 @@
         <v>40013</v>
       </c>
       <c r="C111" t="s">
+        <v>399</v>
+      </c>
+      <c r="D111" t="s">
         <v>400</v>
-      </c>
-      <c r="D111" t="s">
-        <v>401</v>
       </c>
       <c r="E111" s="3">
         <v>0.1</v>
       </c>
       <c r="F111" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" spans="2:7">
@@ -4337,16 +4337,16 @@
         <v>40014</v>
       </c>
       <c r="C112" t="s">
+        <v>402</v>
+      </c>
+      <c r="D112" t="s">
         <v>403</v>
-      </c>
-      <c r="D112" t="s">
-        <v>404</v>
       </c>
       <c r="E112" s="3">
         <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="113" spans="2:7">
@@ -4354,16 +4354,16 @@
         <v>400141</v>
       </c>
       <c r="C113" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D113" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E113" s="3">
         <v>77</v>
       </c>
       <c r="F113" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="114" spans="2:7">
@@ -4371,16 +4371,16 @@
         <v>400142</v>
       </c>
       <c r="C114" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D114" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E114" s="3">
         <v>7</v>
       </c>
       <c r="F114" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="115" spans="2:7">
@@ -4388,16 +4388,16 @@
         <v>40015</v>
       </c>
       <c r="C115" t="s">
+        <v>409</v>
+      </c>
+      <c r="D115" t="s">
         <v>410</v>
-      </c>
-      <c r="D115" t="s">
-        <v>411</v>
       </c>
       <c r="E115" s="3">
         <v>0.5</v>
       </c>
       <c r="F115" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="116" spans="2:7">
@@ -4405,16 +4405,16 @@
         <v>400151</v>
       </c>
       <c r="C116" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D116" t="s">
+        <v>412</v>
+      </c>
+      <c r="E116" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="E116" s="3" t="s">
+      <c r="F116" t="s">
         <v>414</v>
-      </c>
-      <c r="F116" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="117" spans="2:7">
@@ -4422,16 +4422,16 @@
         <v>40016</v>
       </c>
       <c r="C117" t="s">
+        <v>415</v>
+      </c>
+      <c r="D117" t="s">
         <v>416</v>
-      </c>
-      <c r="D117" t="s">
-        <v>417</v>
       </c>
       <c r="E117" s="3">
         <v>2</v>
       </c>
       <c r="F117" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="118" spans="2:7">
@@ -4439,16 +4439,16 @@
         <v>40017</v>
       </c>
       <c r="C118" t="s">
+        <v>418</v>
+      </c>
+      <c r="D118" t="s">
         <v>419</v>
       </c>
-      <c r="D118" t="s">
+      <c r="E118" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="F118" t="s">
         <v>421</v>
-      </c>
-      <c r="F118" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="119" spans="2:7">
@@ -4456,16 +4456,16 @@
         <v>40018</v>
       </c>
       <c r="C119" t="s">
+        <v>422</v>
+      </c>
+      <c r="D119" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="D119" s="3" t="s">
+      <c r="E119" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="E119" s="1" t="s">
+      <c r="F119" t="s">
         <v>425</v>
-      </c>
-      <c r="F119" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="120" spans="2:7">
@@ -4473,16 +4473,16 @@
         <v>40019</v>
       </c>
       <c r="C120" t="s">
+        <v>426</v>
+      </c>
+      <c r="D120" s="3" t="s">
         <v>427</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>428</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F120" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="121" spans="2:7">
@@ -4490,16 +4490,16 @@
         <v>40020</v>
       </c>
       <c r="C121" t="s">
+        <v>429</v>
+      </c>
+      <c r="D121" s="3" t="s">
         <v>430</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>431</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F121" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="122" spans="2:7">
@@ -4507,16 +4507,16 @@
         <v>40021</v>
       </c>
       <c r="C122" t="s">
+        <v>432</v>
+      </c>
+      <c r="D122" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="D122" s="3" t="s">
+      <c r="E122" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E122" s="1" t="s">
+      <c r="F122" t="s">
         <v>435</v>
-      </c>
-      <c r="F122" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="123" spans="2:7">
@@ -4524,16 +4524,16 @@
         <v>40022</v>
       </c>
       <c r="C123" t="s">
+        <v>436</v>
+      </c>
+      <c r="D123" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="D123" s="3" t="s">
+      <c r="E123" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="E123" s="1" t="s">
+      <c r="F123" t="s">
         <v>439</v>
-      </c>
-      <c r="F123" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="124" spans="2:7">
@@ -4541,16 +4541,16 @@
         <v>400221</v>
       </c>
       <c r="C124" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>276</v>
       </c>
       <c r="F124" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="125" s="2" customFormat="1" spans="2:7">
@@ -4558,16 +4558,16 @@
         <v>40023</v>
       </c>
       <c r="C125" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="D125" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>444</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G125" s="5"/>
     </row>
@@ -4576,16 +4576,16 @@
         <v>40024</v>
       </c>
       <c r="C126" t="s">
+        <v>445</v>
+      </c>
+      <c r="D126" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>447</v>
       </c>
       <c r="E126" s="1">
         <v>0.2</v>
       </c>
       <c r="F126" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="127" spans="2:7">
@@ -4593,13 +4593,13 @@
         <v>40025</v>
       </c>
       <c r="C127" t="s">
+        <v>448</v>
+      </c>
+      <c r="D127" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="D127" s="3" t="s">
+      <c r="E127" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>294</v>
       </c>
       <c r="F127" t="s">
         <v>451</v>
@@ -4666,7 +4666,7 @@
         <v>462</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E131" s="4" t="s">
         <v>463</v>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="17355" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1168,7 +1168,7 @@
     <t>EveryRelic</t>
   </si>
   <si>
-    <t>每拥有1个圣物,结算时提供+0.5倍率</t>
+    <t>每拥有1个圣物,结算时提供+3倍率</t>
   </si>
   <si>
     <t>奢侈品</t>
@@ -4173,7 +4173,7 @@
         <v>377</v>
       </c>
       <c r="E102" s="3">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="F102" t="s">
         <v>378</v>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17355" windowHeight="11655"/>
+    <workbookView windowWidth="17640" windowHeight="12240"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="475">
   <si>
     <t>##var</t>
   </si>
@@ -583,7 +583,10 @@
     <t>LuckyStraight</t>
   </si>
   <si>
-    <t>亮牌时,若敌人的牌型大于顺子,则会被强行视作顺子</t>
+    <t>4|15</t>
+  </si>
+  <si>
+    <t>亮牌时,若敌人的牌型大于顺子,则会被强行视作顺子(购买后15次比牌内生效)</t>
   </si>
   <si>
     <t>20024</t>
@@ -928,7 +931,10 @@
     <t>LuckyFlush</t>
   </si>
   <si>
-    <t>亮牌时,若敌人的牌型大于同花,则会被强行视作同花</t>
+    <t>3|10</t>
+  </si>
+  <si>
+    <t>亮牌时,若敌人的牌型大于同花,则会被强行视作同花(购买后10次比牌内生效)</t>
   </si>
   <si>
     <t>30018</t>
@@ -1285,7 +1291,10 @@
     <t>LuckyCouplet</t>
   </si>
   <si>
-    <t>亮牌时,若敌人的牌型大于对子,则会被强行视作对子</t>
+    <t>2|6</t>
+  </si>
+  <si>
+    <t>亮牌时,若敌人的牌型大于对子,则会被强行视作对子(购买后6次比牌内生效)</t>
   </si>
   <si>
     <t>小强</t>
@@ -1619,18 +1628,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1951,7 +1954,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -1975,16 +1978,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
@@ -1993,108 +1996,117 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2445,168 +2457,169 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="5.75833333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.49166666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.475" style="3" customWidth="1"/>
-    <col min="4" max="4" width="21.8416666666667" style="3" customWidth="1"/>
-    <col min="5" max="5" width="8.36666666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.325" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.75833333333333" style="3" customWidth="1"/>
+    <col min="2" max="2" width="7.49166666666667" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.475" style="4" customWidth="1"/>
+    <col min="4" max="4" width="21.8416666666667" style="4" customWidth="1"/>
+    <col min="5" max="5" width="8.36666666666667" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20.325" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="B5" s="3">
+    <row r="5" s="1" customFormat="1" spans="1:7">
+      <c r="B5" s="5">
         <v>10001</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="5">
         <v>1</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="6" t="s">
         <v>17</v>
       </c>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:7">
-      <c r="B6" s="3">
+      <c r="B6" s="5">
         <v>10002</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="5">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:7">
-      <c r="B7" s="3">
+      <c r="B7" s="5">
         <v>10003</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:7">
-      <c r="B8" s="3">
+      <c r="B8" s="5">
         <v>10004</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="5">
         <v>1</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:7">
-      <c r="B9" s="3">
+      <c r="B9" s="5">
         <v>10005</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="5">
         <v>1</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:7">
-      <c r="B10" s="3">
+      <c r="B10" s="5">
         <v>10006</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2615,351 +2628,361 @@
       <c r="E10" s="1">
         <v>3</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:7">
-      <c r="B11" s="3">
+      <c r="B11" s="5">
         <v>10007</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:7">
-      <c r="B12" s="3">
+      <c r="B12" s="5">
         <v>10008</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:7">
-      <c r="B13" s="3">
+      <c r="B13" s="5">
         <v>10009</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:7">
-      <c r="B14" s="3">
+      <c r="B14" s="5">
         <v>10010</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="5" t="s">
         <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="6" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:7">
-      <c r="B15" s="4">
+      <c r="B15" s="7">
         <v>10011</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="7">
         <v>-0.05</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="B16" s="3">
+      <c r="G15" s="8"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:7">
+      <c r="B16" s="5">
         <v>10012</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="5">
         <v>2</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="6" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="3">
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="2:7">
+      <c r="B17" s="5">
         <v>10013</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="5">
         <v>2</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="6" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="3">
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="2:7">
+      <c r="B18" s="5">
         <v>10014</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="6" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="3">
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="2:7">
+      <c r="B19" s="5">
         <v>10015</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="6" t="s">
         <v>66</v>
       </c>
+      <c r="G19" s="6"/>
     </row>
     <row r="20" s="2" customFormat="1" spans="2:7">
-      <c r="B20" s="4">
+      <c r="B20" s="7">
         <v>10016</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="G20" s="5"/>
+      <c r="G20" s="8"/>
     </row>
     <row r="21" s="2" customFormat="1" spans="2:7">
-      <c r="B21" s="4">
+      <c r="B21" s="7">
         <v>10017</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="7">
         <v>0.01</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="3">
+      <c r="G21" s="8"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="2:7">
+      <c r="B22" s="5">
         <v>10018</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="5">
         <v>0.25</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="6" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="3">
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="2:7">
+      <c r="B23" s="5">
         <v>10019</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="5">
         <v>0.2</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="6" t="s">
         <v>79</v>
       </c>
+      <c r="G23" s="6"/>
     </row>
     <row r="24" s="2" customFormat="1" spans="2:7">
-      <c r="B24" s="4">
+      <c r="B24" s="7">
         <v>10020</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="3">
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="2:7">
+      <c r="B25" s="5">
         <v>10021</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="6" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="3"/>
-      <c r="D26"/>
-      <c r="E26" s="3"/>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="2:7">
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="6"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="2:7">
       <c r="B27" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="5">
         <v>1</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="G27"/>
+      <c r="G27" s="6"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="2:7">
       <c r="B28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="6" t="s">
         <v>94</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G28"/>
+      <c r="G28" s="6"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="2:7">
       <c r="B29" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="5">
         <v>1</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G29"/>
+      <c r="G29" s="6"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="2:7">
       <c r="B30" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="6" t="s">
         <v>102</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G30"/>
+      <c r="G30" s="6"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="2:7">
       <c r="B31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="5" t="s">
         <v>105</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -2968,1749 +2991,1864 @@
       <c r="E31" s="1">
         <v>3</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G31"/>
+      <c r="G31" s="6"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="2:7">
       <c r="B32" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="6" t="s">
         <v>110</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="G32"/>
+      <c r="G32" s="6"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="2:7">
       <c r="B33" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="6" t="s">
         <v>114</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="G33"/>
+      <c r="G33" s="6"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="2:7">
       <c r="B34" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="6" t="s">
         <v>118</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G34"/>
+      <c r="G34" s="6"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="2:7">
       <c r="B35" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="5" t="s">
         <v>122</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="G35"/>
-    </row>
-    <row r="36" spans="2:7">
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="2:7">
       <c r="B36" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="5">
         <v>2</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="6" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="37" spans="2:7">
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="2:7">
       <c r="B37" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="5">
         <v>30</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="6" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="38" spans="2:7">
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="2:7">
       <c r="B38" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="5">
         <v>150</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="5" t="s">
         <v>133</v>
       </c>
+      <c r="G38" s="6"/>
     </row>
     <row r="39" s="2" customFormat="1" spans="2:7">
       <c r="B39" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="7">
         <v>1</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="G39" s="5"/>
-    </row>
-    <row r="40" spans="2:7">
+      <c r="G39" s="8"/>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="2:7">
       <c r="B40" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="6" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="41" spans="2:7">
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="2:7">
       <c r="B41" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="5">
         <v>2</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="6" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="42" spans="2:7">
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="2:7">
       <c r="B42" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="5">
         <v>2</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="6" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="43" spans="2:7">
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="2:7">
       <c r="B43" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="6" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="44" spans="2:7">
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" s="1" customFormat="1" spans="2:7">
       <c r="B44" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="5">
         <v>10</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="6" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="45" spans="2:7">
+      <c r="G44" s="6"/>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="2:7">
       <c r="B45" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="5">
         <v>0.2</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="5" t="s">
         <v>163</v>
       </c>
+      <c r="G45" s="6"/>
     </row>
     <row r="46" s="2" customFormat="1" spans="2:7">
       <c r="B46" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E46" s="7">
         <v>1</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="F46" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="G46" s="5"/>
+      <c r="G46" s="8"/>
     </row>
     <row r="47" s="2" customFormat="1" spans="2:7">
       <c r="B47" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E47" s="7">
         <v>3</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="F47" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="G47" s="5"/>
-    </row>
-    <row r="48" spans="2:7">
+      <c r="G47" s="8"/>
+    </row>
+    <row r="48" s="1" customFormat="1" spans="2:7">
       <c r="B48" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="5">
         <v>3</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="6" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="49" spans="2:7">
+      <c r="G48" s="6"/>
+    </row>
+    <row r="49" s="1" customFormat="1" spans="2:7">
       <c r="B49" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="5">
         <v>1</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="6" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="50" spans="2:7">
+      <c r="G49" s="6"/>
+    </row>
+    <row r="50" s="1" customFormat="1" spans="2:7">
       <c r="B50" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="E50" s="3">
-        <v>4</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="E50" s="5" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="51" spans="2:7">
+      <c r="F50" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G50" s="6"/>
+    </row>
+    <row r="51" s="1" customFormat="1" spans="2:7">
       <c r="B51" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C51" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D51" t="s">
+      <c r="C51" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="D51" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F51" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="52" spans="2:7">
+      <c r="F51" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="G51" s="6"/>
+    </row>
+    <row r="52" s="1" customFormat="1" spans="2:7">
       <c r="B52" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C52" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D52" t="s">
+      <c r="C52" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="D52" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="F52" t="s">
+      <c r="E52" s="5" t="s">
         <v>192</v>
       </c>
+      <c r="F52" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="G52" s="6"/>
     </row>
     <row r="53" s="2" customFormat="1" spans="2:7">
       <c r="B53" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C53" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="C53" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="D53" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="E53" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="G53" s="5"/>
-    </row>
-    <row r="54" spans="2:7">
+      <c r="F53" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="G53" s="8"/>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="2:7">
       <c r="B54" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C54" t="s">
         <v>199</v>
       </c>
-      <c r="D54" t="s">
+      <c r="C54" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D54" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E54" s="5">
         <v>0.5</v>
       </c>
-      <c r="F54" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7">
+      <c r="F54" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="G54" s="6"/>
+    </row>
+    <row r="55" s="1" customFormat="1" spans="2:7">
       <c r="B55" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C55" t="s">
         <v>202</v>
       </c>
-      <c r="D55" t="s">
+      <c r="C55" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D55" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E55" s="5">
         <v>0.4</v>
       </c>
-      <c r="F55" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7">
+      <c r="F55" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G55" s="6"/>
+    </row>
+    <row r="56" s="1" customFormat="1" spans="2:7">
       <c r="B56" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C56" t="s">
         <v>205</v>
       </c>
-      <c r="D56" t="s">
+      <c r="C56" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="E56" s="3">
+      <c r="D56" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="E56" s="5">
         <v>3</v>
       </c>
-      <c r="F56" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="57" spans="2:7">
+      <c r="F56" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="G56" s="6"/>
+    </row>
+    <row r="57" s="1" customFormat="1" spans="2:7">
       <c r="B57" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C57" t="s">
         <v>209</v>
       </c>
-      <c r="D57" t="s">
+      <c r="C57" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E57" s="3">
+      <c r="D57" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E57" s="5">
         <v>0.5</v>
       </c>
-      <c r="F57" t="s">
-        <v>211</v>
-      </c>
+      <c r="F57" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="G57" s="6"/>
     </row>
     <row r="58" s="1" customFormat="1" spans="2:7">
       <c r="B58" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C58" t="s">
         <v>213</v>
       </c>
-      <c r="D58" t="s">
+      <c r="C58" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D58" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F58" t="s">
+      <c r="E58" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="G58"/>
-    </row>
-    <row r="59" spans="2:7">
+      <c r="F58" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="G58" s="6"/>
+    </row>
+    <row r="59" s="1" customFormat="1" spans="2:7">
       <c r="B59" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C59" t="s">
         <v>217</v>
       </c>
-      <c r="D59" t="s">
+      <c r="C59" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D59" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="F59" t="s">
+      <c r="E59" s="5" t="s">
         <v>219</v>
       </c>
+      <c r="F59" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="G59" s="6"/>
     </row>
     <row r="60" s="2" customFormat="1" spans="2:7">
       <c r="B60" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C60" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="C60" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="E60" s="4">
+      <c r="D60" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E60" s="7">
         <v>1</v>
       </c>
-      <c r="F60" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="G60" s="5"/>
+      <c r="F60" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G60" s="8"/>
     </row>
     <row r="61" s="2" customFormat="1" spans="2:7">
       <c r="B61" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C61" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="D61" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E61" s="4">
+      <c r="C61" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E61" s="7">
         <v>2</v>
       </c>
-      <c r="F61" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="G61" s="5"/>
+      <c r="F61" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="G61" s="8"/>
     </row>
     <row r="62" s="2" customFormat="1" spans="2:7">
       <c r="B62" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C62" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="D62" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E62" s="4">
+      <c r="C62" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E62" s="7">
         <v>3</v>
       </c>
-      <c r="F62" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="G62" s="5"/>
-    </row>
-    <row r="63" spans="2:7">
-      <c r="C63"/>
-      <c r="E63" s="3"/>
-      <c r="F63"/>
-    </row>
-    <row r="64" spans="2:7">
+      <c r="F62" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="G62" s="8"/>
+    </row>
+    <row r="63" s="1" customFormat="1" spans="2:7">
+      <c r="C63" s="6"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+    </row>
+    <row r="64" s="1" customFormat="1" spans="2:7">
       <c r="B64" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C64" t="s">
         <v>231</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="C64" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="E64" s="3">
+      <c r="D64" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E64" s="5">
         <v>0.05</v>
       </c>
-      <c r="F64" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7">
+      <c r="F64" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="G64" s="6"/>
+    </row>
+    <row r="65" s="1" customFormat="1" spans="2:7">
       <c r="B65" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C65" t="s">
         <v>235</v>
       </c>
-      <c r="D65" t="s">
+      <c r="C65" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="E65" s="3">
+      <c r="D65" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E65" s="5">
         <v>2</v>
       </c>
-      <c r="F65" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="66" spans="2:7">
+      <c r="F65" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="G65" s="6"/>
+    </row>
+    <row r="66" s="1" customFormat="1" spans="2:7">
       <c r="B66" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C66" t="s">
         <v>239</v>
       </c>
-      <c r="D66" t="s">
+      <c r="C66" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="E66" s="3">
+      <c r="D66" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="E66" s="5">
         <v>2</v>
       </c>
-      <c r="F66" t="s">
-        <v>241</v>
-      </c>
+      <c r="F66" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G66" s="6"/>
     </row>
     <row r="67" s="2" customFormat="1" spans="2:7">
       <c r="B67" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C67" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="C67" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="E67" s="4">
+      <c r="D67" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="E67" s="7">
         <v>1</v>
       </c>
-      <c r="F67" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="G67" s="5"/>
-    </row>
-    <row r="68" spans="2:7">
+      <c r="F67" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="G67" s="8"/>
+    </row>
+    <row r="68" s="1" customFormat="1" spans="2:7">
       <c r="B68" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C68" t="s">
         <v>247</v>
       </c>
-      <c r="D68" t="s">
+      <c r="C68" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="E68" s="3">
+      <c r="D68" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E68" s="5">
         <v>1</v>
       </c>
-      <c r="F68" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="69" spans="2:7">
+      <c r="F68" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="G68" s="6"/>
+    </row>
+    <row r="69" s="1" customFormat="1" spans="2:7">
       <c r="B69" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C69" t="s">
         <v>251</v>
       </c>
-      <c r="D69" t="s">
+      <c r="C69" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="E69" s="3">
+      <c r="D69" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E69" s="5">
         <v>1</v>
       </c>
-      <c r="F69" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="70" spans="2:7">
+      <c r="F69" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="G69" s="6"/>
+    </row>
+    <row r="70" s="1" customFormat="1" spans="2:7">
       <c r="B70" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C70" t="s">
         <v>255</v>
       </c>
-      <c r="D70" t="s">
+      <c r="C70" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="E70" s="3">
+      <c r="D70" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="E70" s="5">
         <v>100</v>
       </c>
-      <c r="F70" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="71" spans="2:7">
+      <c r="F70" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="G70" s="6"/>
+    </row>
+    <row r="71" s="1" customFormat="1" spans="2:7">
       <c r="B71" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C71" t="s">
         <v>259</v>
       </c>
-      <c r="D71" t="s">
+      <c r="C71" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="E71" s="3">
+      <c r="D71" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="E71" s="5">
         <v>2</v>
       </c>
-      <c r="F71" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="72" spans="2:7">
+      <c r="F71" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="G71" s="6"/>
+    </row>
+    <row r="72" s="1" customFormat="1" spans="2:7">
       <c r="B72" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C72" t="s">
         <v>263</v>
       </c>
-      <c r="D72" t="s">
+      <c r="C72" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="E72" s="3">
+      <c r="D72" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E72" s="5">
         <v>2</v>
       </c>
-      <c r="F72" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="73" spans="2:7">
+      <c r="F72" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="G72" s="6"/>
+    </row>
+    <row r="73" s="1" customFormat="1" spans="2:7">
       <c r="B73" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C73" t="s">
         <v>267</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="C73" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D73" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E73" s="3">
+      <c r="E73" s="5">
         <v>4</v>
       </c>
-      <c r="F73" t="s">
-        <v>268</v>
-      </c>
+      <c r="F73" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="G73" s="6"/>
     </row>
     <row r="74" s="2" customFormat="1" spans="2:7">
       <c r="B74" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C74" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="C74" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="E74" s="4">
+      <c r="D74" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E74" s="7">
         <v>10</v>
       </c>
-      <c r="F74" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="G74" s="5"/>
+      <c r="F74" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="G74" s="8"/>
     </row>
     <row r="75" s="2" customFormat="1" spans="2:7">
       <c r="B75" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C75" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="C75" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="E75" s="4" t="s">
+      <c r="D75" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="E75" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="G75" s="5"/>
-    </row>
-    <row r="76" spans="2:7">
+      <c r="F75" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="G75" s="8"/>
+    </row>
+    <row r="76" s="1" customFormat="1" spans="2:7">
       <c r="B76" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C76" t="s">
         <v>279</v>
       </c>
-      <c r="D76" t="s">
+      <c r="C76" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="E76" s="3">
+      <c r="D76" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="E76" s="5">
         <v>30</v>
       </c>
-      <c r="F76" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="77" spans="2:7">
+      <c r="F76" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="G76" s="6"/>
+    </row>
+    <row r="77" s="1" customFormat="1" spans="2:7">
       <c r="B77" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C77" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="D77" t="s">
+      <c r="C77" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="D77" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="F77" t="s">
+      <c r="E77" s="5" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="78" spans="2:7">
+      <c r="F77" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G77" s="6"/>
+    </row>
+    <row r="78" s="1" customFormat="1" spans="2:7">
       <c r="B78" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C78" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="D78" t="s">
+      <c r="C78" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="E78" s="3">
+      <c r="D78" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E78" s="5">
         <v>1</v>
       </c>
-      <c r="F78" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="79" spans="2:7">
+      <c r="F78" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G78" s="6"/>
+    </row>
+    <row r="79" s="1" customFormat="1" spans="2:7">
       <c r="B79" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C79" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="D79" t="s">
+      <c r="C79" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="E79" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="F79" t="s">
+      <c r="D79" s="6" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="80" spans="2:7">
+      <c r="E79" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="G79" s="6"/>
+    </row>
+    <row r="80" s="1" customFormat="1" spans="2:7">
       <c r="B80" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C80" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="D80" t="s">
+      <c r="C80" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="E80" s="3">
-        <v>3</v>
-      </c>
-      <c r="F80" t="s">
+      <c r="D80" s="6" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="81" spans="2:7">
+      <c r="E80" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="G80" s="6"/>
+    </row>
+    <row r="81" s="1" customFormat="1" spans="2:7">
       <c r="B81" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="D81" t="s">
         <v>301</v>
       </c>
-      <c r="E81" s="3">
+      <c r="C81" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="E81" s="5">
         <v>0.5</v>
       </c>
-      <c r="F81" t="s">
-        <v>302</v>
-      </c>
+      <c r="F81" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="G81" s="6"/>
     </row>
     <row r="82" s="2" customFormat="1" spans="2:7">
       <c r="B82" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="D82" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="E82" s="4" t="s">
+      <c r="C82" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="F82" s="5" t="s">
+      <c r="D82" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="G82" s="5"/>
-    </row>
-    <row r="83" spans="2:7">
+      <c r="E82" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="G82" s="8"/>
+    </row>
+    <row r="83" s="1" customFormat="1" spans="2:7">
       <c r="B83" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D83" t="s">
         <v>310</v>
       </c>
-      <c r="E83" s="3">
+      <c r="C83" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="E83" s="5">
         <v>0.5</v>
       </c>
-      <c r="F83" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="84" spans="2:7">
+      <c r="F83" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="G83" s="6"/>
+    </row>
+    <row r="84" s="1" customFormat="1" spans="2:7">
       <c r="B84" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="D84" t="s">
         <v>314</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="C84" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F84" t="s">
+      <c r="D84" s="6" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="85" spans="2:7">
+      <c r="E84" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="G84" s="6"/>
+    </row>
+    <row r="85" s="1" customFormat="1" spans="2:7">
       <c r="B85" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D85" t="s">
         <v>319</v>
       </c>
-      <c r="E85" s="3">
+      <c r="C85" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E85" s="5">
         <v>-0.3</v>
       </c>
-      <c r="F85" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="86" spans="2:7">
+      <c r="F85" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G85" s="6"/>
+    </row>
+    <row r="86" s="1" customFormat="1" spans="2:7">
       <c r="B86" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D86" t="s">
         <v>323</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="C86" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="F86" t="s">
+      <c r="D86" s="6" t="s">
         <v>325</v>
       </c>
+      <c r="E86" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="G86" s="6"/>
     </row>
     <row r="87" s="2" customFormat="1" spans="2:7">
       <c r="B87" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="D87" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="E87" s="4">
+      <c r="C87" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="E87" s="7">
         <v>1</v>
       </c>
-      <c r="F87" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="G87" s="5"/>
-    </row>
-    <row r="88" spans="2:7">
+      <c r="F87" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="G87" s="8"/>
+    </row>
+    <row r="88" s="1" customFormat="1" spans="2:7">
       <c r="B88" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="D88" t="s">
         <v>332</v>
       </c>
-      <c r="E88" s="3">
+      <c r="C88" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="E88" s="5">
         <v>-0.3</v>
       </c>
-      <c r="F88" t="s">
-        <v>333</v>
-      </c>
+      <c r="F88" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="G88" s="6"/>
     </row>
     <row r="89" s="2" customFormat="1" spans="2:7">
       <c r="B89" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="D89" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="E89" s="4">
+      <c r="C89" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E89" s="7">
         <v>300</v>
       </c>
-      <c r="F89" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="G89" s="5"/>
+      <c r="F89" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="G89" s="8"/>
     </row>
     <row r="90" s="2" customFormat="1" spans="2:7">
       <c r="B90" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="D90" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="E90" s="4">
+      <c r="C90" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="E90" s="7">
         <v>0.2</v>
       </c>
-      <c r="F90" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="G90" s="5"/>
+      <c r="F90" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="G90" s="8"/>
     </row>
     <row r="91" s="2" customFormat="1" spans="2:7">
       <c r="B91" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="D91" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="E91" s="4" t="s">
+      <c r="C91" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="F91" s="5" t="s">
+      <c r="D91" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="G91" s="5"/>
-    </row>
-    <row r="92" spans="2:7">
+      <c r="E91" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="G91" s="8"/>
+    </row>
+    <row r="92" s="1" customFormat="1" spans="2:7">
       <c r="B92" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C92" t="s">
-        <v>348</v>
+        <v>349</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="E92" s="3">
+        <v>351</v>
+      </c>
+      <c r="E92" s="5">
         <v>-1</v>
       </c>
-      <c r="F92" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="93" spans="2:7">
+      <c r="F92" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="G92" s="6"/>
+    </row>
+    <row r="93" s="1" customFormat="1" spans="2:7">
       <c r="B93" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C93" t="s">
-        <v>352</v>
+        <v>353</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>354</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E93" s="3">
+        <v>355</v>
+      </c>
+      <c r="E93" s="5">
         <v>1</v>
       </c>
-      <c r="F93" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="94" spans="2:7">
+      <c r="F93" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="G93" s="6"/>
+    </row>
+    <row r="94" s="1" customFormat="1" spans="2:7">
       <c r="B94" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C94" t="s">
-        <v>356</v>
-      </c>
-      <c r="D94" t="s">
         <v>357</v>
       </c>
-      <c r="E94" s="3">
+      <c r="C94" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E94" s="5">
         <v>1</v>
       </c>
-      <c r="F94" t="s">
-        <v>358</v>
-      </c>
+      <c r="F94" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="G94" s="6"/>
     </row>
     <row r="95" s="2" customFormat="1" spans="2:7">
       <c r="B95" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E95" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="F95" s="5" t="s">
+      <c r="C95" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="G95" s="5"/>
-    </row>
-    <row r="96" spans="2:7">
-      <c r="B96" s="3"/>
-      <c r="D96"/>
-      <c r="E96" s="3"/>
-      <c r="F96"/>
-    </row>
-    <row r="97" spans="2:7">
-      <c r="B97" s="3">
+      <c r="D95" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="G95" s="8"/>
+    </row>
+    <row r="96" s="1" customFormat="1" spans="2:7">
+      <c r="B96" s="5"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="6"/>
+    </row>
+    <row r="97" s="1" customFormat="1" spans="2:7">
+      <c r="B97" s="5">
         <v>40001</v>
       </c>
-      <c r="C97" s="3">
+      <c r="C97" s="5">
         <v>235</v>
       </c>
-      <c r="D97" t="s">
-        <v>363</v>
-      </c>
-      <c r="E97" s="3">
+      <c r="D97" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E97" s="5">
         <v>1</v>
       </c>
-      <c r="F97" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7">
-      <c r="B98" s="3">
+      <c r="F97" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="G97" s="6"/>
+    </row>
+    <row r="98" s="1" customFormat="1" spans="2:7">
+      <c r="B98" s="5">
         <v>40002</v>
       </c>
-      <c r="C98" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="D98" s="3" t="s">
+      <c r="C98" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="D98" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="E98" s="3">
+      <c r="E98" s="5">
         <v>500</v>
       </c>
-      <c r="F98" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7">
-      <c r="B99" s="3">
+      <c r="F98" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="G98" s="6"/>
+    </row>
+    <row r="99" s="1" customFormat="1" spans="2:7">
+      <c r="B99" s="5">
         <v>40003</v>
       </c>
-      <c r="C99" t="s">
-        <v>367</v>
-      </c>
-      <c r="D99" t="s">
-        <v>368</v>
-      </c>
-      <c r="E99" s="3">
+      <c r="C99" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="E99" s="5">
         <v>1</v>
       </c>
-      <c r="F99" t="s">
-        <v>369</v>
-      </c>
+      <c r="F99" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="G99" s="6"/>
     </row>
     <row r="100" s="2" customFormat="1" spans="2:7">
-      <c r="B100" s="4">
+      <c r="B100" s="7">
         <v>40004</v>
       </c>
-      <c r="C100" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="E100" s="4">
+      <c r="C100" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="E100" s="7">
         <v>1</v>
       </c>
-      <c r="F100" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="G100" s="5"/>
-    </row>
-    <row r="101" spans="2:7">
-      <c r="B101" s="3">
+      <c r="F100" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="G100" s="8"/>
+    </row>
+    <row r="101" s="1" customFormat="1" spans="2:7">
+      <c r="B101" s="5">
         <v>40005</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E101" s="5">
+        <v>12</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="G101" s="6"/>
+    </row>
+    <row r="102" s="1" customFormat="1" spans="2:7">
+      <c r="B102" s="5">
+        <v>40006</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="E102" s="5">
+        <v>3</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="G102" s="6"/>
+    </row>
+    <row r="103" s="2" customFormat="1" spans="2:7">
+      <c r="B103" s="7">
+        <v>40007</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="E103" s="7">
+        <v>3</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="104" s="1" customFormat="1" spans="2:7">
+      <c r="B104" s="5">
+        <v>40008</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="E104" s="5">
+        <v>1</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="105" s="1" customFormat="1" spans="2:7">
+      <c r="B105" s="5">
+        <v>40009</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="E105" s="5">
+        <v>6</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="106" s="1" customFormat="1" spans="2:7">
+      <c r="B106" s="5">
+        <v>400091</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="E106" s="5">
+        <v>66</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="107" s="2" customFormat="1" spans="2:7">
+      <c r="B107" s="7">
+        <v>40010</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="108" s="1" customFormat="1" spans="2:7">
+      <c r="B108" s="5">
+        <v>40011</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="E108" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="109" s="2" customFormat="1" spans="2:7">
+      <c r="B109" s="7">
+        <v>40012</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="D109" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="D101" t="s">
-        <v>374</v>
-      </c>
-      <c r="E101" s="3">
-        <v>12</v>
-      </c>
-      <c r="F101" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="102" spans="2:7">
-      <c r="B102" s="3">
-        <v>40006</v>
-      </c>
-      <c r="C102" t="s">
-        <v>376</v>
-      </c>
-      <c r="D102" t="s">
-        <v>377</v>
-      </c>
-      <c r="E102" s="3">
-        <v>3</v>
-      </c>
-      <c r="F102" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="103" s="2" customFormat="1" spans="2:7">
-      <c r="B103" s="4">
-        <v>40007</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="D103" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="E103" s="4">
-        <v>3</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="104" s="1" customFormat="1" spans="2:7">
-      <c r="B104" s="3">
-        <v>40008</v>
-      </c>
-      <c r="C104" t="s">
-        <v>382</v>
-      </c>
-      <c r="D104" t="s">
-        <v>383</v>
-      </c>
-      <c r="E104" s="3">
-        <v>1</v>
-      </c>
-      <c r="F104" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="105" s="1" customFormat="1" spans="2:7">
-      <c r="B105" s="3">
-        <v>40009</v>
-      </c>
-      <c r="C105" t="s">
-        <v>385</v>
-      </c>
-      <c r="D105" t="s">
-        <v>386</v>
-      </c>
-      <c r="E105" s="3">
-        <v>6</v>
-      </c>
-      <c r="F105" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="106" s="1" customFormat="1" spans="2:7">
-      <c r="B106" s="3">
-        <v>400091</v>
-      </c>
-      <c r="C106" t="s">
-        <v>385</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E106" s="3">
-        <v>66</v>
-      </c>
-      <c r="F106" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="107" s="2" customFormat="1" spans="2:7">
-      <c r="B107" s="4">
-        <v>40010</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="108" s="1" customFormat="1" spans="2:7">
-      <c r="B108" s="3">
-        <v>40011</v>
-      </c>
-      <c r="C108" t="s">
-        <v>393</v>
-      </c>
-      <c r="D108" t="s">
-        <v>394</v>
-      </c>
-      <c r="E108" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="F108" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="109" s="2" customFormat="1" spans="2:7">
-      <c r="B109" s="4">
-        <v>40012</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="E109" s="4">
+      <c r="E109" s="7">
         <v>-2</v>
       </c>
-      <c r="F109" s="5" t="s">
-        <v>397</v>
+      <c r="F109" s="8" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="110" s="2" customFormat="1" spans="2:7">
-      <c r="B110" s="4">
+      <c r="B110" s="7">
         <v>400121</v>
       </c>
-      <c r="C110" s="5" t="s">
-        <v>396</v>
+      <c r="C110" s="8" t="s">
+        <v>398</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E110" s="4">
+      <c r="E110" s="7">
         <v>15</v>
       </c>
-      <c r="F110" s="5" t="s">
-        <v>398</v>
+      <c r="F110" s="8" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="111" s="1" customFormat="1" spans="2:7">
-      <c r="B111" s="3">
+      <c r="B111" s="5">
         <v>40013</v>
       </c>
-      <c r="C111" t="s">
-        <v>399</v>
-      </c>
-      <c r="D111" t="s">
-        <v>400</v>
-      </c>
-      <c r="E111" s="3">
+      <c r="C111" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="E111" s="5">
         <v>0.1</v>
       </c>
-      <c r="F111" t="s">
-        <v>401</v>
+      <c r="F111" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" spans="2:7">
-      <c r="B112" s="3">
+      <c r="B112" s="5">
         <v>40014</v>
       </c>
-      <c r="C112" t="s">
-        <v>402</v>
-      </c>
-      <c r="D112" t="s">
-        <v>403</v>
-      </c>
-      <c r="E112" s="3">
+      <c r="C112" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="E112" s="5">
         <v>1</v>
       </c>
-      <c r="F112" t="s">
+      <c r="F112" s="6" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="113" s="1" customFormat="1" spans="2:7">
+      <c r="B113" s="5">
+        <v>400141</v>
+      </c>
+      <c r="C113" s="6" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="113" spans="2:7">
-      <c r="B113" s="3">
-        <v>400141</v>
-      </c>
-      <c r="C113" t="s">
-        <v>402</v>
-      </c>
-      <c r="D113" t="s">
-        <v>405</v>
-      </c>
-      <c r="E113" s="3">
+      <c r="D113" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="E113" s="5">
         <v>77</v>
       </c>
-      <c r="F113" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="114" spans="2:7">
-      <c r="B114" s="3">
+      <c r="F113" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="G113" s="6"/>
+    </row>
+    <row r="114" s="1" customFormat="1" spans="2:7">
+      <c r="B114" s="5">
         <v>400142</v>
       </c>
-      <c r="C114" t="s">
-        <v>402</v>
-      </c>
-      <c r="D114" t="s">
-        <v>407</v>
-      </c>
-      <c r="E114" s="3">
+      <c r="C114" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="E114" s="5">
         <v>7</v>
       </c>
-      <c r="F114" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="115" spans="2:7">
-      <c r="B115" s="3">
+      <c r="F114" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="G114" s="6"/>
+    </row>
+    <row r="115" s="1" customFormat="1" spans="2:7">
+      <c r="B115" s="5">
         <v>40015</v>
       </c>
-      <c r="C115" t="s">
-        <v>409</v>
-      </c>
-      <c r="D115" t="s">
-        <v>410</v>
-      </c>
-      <c r="E115" s="3">
+      <c r="C115" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="E115" s="5">
         <v>0.5</v>
       </c>
-      <c r="F115" t="s">
+      <c r="F115" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="G115" s="6"/>
+    </row>
+    <row r="116" s="1" customFormat="1" spans="2:7">
+      <c r="B116" s="5">
+        <v>400151</v>
+      </c>
+      <c r="C116" s="6" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="116" spans="2:7">
-      <c r="B116" s="3">
-        <v>400151</v>
-      </c>
-      <c r="C116" t="s">
-        <v>409</v>
-      </c>
-      <c r="D116" t="s">
-        <v>412</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="F116" t="s">
+      <c r="D116" s="6" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="117" spans="2:7">
-      <c r="B117" s="3">
+      <c r="E116" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="G116" s="6"/>
+    </row>
+    <row r="117" s="1" customFormat="1" spans="2:7">
+      <c r="B117" s="5">
         <v>40016</v>
       </c>
-      <c r="C117" t="s">
-        <v>415</v>
-      </c>
-      <c r="D117" t="s">
-        <v>416</v>
-      </c>
-      <c r="E117" s="3">
-        <v>2</v>
-      </c>
-      <c r="F117" t="s">
+      <c r="C117" s="6" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="118" spans="2:7">
-      <c r="B118" s="3">
+      <c r="D117" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="G117" s="6"/>
+    </row>
+    <row r="118" s="1" customFormat="1" spans="2:7">
+      <c r="B118" s="5">
         <v>40017</v>
       </c>
-      <c r="C118" t="s">
-        <v>418</v>
-      </c>
-      <c r="D118" t="s">
-        <v>419</v>
+      <c r="C118" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>422</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="F118" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="119" spans="2:7">
-      <c r="B119" s="3">
+        <v>423</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="G118" s="6"/>
+    </row>
+    <row r="119" s="1" customFormat="1" spans="2:7">
+      <c r="B119" s="5">
         <v>40018</v>
       </c>
-      <c r="C119" t="s">
-        <v>422</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>423</v>
+      <c r="C119" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>426</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="F119" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="120" spans="2:7">
-      <c r="B120" s="3">
+        <v>427</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="G119" s="6"/>
+    </row>
+    <row r="120" s="1" customFormat="1" spans="2:7">
+      <c r="B120" s="5">
         <v>40019</v>
       </c>
-      <c r="C120" t="s">
-        <v>426</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>427</v>
+      <c r="C120" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F120" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="121" spans="2:7">
-      <c r="B121" s="3">
+      <c r="F120" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="G120" s="6"/>
+    </row>
+    <row r="121" s="1" customFormat="1" spans="2:7">
+      <c r="B121" s="5">
         <v>40020</v>
       </c>
-      <c r="C121" t="s">
-        <v>429</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>430</v>
+      <c r="C121" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>433</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F121" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="122" spans="2:7">
-      <c r="B122" s="3">
+      <c r="F121" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="G121" s="6"/>
+    </row>
+    <row r="122" s="1" customFormat="1" spans="2:7">
+      <c r="B122" s="5">
         <v>40021</v>
       </c>
-      <c r="C122" t="s">
-        <v>432</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>433</v>
+      <c r="C122" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>436</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="F122" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="123" spans="2:7">
-      <c r="B123" s="3">
+        <v>437</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="G122" s="6"/>
+    </row>
+    <row r="123" s="1" customFormat="1" spans="2:7">
+      <c r="B123" s="5">
         <v>40022</v>
       </c>
-      <c r="C123" t="s">
-        <v>436</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>437</v>
+      <c r="C123" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>440</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="F123" t="s">
+        <v>441</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="G123" s="6"/>
+    </row>
+    <row r="124" s="1" customFormat="1" spans="2:7">
+      <c r="B124" s="5">
+        <v>400221</v>
+      </c>
+      <c r="C124" s="6" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="124" spans="2:7">
-      <c r="B124" s="3">
-        <v>400221</v>
-      </c>
-      <c r="C124" t="s">
-        <v>436</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>440</v>
+      <c r="D124" s="5" t="s">
+        <v>443</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="F124" t="s">
-        <v>441</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="G124" s="6"/>
     </row>
     <row r="125" s="2" customFormat="1" spans="2:7">
-      <c r="B125" s="4">
+      <c r="B125" s="7">
         <v>40023</v>
       </c>
-      <c r="C125" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>443</v>
+      <c r="C125" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>446</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F125" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="G125" s="5"/>
-    </row>
-    <row r="126" spans="2:7">
-      <c r="B126" s="3">
+      <c r="F125" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="G125" s="8"/>
+    </row>
+    <row r="126" s="1" customFormat="1" spans="2:7">
+      <c r="B126" s="5">
         <v>40024</v>
       </c>
-      <c r="C126" t="s">
-        <v>445</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>446</v>
+      <c r="C126" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>449</v>
       </c>
       <c r="E126" s="1">
         <v>0.2</v>
       </c>
-      <c r="F126" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="127" spans="2:7">
-      <c r="B127" s="3">
+      <c r="F126" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="G126" s="6"/>
+    </row>
+    <row r="127" s="1" customFormat="1" spans="2:7">
+      <c r="B127" s="5">
         <v>40025</v>
       </c>
-      <c r="C127" t="s">
-        <v>448</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>449</v>
+      <c r="C127" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>452</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="F127" t="s">
-        <v>451</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="G127" s="6"/>
     </row>
     <row r="128" s="2" customFormat="1" spans="2:7">
-      <c r="B128" s="4">
+      <c r="B128" s="7">
         <v>40026</v>
       </c>
-      <c r="C128" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="D128" s="5" t="s">
+      <c r="C128" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="D128" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E128" s="4">
+      <c r="E128" s="7">
         <v>2</v>
       </c>
-      <c r="F128" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="G128" s="5"/>
-    </row>
-    <row r="129" spans="2:7">
-      <c r="B129" s="3">
+      <c r="F128" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="G128" s="8"/>
+    </row>
+    <row r="129" s="1" customFormat="1" spans="2:7">
+      <c r="B129" s="5">
         <v>40027</v>
       </c>
-      <c r="C129" t="s">
-        <v>454</v>
-      </c>
-      <c r="D129" t="s">
-        <v>455</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="F129" t="s">
+      <c r="C129" s="6" t="s">
         <v>457</v>
       </c>
+      <c r="D129" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="G129" s="6"/>
     </row>
     <row r="130" s="2" customFormat="1" spans="2:7">
-      <c r="B130" s="4">
+      <c r="B130" s="7">
         <v>40028</v>
       </c>
-      <c r="C130" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="E130" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="F130" s="5" t="s">
+      <c r="C130" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="G130" s="5"/>
+      <c r="D130" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="G130" s="8"/>
     </row>
     <row r="131" s="2" customFormat="1" spans="2:7">
-      <c r="B131" s="4">
+      <c r="B131" s="7">
         <v>40029</v>
       </c>
-      <c r="C131" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="E131" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="G131" s="5"/>
+      <c r="C131" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="G131" s="8"/>
     </row>
     <row r="132" s="2" customFormat="1" spans="2:7">
-      <c r="B132" s="4">
+      <c r="B132" s="7">
         <v>40030</v>
       </c>
-      <c r="C132" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="E132" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="F132" s="5" t="s">
+      <c r="C132" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="G132" s="5"/>
+      <c r="D132" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="G132" s="8"/>
     </row>
     <row r="133" s="2" customFormat="1" spans="2:7">
-      <c r="B133" s="4">
+      <c r="B133" s="7">
         <v>40031</v>
       </c>
-      <c r="C133" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="D133" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="E133" s="4">
+      <c r="C133" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="E133" s="7">
         <v>12</v>
       </c>
-      <c r="F133" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="G133" s="5"/>
+      <c r="F133" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="G133" s="8"/>
+    </row>
+    <row r="134" s="1" customFormat="1" spans="2:7">
+      <c r="C134" s="5"/>
+      <c r="D134" s="5"/>
+      <c r="E134" s="1"/>
+      <c r="F134" s="1"/>
+      <c r="G134" s="6"/>
+    </row>
+    <row r="135" s="1" customFormat="1" spans="2:7">
+      <c r="C135" s="5"/>
+      <c r="D135" s="5"/>
+      <c r="E135" s="1"/>
+      <c r="F135" s="1"/>
+      <c r="G135" s="6"/>
+    </row>
+    <row r="136" s="1" customFormat="1" spans="2:7">
+      <c r="C136" s="5"/>
+      <c r="D136" s="5"/>
+      <c r="E136" s="1"/>
+      <c r="F136" s="1"/>
+      <c r="G136" s="6"/>
+    </row>
+    <row r="137" s="1" customFormat="1" spans="2:7">
+      <c r="C137" s="5"/>
+      <c r="D137" s="5"/>
+      <c r="E137" s="1"/>
+      <c r="F137" s="1"/>
+      <c r="G137" s="6"/>
+    </row>
+    <row r="138" s="1" customFormat="1" spans="2:7">
+      <c r="C138" s="5"/>
+      <c r="D138" s="5"/>
+      <c r="E138" s="1"/>
+      <c r="F138" s="1"/>
+      <c r="G138" s="6"/>
+    </row>
+    <row r="139" s="1" customFormat="1" spans="2:7">
+      <c r="C139" s="5"/>
+      <c r="D139" s="5"/>
+      <c r="E139" s="1"/>
+      <c r="F139" s="1"/>
+      <c r="G139" s="6"/>
+    </row>
+    <row r="140" s="1" customFormat="1" spans="2:7">
+      <c r="C140" s="5"/>
+      <c r="D140" s="5"/>
+      <c r="E140" s="1"/>
+      <c r="F140" s="1"/>
+      <c r="G140" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17640" windowHeight="12240"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -181,7 +181,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>亮出的豹子牌型在结算时提供+7攻击力</t>
+    <t>亮出的炸弹牌型在结算时提供+7攻击力</t>
   </si>
   <si>
     <t>木制圆盾</t>
@@ -403,7 +403,7 @@
     <t>Leopard</t>
   </si>
   <si>
-    <t>亮出的豹子牌型在结算时提供+7倍率</t>
+    <t>亮出的炸弹牌型在结算时提供+7倍率</t>
   </si>
   <si>
     <t>20010</t>
@@ -1045,13 +1045,13 @@
     <t>30026</t>
   </si>
   <si>
-    <t>豹子精髓</t>
+    <t>炸弹精髓</t>
   </si>
   <si>
     <t>FirstLeopardGold</t>
   </si>
   <si>
-    <t>使用后,本局内你亮出豹子时,就会获得300金币</t>
+    <t>使用后,本局内你亮出炸弹时,就会获得300金币</t>
   </si>
   <si>
     <t>30027</t>
@@ -1132,7 +1132,7 @@
     <t>SpecialTwoThreeFive</t>
   </si>
   <si>
-    <t>高牌235等同于豹子牌型,并且可以战胜所有牌型</t>
+    <t>高牌235等同于炸弹牌型,并且可以战胜所有牌型</t>
   </si>
   <si>
     <t>奢华沙发</t>
@@ -2078,27 +2078,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2460,166 +2451,166 @@
   <dimension ref="A1:G140"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="5.75833333333333" style="3" customWidth="1"/>
-    <col min="2" max="2" width="7.49166666666667" style="3" customWidth="1"/>
-    <col min="3" max="3" width="8.475" style="4" customWidth="1"/>
-    <col min="4" max="4" width="21.8416666666667" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.36666666666667" style="3" customWidth="1"/>
-    <col min="6" max="6" width="20.325" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="3" customWidth="1"/>
+    <col min="1" max="1" width="5.75833333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.49166666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.475" style="3" customWidth="1"/>
+    <col min="4" max="4" width="21.8416666666667" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.36666666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.325" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:7">
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>10001</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>1</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="6"/>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:7">
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>10002</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>1</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:7">
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>10003</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:7">
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>10004</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>1</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:7">
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>10005</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>1</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:7">
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>10006</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2628,361 +2619,361 @@
       <c r="E10" s="1">
         <v>3</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:7">
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>10007</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:7">
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>10008</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:7">
-      <c r="B13" s="5">
+      <c r="B13" s="4">
         <v>10009</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>43</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:7">
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>10010</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:7">
-      <c r="B15" s="7">
+    <row r="15" s="1" customFormat="1" spans="1:7">
+      <c r="B15" s="4">
         <v>10011</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="4">
         <v>-0.05</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="8"/>
+      <c r="G15" s="5"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:7">
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>10012</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>2</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="6"/>
+      <c r="G16" s="5"/>
     </row>
     <row r="17" s="1" customFormat="1" spans="2:7">
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>10013</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <v>2</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="6"/>
+      <c r="G17" s="5"/>
     </row>
     <row r="18" s="1" customFormat="1" spans="2:7">
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>10014</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G18" s="6"/>
+      <c r="G18" s="5"/>
     </row>
     <row r="19" s="1" customFormat="1" spans="2:7">
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>10015</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="2:7">
-      <c r="B20" s="7">
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="2:7">
+      <c r="B20" s="4">
         <v>10016</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G20" s="8"/>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="2:7">
-      <c r="B21" s="7">
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="2:7">
+      <c r="B21" s="4">
         <v>10017</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="4">
         <v>0.01</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="G21" s="8"/>
+      <c r="G21" s="5"/>
     </row>
     <row r="22" s="1" customFormat="1" spans="2:7">
-      <c r="B22" s="5">
+      <c r="B22" s="4">
         <v>10018</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="4">
         <v>0.25</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G22" s="6"/>
+      <c r="G22" s="5"/>
     </row>
     <row r="23" s="1" customFormat="1" spans="2:7">
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <v>10019</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="4">
         <v>0.2</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="2:7">
-      <c r="B24" s="7">
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="2:7">
+      <c r="B24" s="4">
         <v>10020</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="G24" s="8"/>
+      <c r="G24" s="5"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="2:7">
-      <c r="B25" s="5">
+      <c r="B25" s="4">
         <v>10021</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="G25" s="6"/>
+      <c r="G25" s="5"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="2:7">
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="5"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="4"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="6"/>
+      <c r="G26" s="5"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="2:7">
       <c r="B27" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="4">
         <v>1</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G27" s="6"/>
+      <c r="G27" s="5"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="2:7">
       <c r="B28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="5" t="s">
         <v>94</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="G28" s="6"/>
+      <c r="G28" s="5"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="2:7">
       <c r="B29" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="4">
         <v>1</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G29" s="6"/>
+      <c r="G29" s="5"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="2:7">
       <c r="B30" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="5" t="s">
         <v>102</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="G30" s="6"/>
+      <c r="G30" s="5"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="2:7">
       <c r="B31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>105</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -2991,1864 +2982,1864 @@
       <c r="E31" s="1">
         <v>3</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G31" s="6"/>
+      <c r="G31" s="5"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="2:7">
       <c r="B32" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="5" t="s">
         <v>110</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="G32" s="6"/>
+      <c r="G32" s="5"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="2:7">
       <c r="B33" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="5" t="s">
         <v>114</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="G33" s="6"/>
+      <c r="G33" s="5"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="2:7">
       <c r="B34" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="5" t="s">
         <v>118</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="G34" s="6"/>
+      <c r="G34" s="5"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="2:7">
       <c r="B35" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="4" t="s">
         <v>122</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F35" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="G35" s="6"/>
+      <c r="G35" s="5"/>
     </row>
     <row r="36" s="1" customFormat="1" spans="2:7">
       <c r="B36" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="4">
         <v>2</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F36" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="G36" s="6"/>
+      <c r="G36" s="5"/>
     </row>
     <row r="37" s="1" customFormat="1" spans="2:7">
       <c r="B37" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="4">
         <v>30</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="G37" s="6"/>
+      <c r="G37" s="5"/>
     </row>
     <row r="38" s="1" customFormat="1" spans="2:7">
       <c r="B38" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="4">
         <v>150</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="G38" s="6"/>
-    </row>
-    <row r="39" s="2" customFormat="1" spans="2:7">
-      <c r="B39" s="2" t="s">
+      <c r="G38" s="5"/>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="2:7">
+      <c r="B39" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="4">
         <v>1</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="G39" s="8"/>
+      <c r="G39" s="5"/>
     </row>
     <row r="40" s="1" customFormat="1" spans="2:7">
       <c r="B40" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="G40" s="6"/>
+      <c r="G40" s="5"/>
     </row>
     <row r="41" s="1" customFormat="1" spans="2:7">
       <c r="B41" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="4">
         <v>2</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G41" s="6"/>
+      <c r="G41" s="5"/>
     </row>
     <row r="42" s="1" customFormat="1" spans="2:7">
       <c r="B42" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="4">
         <v>2</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="G42" s="6"/>
+      <c r="G42" s="5"/>
     </row>
     <row r="43" s="1" customFormat="1" spans="2:7">
       <c r="B43" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F43" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="G43" s="6"/>
+      <c r="G43" s="5"/>
     </row>
     <row r="44" s="1" customFormat="1" spans="2:7">
       <c r="B44" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="4">
         <v>10</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="G44" s="6"/>
+      <c r="G44" s="5"/>
     </row>
     <row r="45" s="1" customFormat="1" spans="2:7">
       <c r="B45" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="4">
         <v>0.2</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="F45" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="G45" s="6"/>
-    </row>
-    <row r="46" s="2" customFormat="1" spans="2:7">
-      <c r="B46" s="2" t="s">
+      <c r="G45" s="5"/>
+    </row>
+    <row r="46" s="1" customFormat="1" spans="2:7">
+      <c r="B46" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="E46" s="7">
+      <c r="E46" s="4">
         <v>1</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F46" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G46" s="8"/>
-    </row>
-    <row r="47" s="2" customFormat="1" spans="2:7">
-      <c r="B47" s="2" t="s">
+      <c r="G46" s="5"/>
+    </row>
+    <row r="47" s="1" customFormat="1" spans="2:7">
+      <c r="B47" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E47" s="7">
+      <c r="E47" s="4">
         <v>3</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="G47" s="8"/>
+      <c r="G47" s="5"/>
     </row>
     <row r="48" s="1" customFormat="1" spans="2:7">
       <c r="B48" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D48" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="4">
         <v>3</v>
       </c>
-      <c r="F48" s="6" t="s">
+      <c r="F48" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="G48" s="6"/>
+      <c r="G48" s="5"/>
     </row>
     <row r="49" s="1" customFormat="1" spans="2:7">
       <c r="B49" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="4">
         <v>1</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F49" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="G49" s="6"/>
+      <c r="G49" s="5"/>
     </row>
     <row r="50" s="1" customFormat="1" spans="2:7">
       <c r="B50" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E50" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F50" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="G50" s="6"/>
+      <c r="G50" s="5"/>
     </row>
     <row r="51" s="1" customFormat="1" spans="2:7">
       <c r="B51" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="E51" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="F51" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="G51" s="6"/>
+      <c r="G51" s="5"/>
     </row>
     <row r="52" s="1" customFormat="1" spans="2:7">
       <c r="B52" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="E52" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="F52" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="G52" s="6"/>
-    </row>
-    <row r="53" s="2" customFormat="1" spans="2:7">
-      <c r="B53" s="2" t="s">
+      <c r="G52" s="5"/>
+    </row>
+    <row r="53" s="1" customFormat="1" spans="2:7">
+      <c r="B53" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E53" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="F53" s="8" t="s">
+      <c r="F53" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="G53" s="8"/>
+      <c r="G53" s="5"/>
     </row>
     <row r="54" s="1" customFormat="1" spans="2:7">
       <c r="B54" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E54" s="4">
         <v>0.5</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F54" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="G54" s="6"/>
+      <c r="G54" s="5"/>
     </row>
     <row r="55" s="1" customFormat="1" spans="2:7">
       <c r="B55" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E55" s="4">
         <v>0.4</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F55" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G55" s="6"/>
+      <c r="G55" s="5"/>
     </row>
     <row r="56" s="1" customFormat="1" spans="2:7">
       <c r="B56" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="4">
         <v>3</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F56" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G56" s="6"/>
+      <c r="G56" s="5"/>
     </row>
     <row r="57" s="1" customFormat="1" spans="2:7">
       <c r="B57" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D57" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="4">
         <v>0.5</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F57" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G57" s="6"/>
+      <c r="G57" s="5"/>
     </row>
     <row r="58" s="1" customFormat="1" spans="2:7">
       <c r="B58" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D58" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F58" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="G58" s="6"/>
+      <c r="G58" s="5"/>
     </row>
     <row r="59" s="1" customFormat="1" spans="2:7">
       <c r="B59" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="E59" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="F59" s="6" t="s">
+      <c r="F59" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="G59" s="6"/>
-    </row>
-    <row r="60" s="2" customFormat="1" spans="2:7">
-      <c r="B60" s="2" t="s">
+      <c r="G59" s="5"/>
+    </row>
+    <row r="60" s="1" customFormat="1" spans="2:7">
+      <c r="B60" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="D60" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="E60" s="7">
+      <c r="E60" s="4">
         <v>1</v>
       </c>
-      <c r="F60" s="8" t="s">
+      <c r="F60" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="G60" s="8"/>
-    </row>
-    <row r="61" s="2" customFormat="1" spans="2:7">
-      <c r="B61" s="2" t="s">
+      <c r="G60" s="5"/>
+    </row>
+    <row r="61" s="1" customFormat="1" spans="2:7">
+      <c r="B61" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D61" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="E61" s="7">
+      <c r="E61" s="4">
         <v>2</v>
       </c>
-      <c r="F61" s="8" t="s">
+      <c r="F61" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G61" s="8"/>
-    </row>
-    <row r="62" s="2" customFormat="1" spans="2:7">
-      <c r="B62" s="2" t="s">
+      <c r="G61" s="5"/>
+    </row>
+    <row r="62" s="1" customFormat="1" spans="2:7">
+      <c r="B62" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="D62" s="7" t="s">
+      <c r="D62" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="E62" s="7">
+      <c r="E62" s="4">
         <v>3</v>
       </c>
-      <c r="F62" s="8" t="s">
+      <c r="F62" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="G62" s="8"/>
+      <c r="G62" s="5"/>
     </row>
     <row r="63" s="1" customFormat="1" spans="2:7">
-      <c r="C63" s="6"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
     </row>
     <row r="64" s="1" customFormat="1" spans="2:7">
       <c r="B64" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E64" s="4">
         <v>0.05</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="F64" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="G64" s="6"/>
+      <c r="G64" s="5"/>
     </row>
     <row r="65" s="1" customFormat="1" spans="2:7">
       <c r="B65" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D65" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="E65" s="5">
+      <c r="E65" s="4">
         <v>2</v>
       </c>
-      <c r="F65" s="6" t="s">
+      <c r="F65" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="G65" s="6"/>
+      <c r="G65" s="5"/>
     </row>
     <row r="66" s="1" customFormat="1" spans="2:7">
       <c r="B66" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="D66" s="6" t="s">
+      <c r="D66" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="E66" s="5">
+      <c r="E66" s="4">
         <v>2</v>
       </c>
-      <c r="F66" s="6" t="s">
+      <c r="F66" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="G66" s="6"/>
-    </row>
-    <row r="67" s="2" customFormat="1" spans="2:7">
-      <c r="B67" s="2" t="s">
+      <c r="G66" s="5"/>
+    </row>
+    <row r="67" s="1" customFormat="1" spans="2:7">
+      <c r="B67" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D67" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="E67" s="7">
+      <c r="E67" s="4">
         <v>1</v>
       </c>
-      <c r="F67" s="8" t="s">
+      <c r="F67" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="G67" s="8"/>
+      <c r="G67" s="5"/>
     </row>
     <row r="68" s="1" customFormat="1" spans="2:7">
       <c r="B68" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D68" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="E68" s="5">
+      <c r="E68" s="4">
         <v>1</v>
       </c>
-      <c r="F68" s="6" t="s">
+      <c r="F68" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="G68" s="6"/>
+      <c r="G68" s="5"/>
     </row>
     <row r="69" s="1" customFormat="1" spans="2:7">
       <c r="B69" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="E69" s="5">
+      <c r="E69" s="4">
         <v>1</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="F69" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="G69" s="6"/>
+      <c r="G69" s="5"/>
     </row>
     <row r="70" s="1" customFormat="1" spans="2:7">
       <c r="B70" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D70" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="E70" s="5">
+      <c r="E70" s="4">
         <v>100</v>
       </c>
-      <c r="F70" s="6" t="s">
+      <c r="F70" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="G70" s="6"/>
+      <c r="G70" s="5"/>
     </row>
     <row r="71" s="1" customFormat="1" spans="2:7">
       <c r="B71" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="D71" s="6" t="s">
+      <c r="D71" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="E71" s="5">
+      <c r="E71" s="4">
         <v>2</v>
       </c>
-      <c r="F71" s="6" t="s">
+      <c r="F71" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="G71" s="6"/>
+      <c r="G71" s="5"/>
     </row>
     <row r="72" s="1" customFormat="1" spans="2:7">
       <c r="B72" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="D72" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="E72" s="5">
+      <c r="E72" s="4">
         <v>2</v>
       </c>
-      <c r="F72" s="6" t="s">
+      <c r="F72" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="G72" s="6"/>
+      <c r="G72" s="5"/>
     </row>
     <row r="73" s="1" customFormat="1" spans="2:7">
       <c r="B73" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C73" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D73" s="5" t="s">
+      <c r="D73" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="E73" s="5">
+      <c r="E73" s="4">
         <v>4</v>
       </c>
-      <c r="F73" s="6" t="s">
+      <c r="F73" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="G73" s="6"/>
-    </row>
-    <row r="74" s="2" customFormat="1" spans="2:7">
-      <c r="B74" s="2" t="s">
+      <c r="G73" s="5"/>
+    </row>
+    <row r="74" s="1" customFormat="1" spans="2:7">
+      <c r="B74" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="D74" s="8" t="s">
+      <c r="D74" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="E74" s="7">
+      <c r="E74" s="4">
         <v>10</v>
       </c>
-      <c r="F74" s="8" t="s">
+      <c r="F74" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="G74" s="8"/>
-    </row>
-    <row r="75" s="2" customFormat="1" spans="2:7">
-      <c r="B75" s="2" t="s">
+      <c r="G74" s="5"/>
+    </row>
+    <row r="75" s="1" customFormat="1" spans="2:7">
+      <c r="B75" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="D75" s="8" t="s">
+      <c r="D75" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="E75" s="7" t="s">
+      <c r="E75" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="F75" s="8" t="s">
+      <c r="F75" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="G75" s="8"/>
+      <c r="G75" s="5"/>
     </row>
     <row r="76" s="1" customFormat="1" spans="2:7">
       <c r="B76" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="D76" s="6" t="s">
+      <c r="D76" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="E76" s="5">
+      <c r="E76" s="4">
         <v>30</v>
       </c>
-      <c r="F76" s="6" t="s">
+      <c r="F76" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="G76" s="6"/>
+      <c r="G76" s="5"/>
     </row>
     <row r="77" s="1" customFormat="1" spans="2:7">
       <c r="B77" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="D77" s="6" t="s">
+      <c r="D77" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="E77" s="5" t="s">
+      <c r="E77" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="F77" s="6" t="s">
+      <c r="F77" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="G77" s="6"/>
+      <c r="G77" s="5"/>
     </row>
     <row r="78" s="1" customFormat="1" spans="2:7">
       <c r="B78" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="C78" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="D78" s="6" t="s">
+      <c r="D78" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="E78" s="5">
+      <c r="E78" s="4">
         <v>1</v>
       </c>
-      <c r="F78" s="6" t="s">
+      <c r="F78" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="G78" s="6"/>
+      <c r="G78" s="5"/>
     </row>
     <row r="79" s="1" customFormat="1" spans="2:7">
       <c r="B79" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="C79" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="D79" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="E79" s="5" t="s">
+      <c r="E79" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="F79" s="6" t="s">
+      <c r="F79" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="G79" s="6"/>
+      <c r="G79" s="5"/>
     </row>
     <row r="80" s="1" customFormat="1" spans="2:7">
       <c r="B80" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="C80" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="D80" s="6" t="s">
+      <c r="D80" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="E80" s="5" t="s">
+      <c r="E80" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="F80" s="6" t="s">
+      <c r="F80" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="G80" s="6"/>
+      <c r="G80" s="5"/>
     </row>
     <row r="81" s="1" customFormat="1" spans="2:7">
       <c r="B81" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="C81" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="D81" s="6" t="s">
+      <c r="D81" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="E81" s="5">
+      <c r="E81" s="4">
         <v>0.5</v>
       </c>
-      <c r="F81" s="6" t="s">
+      <c r="F81" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="G81" s="6"/>
-    </row>
-    <row r="82" s="2" customFormat="1" spans="2:7">
-      <c r="B82" s="2" t="s">
+      <c r="G81" s="5"/>
+    </row>
+    <row r="82" s="1" customFormat="1" spans="2:7">
+      <c r="B82" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C82" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="D82" s="8" t="s">
+      <c r="D82" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="E82" s="7" t="s">
+      <c r="E82" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="F82" s="8" t="s">
+      <c r="F82" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="G82" s="8"/>
+      <c r="G82" s="5"/>
     </row>
     <row r="83" s="1" customFormat="1" spans="2:7">
       <c r="B83" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C83" s="5" t="s">
+      <c r="C83" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="D83" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="E83" s="5">
+      <c r="E83" s="4">
         <v>0.5</v>
       </c>
-      <c r="F83" s="6" t="s">
+      <c r="F83" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="G83" s="6"/>
+      <c r="G83" s="5"/>
     </row>
     <row r="84" s="1" customFormat="1" spans="2:7">
       <c r="B84" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C84" s="5" t="s">
+      <c r="C84" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="D84" s="6" t="s">
+      <c r="D84" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="E84" s="5" t="s">
+      <c r="E84" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="F84" s="6" t="s">
+      <c r="F84" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="G84" s="6"/>
+      <c r="G84" s="5"/>
     </row>
     <row r="85" s="1" customFormat="1" spans="2:7">
       <c r="B85" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C85" s="5" t="s">
+      <c r="C85" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="D85" s="6" t="s">
+      <c r="D85" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="E85" s="5">
+      <c r="E85" s="4">
         <v>-0.3</v>
       </c>
-      <c r="F85" s="6" t="s">
+      <c r="F85" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="G85" s="6"/>
+      <c r="G85" s="5"/>
     </row>
     <row r="86" s="1" customFormat="1" spans="2:7">
       <c r="B86" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="C86" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="D86" s="6" t="s">
+      <c r="D86" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="E86" s="5" t="s">
+      <c r="E86" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="F86" s="6" t="s">
+      <c r="F86" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="G86" s="6"/>
-    </row>
-    <row r="87" s="2" customFormat="1" spans="2:7">
-      <c r="B87" s="2" t="s">
+      <c r="G86" s="5"/>
+    </row>
+    <row r="87" s="1" customFormat="1" spans="2:7">
+      <c r="B87" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C87" s="7" t="s">
+      <c r="C87" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="D87" s="8" t="s">
+      <c r="D87" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="E87" s="7">
+      <c r="E87" s="4">
         <v>1</v>
       </c>
-      <c r="F87" s="8" t="s">
+      <c r="F87" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="G87" s="8"/>
+      <c r="G87" s="5"/>
     </row>
     <row r="88" s="1" customFormat="1" spans="2:7">
       <c r="B88" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="C88" s="5" t="s">
+      <c r="C88" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="D88" s="6" t="s">
+      <c r="D88" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="E88" s="5">
+      <c r="E88" s="4">
         <v>-0.3</v>
       </c>
-      <c r="F88" s="6" t="s">
+      <c r="F88" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="G88" s="6"/>
-    </row>
-    <row r="89" s="2" customFormat="1" spans="2:7">
-      <c r="B89" s="2" t="s">
+      <c r="G88" s="5"/>
+    </row>
+    <row r="89" s="1" customFormat="1" spans="2:7">
+      <c r="B89" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="C89" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="D89" s="8" t="s">
+      <c r="D89" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="E89" s="7">
+      <c r="E89" s="4">
         <v>300</v>
       </c>
-      <c r="F89" s="8" t="s">
+      <c r="F89" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="G89" s="8"/>
-    </row>
-    <row r="90" s="2" customFormat="1" spans="2:7">
-      <c r="B90" s="2" t="s">
+      <c r="G89" s="5"/>
+    </row>
+    <row r="90" s="1" customFormat="1" spans="2:7">
+      <c r="B90" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C90" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="D90" s="8" t="s">
+      <c r="D90" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="E90" s="7">
+      <c r="E90" s="4">
         <v>0.2</v>
       </c>
-      <c r="F90" s="8" t="s">
+      <c r="F90" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="G90" s="8"/>
-    </row>
-    <row r="91" s="2" customFormat="1" spans="2:7">
-      <c r="B91" s="2" t="s">
+      <c r="G90" s="5"/>
+    </row>
+    <row r="91" s="1" customFormat="1" spans="2:7">
+      <c r="B91" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="C91" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="D91" s="8" t="s">
+      <c r="D91" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="E91" s="7" t="s">
+      <c r="E91" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="F91" s="8" t="s">
+      <c r="F91" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="G91" s="8"/>
+      <c r="G91" s="5"/>
     </row>
     <row r="92" s="1" customFormat="1" spans="2:7">
       <c r="B92" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C92" s="6" t="s">
+      <c r="C92" s="5" t="s">
         <v>350</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="E92" s="5">
+      <c r="E92" s="4">
         <v>-1</v>
       </c>
-      <c r="F92" s="6" t="s">
+      <c r="F92" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="G92" s="6"/>
+      <c r="G92" s="5"/>
     </row>
     <row r="93" s="1" customFormat="1" spans="2:7">
       <c r="B93" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="C93" s="6" t="s">
+      <c r="C93" s="5" t="s">
         <v>354</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="E93" s="5">
+      <c r="E93" s="4">
         <v>1</v>
       </c>
-      <c r="F93" s="6" t="s">
+      <c r="F93" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="G93" s="6"/>
+      <c r="G93" s="5"/>
     </row>
     <row r="94" s="1" customFormat="1" spans="2:7">
       <c r="B94" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="C94" s="6" t="s">
+      <c r="C94" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="D94" s="6" t="s">
+      <c r="D94" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="E94" s="5">
+      <c r="E94" s="4">
         <v>1</v>
       </c>
-      <c r="F94" s="6" t="s">
+      <c r="F94" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="G94" s="6"/>
-    </row>
-    <row r="95" s="2" customFormat="1" spans="2:7">
-      <c r="B95" s="2" t="s">
+      <c r="G94" s="5"/>
+    </row>
+    <row r="95" s="1" customFormat="1" spans="2:7">
+      <c r="B95" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="C95" s="7" t="s">
+      <c r="C95" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="D95" s="7" t="s">
+      <c r="D95" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="E95" s="7" t="s">
+      <c r="E95" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="F95" s="8" t="s">
+      <c r="F95" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="G95" s="8"/>
+      <c r="G95" s="5"/>
     </row>
     <row r="96" s="1" customFormat="1" spans="2:7">
-      <c r="B96" s="5"/>
-      <c r="C96" s="5"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="6"/>
-      <c r="G96" s="6"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
     </row>
     <row r="97" s="1" customFormat="1" spans="2:7">
-      <c r="B97" s="5">
+      <c r="B97" s="4">
         <v>40001</v>
       </c>
-      <c r="C97" s="5">
+      <c r="C97" s="4">
         <v>235</v>
       </c>
-      <c r="D97" s="6" t="s">
+      <c r="D97" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="E97" s="5">
+      <c r="E97" s="4">
         <v>1</v>
       </c>
-      <c r="F97" s="6" t="s">
+      <c r="F97" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="G97" s="6"/>
+      <c r="G97" s="5"/>
     </row>
     <row r="98" s="1" customFormat="1" spans="2:7">
-      <c r="B98" s="5">
+      <c r="B98" s="4">
         <v>40002</v>
       </c>
-      <c r="C98" s="5" t="s">
+      <c r="C98" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="D98" s="5" t="s">
+      <c r="D98" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E98" s="5">
+      <c r="E98" s="4">
         <v>500</v>
       </c>
-      <c r="F98" s="6" t="s">
+      <c r="F98" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="G98" s="6"/>
+      <c r="G98" s="5"/>
     </row>
     <row r="99" s="1" customFormat="1" spans="2:7">
-      <c r="B99" s="5">
+      <c r="B99" s="4">
         <v>40003</v>
       </c>
-      <c r="C99" s="6" t="s">
+      <c r="C99" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="D99" s="6" t="s">
+      <c r="D99" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="E99" s="5">
+      <c r="E99" s="4">
         <v>1</v>
       </c>
-      <c r="F99" s="6" t="s">
+      <c r="F99" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="G99" s="6"/>
-    </row>
-    <row r="100" s="2" customFormat="1" spans="2:7">
-      <c r="B100" s="7">
+      <c r="G99" s="5"/>
+    </row>
+    <row r="100" s="1" customFormat="1" spans="2:7">
+      <c r="B100" s="4">
         <v>40004</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="C100" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="D100" s="8" t="s">
+      <c r="D100" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="E100" s="7">
+      <c r="E100" s="4">
         <v>1</v>
       </c>
-      <c r="F100" s="8" t="s">
+      <c r="F100" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="G100" s="8"/>
+      <c r="G100" s="5"/>
     </row>
     <row r="101" s="1" customFormat="1" spans="2:7">
-      <c r="B101" s="5">
+      <c r="B101" s="4">
         <v>40005</v>
       </c>
-      <c r="C101" s="6" t="s">
+      <c r="C101" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="D101" s="6" t="s">
+      <c r="D101" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="E101" s="5">
+      <c r="E101" s="4">
         <v>12</v>
       </c>
-      <c r="F101" s="6" t="s">
+      <c r="F101" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="G101" s="6"/>
+      <c r="G101" s="5"/>
     </row>
     <row r="102" s="1" customFormat="1" spans="2:7">
-      <c r="B102" s="5">
+      <c r="B102" s="4">
         <v>40006</v>
       </c>
-      <c r="C102" s="6" t="s">
+      <c r="C102" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="D102" s="6" t="s">
+      <c r="D102" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="E102" s="5">
+      <c r="E102" s="4">
         <v>3</v>
       </c>
-      <c r="F102" s="6" t="s">
+      <c r="F102" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="G102" s="6"/>
-    </row>
-    <row r="103" s="2" customFormat="1" spans="2:7">
-      <c r="B103" s="7">
+      <c r="G102" s="5"/>
+    </row>
+    <row r="103" s="1" customFormat="1" spans="2:7">
+      <c r="B103" s="4">
         <v>40007</v>
       </c>
-      <c r="C103" s="8" t="s">
+      <c r="C103" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="D103" s="8" t="s">
+      <c r="D103" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="E103" s="7">
+      <c r="E103" s="4">
         <v>3</v>
       </c>
-      <c r="F103" s="8" t="s">
+      <c r="F103" s="5" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" spans="2:7">
-      <c r="B104" s="5">
+      <c r="B104" s="4">
         <v>40008</v>
       </c>
-      <c r="C104" s="6" t="s">
+      <c r="C104" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="D104" s="6" t="s">
+      <c r="D104" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="E104" s="5">
+      <c r="E104" s="4">
         <v>1</v>
       </c>
-      <c r="F104" s="6" t="s">
+      <c r="F104" s="5" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" spans="2:7">
-      <c r="B105" s="5">
+      <c r="B105" s="4">
         <v>40009</v>
       </c>
-      <c r="C105" s="6" t="s">
+      <c r="C105" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="D105" s="6" t="s">
+      <c r="D105" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="E105" s="5">
+      <c r="E105" s="4">
         <v>6</v>
       </c>
-      <c r="F105" s="6" t="s">
+      <c r="F105" s="5" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" spans="2:7">
-      <c r="B106" s="5">
+      <c r="B106" s="4">
         <v>400091</v>
       </c>
-      <c r="C106" s="6" t="s">
+      <c r="C106" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="D106" s="5" t="s">
+      <c r="D106" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="E106" s="5">
+      <c r="E106" s="4">
         <v>66</v>
       </c>
-      <c r="F106" s="6" t="s">
+      <c r="F106" s="5" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="107" s="2" customFormat="1" spans="2:7">
-      <c r="B107" s="7">
+    <row r="107" s="1" customFormat="1" spans="2:7">
+      <c r="B107" s="4">
         <v>40010</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="C107" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="D107" s="8" t="s">
+      <c r="D107" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="E107" s="7" t="s">
+      <c r="E107" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="F107" s="8" t="s">
+      <c r="F107" s="5" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" spans="2:7">
-      <c r="B108" s="5">
+      <c r="B108" s="4">
         <v>40011</v>
       </c>
-      <c r="C108" s="6" t="s">
+      <c r="C108" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="D108" s="6" t="s">
+      <c r="D108" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="E108" s="5">
+      <c r="E108" s="4">
         <v>0.5</v>
       </c>
-      <c r="F108" s="6" t="s">
+      <c r="F108" s="5" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="109" s="2" customFormat="1" spans="2:7">
-      <c r="B109" s="7">
+    <row r="109" s="1" customFormat="1" spans="2:7">
+      <c r="B109" s="4">
         <v>40012</v>
       </c>
-      <c r="C109" s="8" t="s">
+      <c r="C109" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="D109" s="8" t="s">
+      <c r="D109" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="E109" s="7">
+      <c r="E109" s="4">
         <v>-2</v>
       </c>
-      <c r="F109" s="8" t="s">
+      <c r="F109" s="5" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="110" s="2" customFormat="1" spans="2:7">
-      <c r="B110" s="7">
+    <row r="110" s="1" customFormat="1" spans="2:7">
+      <c r="B110" s="4">
         <v>400121</v>
       </c>
-      <c r="C110" s="8" t="s">
+      <c r="C110" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="D110" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E110" s="7">
+      <c r="E110" s="4">
         <v>15</v>
       </c>
-      <c r="F110" s="8" t="s">
+      <c r="F110" s="5" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="111" s="1" customFormat="1" spans="2:7">
-      <c r="B111" s="5">
+      <c r="B111" s="4">
         <v>40013</v>
       </c>
-      <c r="C111" s="6" t="s">
+      <c r="C111" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="D111" s="6" t="s">
+      <c r="D111" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="E111" s="5">
+      <c r="E111" s="4">
         <v>0.1</v>
       </c>
-      <c r="F111" s="6" t="s">
+      <c r="F111" s="5" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" spans="2:7">
-      <c r="B112" s="5">
+      <c r="B112" s="4">
         <v>40014</v>
       </c>
-      <c r="C112" s="6" t="s">
+      <c r="C112" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="D112" s="6" t="s">
+      <c r="D112" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="E112" s="5">
+      <c r="E112" s="4">
         <v>1</v>
       </c>
-      <c r="F112" s="6" t="s">
+      <c r="F112" s="5" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="113" s="1" customFormat="1" spans="2:7">
-      <c r="B113" s="5">
+      <c r="B113" s="4">
         <v>400141</v>
       </c>
-      <c r="C113" s="6" t="s">
+      <c r="C113" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="D113" s="6" t="s">
+      <c r="D113" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="E113" s="5">
+      <c r="E113" s="4">
         <v>77</v>
       </c>
-      <c r="F113" s="6" t="s">
+      <c r="F113" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="G113" s="6"/>
+      <c r="G113" s="5"/>
     </row>
     <row r="114" s="1" customFormat="1" spans="2:7">
-      <c r="B114" s="5">
+      <c r="B114" s="4">
         <v>400142</v>
       </c>
-      <c r="C114" s="6" t="s">
+      <c r="C114" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="D114" s="6" t="s">
+      <c r="D114" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="E114" s="5">
+      <c r="E114" s="4">
         <v>7</v>
       </c>
-      <c r="F114" s="6" t="s">
+      <c r="F114" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="G114" s="6"/>
+      <c r="G114" s="5"/>
     </row>
     <row r="115" s="1" customFormat="1" spans="2:7">
-      <c r="B115" s="5">
+      <c r="B115" s="4">
         <v>40015</v>
       </c>
-      <c r="C115" s="6" t="s">
+      <c r="C115" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="D115" s="6" t="s">
+      <c r="D115" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="E115" s="5">
+      <c r="E115" s="4">
         <v>0.5</v>
       </c>
-      <c r="F115" s="6" t="s">
+      <c r="F115" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="G115" s="6"/>
+      <c r="G115" s="5"/>
     </row>
     <row r="116" s="1" customFormat="1" spans="2:7">
-      <c r="B116" s="5">
+      <c r="B116" s="4">
         <v>400151</v>
       </c>
-      <c r="C116" s="6" t="s">
+      <c r="C116" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="D116" s="6" t="s">
+      <c r="D116" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="E116" s="5" t="s">
+      <c r="E116" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="F116" s="6" t="s">
+      <c r="F116" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="G116" s="6"/>
+      <c r="G116" s="5"/>
     </row>
     <row r="117" s="1" customFormat="1" spans="2:7">
-      <c r="B117" s="5">
+      <c r="B117" s="4">
         <v>40016</v>
       </c>
-      <c r="C117" s="6" t="s">
+      <c r="C117" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="D117" s="6" t="s">
+      <c r="D117" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="E117" s="5" t="s">
+      <c r="E117" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="F117" s="6" t="s">
+      <c r="F117" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="G117" s="6"/>
+      <c r="G117" s="5"/>
     </row>
     <row r="118" s="1" customFormat="1" spans="2:7">
-      <c r="B118" s="5">
+      <c r="B118" s="4">
         <v>40017</v>
       </c>
-      <c r="C118" s="6" t="s">
+      <c r="C118" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="D118" s="6" t="s">
+      <c r="D118" s="5" t="s">
         <v>422</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="F118" s="6" t="s">
+      <c r="F118" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="G118" s="6"/>
+      <c r="G118" s="5"/>
     </row>
     <row r="119" s="1" customFormat="1" spans="2:7">
-      <c r="B119" s="5">
+      <c r="B119" s="4">
         <v>40018</v>
       </c>
-      <c r="C119" s="6" t="s">
+      <c r="C119" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="D119" s="5" t="s">
+      <c r="D119" s="4" t="s">
         <v>426</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="F119" s="6" t="s">
+      <c r="F119" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="G119" s="6"/>
+      <c r="G119" s="5"/>
     </row>
     <row r="120" s="1" customFormat="1" spans="2:7">
-      <c r="B120" s="5">
+      <c r="B120" s="4">
         <v>40019</v>
       </c>
-      <c r="C120" s="6" t="s">
+      <c r="C120" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="D120" s="5" t="s">
+      <c r="D120" s="4" t="s">
         <v>430</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F120" s="6" t="s">
+      <c r="F120" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="G120" s="6"/>
+      <c r="G120" s="5"/>
     </row>
     <row r="121" s="1" customFormat="1" spans="2:7">
-      <c r="B121" s="5">
+      <c r="B121" s="4">
         <v>40020</v>
       </c>
-      <c r="C121" s="6" t="s">
+      <c r="C121" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="D121" s="5" t="s">
+      <c r="D121" s="4" t="s">
         <v>433</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F121" s="6" t="s">
+      <c r="F121" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="G121" s="6"/>
+      <c r="G121" s="5"/>
     </row>
     <row r="122" s="1" customFormat="1" spans="2:7">
-      <c r="B122" s="5">
+      <c r="B122" s="4">
         <v>40021</v>
       </c>
-      <c r="C122" s="6" t="s">
+      <c r="C122" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="D122" s="5" t="s">
+      <c r="D122" s="4" t="s">
         <v>436</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="F122" s="6" t="s">
+      <c r="F122" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="G122" s="6"/>
+      <c r="G122" s="5"/>
     </row>
     <row r="123" s="1" customFormat="1" spans="2:7">
-      <c r="B123" s="5">
+      <c r="B123" s="4">
         <v>40022</v>
       </c>
-      <c r="C123" s="6" t="s">
+      <c r="C123" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="D123" s="5" t="s">
+      <c r="D123" s="4" t="s">
         <v>440</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="F123" s="6" t="s">
+      <c r="F123" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="G123" s="6"/>
+      <c r="G123" s="5"/>
     </row>
     <row r="124" s="1" customFormat="1" spans="2:7">
-      <c r="B124" s="5">
+      <c r="B124" s="4">
         <v>400221</v>
       </c>
-      <c r="C124" s="6" t="s">
+      <c r="C124" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="D124" s="5" t="s">
+      <c r="D124" s="4" t="s">
         <v>443</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="F124" s="6" t="s">
+      <c r="F124" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="G124" s="6"/>
-    </row>
-    <row r="125" s="2" customFormat="1" spans="2:7">
-      <c r="B125" s="7">
+      <c r="G124" s="5"/>
+    </row>
+    <row r="125" s="1" customFormat="1" spans="2:7">
+      <c r="B125" s="4">
         <v>40023</v>
       </c>
-      <c r="C125" s="8" t="s">
+      <c r="C125" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="D125" s="7" t="s">
+      <c r="D125" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="E125" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F125" s="8" t="s">
+      <c r="F125" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="G125" s="8"/>
+      <c r="G125" s="5"/>
     </row>
     <row r="126" s="1" customFormat="1" spans="2:7">
-      <c r="B126" s="5">
+      <c r="B126" s="4">
         <v>40024</v>
       </c>
-      <c r="C126" s="6" t="s">
+      <c r="C126" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="D126" s="5" t="s">
+      <c r="D126" s="4" t="s">
         <v>449</v>
       </c>
       <c r="E126" s="1">
         <v>0.2</v>
       </c>
-      <c r="F126" s="6" t="s">
+      <c r="F126" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="G126" s="6"/>
+      <c r="G126" s="5"/>
     </row>
     <row r="127" s="1" customFormat="1" spans="2:7">
-      <c r="B127" s="5">
+      <c r="B127" s="4">
         <v>40025</v>
       </c>
-      <c r="C127" s="6" t="s">
+      <c r="C127" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="D127" s="5" t="s">
+      <c r="D127" s="4" t="s">
         <v>452</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="F127" s="6" t="s">
+      <c r="F127" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="G127" s="6"/>
-    </row>
-    <row r="128" s="2" customFormat="1" spans="2:7">
-      <c r="B128" s="7">
+      <c r="G127" s="5"/>
+    </row>
+    <row r="128" s="1" customFormat="1" spans="2:7">
+      <c r="B128" s="4">
         <v>40026</v>
       </c>
-      <c r="C128" s="8" t="s">
+      <c r="C128" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="D128" s="8" t="s">
+      <c r="D128" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E128" s="7">
+      <c r="E128" s="4">
         <v>2</v>
       </c>
-      <c r="F128" s="8" t="s">
+      <c r="F128" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="G128" s="8"/>
+      <c r="G128" s="5"/>
     </row>
     <row r="129" s="1" customFormat="1" spans="2:7">
-      <c r="B129" s="5">
+      <c r="B129" s="4">
         <v>40027</v>
       </c>
-      <c r="C129" s="6" t="s">
+      <c r="C129" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="D129" s="6" t="s">
+      <c r="D129" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="E129" s="5" t="s">
+      <c r="E129" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="F129" s="6" t="s">
+      <c r="F129" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="G129" s="6"/>
-    </row>
-    <row r="130" s="2" customFormat="1" spans="2:7">
-      <c r="B130" s="7">
+      <c r="G129" s="5"/>
+    </row>
+    <row r="130" s="1" customFormat="1" spans="2:7">
+      <c r="B130" s="4">
         <v>40028</v>
       </c>
-      <c r="C130" s="8" t="s">
+      <c r="C130" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="D130" s="8" t="s">
+      <c r="D130" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="E130" s="7" t="s">
+      <c r="E130" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="F130" s="8" t="s">
+      <c r="F130" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="G130" s="8"/>
-    </row>
-    <row r="131" s="2" customFormat="1" spans="2:7">
-      <c r="B131" s="7">
+      <c r="G130" s="5"/>
+    </row>
+    <row r="131" s="1" customFormat="1" spans="2:7">
+      <c r="B131" s="4">
         <v>40029</v>
       </c>
-      <c r="C131" s="8" t="s">
+      <c r="C131" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="D131" s="8" t="s">
+      <c r="D131" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="E131" s="7" t="s">
+      <c r="E131" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="F131" s="8" t="s">
+      <c r="F131" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="G131" s="8"/>
-    </row>
-    <row r="132" s="2" customFormat="1" spans="2:7">
-      <c r="B132" s="7">
+      <c r="G131" s="5"/>
+    </row>
+    <row r="132" s="1" customFormat="1" spans="2:7">
+      <c r="B132" s="4">
         <v>40030</v>
       </c>
-      <c r="C132" s="8" t="s">
+      <c r="C132" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D132" s="8" t="s">
+      <c r="D132" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="E132" s="7" t="s">
+      <c r="E132" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="F132" s="8" t="s">
+      <c r="F132" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="G132" s="8"/>
-    </row>
-    <row r="133" s="2" customFormat="1" spans="2:7">
-      <c r="B133" s="7">
+      <c r="G132" s="5"/>
+    </row>
+    <row r="133" s="1" customFormat="1" spans="2:7">
+      <c r="B133" s="4">
         <v>40031</v>
       </c>
-      <c r="C133" s="7" t="s">
+      <c r="C133" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="D133" s="8" t="s">
+      <c r="D133" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="E133" s="7">
+      <c r="E133" s="4">
         <v>12</v>
       </c>
-      <c r="F133" s="8" t="s">
+      <c r="F133" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="G133" s="8"/>
+      <c r="G133" s="5"/>
     </row>
     <row r="134" s="1" customFormat="1" spans="2:7">
-      <c r="C134" s="5"/>
-      <c r="D134" s="5"/>
+      <c r="C134" s="4"/>
+      <c r="D134" s="4"/>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
-      <c r="G134" s="6"/>
+      <c r="G134" s="5"/>
     </row>
     <row r="135" s="1" customFormat="1" spans="2:7">
-      <c r="C135" s="5"/>
-      <c r="D135" s="5"/>
+      <c r="C135" s="4"/>
+      <c r="D135" s="4"/>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
-      <c r="G135" s="6"/>
+      <c r="G135" s="5"/>
     </row>
     <row r="136" s="1" customFormat="1" spans="2:7">
-      <c r="C136" s="5"/>
-      <c r="D136" s="5"/>
+      <c r="C136" s="4"/>
+      <c r="D136" s="4"/>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
-      <c r="G136" s="6"/>
+      <c r="G136" s="5"/>
     </row>
     <row r="137" s="1" customFormat="1" spans="2:7">
-      <c r="C137" s="5"/>
-      <c r="D137" s="5"/>
+      <c r="C137" s="4"/>
+      <c r="D137" s="4"/>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
-      <c r="G137" s="6"/>
+      <c r="G137" s="5"/>
     </row>
     <row r="138" s="1" customFormat="1" spans="2:7">
-      <c r="C138" s="5"/>
-      <c r="D138" s="5"/>
+      <c r="C138" s="4"/>
+      <c r="D138" s="4"/>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
-      <c r="G138" s="6"/>
+      <c r="G138" s="5"/>
     </row>
     <row r="139" s="1" customFormat="1" spans="2:7">
-      <c r="C139" s="5"/>
-      <c r="D139" s="5"/>
+      <c r="C139" s="4"/>
+      <c r="D139" s="4"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
-      <c r="G139" s="6"/>
+      <c r="G139" s="5"/>
     </row>
     <row r="140" s="1" customFormat="1" spans="2:7">
-      <c r="C140" s="5"/>
-      <c r="D140" s="5"/>
+      <c r="C140" s="4"/>
+      <c r="D140" s="4"/>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
-      <c r="G140" s="6"/>
+      <c r="G140" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="530">
   <si>
     <t>##var</t>
   </si>
@@ -727,6 +727,30 @@
     <t>亮牌时的第三张牌提供其点数对应的攻击力加成</t>
   </si>
   <si>
+    <t>疯狂猴子</t>
+  </si>
+  <si>
+    <t>结算时提供+8倍率</t>
+  </si>
+  <si>
+    <t>SelfDestroyPerRound</t>
+  </si>
+  <si>
+    <t>回合结束后,有18%的概率摧毁此圣物</t>
+  </si>
+  <si>
+    <t>贪婪</t>
+  </si>
+  <si>
+    <t>SelfMultWinLose</t>
+  </si>
+  <si>
+    <t>1|1</t>
+  </si>
+  <si>
+    <t>每次比牌胜利后,此圣物倍率+1;每次失败后-1</t>
+  </si>
+  <si>
     <t>30001</t>
   </si>
   <si>
@@ -865,9 +889,6 @@
     <t>EveryCardAttackForever</t>
   </si>
   <si>
-    <t>1|1</t>
-  </si>
-  <si>
     <t>回合首次亮牌时,随机有1张牌提供的攻击力永久+1</t>
   </si>
   <si>
@@ -1129,6 +1150,81 @@
     <t>亮出的每张牌都提供其点数对应的攻击力加成</t>
   </si>
   <si>
+    <t>倍率叠加</t>
+  </si>
+  <si>
+    <t>UseConsumableGetMult</t>
+  </si>
+  <si>
+    <t>每使用过1次消耗类的圣物,此圣物就会在结算时永久提供+0.5倍率</t>
+  </si>
+  <si>
+    <t>力量叠加</t>
+  </si>
+  <si>
+    <t>UseConsumableGetAttack</t>
+  </si>
+  <si>
+    <t>每使用过1次消耗类的圣物,此圣物就会永久提供+1攻击力</t>
+  </si>
+  <si>
+    <t>召唤</t>
+  </si>
+  <si>
+    <t>SummonConsumable</t>
+  </si>
+  <si>
+    <t>如果你亮出的牌型为同花顺,则会随机生成一个消耗性圣物,前提是圣物栏有空位</t>
+  </si>
+  <si>
+    <t>国王领域</t>
+  </si>
+  <si>
+    <t>UnshownRankMult</t>
+  </si>
+  <si>
+    <t>13|9</t>
+  </si>
+  <si>
+    <t>比牌时留在手牌中的每一张K,都会提供+9倍率</t>
+  </si>
+  <si>
+    <t>皇后领域</t>
+  </si>
+  <si>
+    <t>12|9</t>
+  </si>
+  <si>
+    <t>比牌时留在手牌中的每一张Q,都会提供+9倍率</t>
+  </si>
+  <si>
+    <t>复制</t>
+  </si>
+  <si>
+    <t>CopyRandomRelic</t>
+  </si>
+  <si>
+    <t>每回合随机复制1个你栏位中其他圣物的能力</t>
+  </si>
+  <si>
+    <t>借花献佛</t>
+  </si>
+  <si>
+    <t>DamagePerLevelEntry</t>
+  </si>
+  <si>
+    <t>本关每存在1条关卡机制,你造成的伤害+40%</t>
+  </si>
+  <si>
+    <t>妙手</t>
+  </si>
+  <si>
+    <t>PeekSteal</t>
+  </si>
+  <si>
+    <t>使用透视时,随机抽走该敌人1张手牌,与你手中点数最小的1张交换</t>
+  </si>
+  <si>
     <t>SpecialTwoThreeFive</t>
   </si>
   <si>
@@ -1457,6 +1553,75 @@
   </si>
   <si>
     <t>在结算时,每剩余1个未使用的搓牌次数,就提供+12攻击力</t>
+  </si>
+  <si>
+    <t>高档甜品</t>
+  </si>
+  <si>
+    <t>SelfDecayAttack</t>
+  </si>
+  <si>
+    <t>100|5</t>
+  </si>
+  <si>
+    <t>提供+100攻击力,但每次比牌后此效果会-5攻击力</t>
+  </si>
+  <si>
+    <t>第六感</t>
+  </si>
+  <si>
+    <t>比牌即使牌型小于对方,也会有10%的概率获胜</t>
+  </si>
+  <si>
+    <t>炸弹恶魔</t>
+  </si>
+  <si>
+    <t>FixedTypeCountMult</t>
+  </si>
+  <si>
+    <t>6|10</t>
+  </si>
+  <si>
+    <t>每亮出过1次炸弹,该圣物就会在结算时提供+10倍率</t>
+  </si>
+  <si>
+    <t>消费主义</t>
+  </si>
+  <si>
+    <t>ShopRefreshGetMult</t>
+  </si>
+  <si>
+    <t>在商店中每刷新1次,该圣物就会提供+1倍率</t>
+  </si>
+  <si>
+    <t>高档饮品</t>
+  </si>
+  <si>
+    <t>SelfDecayMult</t>
+  </si>
+  <si>
+    <t>20|1</t>
+  </si>
+  <si>
+    <t>提供+20倍率,但每次比牌后此效果会-1倍率</t>
+  </si>
+  <si>
+    <t>幸运之子</t>
+  </si>
+  <si>
+    <t>LuckyDouble</t>
+  </si>
+  <si>
+    <t>将你持有的圣物中所有关于概率的数字翻倍</t>
+  </si>
+  <si>
+    <t>万能A</t>
+  </si>
+  <si>
+    <t>WildAce</t>
+  </si>
+  <si>
+    <t>你的A可以当作任意花色与任意点数使用</t>
   </si>
 </sst>
 </file>
@@ -2078,12 +2243,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2091,13 +2253,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2448,169 +2604,169 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="5.75833333333333" style="2" customWidth="1"/>
-    <col min="2" max="2" width="7.49166666666667" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.475" style="3" customWidth="1"/>
-    <col min="4" max="4" width="21.8416666666667" style="3" customWidth="1"/>
-    <col min="5" max="5" width="8.36666666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.325" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2" customWidth="1"/>
+    <col min="1" max="1" width="5.75833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.49166666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.475" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.8416666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.36666666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.325" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:7">
-      <c r="B5" s="4">
+      <c r="B5" s="2">
         <v>10001</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="2">
         <v>1</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:7">
-      <c r="B6" s="4">
+      <c r="B6" s="2">
         <v>10002</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="2">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:7">
-      <c r="B7" s="4">
+      <c r="B7" s="2">
         <v>10003</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:7">
-      <c r="B8" s="4">
+      <c r="B8" s="2">
         <v>10004</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="2">
         <v>1</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:7">
-      <c r="B9" s="4">
+      <c r="B9" s="2">
         <v>10005</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="2">
         <v>1</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:7">
-      <c r="B10" s="4">
+      <c r="B10" s="2">
         <v>10006</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2619,361 +2775,361 @@
       <c r="E10" s="1">
         <v>3</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:7">
-      <c r="B11" s="4">
+      <c r="B11" s="2">
         <v>10007</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:7">
-      <c r="B12" s="4">
+      <c r="B12" s="2">
         <v>10008</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" t="s">
         <v>39</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:7">
-      <c r="B13" s="4">
+      <c r="B13" s="2">
         <v>10009</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" t="s">
         <v>43</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:7">
-      <c r="B14" s="4">
+      <c r="B14" s="2">
         <v>10010</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:7">
-      <c r="B15" s="4">
+      <c r="B15" s="2">
         <v>10011</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="2">
         <v>-0.05</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:7">
-      <c r="B16" s="4">
+      <c r="B16" s="2">
         <v>10012</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="2">
         <v>2</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="5"/>
+      <c r="G16"/>
     </row>
     <row r="17" s="1" customFormat="1" spans="2:7">
-      <c r="B17" s="4">
+      <c r="B17" s="2">
         <v>10013</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="2">
         <v>2</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="5"/>
+      <c r="G17"/>
     </row>
     <row r="18" s="1" customFormat="1" spans="2:7">
-      <c r="B18" s="4">
+      <c r="B18" s="2">
         <v>10014</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" t="s">
         <v>62</v>
       </c>
-      <c r="G18" s="5"/>
+      <c r="G18"/>
     </row>
     <row r="19" s="1" customFormat="1" spans="2:7">
-      <c r="B19" s="4">
+      <c r="B19" s="2">
         <v>10015</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="5"/>
+      <c r="G19"/>
     </row>
     <row r="20" s="1" customFormat="1" spans="2:7">
-      <c r="B20" s="4">
+      <c r="B20" s="2">
         <v>10016</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" t="s">
         <v>70</v>
       </c>
-      <c r="G20" s="5"/>
+      <c r="G20"/>
     </row>
     <row r="21" s="1" customFormat="1" spans="2:7">
-      <c r="B21" s="4">
+      <c r="B21" s="2">
         <v>10017</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="2">
         <v>0.01</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" t="s">
         <v>73</v>
       </c>
-      <c r="G21" s="5"/>
+      <c r="G21"/>
     </row>
     <row r="22" s="1" customFormat="1" spans="2:7">
-      <c r="B22" s="4">
+      <c r="B22" s="2">
         <v>10018</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" t="s">
         <v>74</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="2">
         <v>0.25</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" t="s">
         <v>76</v>
       </c>
-      <c r="G22" s="5"/>
+      <c r="G22"/>
     </row>
     <row r="23" s="1" customFormat="1" spans="2:7">
-      <c r="B23" s="4">
+      <c r="B23" s="2">
         <v>10019</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="2">
         <v>0.2</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" t="s">
         <v>79</v>
       </c>
-      <c r="G23" s="5"/>
+      <c r="G23"/>
     </row>
     <row r="24" s="1" customFormat="1" spans="2:7">
-      <c r="B24" s="4">
+      <c r="B24" s="2">
         <v>10020</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" t="s">
         <v>80</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" t="s">
         <v>81</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" t="s">
         <v>83</v>
       </c>
-      <c r="G24" s="5"/>
+      <c r="G24"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="2:7">
-      <c r="B25" s="4">
+      <c r="B25" s="2">
         <v>10021</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" t="s">
         <v>85</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" t="s">
         <v>87</v>
       </c>
-      <c r="G25" s="5"/>
+      <c r="G25"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="2:7">
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="4"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26"/>
+      <c r="E26" s="2"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="5"/>
+      <c r="G26"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="2:7">
       <c r="B27" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="2">
         <v>1</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" t="s">
         <v>91</v>
       </c>
-      <c r="G27" s="5"/>
+      <c r="G27"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="2:7">
       <c r="B28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" t="s">
         <v>94</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" t="s">
         <v>95</v>
       </c>
-      <c r="G28" s="5"/>
+      <c r="G28"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="2:7">
       <c r="B29" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" t="s">
         <v>98</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="2">
         <v>1</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" t="s">
         <v>99</v>
       </c>
-      <c r="G29" s="5"/>
+      <c r="G29"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="2:7">
       <c r="B30" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" t="s">
         <v>102</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" t="s">
         <v>103</v>
       </c>
-      <c r="G30" s="5"/>
+      <c r="G30"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="2:7">
       <c r="B31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="2" t="s">
         <v>105</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -2982,1864 +3138,2128 @@
       <c r="E31" s="1">
         <v>3</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" t="s">
         <v>107</v>
       </c>
-      <c r="G31" s="5"/>
+      <c r="G31"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="2:7">
       <c r="B32" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" t="s">
         <v>110</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" t="s">
         <v>111</v>
       </c>
-      <c r="G32" s="5"/>
+      <c r="G32"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="2:7">
       <c r="B33" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" t="s">
         <v>114</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" t="s">
         <v>115</v>
       </c>
-      <c r="G33" s="5"/>
+      <c r="G33"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="2:7">
       <c r="B34" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" t="s">
         <v>118</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" t="s">
         <v>119</v>
       </c>
-      <c r="G34" s="5"/>
+      <c r="G34"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="2:7">
       <c r="B35" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="2" t="s">
         <v>122</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="F35" t="s">
         <v>123</v>
       </c>
-      <c r="G35" s="5"/>
+      <c r="G35"/>
     </row>
     <row r="36" s="1" customFormat="1" spans="2:7">
       <c r="B36" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="2">
         <v>2</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" t="s">
         <v>126</v>
       </c>
-      <c r="G36" s="5"/>
+      <c r="G36"/>
     </row>
     <row r="37" s="1" customFormat="1" spans="2:7">
       <c r="B37" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="2">
         <v>30</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" t="s">
         <v>129</v>
       </c>
-      <c r="G37" s="5"/>
+      <c r="G37"/>
     </row>
     <row r="38" s="1" customFormat="1" spans="2:7">
       <c r="B38" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" t="s">
         <v>132</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38" s="2">
         <v>150</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="G38" s="5"/>
+      <c r="G38"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="2:7">
       <c r="B39" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="2">
         <v>1</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G39" s="5"/>
+      <c r="G39"/>
     </row>
     <row r="40" s="1" customFormat="1" spans="2:7">
       <c r="B40" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" t="s">
         <v>142</v>
       </c>
-      <c r="G40" s="5"/>
+      <c r="G40"/>
     </row>
     <row r="41" s="1" customFormat="1" spans="2:7">
       <c r="B41" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" t="s">
         <v>145</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="2">
         <v>2</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" t="s">
         <v>146</v>
       </c>
-      <c r="G41" s="5"/>
+      <c r="G41"/>
     </row>
     <row r="42" s="1" customFormat="1" spans="2:7">
       <c r="B42" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" t="s">
         <v>149</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="2">
         <v>2</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" t="s">
         <v>150</v>
       </c>
-      <c r="G42" s="5"/>
+      <c r="G42"/>
     </row>
     <row r="43" s="1" customFormat="1" spans="2:7">
       <c r="B43" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" t="s">
         <v>153</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" t="s">
         <v>155</v>
       </c>
-      <c r="G43" s="5"/>
+      <c r="G43"/>
     </row>
     <row r="44" s="1" customFormat="1" spans="2:7">
       <c r="B44" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" t="s">
         <v>158</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E44" s="2">
         <v>10</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="F44" t="s">
         <v>159</v>
       </c>
-      <c r="G44" s="5"/>
+      <c r="G44"/>
     </row>
     <row r="45" s="1" customFormat="1" spans="2:7">
       <c r="B45" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D45" t="s">
         <v>162</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E45" s="2">
         <v>0.2</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="G45" s="5"/>
+      <c r="G45"/>
     </row>
     <row r="46" s="1" customFormat="1" spans="2:7">
       <c r="B46" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" t="s">
         <v>166</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E46" s="2">
         <v>1</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="F46" t="s">
         <v>167</v>
       </c>
-      <c r="G46" s="5"/>
+      <c r="G46"/>
     </row>
     <row r="47" s="1" customFormat="1" spans="2:7">
       <c r="B47" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" t="s">
         <v>170</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E47" s="2">
         <v>3</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="F47" t="s">
         <v>171</v>
       </c>
-      <c r="G47" s="5"/>
+      <c r="G47"/>
     </row>
     <row r="48" s="1" customFormat="1" spans="2:7">
       <c r="B48" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" t="s">
         <v>174</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E48" s="2">
         <v>3</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F48" t="s">
         <v>175</v>
       </c>
-      <c r="G48" s="5"/>
+      <c r="G48"/>
     </row>
     <row r="49" s="1" customFormat="1" spans="2:7">
       <c r="B49" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" t="s">
         <v>178</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E49" s="2">
         <v>1</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="F49" t="s">
         <v>179</v>
       </c>
-      <c r="G49" s="5"/>
+      <c r="G49"/>
     </row>
     <row r="50" s="1" customFormat="1" spans="2:7">
       <c r="B50" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" t="s">
         <v>182</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="F50" t="s">
         <v>184</v>
       </c>
-      <c r="G50" s="5"/>
+      <c r="G50"/>
     </row>
     <row r="51" s="1" customFormat="1" spans="2:7">
       <c r="B51" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="D51" t="s">
         <v>187</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="F51" t="s">
         <v>188</v>
       </c>
-      <c r="G51" s="5"/>
+      <c r="G51"/>
     </row>
     <row r="52" s="1" customFormat="1" spans="2:7">
       <c r="B52" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D52" t="s">
         <v>191</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="F52" t="s">
         <v>193</v>
       </c>
-      <c r="G52" s="5"/>
+      <c r="G52"/>
     </row>
     <row r="53" s="1" customFormat="1" spans="2:7">
       <c r="B53" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D53" t="s">
         <v>196</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="F53" t="s">
         <v>198</v>
       </c>
-      <c r="G53" s="5"/>
+      <c r="G53"/>
     </row>
     <row r="54" s="1" customFormat="1" spans="2:7">
       <c r="B54" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" t="s">
         <v>200</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D54" t="s">
         <v>75</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E54" s="2">
         <v>0.5</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="F54" t="s">
         <v>201</v>
       </c>
-      <c r="G54" s="5"/>
+      <c r="G54"/>
     </row>
     <row r="55" s="1" customFormat="1" spans="2:7">
       <c r="B55" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" t="s">
         <v>203</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="D55" t="s">
         <v>78</v>
       </c>
-      <c r="E55" s="4">
+      <c r="E55" s="2">
         <v>0.4</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="F55" t="s">
         <v>204</v>
       </c>
-      <c r="G55" s="5"/>
+      <c r="G55"/>
     </row>
     <row r="56" s="1" customFormat="1" spans="2:7">
       <c r="B56" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" t="s">
         <v>206</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" t="s">
         <v>207</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E56" s="2">
         <v>3</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" t="s">
         <v>208</v>
       </c>
-      <c r="G56" s="5"/>
+      <c r="G56"/>
     </row>
     <row r="57" s="1" customFormat="1" spans="2:7">
       <c r="B57" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" t="s">
         <v>210</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D57" t="s">
         <v>211</v>
       </c>
-      <c r="E57" s="4">
+      <c r="E57" s="2">
         <v>0.5</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="F57" t="s">
         <v>212</v>
       </c>
-      <c r="G57" s="5"/>
+      <c r="G57"/>
     </row>
     <row r="58" s="1" customFormat="1" spans="2:7">
       <c r="B58" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" t="s">
         <v>214</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D58" t="s">
         <v>85</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="E58" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="F58" t="s">
         <v>216</v>
       </c>
-      <c r="G58" s="5"/>
+      <c r="G58"/>
     </row>
     <row r="59" s="1" customFormat="1" spans="2:7">
       <c r="B59" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" t="s">
         <v>218</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D59" t="s">
         <v>85</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E59" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="F59" t="s">
         <v>220</v>
       </c>
-      <c r="G59" s="5"/>
+      <c r="G59"/>
     </row>
     <row r="60" s="1" customFormat="1" spans="2:7">
       <c r="B60" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E60" s="4">
+      <c r="E60" s="2">
         <v>1</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="F60" t="s">
         <v>224</v>
       </c>
-      <c r="G60" s="5"/>
+      <c r="G60"/>
     </row>
     <row r="61" s="1" customFormat="1" spans="2:7">
       <c r="B61" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E61" s="2">
         <v>2</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="F61" t="s">
         <v>227</v>
       </c>
-      <c r="G61" s="5"/>
+      <c r="G61"/>
     </row>
     <row r="62" s="1" customFormat="1" spans="2:7">
       <c r="B62" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E62" s="4">
+      <c r="E62" s="2">
         <v>3</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="F62" t="s">
         <v>230</v>
       </c>
-      <c r="G62" s="5"/>
+      <c r="G62"/>
     </row>
     <row r="63" s="1" customFormat="1" spans="2:7">
-      <c r="C63" s="5"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
+      <c r="B63" s="2">
+        <v>20036</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" s="1">
+        <v>8</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G63"/>
     </row>
     <row r="64" s="1" customFormat="1" spans="2:7">
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="2">
+        <v>20037</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="E64" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="F64" s="5" t="s">
+      <c r="E64" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="G64" s="5"/>
+      <c r="G64"/>
     </row>
     <row r="65" s="1" customFormat="1" spans="2:7">
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="2">
+        <v>20038</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="D65" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="E65" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="E65" s="4">
-        <v>2</v>
-      </c>
-      <c r="F65" s="5" t="s">
+      <c r="F65" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="G65" s="5"/>
+      <c r="G65"/>
     </row>
     <row r="66" s="1" customFormat="1" spans="2:7">
-      <c r="B66" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="E66" s="4">
-        <v>2</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="G66" s="5"/>
+      <c r="C66"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66"/>
+      <c r="G66"/>
     </row>
     <row r="67" s="1" customFormat="1" spans="2:7">
       <c r="B67" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="E67" s="4">
-        <v>1</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="G67" s="5"/>
+        <v>239</v>
+      </c>
+      <c r="C67" t="s">
+        <v>240</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="F67" t="s">
+        <v>242</v>
+      </c>
+      <c r="G67"/>
     </row>
     <row r="68" s="1" customFormat="1" spans="2:7">
       <c r="B68" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="E68" s="4">
-        <v>1</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="G68" s="5"/>
+        <v>243</v>
+      </c>
+      <c r="C68" t="s">
+        <v>244</v>
+      </c>
+      <c r="D68" t="s">
+        <v>245</v>
+      </c>
+      <c r="E68" s="2">
+        <v>2</v>
+      </c>
+      <c r="F68" t="s">
+        <v>246</v>
+      </c>
+      <c r="G68"/>
     </row>
     <row r="69" s="1" customFormat="1" spans="2:7">
       <c r="B69" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="E69" s="4">
-        <v>1</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="G69" s="5"/>
+        <v>247</v>
+      </c>
+      <c r="C69" t="s">
+        <v>248</v>
+      </c>
+      <c r="D69" t="s">
+        <v>249</v>
+      </c>
+      <c r="E69" s="2">
+        <v>2</v>
+      </c>
+      <c r="F69" t="s">
+        <v>250</v>
+      </c>
+      <c r="G69"/>
     </row>
     <row r="70" s="1" customFormat="1" spans="2:7">
       <c r="B70" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="E70" s="4">
-        <v>100</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="G70" s="5"/>
+        <v>251</v>
+      </c>
+      <c r="C70" t="s">
+        <v>252</v>
+      </c>
+      <c r="D70" t="s">
+        <v>253</v>
+      </c>
+      <c r="E70" s="2">
+        <v>1</v>
+      </c>
+      <c r="F70" t="s">
+        <v>254</v>
+      </c>
+      <c r="G70"/>
     </row>
     <row r="71" s="1" customFormat="1" spans="2:7">
       <c r="B71" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E71" s="4">
-        <v>2</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="G71" s="5"/>
+        <v>255</v>
+      </c>
+      <c r="C71" t="s">
+        <v>256</v>
+      </c>
+      <c r="D71" t="s">
+        <v>257</v>
+      </c>
+      <c r="E71" s="2">
+        <v>1</v>
+      </c>
+      <c r="F71" t="s">
+        <v>258</v>
+      </c>
+      <c r="G71"/>
     </row>
     <row r="72" s="1" customFormat="1" spans="2:7">
       <c r="B72" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E72" s="4">
-        <v>2</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="G72" s="5"/>
+        <v>259</v>
+      </c>
+      <c r="C72" t="s">
+        <v>260</v>
+      </c>
+      <c r="D72" t="s">
+        <v>261</v>
+      </c>
+      <c r="E72" s="2">
+        <v>1</v>
+      </c>
+      <c r="F72" t="s">
+        <v>262</v>
+      </c>
+      <c r="G72"/>
     </row>
     <row r="73" s="1" customFormat="1" spans="2:7">
       <c r="B73" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E73" s="4">
-        <v>4</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="G73" s="5"/>
+        <v>263</v>
+      </c>
+      <c r="C73" t="s">
+        <v>264</v>
+      </c>
+      <c r="D73" t="s">
+        <v>265</v>
+      </c>
+      <c r="E73" s="2">
+        <v>100</v>
+      </c>
+      <c r="F73" t="s">
+        <v>266</v>
+      </c>
+      <c r="G73"/>
     </row>
     <row r="74" s="1" customFormat="1" spans="2:7">
       <c r="B74" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C74" t="s">
+        <v>268</v>
+      </c>
+      <c r="D74" t="s">
+        <v>269</v>
+      </c>
+      <c r="E74" s="2">
+        <v>2</v>
+      </c>
+      <c r="F74" t="s">
         <v>270</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="E74" s="4">
-        <v>10</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="G74" s="5"/>
+      <c r="G74"/>
     </row>
     <row r="75" s="1" customFormat="1" spans="2:7">
       <c r="B75" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C75" t="s">
+        <v>272</v>
+      </c>
+      <c r="D75" t="s">
+        <v>273</v>
+      </c>
+      <c r="E75" s="2">
+        <v>2</v>
+      </c>
+      <c r="F75" t="s">
         <v>274</v>
       </c>
-      <c r="C75" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="G75" s="5"/>
+      <c r="G75"/>
     </row>
     <row r="76" s="1" customFormat="1" spans="2:7">
       <c r="B76" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="E76" s="4">
-        <v>30</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G76" s="5"/>
+        <v>275</v>
+      </c>
+      <c r="C76" t="s">
+        <v>276</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E76" s="2">
+        <v>4</v>
+      </c>
+      <c r="F76" t="s">
+        <v>277</v>
+      </c>
+      <c r="G76"/>
     </row>
     <row r="77" s="1" customFormat="1" spans="2:7">
       <c r="B77" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="G77" s="5"/>
+        <v>278</v>
+      </c>
+      <c r="C77" t="s">
+        <v>279</v>
+      </c>
+      <c r="D77" t="s">
+        <v>280</v>
+      </c>
+      <c r="E77" s="2">
+        <v>10</v>
+      </c>
+      <c r="F77" t="s">
+        <v>281</v>
+      </c>
+      <c r="G77"/>
     </row>
     <row r="78" s="1" customFormat="1" spans="2:7">
       <c r="B78" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="E78" s="4">
-        <v>1</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="G78" s="5"/>
+        <v>282</v>
+      </c>
+      <c r="C78" t="s">
+        <v>283</v>
+      </c>
+      <c r="D78" t="s">
+        <v>284</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F78" t="s">
+        <v>285</v>
+      </c>
+      <c r="G78"/>
     </row>
     <row r="79" s="1" customFormat="1" spans="2:7">
       <c r="B79" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="G79" s="5"/>
+        <v>286</v>
+      </c>
+      <c r="C79" t="s">
+        <v>287</v>
+      </c>
+      <c r="D79" t="s">
+        <v>288</v>
+      </c>
+      <c r="E79" s="2">
+        <v>30</v>
+      </c>
+      <c r="F79" t="s">
+        <v>289</v>
+      </c>
+      <c r="G79"/>
     </row>
     <row r="80" s="1" customFormat="1" spans="2:7">
       <c r="B80" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="G80" s="5"/>
+        <v>290</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D80" t="s">
+        <v>292</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F80" t="s">
+        <v>294</v>
+      </c>
+      <c r="G80"/>
     </row>
     <row r="81" s="1" customFormat="1" spans="2:7">
       <c r="B81" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="E81" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="G81" s="5"/>
+        <v>295</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D81" t="s">
+        <v>297</v>
+      </c>
+      <c r="E81" s="2">
+        <v>1</v>
+      </c>
+      <c r="F81" t="s">
+        <v>298</v>
+      </c>
+      <c r="G81"/>
     </row>
     <row r="82" s="1" customFormat="1" spans="2:7">
       <c r="B82" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="G82" s="5"/>
+        <v>299</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D82" t="s">
+        <v>301</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F82" t="s">
+        <v>302</v>
+      </c>
+      <c r="G82"/>
     </row>
     <row r="83" s="1" customFormat="1" spans="2:7">
       <c r="B83" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="E83" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="G83" s="5"/>
+        <v>303</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D83" t="s">
+        <v>305</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F83" t="s">
+        <v>307</v>
+      </c>
+      <c r="G83"/>
     </row>
     <row r="84" s="1" customFormat="1" spans="2:7">
       <c r="B84" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="G84" s="5"/>
+        <v>308</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D84" t="s">
+        <v>310</v>
+      </c>
+      <c r="E84" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F84" t="s">
+        <v>311</v>
+      </c>
+      <c r="G84"/>
     </row>
     <row r="85" s="1" customFormat="1" spans="2:7">
       <c r="B85" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="E85" s="4">
-        <v>-0.3</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="G85" s="5"/>
+        <v>312</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D85" t="s">
+        <v>314</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F85" t="s">
+        <v>316</v>
+      </c>
+      <c r="G85"/>
     </row>
     <row r="86" s="1" customFormat="1" spans="2:7">
       <c r="B86" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="G86" s="5"/>
+        <v>317</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D86" t="s">
+        <v>319</v>
+      </c>
+      <c r="E86" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F86" t="s">
+        <v>320</v>
+      </c>
+      <c r="G86"/>
     </row>
     <row r="87" s="1" customFormat="1" spans="2:7">
       <c r="B87" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="E87" s="4">
-        <v>1</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="G87" s="5"/>
+        <v>321</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D87" t="s">
+        <v>323</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F87" t="s">
+        <v>325</v>
+      </c>
+      <c r="G87"/>
     </row>
     <row r="88" s="1" customFormat="1" spans="2:7">
       <c r="B88" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="E88" s="4">
+        <v>326</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D88" t="s">
+        <v>328</v>
+      </c>
+      <c r="E88" s="2">
         <v>-0.3</v>
       </c>
-      <c r="F88" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="G88" s="5"/>
+      <c r="F88" t="s">
+        <v>329</v>
+      </c>
+      <c r="G88"/>
     </row>
     <row r="89" s="1" customFormat="1" spans="2:7">
       <c r="B89" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="E89" s="4">
-        <v>300</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="G89" s="5"/>
+        <v>330</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D89" t="s">
+        <v>332</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="F89" t="s">
+        <v>334</v>
+      </c>
+      <c r="G89"/>
     </row>
     <row r="90" s="1" customFormat="1" spans="2:7">
       <c r="B90" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="E90" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="G90" s="5"/>
+        <v>335</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D90" t="s">
+        <v>337</v>
+      </c>
+      <c r="E90" s="2">
+        <v>1</v>
+      </c>
+      <c r="F90" t="s">
+        <v>338</v>
+      </c>
+      <c r="G90"/>
     </row>
     <row r="91" s="1" customFormat="1" spans="2:7">
       <c r="B91" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="G91" s="5"/>
+        <v>339</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D91" t="s">
+        <v>341</v>
+      </c>
+      <c r="E91" s="2">
+        <v>-0.3</v>
+      </c>
+      <c r="F91" t="s">
+        <v>342</v>
+      </c>
+      <c r="G91"/>
     </row>
     <row r="92" s="1" customFormat="1" spans="2:7">
       <c r="B92" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="E92" s="4">
-        <v>-1</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="G92" s="5"/>
+        <v>343</v>
+      </c>
+      <c r="C92" t="s">
+        <v>344</v>
+      </c>
+      <c r="D92" t="s">
+        <v>345</v>
+      </c>
+      <c r="E92" s="2">
+        <v>300</v>
+      </c>
+      <c r="F92" t="s">
+        <v>346</v>
+      </c>
+      <c r="G92"/>
     </row>
     <row r="93" s="1" customFormat="1" spans="2:7">
       <c r="B93" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="E93" s="4">
-        <v>1</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="G93" s="5"/>
+        <v>347</v>
+      </c>
+      <c r="C93" t="s">
+        <v>348</v>
+      </c>
+      <c r="D93" t="s">
+        <v>349</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F93" t="s">
+        <v>350</v>
+      </c>
+      <c r="G93"/>
     </row>
     <row r="94" s="1" customFormat="1" spans="2:7">
       <c r="B94" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="E94" s="4">
-        <v>1</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="G94" s="5"/>
+        <v>351</v>
+      </c>
+      <c r="C94" t="s">
+        <v>352</v>
+      </c>
+      <c r="D94" t="s">
+        <v>353</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F94" t="s">
+        <v>355</v>
+      </c>
+      <c r="G94"/>
     </row>
     <row r="95" s="1" customFormat="1" spans="2:7">
       <c r="B95" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C95" t="s">
+        <v>357</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E95" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F95" t="s">
+        <v>359</v>
+      </c>
+      <c r="G95"/>
+    </row>
+    <row r="96" s="1" customFormat="1" spans="2:7">
+      <c r="B96" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C96" t="s">
         <v>361</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="D96" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="D95" s="4" t="s">
+      <c r="E96" s="2">
+        <v>1</v>
+      </c>
+      <c r="F96" t="s">
+        <v>363</v>
+      </c>
+      <c r="G96"/>
+    </row>
+    <row r="97" s="1" customFormat="1" spans="2:7">
+      <c r="B97" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C97" t="s">
+        <v>365</v>
+      </c>
+      <c r="D97" t="s">
+        <v>366</v>
+      </c>
+      <c r="E97" s="2">
+        <v>1</v>
+      </c>
+      <c r="F97" t="s">
+        <v>367</v>
+      </c>
+      <c r="G97"/>
+    </row>
+    <row r="98" s="1" customFormat="1" spans="2:7">
+      <c r="B98" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E95" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="G95" s="5"/>
-    </row>
-    <row r="96" s="1" customFormat="1" spans="2:7">
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="5"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="5"/>
-      <c r="G96" s="5"/>
-    </row>
-    <row r="97" s="1" customFormat="1" spans="2:7">
-      <c r="B97" s="4">
+      <c r="E98" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F98" t="s">
+        <v>371</v>
+      </c>
+      <c r="G98"/>
+    </row>
+    <row r="99" s="1" customFormat="1" spans="2:7">
+      <c r="B99" s="2">
+        <v>30033</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E99" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G99"/>
+    </row>
+    <row r="100" s="1" customFormat="1" spans="2:7">
+      <c r="B100" s="2">
+        <v>30034</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E100" s="1">
+        <v>1</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G100"/>
+    </row>
+    <row r="101" s="1" customFormat="1" spans="2:7">
+      <c r="B101" s="2">
+        <v>30035</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E101" s="1">
+        <v>1</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G101"/>
+    </row>
+    <row r="102" s="1" customFormat="1" spans="2:7">
+      <c r="B102" s="2">
+        <v>30036</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="G102"/>
+    </row>
+    <row r="103" spans="2:7">
+      <c r="B103" s="2">
+        <v>30037</v>
+      </c>
+      <c r="C103" t="s">
+        <v>385</v>
+      </c>
+      <c r="D103" t="s">
+        <v>382</v>
+      </c>
+      <c r="E103" t="s">
+        <v>386</v>
+      </c>
+      <c r="F103" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7">
+      <c r="B104" s="2">
+        <v>30038</v>
+      </c>
+      <c r="C104" t="s">
+        <v>388</v>
+      </c>
+      <c r="D104" t="s">
+        <v>389</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+      <c r="F104" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7">
+      <c r="B105" s="2">
+        <v>30039</v>
+      </c>
+      <c r="C105" t="s">
+        <v>391</v>
+      </c>
+      <c r="D105" t="s">
+        <v>392</v>
+      </c>
+      <c r="E105">
+        <v>0.4</v>
+      </c>
+      <c r="F105" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7">
+      <c r="B106" s="2">
+        <v>30040</v>
+      </c>
+      <c r="C106" t="s">
+        <v>394</v>
+      </c>
+      <c r="D106" t="s">
+        <v>395</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+      <c r="F106" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="107" s="1" customFormat="1" spans="2:7">
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107"/>
+      <c r="E107" s="2"/>
+      <c r="F107"/>
+      <c r="G107"/>
+    </row>
+    <row r="108" s="1" customFormat="1" spans="2:7">
+      <c r="B108" s="2">
         <v>40001</v>
       </c>
-      <c r="C97" s="4">
+      <c r="C108" s="2">
         <v>235</v>
       </c>
-      <c r="D97" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="E97" s="4">
+      <c r="D108" t="s">
+        <v>397</v>
+      </c>
+      <c r="E108" s="2">
         <v>1</v>
       </c>
-      <c r="F97" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="G97" s="5"/>
-    </row>
-    <row r="98" s="1" customFormat="1" spans="2:7">
-      <c r="B98" s="4">
+      <c r="F108" t="s">
+        <v>398</v>
+      </c>
+      <c r="G108"/>
+    </row>
+    <row r="109" s="1" customFormat="1" spans="2:7">
+      <c r="B109" s="2">
         <v>40002</v>
       </c>
-      <c r="C98" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="D98" s="4" t="s">
+      <c r="C109" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D109" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E98" s="4">
+      <c r="E109" s="2">
         <v>500</v>
       </c>
-      <c r="F98" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="G98" s="5"/>
-    </row>
-    <row r="99" s="1" customFormat="1" spans="2:7">
-      <c r="B99" s="4">
+      <c r="F109" t="s">
+        <v>400</v>
+      </c>
+      <c r="G109"/>
+    </row>
+    <row r="110" s="1" customFormat="1" spans="2:7">
+      <c r="B110" s="2">
         <v>40003</v>
       </c>
-      <c r="C99" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="E99" s="4">
+      <c r="C110" t="s">
+        <v>401</v>
+      </c>
+      <c r="D110" t="s">
+        <v>402</v>
+      </c>
+      <c r="E110" s="2">
         <v>1</v>
       </c>
-      <c r="F99" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="G99" s="5"/>
-    </row>
-    <row r="100" s="1" customFormat="1" spans="2:7">
-      <c r="B100" s="4">
+      <c r="F110" t="s">
+        <v>403</v>
+      </c>
+      <c r="G110"/>
+    </row>
+    <row r="111" s="1" customFormat="1" spans="2:7">
+      <c r="B111" s="2">
         <v>40004</v>
       </c>
-      <c r="C100" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="E100" s="4">
+      <c r="C111" t="s">
+        <v>404</v>
+      </c>
+      <c r="D111" t="s">
+        <v>405</v>
+      </c>
+      <c r="E111" s="2">
         <v>1</v>
       </c>
-      <c r="F100" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="G100" s="5"/>
-    </row>
-    <row r="101" s="1" customFormat="1" spans="2:7">
-      <c r="B101" s="4">
+      <c r="F111" t="s">
+        <v>406</v>
+      </c>
+      <c r="G111"/>
+    </row>
+    <row r="112" s="1" customFormat="1" spans="2:7">
+      <c r="B112" s="2">
         <v>40005</v>
       </c>
-      <c r="C101" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="E101" s="4">
+      <c r="C112" t="s">
+        <v>407</v>
+      </c>
+      <c r="D112" t="s">
+        <v>408</v>
+      </c>
+      <c r="E112" s="2">
         <v>12</v>
       </c>
-      <c r="F101" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="G101" s="5"/>
-    </row>
-    <row r="102" s="1" customFormat="1" spans="2:7">
-      <c r="B102" s="4">
+      <c r="F112" t="s">
+        <v>409</v>
+      </c>
+      <c r="G112"/>
+    </row>
+    <row r="113" s="1" customFormat="1" spans="2:7">
+      <c r="B113" s="2">
         <v>40006</v>
       </c>
-      <c r="C102" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="E102" s="4">
+      <c r="C113" t="s">
+        <v>410</v>
+      </c>
+      <c r="D113" t="s">
+        <v>411</v>
+      </c>
+      <c r="E113" s="2">
         <v>3</v>
       </c>
-      <c r="F102" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="G102" s="5"/>
-    </row>
-    <row r="103" s="1" customFormat="1" spans="2:7">
-      <c r="B103" s="4">
+      <c r="F113" t="s">
+        <v>412</v>
+      </c>
+      <c r="G113"/>
+    </row>
+    <row r="114" s="1" customFormat="1" spans="2:7">
+      <c r="B114" s="2">
         <v>40007</v>
       </c>
-      <c r="C103" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="D103" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="E103" s="4">
+      <c r="C114" t="s">
+        <v>413</v>
+      </c>
+      <c r="D114" t="s">
+        <v>414</v>
+      </c>
+      <c r="E114" s="2">
         <v>3</v>
       </c>
-      <c r="F103" s="5" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="104" s="1" customFormat="1" spans="2:7">
-      <c r="B104" s="4">
+      <c r="F114" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="115" s="1" customFormat="1" spans="2:7">
+      <c r="B115" s="2">
         <v>40008</v>
       </c>
-      <c r="C104" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="E104" s="4">
+      <c r="C115" t="s">
+        <v>416</v>
+      </c>
+      <c r="D115" t="s">
+        <v>417</v>
+      </c>
+      <c r="E115" s="2">
         <v>1</v>
       </c>
-      <c r="F104" s="5" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="105" s="1" customFormat="1" spans="2:7">
-      <c r="B105" s="4">
+      <c r="F115" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="116" s="1" customFormat="1" spans="2:7">
+      <c r="B116" s="2">
         <v>40009</v>
       </c>
-      <c r="C105" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="E105" s="4">
+      <c r="C116" t="s">
+        <v>419</v>
+      </c>
+      <c r="D116" t="s">
+        <v>420</v>
+      </c>
+      <c r="E116" s="2">
         <v>6</v>
       </c>
-      <c r="F105" s="5" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="106" s="1" customFormat="1" spans="2:7">
-      <c r="B106" s="4">
+      <c r="F116" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="117" s="1" customFormat="1" spans="2:7">
+      <c r="B117" s="2">
         <v>400091</v>
       </c>
-      <c r="C106" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="E106" s="4">
+      <c r="C117" t="s">
+        <v>419</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E117" s="2">
         <v>66</v>
       </c>
-      <c r="F106" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="107" s="1" customFormat="1" spans="2:7">
-      <c r="B107" s="4">
+      <c r="F117" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="118" s="1" customFormat="1" spans="2:7">
+      <c r="B118" s="2">
         <v>40010</v>
       </c>
-      <c r="C107" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="108" s="1" customFormat="1" spans="2:7">
-      <c r="B108" s="4">
+      <c r="C118" t="s">
+        <v>424</v>
+      </c>
+      <c r="D118" t="s">
+        <v>425</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F118" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="119" s="1" customFormat="1" spans="2:7">
+      <c r="B119" s="2">
         <v>40011</v>
       </c>
-      <c r="C108" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="E108" s="4">
+      <c r="C119" t="s">
+        <v>427</v>
+      </c>
+      <c r="D119" t="s">
+        <v>428</v>
+      </c>
+      <c r="E119" s="2">
         <v>0.5</v>
       </c>
-      <c r="F108" s="5" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="109" s="1" customFormat="1" spans="2:7">
-      <c r="B109" s="4">
+      <c r="F119" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="120" s="1" customFormat="1" spans="2:7">
+      <c r="B120" s="2">
         <v>40012</v>
       </c>
-      <c r="C109" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="E109" s="4">
+      <c r="C120" t="s">
+        <v>430</v>
+      </c>
+      <c r="D120" t="s">
+        <v>405</v>
+      </c>
+      <c r="E120" s="2">
         <v>-2</v>
       </c>
-      <c r="F109" s="5" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="110" s="1" customFormat="1" spans="2:7">
-      <c r="B110" s="4">
+      <c r="F120" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="121" s="1" customFormat="1" spans="2:7">
+      <c r="B121" s="2">
         <v>400121</v>
       </c>
-      <c r="C110" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="D110" s="1" t="s">
+      <c r="C121" t="s">
+        <v>430</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E110" s="4">
+      <c r="E121" s="2">
         <v>15</v>
       </c>
-      <c r="F110" s="5" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="111" s="1" customFormat="1" spans="2:7">
-      <c r="B111" s="4">
+      <c r="F121" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="122" s="1" customFormat="1" spans="2:7">
+      <c r="B122" s="2">
         <v>40013</v>
       </c>
-      <c r="C111" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="D111" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="E111" s="4">
+      <c r="C122" t="s">
+        <v>433</v>
+      </c>
+      <c r="D122" t="s">
+        <v>434</v>
+      </c>
+      <c r="E122" s="2">
         <v>0.1</v>
       </c>
-      <c r="F111" s="5" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="112" s="1" customFormat="1" spans="2:7">
-      <c r="B112" s="4">
+      <c r="F122" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="123" s="1" customFormat="1" spans="2:7">
+      <c r="B123" s="2">
         <v>40014</v>
       </c>
-      <c r="C112" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="E112" s="4">
+      <c r="C123" t="s">
+        <v>436</v>
+      </c>
+      <c r="D123" t="s">
+        <v>437</v>
+      </c>
+      <c r="E123" s="2">
         <v>1</v>
       </c>
-      <c r="F112" s="5" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="113" s="1" customFormat="1" spans="2:7">
-      <c r="B113" s="4">
+      <c r="F123" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="124" s="1" customFormat="1" spans="2:7">
+      <c r="B124" s="2">
         <v>400141</v>
       </c>
-      <c r="C113" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="E113" s="4">
+      <c r="C124" t="s">
+        <v>436</v>
+      </c>
+      <c r="D124" t="s">
+        <v>439</v>
+      </c>
+      <c r="E124" s="2">
         <v>77</v>
       </c>
-      <c r="F113" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="G113" s="5"/>
-    </row>
-    <row r="114" s="1" customFormat="1" spans="2:7">
-      <c r="B114" s="4">
+      <c r="F124" t="s">
+        <v>440</v>
+      </c>
+      <c r="G124"/>
+    </row>
+    <row r="125" s="1" customFormat="1" spans="2:7">
+      <c r="B125" s="2">
         <v>400142</v>
       </c>
-      <c r="C114" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="E114" s="4">
+      <c r="C125" t="s">
+        <v>436</v>
+      </c>
+      <c r="D125" t="s">
+        <v>441</v>
+      </c>
+      <c r="E125" s="2">
         <v>7</v>
       </c>
-      <c r="F114" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="G114" s="5"/>
-    </row>
-    <row r="115" s="1" customFormat="1" spans="2:7">
-      <c r="B115" s="4">
+      <c r="F125" t="s">
+        <v>442</v>
+      </c>
+      <c r="G125"/>
+    </row>
+    <row r="126" s="1" customFormat="1" spans="2:7">
+      <c r="B126" s="2">
         <v>40015</v>
       </c>
-      <c r="C115" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="E115" s="4">
+      <c r="C126" t="s">
+        <v>443</v>
+      </c>
+      <c r="D126" t="s">
+        <v>444</v>
+      </c>
+      <c r="E126" s="2">
         <v>0.5</v>
       </c>
-      <c r="F115" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="G115" s="5"/>
-    </row>
-    <row r="116" s="1" customFormat="1" spans="2:7">
-      <c r="B116" s="4">
+      <c r="F126" t="s">
+        <v>445</v>
+      </c>
+      <c r="G126"/>
+    </row>
+    <row r="127" s="1" customFormat="1" spans="2:7">
+      <c r="B127" s="2">
         <v>400151</v>
       </c>
-      <c r="C116" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="E116" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="G116" s="5"/>
-    </row>
-    <row r="117" s="1" customFormat="1" spans="2:7">
-      <c r="B117" s="4">
+      <c r="C127" t="s">
+        <v>443</v>
+      </c>
+      <c r="D127" t="s">
+        <v>446</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F127" t="s">
+        <v>448</v>
+      </c>
+      <c r="G127"/>
+    </row>
+    <row r="128" s="1" customFormat="1" spans="2:7">
+      <c r="B128" s="2">
         <v>40016</v>
       </c>
-      <c r="C117" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="E117" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="F117" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="G117" s="5"/>
-    </row>
-    <row r="118" s="1" customFormat="1" spans="2:7">
-      <c r="B118" s="4">
+      <c r="C128" t="s">
+        <v>449</v>
+      </c>
+      <c r="D128" t="s">
+        <v>450</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F128" t="s">
+        <v>452</v>
+      </c>
+      <c r="G128"/>
+    </row>
+    <row r="129" s="1" customFormat="1" spans="2:7">
+      <c r="B129" s="2">
         <v>40017</v>
       </c>
-      <c r="C118" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="D118" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="G118" s="5"/>
-    </row>
-    <row r="119" s="1" customFormat="1" spans="2:7">
-      <c r="B119" s="4">
+      <c r="C129" t="s">
+        <v>453</v>
+      </c>
+      <c r="D129" t="s">
+        <v>454</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="F129" t="s">
+        <v>456</v>
+      </c>
+      <c r="G129"/>
+    </row>
+    <row r="130" s="1" customFormat="1" spans="2:7">
+      <c r="B130" s="2">
         <v>40018</v>
       </c>
-      <c r="C119" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="D119" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="F119" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="G119" s="5"/>
-    </row>
-    <row r="120" s="1" customFormat="1" spans="2:7">
-      <c r="B120" s="4">
+      <c r="C130" t="s">
+        <v>457</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F130" t="s">
+        <v>460</v>
+      </c>
+      <c r="G130"/>
+    </row>
+    <row r="131" s="1" customFormat="1" spans="2:7">
+      <c r="B131" s="2">
         <v>40019</v>
       </c>
-      <c r="C120" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="D120" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="E120" s="1" t="s">
+      <c r="C131" t="s">
+        <v>461</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E131" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F120" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="G120" s="5"/>
-    </row>
-    <row r="121" s="1" customFormat="1" spans="2:7">
-      <c r="B121" s="4">
+      <c r="F131" t="s">
+        <v>463</v>
+      </c>
+      <c r="G131"/>
+    </row>
+    <row r="132" s="1" customFormat="1" spans="2:7">
+      <c r="B132" s="2">
         <v>40020</v>
       </c>
-      <c r="C121" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="E121" s="1" t="s">
+      <c r="C132" t="s">
+        <v>464</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F121" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="G121" s="5"/>
-    </row>
-    <row r="122" s="1" customFormat="1" spans="2:7">
-      <c r="B122" s="4">
+      <c r="F132" t="s">
+        <v>466</v>
+      </c>
+      <c r="G132"/>
+    </row>
+    <row r="133" s="1" customFormat="1" spans="2:7">
+      <c r="B133" s="2">
         <v>40021</v>
       </c>
-      <c r="C122" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="G122" s="5"/>
-    </row>
-    <row r="123" s="1" customFormat="1" spans="2:7">
-      <c r="B123" s="4">
+      <c r="C133" t="s">
+        <v>467</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="F133" t="s">
+        <v>470</v>
+      </c>
+      <c r="G133"/>
+    </row>
+    <row r="134" s="1" customFormat="1" spans="2:7">
+      <c r="B134" s="2">
         <v>40022</v>
       </c>
-      <c r="C123" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="F123" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="G123" s="5"/>
-    </row>
-    <row r="124" s="1" customFormat="1" spans="2:7">
-      <c r="B124" s="4">
+      <c r="C134" t="s">
+        <v>471</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="F134" t="s">
+        <v>474</v>
+      </c>
+      <c r="G134"/>
+    </row>
+    <row r="135" s="1" customFormat="1" spans="2:7">
+      <c r="B135" s="2">
         <v>400221</v>
       </c>
-      <c r="C124" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="G124" s="5"/>
-    </row>
-    <row r="125" s="1" customFormat="1" spans="2:7">
-      <c r="B125" s="4">
+      <c r="C135" t="s">
+        <v>471</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F135" t="s">
+        <v>476</v>
+      </c>
+      <c r="G135"/>
+    </row>
+    <row r="136" s="1" customFormat="1" spans="2:7">
+      <c r="B136" s="2">
         <v>40023</v>
       </c>
-      <c r="C125" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="E125" s="1" t="s">
+      <c r="C136" t="s">
+        <v>477</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F125" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="G125" s="5"/>
-    </row>
-    <row r="126" s="1" customFormat="1" spans="2:7">
-      <c r="B126" s="4">
+      <c r="F136" t="s">
+        <v>479</v>
+      </c>
+      <c r="G136"/>
+    </row>
+    <row r="137" s="1" customFormat="1" spans="2:7">
+      <c r="B137" s="2">
         <v>40024</v>
       </c>
-      <c r="C126" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="E126" s="1">
+      <c r="C137" t="s">
+        <v>480</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="E137" s="1">
         <v>0.2</v>
       </c>
-      <c r="F126" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="G126" s="5"/>
-    </row>
-    <row r="127" s="1" customFormat="1" spans="2:7">
-      <c r="B127" s="4">
+      <c r="F137" t="s">
+        <v>482</v>
+      </c>
+      <c r="G137"/>
+    </row>
+    <row r="138" s="1" customFormat="1" spans="2:7">
+      <c r="B138" s="2">
         <v>40025</v>
       </c>
-      <c r="C127" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="F127" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="G127" s="5"/>
-    </row>
-    <row r="128" s="1" customFormat="1" spans="2:7">
-      <c r="B128" s="4">
+      <c r="C138" t="s">
+        <v>483</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="F138" t="s">
+        <v>486</v>
+      </c>
+      <c r="G138"/>
+    </row>
+    <row r="139" s="1" customFormat="1" spans="2:7">
+      <c r="B139" s="2">
         <v>40026</v>
       </c>
-      <c r="C128" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="D128" s="5" t="s">
+      <c r="C139" t="s">
+        <v>487</v>
+      </c>
+      <c r="D139" t="s">
         <v>75</v>
       </c>
-      <c r="E128" s="4">
+      <c r="E139" s="2">
         <v>2</v>
       </c>
-      <c r="F128" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="G128" s="5"/>
-    </row>
-    <row r="129" s="1" customFormat="1" spans="2:7">
-      <c r="B129" s="4">
+      <c r="F139" t="s">
+        <v>488</v>
+      </c>
+      <c r="G139"/>
+    </row>
+    <row r="140" s="1" customFormat="1" spans="2:7">
+      <c r="B140" s="2">
         <v>40027</v>
       </c>
-      <c r="C129" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="D129" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="E129" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="G129" s="5"/>
-    </row>
-    <row r="130" s="1" customFormat="1" spans="2:7">
-      <c r="B130" s="4">
+      <c r="C140" t="s">
+        <v>489</v>
+      </c>
+      <c r="D140" t="s">
+        <v>490</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="F140" t="s">
+        <v>492</v>
+      </c>
+      <c r="G140"/>
+    </row>
+    <row r="141" s="1" customFormat="1" spans="2:7">
+      <c r="B141" s="2">
         <v>40028</v>
       </c>
-      <c r="C130" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="E130" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="G130" s="5"/>
-    </row>
-    <row r="131" s="1" customFormat="1" spans="2:7">
-      <c r="B131" s="4">
+      <c r="C141" t="s">
+        <v>493</v>
+      </c>
+      <c r="D141" t="s">
+        <v>494</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="F141" t="s">
+        <v>496</v>
+      </c>
+      <c r="G141"/>
+    </row>
+    <row r="142" s="1" customFormat="1" spans="2:7">
+      <c r="B142" s="2">
         <v>40029</v>
       </c>
-      <c r="C131" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="E131" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="G131" s="5"/>
-    </row>
-    <row r="132" s="1" customFormat="1" spans="2:7">
-      <c r="B132" s="4">
+      <c r="C142" t="s">
+        <v>497</v>
+      </c>
+      <c r="D142" t="s">
+        <v>353</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F142" t="s">
+        <v>499</v>
+      </c>
+      <c r="G142"/>
+    </row>
+    <row r="143" s="1" customFormat="1" spans="2:7">
+      <c r="B143" s="2">
         <v>40030</v>
       </c>
-      <c r="C132" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="E132" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="F132" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="G132" s="5"/>
-    </row>
-    <row r="133" s="1" customFormat="1" spans="2:7">
-      <c r="B133" s="4">
+      <c r="C143" t="s">
+        <v>500</v>
+      </c>
+      <c r="D143" t="s">
+        <v>501</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="F143" t="s">
+        <v>503</v>
+      </c>
+      <c r="G143"/>
+    </row>
+    <row r="144" s="1" customFormat="1" spans="2:7">
+      <c r="B144" s="2">
         <v>40031</v>
       </c>
-      <c r="C133" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="D133" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="E133" s="4">
+      <c r="C144" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D144" t="s">
+        <v>505</v>
+      </c>
+      <c r="E144" s="2">
         <v>12</v>
       </c>
-      <c r="F133" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="G133" s="5"/>
-    </row>
-    <row r="134" s="1" customFormat="1" spans="2:7">
-      <c r="C134" s="4"/>
-      <c r="D134" s="4"/>
-      <c r="E134" s="1"/>
-      <c r="F134" s="1"/>
-      <c r="G134" s="5"/>
-    </row>
-    <row r="135" s="1" customFormat="1" spans="2:7">
-      <c r="C135" s="4"/>
-      <c r="D135" s="4"/>
-      <c r="E135" s="1"/>
-      <c r="F135" s="1"/>
-      <c r="G135" s="5"/>
-    </row>
-    <row r="136" s="1" customFormat="1" spans="2:7">
-      <c r="C136" s="4"/>
-      <c r="D136" s="4"/>
-      <c r="E136" s="1"/>
-      <c r="F136" s="1"/>
-      <c r="G136" s="5"/>
-    </row>
-    <row r="137" s="1" customFormat="1" spans="2:7">
-      <c r="C137" s="4"/>
-      <c r="D137" s="4"/>
-      <c r="E137" s="1"/>
-      <c r="F137" s="1"/>
-      <c r="G137" s="5"/>
-    </row>
-    <row r="138" s="1" customFormat="1" spans="2:7">
-      <c r="C138" s="4"/>
-      <c r="D138" s="4"/>
-      <c r="E138" s="1"/>
-      <c r="F138" s="1"/>
-      <c r="G138" s="5"/>
-    </row>
-    <row r="139" s="1" customFormat="1" spans="2:7">
-      <c r="C139" s="4"/>
-      <c r="D139" s="4"/>
-      <c r="E139" s="1"/>
-      <c r="F139" s="1"/>
-      <c r="G139" s="5"/>
-    </row>
-    <row r="140" s="1" customFormat="1" spans="2:7">
-      <c r="C140" s="4"/>
-      <c r="D140" s="4"/>
-      <c r="E140" s="1"/>
-      <c r="F140" s="1"/>
-      <c r="G140" s="5"/>
+      <c r="F144" t="s">
+        <v>506</v>
+      </c>
+      <c r="G144"/>
+    </row>
+    <row r="145" spans="2:6">
+      <c r="B145" s="2">
+        <v>40032</v>
+      </c>
+      <c r="C145" t="s">
+        <v>507</v>
+      </c>
+      <c r="D145" t="s">
+        <v>508</v>
+      </c>
+      <c r="E145" t="s">
+        <v>509</v>
+      </c>
+      <c r="F145" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6">
+      <c r="B146" s="2">
+        <v>40033</v>
+      </c>
+      <c r="C146" t="s">
+        <v>511</v>
+      </c>
+      <c r="D146" t="s">
+        <v>310</v>
+      </c>
+      <c r="E146">
+        <v>0.1</v>
+      </c>
+      <c r="F146" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6">
+      <c r="B147" s="2">
+        <v>40034</v>
+      </c>
+      <c r="C147" t="s">
+        <v>513</v>
+      </c>
+      <c r="D147" t="s">
+        <v>514</v>
+      </c>
+      <c r="E147" t="s">
+        <v>515</v>
+      </c>
+      <c r="F147" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="148" spans="2:6">
+      <c r="B148" s="2">
+        <v>40035</v>
+      </c>
+      <c r="C148" t="s">
+        <v>517</v>
+      </c>
+      <c r="D148" t="s">
+        <v>518</v>
+      </c>
+      <c r="E148">
+        <v>1</v>
+      </c>
+      <c r="F148" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6">
+      <c r="B149" s="2">
+        <v>40036</v>
+      </c>
+      <c r="C149" t="s">
+        <v>520</v>
+      </c>
+      <c r="D149" t="s">
+        <v>521</v>
+      </c>
+      <c r="E149" t="s">
+        <v>522</v>
+      </c>
+      <c r="F149" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6">
+      <c r="B150" s="2">
+        <v>40037</v>
+      </c>
+      <c r="C150" t="s">
+        <v>524</v>
+      </c>
+      <c r="D150" t="s">
+        <v>525</v>
+      </c>
+      <c r="E150">
+        <v>1</v>
+      </c>
+      <c r="F150" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="151" spans="2:6">
+      <c r="B151" s="2">
+        <v>40038</v>
+      </c>
+      <c r="C151" t="s">
+        <v>527</v>
+      </c>
+      <c r="D151" t="s">
+        <v>528</v>
+      </c>
+      <c r="E151">
+        <v>1</v>
+      </c>
+      <c r="F151" t="s">
+        <v>529</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/RelicEntryConfig.xlsx
+++ b/Config/RelicEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12510" windowHeight="11235"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="663">
   <si>
     <t>##var</t>
   </si>
@@ -478,6 +478,9 @@
     <t>小精灵</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>每回合结束后恢复2点血量</t>
   </si>
   <si>
@@ -487,7 +490,10 @@
     <t>HeroHpMax</t>
   </si>
   <si>
-    <t>获得30点生命上限</t>
+    <t>60</t>
+  </si>
+  <si>
+    <t>获得60点生命上限</t>
   </si>
   <si>
     <t>20011</t>
@@ -814,267 +820,270 @@
     <t>SelfMultWinLose</t>
   </si>
   <si>
+    <t>0.25|0.25</t>
+  </si>
+  <si>
+    <t>每次比牌胜利后,此圣物倍率+0.25;每次失败后-0.25</t>
+  </si>
+  <si>
+    <t>傲慢披风</t>
+  </si>
+  <si>
+    <t>HighHpDamageUp</t>
+  </si>
+  <si>
+    <t>0.7|0.25</t>
+  </si>
+  <si>
+    <t>生命高于70%时,你造成的伤害+25%</t>
+  </si>
+  <si>
+    <t>纯色西装</t>
+  </si>
+  <si>
+    <t>SameColorDamageUp</t>
+  </si>
+  <si>
+    <t>亮出的三张牌同色(全红或全黑)时,本次伤害+30%</t>
+  </si>
+  <si>
+    <t>千术手套</t>
+  </si>
+  <si>
+    <t>ReplaceCardsNum</t>
+  </si>
+  <si>
+    <t>每关[替换]使用次数+1</t>
+  </si>
+  <si>
+    <t>救济金</t>
+  </si>
+  <si>
+    <t>LowGoldGetGold</t>
+  </si>
+  <si>
+    <t>20|15</t>
+  </si>
+  <si>
+    <t>每回合开始时,若金币不足20,获得15金币</t>
+  </si>
+  <si>
+    <t>肾上腺素</t>
+  </si>
+  <si>
+    <t>CriticalHealHp</t>
+  </si>
+  <si>
+    <t>暴击时,回复8点生命</t>
+  </si>
+  <si>
+    <t>藏宝图</t>
+  </si>
+  <si>
+    <t>KillDropConsumable</t>
+  </si>
+  <si>
+    <t>击败敌人后,有25%概率获得1件随机消耗性圣物(圣物栏有空位时)</t>
+  </si>
+  <si>
+    <t>捡漏</t>
+  </si>
+  <si>
+    <t>ShopRareGuarantee</t>
+  </si>
+  <si>
+    <t>每次进入商店时,有30%概率其中1件圣物为稀有或更高品质</t>
+  </si>
+  <si>
+    <t>老主顾</t>
+  </si>
+  <si>
+    <t>RefreshPriceFixed</t>
+  </si>
+  <si>
+    <t>商店刷新价格不再随次数上涨</t>
+  </si>
+  <si>
+    <t>以下犯上</t>
+  </si>
+  <si>
+    <t>UnderdogDamageUp</t>
+  </si>
+  <si>
+    <t>对手攻击力高于你时,你造成的伤害+25%</t>
+  </si>
+  <si>
+    <t>养精蓄锐</t>
+  </si>
+  <si>
+    <t>UnusedSkillDamageUp</t>
+  </si>
+  <si>
+    <t>本回合未使用任何技能时,你造成的伤害+25%</t>
+  </si>
+  <si>
+    <t>残影</t>
+  </si>
+  <si>
+    <t>MissGetGold</t>
+  </si>
+  <si>
+    <t>闪避成功时,获得10金币</t>
+  </si>
+  <si>
+    <t>牌型图鉴</t>
+  </si>
+  <si>
+    <t>FirstTypeGetAttack</t>
+  </si>
+  <si>
+    <t>3|7</t>
+  </si>
+  <si>
+    <t>本局每首次亮出1种牌型,永久+3攻击力(最多7种)</t>
+  </si>
+  <si>
+    <t>30001</t>
+  </si>
+  <si>
+    <t>疯狂面具</t>
+  </si>
+  <si>
+    <t>BloodSucking</t>
+  </si>
+  <si>
+    <t>造成伤害时,获得5%的生命窃取</t>
+  </si>
+  <si>
+    <t>30002</t>
+  </si>
+  <si>
+    <t>回旋刃</t>
+  </si>
+  <si>
+    <t>DoubleCardAttack</t>
+  </si>
+  <si>
+    <t>亮出的牌点数提供的攻击力加成翻倍</t>
+  </si>
+  <si>
+    <t>30003</t>
+  </si>
+  <si>
+    <t>致胜之剑</t>
+  </si>
+  <si>
+    <t>TheSwordOfVictory</t>
+  </si>
+  <si>
+    <t>结算伤害时,将留在手牌上最大的牌点数×2转化为额外攻击力</t>
+  </si>
+  <si>
+    <t>30004</t>
+  </si>
+  <si>
+    <t>搓牌能手</t>
+  </si>
+  <si>
+    <t>EveryUseRubbingNum</t>
+  </si>
+  <si>
+    <t>每搓1次牌,结算时提供的倍率+1</t>
+  </si>
+  <si>
+    <t>30005</t>
+  </si>
+  <si>
+    <t>会员卡</t>
+  </si>
+  <si>
+    <t>FreeShopRefresh</t>
+  </si>
+  <si>
+    <t>每次进入商店提供1次免费刷新的机会</t>
+  </si>
+  <si>
+    <t>30006</t>
+  </si>
+  <si>
+    <t>错峰出行</t>
+  </si>
+  <si>
+    <t>SpecialStraight</t>
+  </si>
+  <si>
+    <t>顺子牌型可以相隔1点组成[例如:2,4,5]</t>
+  </si>
+  <si>
+    <t>30007</t>
+  </si>
+  <si>
+    <t>致命黑八</t>
+  </si>
+  <si>
+    <t>SpecialEightCard</t>
+  </si>
+  <si>
+    <t>亮出的每张8在结算时提供+100攻击力</t>
+  </si>
+  <si>
+    <t>30008</t>
+  </si>
+  <si>
+    <t>偶数韵律</t>
+  </si>
+  <si>
+    <t>EvenNumberCard</t>
+  </si>
+  <si>
+    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+2倍率</t>
+  </si>
+  <si>
+    <t>30009</t>
+  </si>
+  <si>
+    <t>奇数韵律</t>
+  </si>
+  <si>
+    <t>OddNumberCard</t>
+  </si>
+  <si>
+    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+2倍率</t>
+  </si>
+  <si>
+    <t>30010</t>
+  </si>
+  <si>
+    <t>贵族</t>
+  </si>
+  <si>
+    <t>亮出的每张人头牌在结算时提供+4倍率</t>
+  </si>
+  <si>
+    <t>30011</t>
+  </si>
+  <si>
+    <t>工资卡</t>
+  </si>
+  <si>
+    <t>KillAfterSellingPrice</t>
+  </si>
+  <si>
+    <t>每击杀1名敌人,这件圣物的出售价格+10金币</t>
+  </si>
+  <si>
+    <t>30012</t>
+  </si>
+  <si>
+    <t>训练</t>
+  </si>
+  <si>
+    <t>EveryCardAttackForever</t>
+  </si>
+  <si>
     <t>1|1</t>
   </si>
   <si>
-    <t>每次比牌胜利后,此圣物倍率+1;每次失败后-1</t>
-  </si>
-  <si>
-    <t>傲慢披风</t>
-  </si>
-  <si>
-    <t>HighHpDamageUp</t>
-  </si>
-  <si>
-    <t>0.7|0.25</t>
-  </si>
-  <si>
-    <t>生命高于70%时,你造成的伤害+25%</t>
-  </si>
-  <si>
-    <t>纯色西装</t>
-  </si>
-  <si>
-    <t>SameColorDamageUp</t>
-  </si>
-  <si>
-    <t>亮出的三张牌同色(全红或全黑)时,本次伤害+30%</t>
-  </si>
-  <si>
-    <t>千术手套</t>
-  </si>
-  <si>
-    <t>ReplaceCardsNum</t>
-  </si>
-  <si>
-    <t>每关[替换]使用次数+1</t>
-  </si>
-  <si>
-    <t>救济金</t>
-  </si>
-  <si>
-    <t>LowGoldGetGold</t>
-  </si>
-  <si>
-    <t>20|15</t>
-  </si>
-  <si>
-    <t>每回合开始时,若金币不足20,获得15金币</t>
-  </si>
-  <si>
-    <t>肾上腺素</t>
-  </si>
-  <si>
-    <t>CriticalHealHp</t>
-  </si>
-  <si>
-    <t>暴击时,回复8点生命</t>
-  </si>
-  <si>
-    <t>藏宝图</t>
-  </si>
-  <si>
-    <t>KillDropConsumable</t>
-  </si>
-  <si>
-    <t>击败敌人后,有25%概率获得1件随机消耗性圣物(圣物栏有空位时)</t>
-  </si>
-  <si>
-    <t>捡漏</t>
-  </si>
-  <si>
-    <t>ShopRareGuarantee</t>
-  </si>
-  <si>
-    <t>每次进入商店时,有50%概率其中1件圣物为稀有或更高品质</t>
-  </si>
-  <si>
-    <t>老主顾</t>
-  </si>
-  <si>
-    <t>RefreshPriceFixed</t>
-  </si>
-  <si>
-    <t>商店刷新价格不再随次数上涨</t>
-  </si>
-  <si>
-    <t>以下犯上</t>
-  </si>
-  <si>
-    <t>UnderdogDamageUp</t>
-  </si>
-  <si>
-    <t>对手攻击力高于你时,你造成的伤害+25%</t>
-  </si>
-  <si>
-    <t>养精蓄锐</t>
-  </si>
-  <si>
-    <t>UnusedSkillDamageUp</t>
-  </si>
-  <si>
-    <t>本回合未使用任何技能时,你造成的伤害+25%</t>
-  </si>
-  <si>
-    <t>残影</t>
-  </si>
-  <si>
-    <t>MissGetGold</t>
-  </si>
-  <si>
-    <t>闪避成功时,获得10金币</t>
-  </si>
-  <si>
-    <t>牌型图鉴</t>
-  </si>
-  <si>
-    <t>FirstTypeGetAttack</t>
-  </si>
-  <si>
-    <t>2|7</t>
-  </si>
-  <si>
-    <t>本局每首次亮出1种牌型,永久+2攻击力(最多7种)</t>
-  </si>
-  <si>
-    <t>30001</t>
-  </si>
-  <si>
-    <t>疯狂面具</t>
-  </si>
-  <si>
-    <t>BloodSucking</t>
-  </si>
-  <si>
-    <t>造成伤害时,获得5%的生命窃取</t>
-  </si>
-  <si>
-    <t>30002</t>
-  </si>
-  <si>
-    <t>回旋刃</t>
-  </si>
-  <si>
-    <t>DoubleCardAttack</t>
-  </si>
-  <si>
-    <t>亮出的牌点数提供的攻击力加成翻倍</t>
-  </si>
-  <si>
-    <t>30003</t>
-  </si>
-  <si>
-    <t>致胜之剑</t>
-  </si>
-  <si>
-    <t>TheSwordOfVictory</t>
-  </si>
-  <si>
-    <t>结算伤害时,将留在手牌上最大的牌点数×2转化为额外攻击力</t>
-  </si>
-  <si>
-    <t>30004</t>
-  </si>
-  <si>
-    <t>搓牌能手</t>
-  </si>
-  <si>
-    <t>EveryUseRubbingNum</t>
-  </si>
-  <si>
-    <t>每搓1次牌,结算时提供的倍率+1</t>
-  </si>
-  <si>
-    <t>30005</t>
-  </si>
-  <si>
-    <t>会员卡</t>
-  </si>
-  <si>
-    <t>FreeShopRefresh</t>
-  </si>
-  <si>
-    <t>每次进入商店提供1次免费刷新的机会</t>
-  </si>
-  <si>
-    <t>30006</t>
-  </si>
-  <si>
-    <t>错峰出行</t>
-  </si>
-  <si>
-    <t>SpecialStraight</t>
-  </si>
-  <si>
-    <t>顺子牌型可以相隔1点组成[例如:2,4,5]</t>
-  </si>
-  <si>
-    <t>30007</t>
-  </si>
-  <si>
-    <t>致命黑八</t>
-  </si>
-  <si>
-    <t>SpecialEightCard</t>
-  </si>
-  <si>
-    <t>亮出的每张8在结算时提供+100攻击力</t>
-  </si>
-  <si>
-    <t>30008</t>
-  </si>
-  <si>
-    <t>偶数韵律</t>
-  </si>
-  <si>
-    <t>EvenNumberCard</t>
-  </si>
-  <si>
-    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+2倍率</t>
-  </si>
-  <si>
-    <t>30009</t>
-  </si>
-  <si>
-    <t>奇数韵律</t>
-  </si>
-  <si>
-    <t>OddNumberCard</t>
-  </si>
-  <si>
-    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+2倍率</t>
-  </si>
-  <si>
-    <t>30010</t>
-  </si>
-  <si>
-    <t>贵族</t>
-  </si>
-  <si>
-    <t>亮出的每张人头牌在结算时提供+4倍率</t>
-  </si>
-  <si>
-    <t>30011</t>
-  </si>
-  <si>
-    <t>工资卡</t>
-  </si>
-  <si>
-    <t>KillAfterSellingPrice</t>
-  </si>
-  <si>
-    <t>每击杀1名敌人,这件圣物的出售价格+10金币</t>
-  </si>
-  <si>
-    <t>30012</t>
-  </si>
-  <si>
-    <t>训练</t>
-  </si>
-  <si>
-    <t>EveryCardAttackForever</t>
-  </si>
-  <si>
     <t>回合首次亮牌时,随机有1张牌提供的攻击力永久+1</t>
   </si>
   <si>
@@ -1087,7 +1096,10 @@
     <t>SpecialNineCard</t>
   </si>
   <si>
-    <t>亮出的每张9在结算时提供12金币</t>
+    <t>25</t>
+  </si>
+  <si>
+    <t>亮出的每张9在结算时提供25金币</t>
   </si>
   <si>
     <t>30014</t>
@@ -1099,10 +1111,10 @@
     <t>DefeatAllGetGoldAndReplyHp</t>
   </si>
   <si>
-    <t>15|20</t>
-  </si>
-  <si>
-    <t>如果本回合牌型小于所有敌人,则立即获得15金币并回复20点血量</t>
+    <t>25|40</t>
+  </si>
+  <si>
+    <t>如果本回合牌型小于所有敌人,则立即获得25金币并回复40点血量</t>
   </si>
   <si>
     <t>30015</t>
@@ -1165,10 +1177,10 @@
     <t>NoKillMonsterGetMagnification</t>
   </si>
   <si>
-    <t>1|0.5</t>
-  </si>
-  <si>
-    <t>每击杀1名敌人,结算时就永久提供+0.5倍率</t>
+    <t>1|0.3</t>
+  </si>
+  <si>
+    <t>每击杀1名敌人,结算时就永久提供+0.3倍率</t>
   </si>
   <si>
     <t>30020</t>
@@ -1351,7 +1363,10 @@
     <t>UseConsumableGetAttack</t>
   </si>
   <si>
-    <t>每使用过1次消耗类的圣物,此圣物就会永久提供+1攻击力</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>每使用过1次消耗类的圣物,此圣物就会永久提供+3攻击力</t>
   </si>
   <si>
     <t>召唤</t>
@@ -1483,7 +1498,7 @@
     <t>KeepConsumablePer</t>
   </si>
   <si>
-    <t>使用消耗性圣物时,有50%概率不消耗</t>
+    <t>使用消耗性圣物时,有30%概率不消耗</t>
   </si>
   <si>
     <t>乘胜追击</t>
@@ -1657,7 +1672,10 @@
     <t>RubbingCardRelic</t>
   </si>
   <si>
-    <t>每使用1次搓牌,该圣物永久提供+0.1倍率</t>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>每使用1次搓牌,该圣物永久提供+0.25倍率</t>
   </si>
   <si>
     <t>幸运七</t>
@@ -1823,9 +1841,6 @@
   </si>
   <si>
     <t>UseRoundNullify</t>
-  </si>
-  <si>
-    <t>1|0.3</t>
   </si>
   <si>
     <t>使用后,本次比牌你受到的所有伤害变为0,并恢复30%血量</t>
@@ -3728,326 +3743,326 @@
       <c r="D43" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E43" s="2">
-        <v>2</v>
+      <c r="E43" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="F43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G43"/>
     </row>
     <row r="44" s="1" customFormat="1" spans="2:7">
       <c r="B44" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>147</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E44" s="2">
-        <v>30</v>
+        <v>151</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="F44" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G44"/>
     </row>
     <row r="45" s="1" customFormat="1" spans="2:7">
       <c r="B45" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D45" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E45" s="2">
         <v>150</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G45"/>
     </row>
     <row r="46" s="1" customFormat="1" spans="2:7">
       <c r="B46" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E46" s="2">
         <v>1</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G46"/>
     </row>
     <row r="47" s="1" customFormat="1" spans="2:7">
       <c r="B47" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F47" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G47"/>
     </row>
     <row r="48" s="1" customFormat="1" spans="2:7">
       <c r="B48" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D48" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E48" s="2">
         <v>2</v>
       </c>
       <c r="F48" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G48"/>
     </row>
     <row r="49" s="1" customFormat="1" spans="2:7">
       <c r="B49" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D49" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E49" s="2">
         <v>2</v>
       </c>
       <c r="F49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G49"/>
     </row>
     <row r="50" s="1" customFormat="1" spans="2:7">
       <c r="B50" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F50" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G50"/>
     </row>
     <row r="51" s="1" customFormat="1" spans="2:7">
       <c r="B51" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D51" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E51" s="2">
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G51"/>
     </row>
     <row r="52" s="1" customFormat="1" spans="2:7">
       <c r="B52" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D52" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E52" s="2">
         <v>0.2</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G52"/>
     </row>
     <row r="53" s="1" customFormat="1" spans="2:7">
       <c r="B53" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D53" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E53" s="2">
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G53"/>
     </row>
     <row r="54" s="1" customFormat="1" spans="2:7">
       <c r="B54" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D54" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E54" s="2">
         <v>3</v>
       </c>
       <c r="F54" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G54"/>
     </row>
     <row r="55" s="1" customFormat="1" spans="2:7">
       <c r="B55" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D55" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E55" s="2">
         <v>3</v>
       </c>
       <c r="F55" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G55"/>
     </row>
     <row r="56" s="1" customFormat="1" spans="2:7">
       <c r="B56" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D56" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E56" s="2">
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G56"/>
     </row>
     <row r="57" s="1" customFormat="1" spans="2:7">
       <c r="B57" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D57" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F57" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G57"/>
     </row>
     <row r="58" s="1" customFormat="1" spans="2:7">
       <c r="B58" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D58" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F58" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G58"/>
     </row>
     <row r="59" s="1" customFormat="1" spans="2:7">
       <c r="B59" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D59" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F59" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G59"/>
     </row>
     <row r="60" s="1" customFormat="1" spans="2:7">
       <c r="B60" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D60" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F60" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G60"/>
     </row>
     <row r="61" s="1" customFormat="1" spans="2:7">
       <c r="B61" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C61" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D61" t="s">
         <v>75</v>
@@ -4056,16 +4071,16 @@
         <v>0.5</v>
       </c>
       <c r="F61" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G61"/>
     </row>
     <row r="62" s="1" customFormat="1" spans="2:7">
       <c r="B62" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C62" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D62" t="s">
         <v>78</v>
@@ -4074,133 +4089,133 @@
         <v>0.4</v>
       </c>
       <c r="F62" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G62"/>
     </row>
     <row r="63" s="1" customFormat="1" spans="2:7">
       <c r="B63" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C63" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D63" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E63" s="2">
         <v>3</v>
       </c>
       <c r="F63" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G63"/>
     </row>
     <row r="64" s="1" customFormat="1" spans="2:7">
       <c r="B64" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C64" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D64" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E64" s="2">
         <v>0.5</v>
       </c>
       <c r="F64" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G64"/>
     </row>
     <row r="65" s="1" customFormat="1" spans="2:7">
       <c r="B65" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C65" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D65" t="s">
         <v>85</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F65" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G65"/>
     </row>
     <row r="66" s="1" customFormat="1" spans="2:7">
       <c r="B66" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C66" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D66" t="s">
         <v>85</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F66" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G66"/>
     </row>
     <row r="67" s="1" customFormat="1" spans="2:7">
       <c r="B67" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E67" s="2">
         <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G67"/>
     </row>
     <row r="68" s="1" customFormat="1" spans="2:7">
       <c r="B68" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="E68" s="2">
         <v>2</v>
       </c>
       <c r="F68" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G68"/>
     </row>
     <row r="69" s="1" customFormat="1" spans="2:7">
       <c r="B69" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E69" s="2">
         <v>3</v>
       </c>
       <c r="F69" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G69"/>
     </row>
@@ -4209,7 +4224,7 @@
         <v>20036</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>16</v>
@@ -4218,7 +4233,7 @@
         <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G70"/>
     </row>
@@ -4227,16 +4242,16 @@
         <v>20037</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E71" s="1">
         <v>0.18</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G71"/>
     </row>
@@ -4245,16 +4260,16 @@
         <v>20038</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G72"/>
     </row>
@@ -4263,16 +4278,16 @@
         <v>20039</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D73" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F73" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" spans="2:7">
@@ -4280,16 +4295,16 @@
         <v>20040</v>
       </c>
       <c r="C74" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D74" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E74" s="2">
         <v>0.3</v>
       </c>
       <c r="F74" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" spans="2:7">
@@ -4297,16 +4312,16 @@
         <v>20041</v>
       </c>
       <c r="C75" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D75" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E75" s="2">
         <v>1</v>
       </c>
       <c r="F75" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" spans="2:7">
@@ -4314,16 +4329,16 @@
         <v>20042</v>
       </c>
       <c r="C76" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D76" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F76" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" spans="2:7">
@@ -4331,16 +4346,16 @@
         <v>20043</v>
       </c>
       <c r="C77" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D77" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E77" s="2">
         <v>8</v>
       </c>
       <c r="F77" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" spans="2:7">
@@ -4348,16 +4363,16 @@
         <v>20044</v>
       </c>
       <c r="C78" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D78" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E78" s="2">
         <v>0.25</v>
       </c>
       <c r="F78" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" spans="2:7">
@@ -4365,16 +4380,16 @@
         <v>20045</v>
       </c>
       <c r="C79" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D79" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E79" s="2">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F79" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" spans="2:7">
@@ -4382,16 +4397,16 @@
         <v>20046</v>
       </c>
       <c r="C80" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D80" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E80" s="2">
         <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="1" spans="2:7">
@@ -4399,16 +4414,16 @@
         <v>20047</v>
       </c>
       <c r="C81" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D81" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E81" s="2">
         <v>0.25</v>
       </c>
       <c r="F81" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="82" s="1" customFormat="1" spans="2:7">
@@ -4416,16 +4431,16 @@
         <v>20048</v>
       </c>
       <c r="C82" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D82" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E82" s="2">
         <v>0.25</v>
       </c>
       <c r="F82" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="83" s="1" customFormat="1" spans="2:7">
@@ -4433,16 +4448,16 @@
         <v>20049</v>
       </c>
       <c r="C83" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D83" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E83" s="2">
         <v>10</v>
       </c>
       <c r="F83" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="84" s="1" customFormat="1" spans="2:7">
@@ -4450,16 +4465,16 @@
         <v>20050</v>
       </c>
       <c r="C84" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D84" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F84" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="85" s="1" customFormat="1" spans="2:7">
@@ -4471,573 +4486,573 @@
     </row>
     <row r="86" s="1" customFormat="1" spans="2:7">
       <c r="B86" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C86" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E86" s="2">
         <v>0.05</v>
       </c>
       <c r="F86" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G86"/>
     </row>
     <row r="87" s="1" customFormat="1" spans="2:7">
       <c r="B87" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C87" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D87" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E87" s="2">
         <v>2</v>
       </c>
       <c r="F87" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G87"/>
     </row>
     <row r="88" s="1" customFormat="1" spans="2:7">
       <c r="B88" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C88" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D88" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E88" s="2">
         <v>2</v>
       </c>
       <c r="F88" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G88"/>
     </row>
     <row r="89" s="1" customFormat="1" spans="2:7">
       <c r="B89" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C89" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D89" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E89" s="2">
         <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G89"/>
     </row>
     <row r="90" s="1" customFormat="1" spans="2:7">
       <c r="B90" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C90" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D90" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E90" s="2">
         <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G90"/>
     </row>
     <row r="91" s="1" customFormat="1" spans="2:7">
       <c r="B91" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C91" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D91" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E91" s="2">
         <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G91"/>
     </row>
     <row r="92" s="1" customFormat="1" spans="2:7">
       <c r="B92" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C92" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D92" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E92" s="2">
         <v>100</v>
       </c>
       <c r="F92" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G92"/>
     </row>
     <row r="93" s="1" customFormat="1" spans="2:7">
       <c r="B93" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C93" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D93" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E93" s="2">
         <v>2</v>
       </c>
       <c r="F93" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G93"/>
     </row>
     <row r="94" s="1" customFormat="1" spans="2:7">
       <c r="B94" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C94" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D94" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E94" s="2">
         <v>2</v>
       </c>
       <c r="F94" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G94"/>
     </row>
     <row r="95" s="1" customFormat="1" spans="2:7">
       <c r="B95" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C95" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E95" s="2">
         <v>4</v>
       </c>
       <c r="F95" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G95"/>
     </row>
     <row r="96" s="1" customFormat="1" spans="2:7">
       <c r="B96" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C96" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D96" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E96" s="2">
         <v>10</v>
       </c>
       <c r="F96" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G96"/>
     </row>
     <row r="97" s="1" customFormat="1" spans="2:7">
       <c r="B97" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C97" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D97" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>260</v>
+        <v>349</v>
       </c>
       <c r="F97" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G97"/>
     </row>
     <row r="98" s="1" customFormat="1" spans="2:7">
       <c r="B98" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C98" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D98" t="s">
-        <v>350</v>
-      </c>
-      <c r="E98" s="2">
-        <v>12</v>
+        <v>353</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>354</v>
       </c>
       <c r="F98" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G98"/>
     </row>
     <row r="99" s="1" customFormat="1" spans="2:7">
       <c r="B99" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D99" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="F99" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="G99"/>
     </row>
     <row r="100" s="1" customFormat="1" spans="2:7">
       <c r="B100" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D100" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E100" s="2">
         <v>1</v>
       </c>
       <c r="F100" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G100"/>
     </row>
     <row r="101" s="1" customFormat="1" spans="2:7">
       <c r="B101" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>260</v>
+        <v>349</v>
       </c>
       <c r="F101" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G101"/>
     </row>
     <row r="102" s="1" customFormat="1" spans="2:7">
       <c r="B102" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D102" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F102" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="G102"/>
     </row>
     <row r="103" spans="2:7">
       <c r="B103" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D103" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E103" s="2">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F103" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="104" spans="2:7">
       <c r="B104" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D104" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F104" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="105" spans="2:7">
       <c r="B105" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D105" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E105" s="2">
         <v>0.5</v>
       </c>
       <c r="F105" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="106" spans="2:7">
       <c r="B106" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D106" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F106" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" spans="2:7">
       <c r="B107" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D107" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E107" s="2">
         <v>-0.3</v>
       </c>
       <c r="F107" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="G107"/>
     </row>
     <row r="108" s="1" customFormat="1" spans="2:7">
       <c r="B108" s="1" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D108" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F108" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="G108"/>
     </row>
     <row r="109" s="1" customFormat="1" spans="2:7">
       <c r="B109" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D109" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E109" s="2">
         <v>1</v>
       </c>
       <c r="F109" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G109"/>
     </row>
     <row r="110" s="1" customFormat="1" spans="2:7">
       <c r="B110" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D110" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E110" s="2">
         <v>-0.3</v>
       </c>
       <c r="F110" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="G110"/>
     </row>
     <row r="111" s="1" customFormat="1" spans="2:7">
       <c r="B111" s="1" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C111" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D111" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E111" s="2">
         <v>300</v>
       </c>
       <c r="F111" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="G111"/>
     </row>
     <row r="112" s="1" customFormat="1" spans="2:7">
       <c r="B112" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C112" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D112" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E112" s="2">
         <v>0.2</v>
       </c>
       <c r="F112" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="G112"/>
     </row>
     <row r="113" s="1" customFormat="1" spans="2:7">
       <c r="B113" s="1" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C113" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D113" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F113" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="G113"/>
     </row>
     <row r="114" s="1" customFormat="1" spans="2:7">
       <c r="B114" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C114" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E114" s="2">
         <v>-1</v>
       </c>
       <c r="F114" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="G114"/>
     </row>
     <row r="115" s="1" customFormat="1" spans="2:7">
       <c r="B115" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C115" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E115" s="2">
         <v>1</v>
       </c>
       <c r="F115" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="G115"/>
     </row>
     <row r="116" s="1" customFormat="1" spans="2:7">
       <c r="B116" s="1" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C116" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D116" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E116" s="2">
         <v>1</v>
       </c>
       <c r="F116" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="G116"/>
     </row>
     <row r="117" s="1" customFormat="1" spans="2:7">
       <c r="B117" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="F117" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="G117"/>
     </row>
@@ -5046,16 +5061,16 @@
         <v>30033</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E118" s="1">
         <v>0.5</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="G118"/>
     </row>
@@ -5064,16 +5079,16 @@
         <v>30034</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="E119" s="1">
-        <v>1</v>
+        <v>442</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="G119"/>
     </row>
@@ -5082,16 +5097,16 @@
         <v>30035</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="E120" s="1">
         <v>1</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="G120"/>
     </row>
@@ -5100,16 +5115,16 @@
         <v>30036</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="G121"/>
     </row>
@@ -5118,16 +5133,16 @@
         <v>30037</v>
       </c>
       <c r="C122" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="D122" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F122" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="123" s="1" customFormat="1" spans="2:7">
@@ -5135,16 +5150,16 @@
         <v>30038</v>
       </c>
       <c r="C123" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D123" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="E123" s="2">
         <v>1</v>
       </c>
       <c r="F123" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="124" s="1" customFormat="1" spans="2:7">
@@ -5152,16 +5167,16 @@
         <v>30039</v>
       </c>
       <c r="C124" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="D124" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E124" s="2">
         <v>0.4</v>
       </c>
       <c r="F124" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="125" s="1" customFormat="1" spans="2:7">
@@ -5169,16 +5184,16 @@
         <v>30040</v>
       </c>
       <c r="C125" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D125" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="E125" s="2">
         <v>1</v>
       </c>
       <c r="F125" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="126" s="1" customFormat="1" spans="2:7">
@@ -5186,16 +5201,16 @@
         <v>30041</v>
       </c>
       <c r="C126" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D126" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F126" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="127" s="1" customFormat="1" spans="2:7">
@@ -5203,16 +5218,16 @@
         <v>30042</v>
       </c>
       <c r="C127" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D127" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E127" s="2">
         <v>-100</v>
       </c>
       <c r="F127" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="128" s="1" customFormat="1" spans="2:7">
@@ -5220,16 +5235,16 @@
         <v>30043</v>
       </c>
       <c r="C128" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D128" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="E128" s="2">
         <v>45</v>
       </c>
       <c r="F128" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="129" s="1" customFormat="1" spans="2:7">
@@ -5237,16 +5252,16 @@
         <v>30044</v>
       </c>
       <c r="C129" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="D129" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="E129" s="2">
         <v>60</v>
       </c>
       <c r="F129" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="130" s="1" customFormat="1" spans="2:7">
@@ -5254,16 +5269,16 @@
         <v>30045</v>
       </c>
       <c r="C130" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="D130" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E130" s="2">
         <v>-6</v>
       </c>
       <c r="F130" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="131" s="1" customFormat="1" spans="2:7">
@@ -5271,16 +5286,16 @@
         <v>30046</v>
       </c>
       <c r="C131" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="D131" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="E131" s="2">
         <v>30</v>
       </c>
       <c r="F131" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="132" s="1" customFormat="1" spans="2:7">
@@ -5288,16 +5303,16 @@
         <v>30047</v>
       </c>
       <c r="C132" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D132" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="F132" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="133" s="1" customFormat="1" spans="2:7">
@@ -5305,16 +5320,16 @@
         <v>30048</v>
       </c>
       <c r="C133" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D133" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="E133" s="2">
         <v>2</v>
       </c>
       <c r="F133" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="134" s="1" customFormat="1" spans="2:7">
@@ -5322,16 +5337,16 @@
         <v>30049</v>
       </c>
       <c r="C134" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D134" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="E134" s="2">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F134" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="135" s="1" customFormat="1" spans="2:7">
@@ -5339,16 +5354,16 @@
         <v>30050</v>
       </c>
       <c r="C135" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="D135" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E135" s="2">
         <v>15</v>
       </c>
       <c r="F135" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="136" s="1" customFormat="1" spans="2:7">
@@ -5356,16 +5371,16 @@
         <v>30051</v>
       </c>
       <c r="C136" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="D136" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="E136" s="2">
         <v>0.3</v>
       </c>
       <c r="F136" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="137" s="1" customFormat="1" spans="2:7">
@@ -5373,16 +5388,16 @@
         <v>30052</v>
       </c>
       <c r="C137" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D137" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="E137" s="2">
         <v>0.08</v>
       </c>
       <c r="F137" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="138" s="1" customFormat="1" spans="2:7">
@@ -5390,16 +5405,16 @@
         <v>30053</v>
       </c>
       <c r="C138" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D138" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="E138" s="2">
         <v>0.3</v>
       </c>
       <c r="F138" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="139" s="1" customFormat="1" spans="2:7">
@@ -5407,16 +5422,16 @@
         <v>30054</v>
       </c>
       <c r="C139" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="D139" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="E139" s="2">
         <v>8</v>
       </c>
       <c r="F139" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="140" s="1" customFormat="1" spans="2:7">
@@ -5424,16 +5439,16 @@
         <v>30055</v>
       </c>
       <c r="C140" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D140" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="F140" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" spans="2:7">
@@ -5452,13 +5467,13 @@
         <v>235</v>
       </c>
       <c r="D142" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="E142" s="2">
         <v>1</v>
       </c>
       <c r="F142" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="G142"/>
     </row>
@@ -5467,16 +5482,16 @@
         <v>40002</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E143" s="2">
         <v>240</v>
       </c>
       <c r="F143" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="G143"/>
     </row>
@@ -5485,16 +5500,16 @@
         <v>40003</v>
       </c>
       <c r="C144" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="D144" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="E144" s="2">
         <v>1</v>
       </c>
       <c r="F144" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="G144"/>
     </row>
@@ -5503,16 +5518,16 @@
         <v>40004</v>
       </c>
       <c r="C145" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="D145" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="E145" s="2">
         <v>1</v>
       </c>
       <c r="F145" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="146" spans="2:6">
@@ -5520,16 +5535,16 @@
         <v>40005</v>
       </c>
       <c r="C146" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="D146" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E146" s="2">
         <v>12</v>
       </c>
       <c r="F146" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="147" spans="2:6">
@@ -5537,16 +5552,16 @@
         <v>40006</v>
       </c>
       <c r="C147" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="D147" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="E147" s="2">
         <v>3</v>
       </c>
       <c r="F147" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="148" spans="2:6">
@@ -5554,16 +5569,16 @@
         <v>40007</v>
       </c>
       <c r="C148" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="D148" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="E148" s="2">
         <v>3</v>
       </c>
       <c r="F148" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
     </row>
     <row r="149" spans="2:6">
@@ -5571,16 +5586,16 @@
         <v>40008</v>
       </c>
       <c r="C149" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="D149" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="E149" s="2">
         <v>1</v>
       </c>
       <c r="F149" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="150" spans="2:6">
@@ -5588,16 +5603,16 @@
         <v>40009</v>
       </c>
       <c r="C150" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="D150" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="E150" s="2">
         <v>6</v>
       </c>
       <c r="F150" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
     </row>
     <row r="151" spans="2:6">
@@ -5605,16 +5620,16 @@
         <v>400091</v>
       </c>
       <c r="C151" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="E151" s="2">
         <v>66</v>
       </c>
       <c r="F151" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
     </row>
     <row r="152" spans="2:6">
@@ -5622,16 +5637,16 @@
         <v>40010</v>
       </c>
       <c r="C152" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="D152" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>260</v>
+        <v>349</v>
       </c>
       <c r="F152" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="153" spans="2:6">
@@ -5639,16 +5654,16 @@
         <v>40011</v>
       </c>
       <c r="C153" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="D153" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="E153" s="2">
         <v>0.5</v>
       </c>
       <c r="F153" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
     </row>
     <row r="154" spans="2:6">
@@ -5656,16 +5671,16 @@
         <v>40012</v>
       </c>
       <c r="C154" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="D154" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="E154" s="2">
         <v>-2</v>
       </c>
       <c r="F154" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
     </row>
     <row r="155" spans="2:6">
@@ -5673,7 +5688,7 @@
         <v>400121</v>
       </c>
       <c r="C155" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>16</v>
@@ -5682,7 +5697,7 @@
         <v>15</v>
       </c>
       <c r="F155" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="156" spans="2:6">
@@ -5690,16 +5705,16 @@
         <v>40013</v>
       </c>
       <c r="C156" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="D156" t="s">
-        <v>540</v>
-      </c>
-      <c r="E156" s="2">
-        <v>0.1</v>
+        <v>545</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>546</v>
       </c>
       <c r="F156" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
     </row>
     <row r="157" spans="2:6">
@@ -5707,16 +5722,16 @@
         <v>40014</v>
       </c>
       <c r="C157" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D157" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="E157" s="2">
         <v>1</v>
       </c>
       <c r="F157" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
     </row>
     <row r="158" spans="2:6">
@@ -5724,16 +5739,16 @@
         <v>400141</v>
       </c>
       <c r="C158" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D158" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="E158" s="2">
         <v>77</v>
       </c>
       <c r="F158" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
     </row>
     <row r="159" spans="2:6">
@@ -5741,16 +5756,16 @@
         <v>400142</v>
       </c>
       <c r="C159" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D159" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="E159" s="2">
         <v>7</v>
       </c>
       <c r="F159" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
     </row>
     <row r="160" spans="2:6">
@@ -5758,16 +5773,16 @@
         <v>40015</v>
       </c>
       <c r="C160" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="D160" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E160" s="2">
         <v>0.5</v>
       </c>
       <c r="F160" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="161" spans="2:6">
@@ -5775,16 +5790,16 @@
         <v>400151</v>
       </c>
       <c r="C161" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="D161" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F161" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
     </row>
     <row r="162" spans="2:6">
@@ -5792,16 +5807,16 @@
         <v>40016</v>
       </c>
       <c r="C162" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="D162" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="F162" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
     </row>
     <row r="163" spans="2:6">
@@ -5809,16 +5824,16 @@
         <v>40017</v>
       </c>
       <c r="C163" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="D163" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="F163" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
     </row>
     <row r="164" spans="2:6">
@@ -5826,16 +5841,16 @@
         <v>40018</v>
       </c>
       <c r="C164" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="F164" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
     </row>
     <row r="165" spans="2:6">
@@ -5843,16 +5858,16 @@
         <v>40019</v>
       </c>
       <c r="C165" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F165" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
     </row>
     <row r="166" spans="2:6">
@@ -5860,16 +5875,16 @@
         <v>40020</v>
       </c>
       <c r="C166" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F166" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
     </row>
     <row r="167" spans="2:6">
@@ -5877,16 +5892,16 @@
         <v>40021</v>
       </c>
       <c r="C167" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="F167" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
     </row>
     <row r="168" spans="2:6">
@@ -5894,16 +5909,16 @@
         <v>40022</v>
       </c>
       <c r="C168" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="F168" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
     </row>
     <row r="169" spans="2:6">
@@ -5911,16 +5926,16 @@
         <v>400221</v>
       </c>
       <c r="C169" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>260</v>
+        <v>349</v>
       </c>
       <c r="F169" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
     </row>
     <row r="170" spans="2:6">
@@ -5928,16 +5943,16 @@
         <v>40023</v>
       </c>
       <c r="C170" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F170" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
     </row>
     <row r="171" spans="2:6">
@@ -5945,16 +5960,16 @@
         <v>40024</v>
       </c>
       <c r="C171" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="E171" s="1">
         <v>0.2</v>
       </c>
       <c r="F171" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
     </row>
     <row r="172" spans="2:6">
@@ -5962,16 +5977,16 @@
         <v>40025</v>
       </c>
       <c r="C172" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="F172" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
     <row r="173" spans="2:6">
@@ -5979,7 +5994,7 @@
         <v>40026</v>
       </c>
       <c r="C173" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="D173" t="s">
         <v>75</v>
@@ -5988,7 +6003,7 @@
         <v>2</v>
       </c>
       <c r="F173" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="174" spans="2:6">
@@ -5996,16 +6011,16 @@
         <v>40027</v>
       </c>
       <c r="C174" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="D174" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>597</v>
+        <v>381</v>
       </c>
       <c r="F174" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
     </row>
     <row r="175" spans="2:6">
@@ -6013,16 +6028,16 @@
         <v>40028</v>
       </c>
       <c r="C175" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="D175" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="F175" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
     </row>
     <row r="176" spans="2:6">
@@ -6030,16 +6045,16 @@
         <v>40029</v>
       </c>
       <c r="C176" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="D176" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="F176" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="177" spans="2:6">
@@ -6047,16 +6062,16 @@
         <v>40030</v>
       </c>
       <c r="C177" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D177" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="F177" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
     <row r="178" spans="2:6">
@@ -6064,16 +6079,16 @@
         <v>40031</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D178" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E178" s="2">
         <v>12</v>
       </c>
       <c r="F178" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
     </row>
     <row r="179" spans="2:6">
@@ -6081,16 +6096,16 @@
         <v>40032</v>
       </c>
       <c r="C179" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="D179" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="F179" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
     </row>
     <row r="180" spans="2:6">
@@ -6098,16 +6113,16 @@
         <v>40033</v>
       </c>
       <c r="C180" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="D180" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E180" s="2">
         <v>0.1</v>
       </c>
       <c r="F180" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="181" spans="2:6">
@@ -6115,16 +6130,16 @@
         <v>40034</v>
       </c>
       <c r="C181" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="D181" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="F181" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
     </row>
     <row r="182" spans="2:6">
@@ -6132,16 +6147,16 @@
         <v>40035</v>
       </c>
       <c r="C182" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="D182" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="E182" s="2">
         <v>1</v>
       </c>
       <c r="F182" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="183" spans="2:6">
@@ -6149,16 +6164,16 @@
         <v>40036</v>
       </c>
       <c r="C183" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="D183" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="F183" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="184" spans="2:6">
@@ -6166,16 +6181,16 @@
         <v>40037</v>
       </c>
       <c r="C184" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="D184" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="E184" s="2">
         <v>1</v>
       </c>
       <c r="F184" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
     </row>
     <row r="185" spans="2:6">
@@ -6183,16 +6198,16 @@
         <v>40038</v>
       </c>
       <c r="C185" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="D185" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="E185" s="2">
         <v>1</v>
       </c>
       <c r="F185" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
     </row>
     <row r="186" spans="2:6">
@@ -6200,16 +6215,16 @@
         <v>40039</v>
       </c>
       <c r="C186" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="D186" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="E186" s="2">
         <v>1</v>
       </c>
       <c r="F186" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
     </row>
     <row r="187" spans="2:6">
@@ -6217,16 +6232,16 @@
         <v>40040</v>
       </c>
       <c r="C187" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="D187" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="E187" s="2">
         <v>0.5</v>
       </c>
       <c r="F187" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
     </row>
     <row r="188" spans="2:6">
@@ -6234,16 +6249,16 @@
         <v>40041</v>
       </c>
       <c r="C188" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="D188" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="E188" s="2">
         <v>15</v>
       </c>
       <c r="F188" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
     </row>
     <row r="189" spans="2:6">
@@ -6251,16 +6266,16 @@
         <v>40042</v>
       </c>
       <c r="C189" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="D189" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="E189" s="2">
         <v>1</v>
       </c>
       <c r="F189" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
     </row>
     <row r="190" spans="2:6">
@@ -6268,16 +6283,16 @@
         <v>40043</v>
       </c>
       <c r="C190" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="D190" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="E190" s="2">
         <v>0.5</v>
       </c>
       <c r="F190" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
     </row>
     <row r="191" spans="2:6">
@@ -6285,16 +6300,16 @@
         <v>40044</v>
       </c>
       <c r="C191" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="D191" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="E191" s="2">
         <v>0.5</v>
       </c>
       <c r="F191" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
     </row>
     <row r="192" spans="2:6">
@@ -6302,16 +6317,16 @@
         <v>40045</v>
       </c>
       <c r="C192" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="D192" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F192" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
     </row>
   </sheetData>
